--- a/output/CS/processed_sfia_CS.xlsx
+++ b/output/CS/processed_sfia_CS.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. contributes to the collection and analysis of information to support strategy development. x000d assists in the preparation of reports and insights for strategic planning.x000d supports the communication of strategic plans and related change initiatives to relevant stakeholders. x000d helps monitor progress against strategic objectives and provides feedback.</t>
+          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. contributes to the collection and analysis of information to support strategy development. assists in the preparation of reports and insights for strategic planning. supports the communication of strategic plans and related change initiatives to relevant stakeholders. helps monitor progress against strategic objectives and provides feedback.</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. collates information and creates reports and insights to support strategy management processes.x000d ensures all stakeholders are aware of the strategic management approach and timetables. provides support and guidance to help stakeholders adhere to the approach.x000d develops and communicates plans to drive forward the strategy and related change planning.x000d contributes to the development of policies, standards and guidelines for strategy development and planning.</t>
+          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. collates information and creates reports and insights to support strategy management processes. ensures all stakeholders are aware of the strategic management approach and timetables. provides support and guidance to help stakeholders adhere to the approach. develops and communicates plans to drive forward the strategy and related change planning. contributes to the development of policies, standards and guidelines for strategy development and planning.</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. sets policies, standards and guidelines for how the organisation conducts strategy development and planning.x000d leads and manages the creation or review of a strategy that meets the requirements of the business. x000d develops, communicates, implements and reviews the processes which embed strategic management in the operational management of the organisation.</t>
+          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. sets policies, standards and guidelines for how the organisation conducts strategy development and planning. leads and manages the creation or review of a strategy that meets the requirements of the business. develops, communicates, implements and reviews the processes which embed strategic management in the operational management of the organisation.</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. leads the definition, implementation and communication of the organisations strategic management framework. x000d directs the creation and review of a strategy and plans to support the strategic requirements of the business.</t>
+          <t>creating and maintaining organisationallevel strategies to align overall business plans, actions and resources with highlevel business objectives. leads the definition, implementation and communication of the organisations strategic management framework. directs the creation and review of a strategy and plans to support the strategic requirements of the business.</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>coordinating information and technology strategies where the adoption of a common approach would benefit the organisation. maintains awareness of the global needs of the organisation. x000d promotes the benefits that a common approach to technology deployment will bring to the entire organisation.x000d coordinates and collaborates with others on the promotion, acquisition, development and implementation of information systems and services.</t>
+          <t>coordinating information and technology strategies where the adoption of a common approach would benefit the organisation. maintains awareness of the global needs of the organisation. promotes the benefits that a common approach to technology deployment will bring to the entire organisation. coordinates and collaborates with others on the promotion, acquisition, development and implementation of information systems and services.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>coordinating information and technology strategies where the adoption of a common approach would benefit the organisation. establishes the organisations strategy for managing information and communicates the policies, standards, procedures and methods necessary to implement the strategy. x000d coordinates all aspects of management of the lifecycle of information systems. x000d represents the interests of the entire organisation to general management and external bodies on matters relating to information strategy.</t>
+          <t>coordinating information and technology strategies where the adoption of a common approach would benefit the organisation. establishes the organisations strategy for managing information and communicates the policies, standards, procedures and methods necessary to implement the strategy. coordinates all aspects of management of the lifecycle of information systems. represents the interests of the entire organisation to general management and external bodies on matters relating to information strategy.</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>enabling the effective management and use of information assets. supports teams and individuals to identify and organise information assets and repositories in line with policy and practices.x000d conducts routine searches for nonsensitive information needed to support organisational decision making.x000d supports users to find and access information resources based on their requirements and approved access.</t>
+          <t>enabling the effective management and use of information assets. supports teams and individuals to identify and organise information assets and repositories in line with policy and practices. conducts routine searches for nonsensitive information needed to support organisational decision making. supports users to find and access information resources based on their requirements and approved access.</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>enabling the effective management and use of information assets. enables the organisation to organise, control and discover information assets.x000d supports the organisation to identify, catalogue and categorise information types and information repositories in line with information management strategies and practices.x000d enables users to find information through appropriate use of metadata and search tools.x000d provides advice and guidance to enable good information management practices to be adopted across the organisation.</t>
+          <t>enabling the effective management and use of information assets. enables the organisation to organise, control and discover information assets. supports the organisation to identify, catalogue and categorise information types and information repositories in line with information management strategies and practices. enables users to find information through appropriate use of metadata and search tools. provides advice and guidance to enable good information management practices to be adopted across the organisation.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>enabling the effective management and use of information assets. ensures implementation of information and records management policies and standard practice. communicates the benefits and value of information management. x000d plans effective information storage, sharing and publishing within the organisation. develops organisational taxonomy for information assets. x000d provides expert advice and guidance to enable the organisation to get maximum value from its information assets. x000d assesses issues that might prevent the organisation from making maximum use of its information assets. contributes to the development of policy, standards and procedures for compliance with relevant legislation.</t>
+          <t>enabling the effective management and use of information assets. ensures implementation of information and records management policies and standard practice. communicates the benefits and value of information management. plans effective information storage, sharing and publishing within the organisation. develops organisational taxonomy for information assets. provides expert advice and guidance to enable the organisation to get maximum value from its information assets. assesses issues that might prevent the organisation from making maximum use of its information assets. contributes to the development of policy, standards and procedures for compliance with relevant legislation.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enabling the effective management and use of information assets. leads and plans activities to communicate and implement information management strategies and policies. x000d develops organisational policies, standards and guidelines for information management. x000d ensures the information required to support the organisation is defined. creates information management processes. x000d coordinates internal and externally sourced information resources to meet specific business objectives.</t>
+          <t>enabling the effective management and use of information assets. leads and plans activities to communicate and implement information management strategies and policies. develops organisational policies, standards and guidelines for information management. ensures the information required to support the organisation is defined. creates information management processes. coordinates internal and externally sourced information resources to meet specific business objectives.</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enabling the effective management and use of information assets. establishes and communicates the organisations information management strategy. x000d specifies at a strategic level the information needed to support the business strategy and business functions. x000d directs information resources to create value for stakeholders. x000d accountable for compliance with regulations, standards and codes of good practice relating to all aspects of information management.</t>
+          <t>enabling the effective management and use of information assets. establishes and communicates the organisations information management strategy. specifies at a strategic level the information needed to support the business strategy and business functions. directs information resources to create value for stakeholders. accountable for compliance with regulations, standards and codes of good practice relating to all aspects of information management.</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. develops models and plans to drive the execution of the business strategy, taking advantage of opportunities to improve business performance. x000d contributes to creating and reviewing a systems capability strategy which meets the businesss strategic requirements. x000d creates and maintains roadmaps to guide the execution of business strategy and capability improvements.x000d determines requirements and specifies effective business processes, through improvements in technology, information or data practices, organisation, roles, procedures and equipment.</t>
+          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. develops models and plans to drive the execution of the business strategy, taking advantage of opportunities to improve business performance. contributes to creating and reviewing a systems capability strategy which meets the businesss strategic requirements. creates and maintains roadmaps to guide the execution of business strategy and capability improvements. determines requirements and specifies effective business processes, through improvements in technology, information or data practices, organisation, roles, procedures and equipment.</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. develops enterprisewide architecture and processes to embed strategic change management within the organisation. x000d leads the creation and review of a systems capability strategy aligned with business requirements. develops roadmaps for enterprise architecture and initiatives, ensuring stakeholder buyin. x000d captures and prioritises market and environmental trends, business strategies and objectives, identifying alternative strategies. develops business cases for approval, funding and prioritisation of highlevel initiatives.x000d sets strategies, policies, standards and practices to ensure compliance between business strategies, technology strategies and enterprise transformation activities.</t>
+          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. develops enterprisewide architecture and processes to embed strategic change management within the organisation. leads the creation and review of a systems capability strategy aligned with business requirements. develops roadmaps for enterprise architecture and initiatives, ensuring stakeholder buyin. captures and prioritises market and environmental trends, business strategies and objectives, identifying alternative strategies. develops business cases for approval, funding and prioritisation of highlevel initiatives. sets strategies, policies, standards and practices to ensure compliance between business strategies, technology strategies and enterprise transformation activities.</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. directs the development of enterprisewide architecture and processes to embed the strategic application of change in the management of the organisation. x000d directs the creation and review of an enterprise capability strategy to support the strategic requirements of the business. oversees the creation and implementation of roadmaps to guide longterm enterprise transformation and strategic alignment.x000d identifies the business benefits of alternative strategies.x000d ensures compliance between business strategies, enterprise transformation activities and technology directions, setting strategies, policies, standards and practices.</t>
+          <t>aligning an organisations technology strategy with its business mission, strategy and processes and documenting this using architectural models. directs the development of enterprisewide architecture and processes to embed the strategic application of change in the management of the organisation. directs the creation and review of an enterprise capability strategy to support the strategic requirements of the business. oversees the creation and implementation of roadmaps to guide longterm enterprise transformation and strategic alignment. identifies the business benefits of alternative strategies. ensures compliance between business strategies, enterprise transformation activities and technology directions, setting strategies, policies, standards and practices.</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. contributes to the development of solution architectures in specific business, infrastructure or functional areas. x000d identifies and evaluates alternative architectures and the tradeoffs in cost, performance and scalability. determines and documents architecturally significant decisions. x000d produces specifications of cloudbased or onpremises components, tiers and interfaces, for translation into detailed designs using selected services and products. x000d supports projects or change initiatives through the preparation of technical plans and application of design principles. aligns solutions with enterprise and solution architecture standards including security.</t>
+          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. contributes to the development of solution architectures in specific business, infrastructure or functional areas. identifies and evaluates alternative architectures and the tradeoffs in cost, performance and scalability. determines and documents architecturally significant decisions. produces specifications of cloudbased or onpremises components, tiers and interfaces, for translation into detailed designs using selected services and products. supports projects or change initiatives through the preparation of technical plans and application of design principles. aligns solutions with enterprise and solution architecture standards including security.</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. leads the development of solution architectures in specific business, infrastructure or functional areas. x000d leads the preparation of technical plans and ensures appropriate technical resources are made available. ensures appropriate tools and methods are available, understood and employed in architecture development.x000d provides technical guidance and governance on solution development and integration. evaluates requests for changes and deviations from specifications and recommends actions.x000d ensures relevant technical strategies, policies, standards and practices including security and cost management are applied correctly.</t>
+          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. leads the development of solution architectures in specific business, infrastructure or functional areas. leads the preparation of technical plans and ensures appropriate technical resources are made available. ensures appropriate tools and methods are available, understood and employed in architecture development. provides technical guidance and governance on solution development and integration. evaluates requests for changes and deviations from specifications and recommends actions. ensures relevant technical strategies, policies, standards and practices including security and cost management are applied correctly.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. leads the development of architectures for complex solutions ensuring consistency with agreed requirements. x000d establishes policies, principles and practices for the selection of solution architecture components. x000d manages tradeoffs and balances functional, service quality, cost efficiency and systems management requirements within a significant area of the organisation. communicates proposed decisions to stakeholders.x000d coordinates and manages the target architecture across multiple projects or initiatives. maintains a stable, viable architecture and ensures consistency of design and adherence to appropriate standards across multiple projects or initiatives.</t>
+          <t>developing and communicating a multidimensional solution architecture to deliver agreed business outcomes. leads the development of architectures for complex solutions ensuring consistency with agreed requirements. establishes policies, principles and practices for the selection of solution architecture components. manages tradeoffs and balances functional, service quality, cost efficiency and systems management requirements within a significant area of the organisation. communicates proposed decisions to stakeholders. coordinates and manages the target architecture across multiple projects or initiatives. maintains a stable, viable architecture and ensures consistency of design and adherence to appropriate standards across multiple projects or initiatives.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. manages the innovation pipeline and executes innovation processes. x000d develops and adapts innovation tools, processes and infrastructures to drive the process of innovation. identifies resources and capabilities needed to support innovation. x000d encourages and motivates innovation communities, teams and individuals to share creative ideas and learn from failures. x000d manages and facilitates the communication and open flow of creative ideas between interested parties and the setup of innovation networks and communities.</t>
+          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. manages the innovation pipeline and executes innovation processes. develops and adapts innovation tools, processes and infrastructures to drive the process of innovation. identifies resources and capabilities needed to support innovation. encourages and motivates innovation communities, teams and individuals to share creative ideas and learn from failures. manages and facilitates the communication and open flow of creative ideas between interested parties and the setup of innovation networks and communities.</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. obtains organisational commitment to innovation. x000d develops organisational capabilities to drive innovation. x000d leads and plans the development of innovation capabilities and implementation of innovation processes, tools and frameworks. x000d leads the communication and an open flow of creative ideas between interested parties and the setup of innovation networks and communities.</t>
+          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. obtains organisational commitment to innovation. develops organisational capabilities to drive innovation. leads and plans the development of innovation capabilities and implementation of innovation processes, tools and frameworks. leads the communication and an open flow of creative ideas between interested parties and the setup of innovation networks and communities.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. leads development of a culture that encourages innovation, risktaking and collaboration. x000d embeds innovation processes throughout business units and links strategy execution with innovation. x000d aligns organisational and individual objectives, measures and rewards with innovation.</t>
+          <t>identifying, prioritising, incubating and exploiting opportunities provided by information, communication and digital technologies. leads development of a culture that encourages innovation, risktaking and collaboration. embeds innovation processes throughout business units and links strategy execution with innovation. aligns organisational and individual objectives, measures and rewards with innovation.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. supports monitoring of the external environment and assessment of emerging technologies. x000d contributes to the creation of reports, technology roadmapping and the sharing of knowledge and insights.</t>
+          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. supports monitoring of the external environment and assessment of emerging technologies. contributes to the creation of reports, technology roadmapping and the sharing of knowledge and insights.</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. monitors the external environment to gather intelligence on emerging technologies. x000d assesses and documents the impacts, threats and opportunities to the organisation. x000d creates reports and technology roadmaps and shares knowledge and insights with others.</t>
+          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. monitors the external environment to gather intelligence on emerging technologies. assesses and documents the impacts, threats and opportunities to the organisation. creates reports and technology roadmaps and shares knowledge and insights with others.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. plans and leads the identification and assessment of emerging technologies and the evaluation of potential impacts, threats and opportunities.x000d creates technology roadmaps that align organisational plans with emerging technology solutions. engages with, and influences, relevant stakeholders to obtain organisational commitment to technology roadmaps. x000d develops organisational guidelines for monitoring emerging technologies. x000d collaborates with internal and external parties to facilitate intelligence gathering.</t>
+          <t>identifying and assessing new and emerging technologies, products, services, methods and techniques. plans and leads the identification and assessment of emerging technologies and the evaluation of potential impacts, threats and opportunities. creates technology roadmaps that align organisational plans with emerging technology solutions. engages with, and influences, relevant stakeholders to obtain organisational commitment to technology roadmaps. develops organisational guidelines for monitoring emerging technologies. collaborates with internal and external parties to facilitate intelligence gathering.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. within given research goals, assists in selection and review of credible and reliable resources. x000d searches for relevant material using specialised websites and sources, reads relevant articles to update knowledge of the relevant field. x000d reports on work carried out and may contribute sections of publicationquality material. x000d curates, under guidance, a personal collection of relevant material.</t>
+          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. within given research goals, assists in selection and review of credible and reliable resources. searches for relevant material using specialised websites and sources, reads relevant articles to update knowledge of the relevant field. reports on work carried out and may contribute sections of publicationquality material. curates, under guidance, a personal collection of relevant material.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. within given research goals, builds on and refines appropriate outline ideas for research, including evaluation, development, demonstration and implementation. x000d applies standard methods to collect and analyse quantitative and qualitative data. creates research reports to communicate research methodology, findings and conclusions. x000d contributes sections of publicationquality material. x000d uses available resources to update knowledge of any relevant field and curates a personal collection of relevant material. participates in research communities.</t>
+          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. within given research goals, builds on and refines appropriate outline ideas for research, including evaluation, development, demonstration and implementation. applies standard methods to collect and analyse quantitative and qualitative data. creates research reports to communicate research methodology, findings and conclusions. contributes sections of publicationquality material. uses available resources to update knowledge of any relevant field and curates a personal collection of relevant material. participates in research communities.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. builds on and refines appropriate outline ideas for the evaluation, development, demonstration and implementation of research. x000d contributes to research goals and funding proposals. collects and analyses qualitative and quantitative data as required. x000d contributes to research plans and identifies appropriate opportunities for publication and dissemination of research findings. makes an active contribution to research communities.x000d presents papers at conferences, contributes significant sections of publicationquality material and presents reports to clients.</t>
+          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. builds on and refines appropriate outline ideas for the evaluation, development, demonstration and implementation of research. contributes to research goals and funding proposals. collects and analyses qualitative and quantitative data as required. contributes to research plans and identifies appropriate opportunities for publication and dissemination of research findings. makes an active contribution to research communities. presents papers at conferences, contributes significant sections of publicationquality material and presents reports to clients.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. agrees research goals and methods and performs projects to generate original ideas. x000d attracts and manages external research funding. maintains a strong external network within own area of specialism. x000d provides advice on performing research. selects and adapts data collection tools and techniques. develops, reviews and constructively criticises the research and ideas of others. shares demonstrations of research findings.x000d takes part in professional activities outside own employing organisation. presents papers at significant conferences, writes articles for specialist journals and presents reports to key stakeholders.</t>
+          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. agrees research goals and methods and performs projects to generate original ideas. attracts and manages external research funding. maintains a strong external network within own area of specialism. provides advice on performing research. selects and adapts data collection tools and techniques. develops, reviews and constructively criticises the research and ideas of others. shares demonstrations of research findings. takes part in professional activities outside own employing organisation. presents papers at significant conferences, writes articles for specialist journals and presents reports to key stakeholders.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. develops the organisations research policy and supervises the work of research functions. x000d promotes activities externally, attracts and manages significant portfolios of research funding. x000d sets research goals and authorises research proposals. leads strategic andor interdisciplinary research projects. maintains a strong external network reaching beyond own immediate area of specialism. x000d takes a leading part in professional activities outside own employing organisation. presents keynote papers at major conferences, writes articles for high impact journals and presents reports to major clients.</t>
+          <t>systematically creating new knowledge by data gathering, innovation, experimentation, evaluation and dissemination. develops the organisations research policy and supervises the work of research functions. promotes activities externally, attracts and manages significant portfolios of research funding. sets research goals and authorises research proposals. leads strategic andor interdisciplinary research projects. maintains a strong external network reaching beyond own immediate area of specialism. takes a leading part in professional activities outside own employing organisation. presents keynote papers at major conferences, writes articles for high impact journals and presents reports to major clients.</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. assesses and reports on how different tactical decisions affect sustainability. x000d evaluates factors and risks political, legislative, technological, economic, social that impact on operational processes and strategic direction.x000d evaluates and reports on the implementation of sustainability measures in specific areas.</t>
+          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. assesses and reports on how different tactical decisions affect sustainability. evaluates factors and risks political, legislative, technological, economic, social that impact on operational processes and strategic direction. evaluates and reports on the implementation of sustainability measures in specific areas.</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. provides expert advice and guidance on planning, designing and implementing sustainability solutions. x000d evaluates and selects sustainability methods, tools and practices to be used in line with agreed policies and standards. x000d identifies and recommends improvements to the organisations approach to sustainability.</t>
+          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. provides expert advice and guidance on planning, designing and implementing sustainability solutions. evaluates and selects sustainability methods, tools and practices to be used in line with agreed policies and standards. identifies and recommends improvements to the organisations approach to sustainability.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. develops and promotes organisational strategies, policies, standards and guidelines for sustainability. x000d leads the introduction and use of sustainability techniques, methodologies and tools.</t>
+          <t>advising and leading sustainability initiatives to reduce environmental impact and ensure compliance with relevant standards and regulations. develops and promotes organisational strategies, policies, standards and guidelines for sustainability. leads the introduction and use of sustainability techniques, methodologies and tools.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. monitors and maintains financial records to ensure compliance and audit requirements are met.x000d provides general support in financial planning and budgeting by compiling and reporting on financial data.x000d supports decisionmaking by collating and summarising financial information at a high level.x000d collaborates with business units to gather financial data and understand operational needs.</t>
+          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. monitors and maintains financial records to ensure compliance and audit requirements are met. provides general support in financial planning and budgeting by compiling and reporting on financial data. supports decisionmaking by collating and summarising financial information at a high level. collaborates with business units to gather financial data and understand operational needs.</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. provides general advice and guidance on financial planning, budgeting and accounting using recognised practices and standards.x000d develops highlevel financial plans and forecasts to guide organisational strategies and plans.x000d monitors expenditure to ensure alignment with budgetary goals.x000d contributes to financial control frameworks and supports strategic decisionmaking by summarising expenditure trends and variances.</t>
+          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. provides general advice and guidance on financial planning, budgeting and accounting using recognised practices and standards. develops highlevel financial plans and forecasts to guide organisational strategies and plans. monitors expenditure to ensure alignment with budgetary goals. contributes to financial control frameworks and supports strategic decisionmaking by summarising expenditure trends and variances.</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. develops organisational policies, standards and guidelines for financial management to support strategic business goals.x000d promotes financial governance and drives adherence to financial policies and standards. collaborates with senior leaders and business unit heads to ensure financial strategies support overall business objectives.x000d oversees the setting and management of financial budgets and targets at a strategic level.x000d leads highlevel reviews of financial performance and implements improvements to align budget usage with organisational priorities.</t>
+          <t>managing the effective use and control of financial resources to support business strategies, compliance and risk mitigation. develops organisational policies, standards and guidelines for financial management to support strategic business goals. promotes financial governance and drives adherence to financial policies and standards. collaborates with senior leaders and business unit heads to ensure financial strategies support overall business objectives. oversees the setting and management of financial budgets and targets at a strategic level. leads highlevel reviews of financial performance and implements improvements to align budget usage with organisational priorities.</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>assessing the attractiveness of possible investments or projects. develops and documents investment appraisals for a range of different projects. x000d identifies suitable appraisal techniques based on the characteristics of a project. x000d collects the information required to create an investment appraisal in collaboration with internal and external stakeholders. presents findings of investment appraisals to selected stakeholders. x000d refines and maintains investment appraisals.</t>
+          <t>assessing the attractiveness of possible investments or projects. develops and documents investment appraisals for a range of different projects. identifies suitable appraisal techniques based on the characteristics of a project. collects the information required to create an investment appraisal in collaboration with internal and external stakeholders. presents findings of investment appraisals to selected stakeholders. refines and maintains investment appraisals.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>assessing the attractiveness of possible investments or projects. advises on investment appraisal approaches and tailors organisational standards to the context of portfoliosprogrammes. x000d leads investment appraisal activities for simple portfolios and programmes and complex projects.</t>
+          <t>assessing the attractiveness of possible investments or projects. advises on investment appraisal approaches and tailors organisational standards to the context of portfoliosprogrammes. leads investment appraisal activities for simple portfolios and programmes and complex projects.</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>assessing the attractiveness of possible investments or projects. develops organisational policies, standards and guidelines for investment appraisals. x000d leads activities to establish consistent appraisal across the component projects and programmes within a portfolio. x000d reviews investment appraisals for highvalue initiatives to assure their quality. x000d leads investment appraisal activities for complex programmes of work and portfolios.</t>
+          <t>assessing the attractiveness of possible investments or projects. develops organisational policies, standards and guidelines for investment appraisals. leads activities to establish consistent appraisal across the component projects and programmes within a portfolio. reviews investment appraisals for highvalue initiatives to assure their quality. leads investment appraisal activities for complex programmes of work and portfolios.</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. supports the identification and tracking of benefits for projects and programmes. x000d collects data to measure benefits realisation.</t>
+          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. supports the identification and tracking of benefits for projects and programmes. collects data to measure benefits realisation.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. contributes to the development and implementation of benefits management plans for projects and programmes. x000d engages with stakeholders to identify and quantify benefits and to establish metrics and mechanisms for tracking benefits realisation. x000d monitors and reports on progress towards benefits realisation. x000d identifies risks and issues that may impact benefits delivery and escalates as appropriate. supports the embedding of benefits management practices across the organisation.</t>
+          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. contributes to the development and implementation of benefits management plans for projects and programmes. engages with stakeholders to identify and quantify benefits and to establish metrics and mechanisms for tracking benefits realisation. monitors and reports on progress towards benefits realisation. identifies risks and issues that may impact benefits delivery and escalates as appropriate. supports the embedding of benefits management practices across the organisation.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. leads activities required in the realisation of the benefits of each part of the change programme. x000d identifies specific metrics and mechanisms to measure benefits and plans to activate these mechanisms at the required time. monitors benefits against what was predicted in the business case. x000d ensures all participants are engaged throughout the change programme and fully prepared to exploit the new operational business environment. x000d supports operational managers to ensure all plans, work packages and deliverables are aligned with the expected benefits.</t>
+          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. leads activities required in the realisation of the benefits of each part of the change programme. identifies specific metrics and mechanisms to measure benefits and plans to activate these mechanisms at the required time. monitors benefits against what was predicted in the business case. ensures all participants are engaged throughout the change programme and fully prepared to exploit the new operational business environment. supports operational managers to ensure all plans, work packages and deliverables are aligned with the expected benefits.</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. works with operational managers to ensure maximum improvements are made as groups of projects deliver their products into operational use. x000d communicates the change programme vision to staff at all levels of the business and keeps a focus on business objectives. x000d maintains the business case for funding the programme and confirms continuing business viability of the programme at regular intervals.</t>
+          <t>forecasting, planning and monitoring the emergence and effective realisation of anticipated benefits from projects and programmes. works with operational managers to ensure maximum improvements are made as groups of projects deliver their products into operational use. communicates the change programme vision to staff at all levels of the business and keeps a focus on business objectives. maintains the business case for funding the programme and confirms continuing business viability of the programme at regular intervals.</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. assists in gathering financial data and preparing basic budget templates under supervision. x000d supports the budgeting and forecasting process by completing assigned tasks.</t>
+          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. assists in gathering financial data and preparing basic budget templates under supervision. supports the budgeting and forecasting process by completing assigned tasks.</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. performs specified tasks in the budgeting and forecasting process, including data analysis and report preparation, using standard methods. x000d identifies and resolves routine budgeting and forecasting issues. x000d communicates budget and forecast information to relevant stakeholders.</t>
+          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. performs specified tasks in the budgeting and forecasting process, including data analysis and report preparation, using standard methods. identifies and resolves routine budgeting and forecasting issues. communicates budget and forecast information to relevant stakeholders.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. contributes to the development of budgets and forecasts for specific areas of responsibility.x000d gathers and analyses financial data and prepares budget templates and reports.x000d supports stakeholder communication and collaboration in the budgeting and forecasting process.</t>
+          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. contributes to the development of budgets and forecasts for specific areas of responsibility. gathers and analyses financial data and prepares budget templates and reports. supports stakeholder communication and collaboration in the budgeting and forecasting process.</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. leads the development of budgets and forecasts for a department or function.x000d provides authoritative advice and guidance on budgeting and forecasting practices. selects and applies appropriate budgeting and forecasting methodologies and tools.x000d incorporates scenario planning, sensitivity analysis and risk assessment into the budgeting and forecasting process.x000d collaborates with stakeholders to align budgets and forecasts with organisational objectives and business metrics.</t>
+          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. leads the development of budgets and forecasts for a department or function. provides authoritative advice and guidance on budgeting and forecasting practices. selects and applies appropriate budgeting and forecasting methodologies and tools. incorporates scenario planning, sensitivity analysis and risk assessment into the budgeting and forecasting process. collaborates with stakeholders to align budgets and forecasts with organisational objectives and business metrics.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. develops and implements budgeting and forecasting strategies, policies and processes aligned with overall organisational objectives and business metrics. x000d drives the adoption of good working practices across the organisation.x000d oversees the development of complex financial models and scenario analyses to support strategic decisionmaking. provides insights and recommendations to optimise investments and resource allocation.x000d collaborates with senior leaders to ensure budgets and forecasts support longterm organisational goals and drive value creation. sets the vision and direction for budgeting and forecasting practices.</t>
+          <t>developing and managing financial budgets and forecasts to enable effective decisionmaking and resource allocation. develops and implements budgeting and forecasting strategies, policies and processes aligned with overall organisational objectives and business metrics. drives the adoption of good working practices across the organisation. oversees the development of complex financial models and scenario analyses to support strategic decisionmaking. provides insights and recommendations to optimise investments and resource allocation. collaborates with senior leaders to ensure budgets and forecasts support longterm organisational goals and drive value creation. sets the vision and direction for budgeting and forecasting practices.</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. assists in collecting and organising financial data and preparing basic reports under supervision. x000d supports the financial analysis process by completing assigned tasks and seeking guidance when needed.</t>
+          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. assists in collecting and organising financial data and preparing basic reports under supervision. supports the financial analysis process by completing assigned tasks and seeking guidance when needed.</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. applies established financial analysis techniques and processes to carry out specific tasks such as detailed data analysis, report generation and interpretation of financial metrics. x000d contributes to the development of actionable insights for decisionmaking.x000d communicates financial analysis findings to relevant stakeholders.</t>
+          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. applies established financial analysis techniques and processes to carry out specific tasks such as detailed data analysis, report generation and interpretation of financial metrics. contributes to the development of actionable insights for decisionmaking. communicates financial analysis findings to relevant stakeholders.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. performs financial analysis for specific areas, using standard techniques and tools. x000d prepares reports and provides insights to support decisionmaking. conducts costbenefit analyses and supports stakeholder collaboration in the cost management process. x000d collaborates with stakeholders to understand requirements and deliver relevant analysis. x000d supports the development and maintenance of financial models.</t>
+          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. performs financial analysis for specific areas, using standard techniques and tools. prepares reports and provides insights to support decisionmaking. conducts costbenefit analyses and supports stakeholder collaboration in the cost management process. collaborates with stakeholders to understand requirements and deliver relevant analysis. supports the development and maintenance of financial models.</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. leads financial analysis activities for a department or function, applying advanced techniques and tools. develops and maintains complex financial models.x000d conducts scenario planning and sensitivity analysis to support decisionmaking. provides authoritative advice and guidance on recommended financial analysis practices.x000d presents findings and recommendations to senior stakeholders, linking financial performance to business outcomes. collaborates with stakeholders to align analysis with organisational objectives.</t>
+          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. leads financial analysis activities for a department or function, applying advanced techniques and tools. develops and maintains complex financial models. conducts scenario planning and sensitivity analysis to support decisionmaking. provides authoritative advice and guidance on recommended financial analysis practices. presents findings and recommendations to senior stakeholders, linking financial performance to business outcomes. collaborates with stakeholders to align analysis with organisational objectives.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. defines and leads the organisations approach to financial analysis, aligning it with strategic objectives and business value creation.x000d develops and implements enterprisewide financial analysis policies, standards and processes. drives a culture of datadriven decisionmaking and continuous improvement in financial management.x000d provides strategic insights and recommendations based on comprehensive financial analysis, linking performance to business strategy.</t>
+          <t>conducting indepth analysis of financial data to derive insights and support decisionmaking. defines and leads the organisations approach to financial analysis, aligning it with strategic objectives and business value creation. develops and implements enterprisewide financial analysis policies, standards and processes. drives a culture of datadriven decisionmaking and continuous improvement in financial management. provides strategic insights and recommendations based on comprehensive financial analysis, linking performance to business strategy.</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>planning, controlling and analysing costs to enable the effective use of financial resources. assists in gathering cost data and preparing basic cost reports under supervision. x000d supports the cost management process by completing assigned tasks and seeking guidance when needed.</t>
+          <t>planning, controlling and analysing costs to enable the effective use of financial resources. assists in gathering cost data and preparing basic cost reports under supervision. supports the cost management process by completing assigned tasks and seeking guidance when needed.</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>planning, controlling and analysing costs to enable the effective use of financial resources. applies standard cost management techniques and processes to monitor and report on costs within a specific area of responsibility.x000d identifies and escalates cost variances and supports the implementation of costsaving initiatives. collaborates with stakeholders to gather cost data and provide reports.</t>
+          <t>planning, controlling and analysing costs to enable the effective use of financial resources. applies standard cost management techniques and processes to monitor and report on costs within a specific area of responsibility. identifies and escalates cost variances and supports the implementation of costsaving initiatives. collaborates with stakeholders to gather cost data and provide reports.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>planning, controlling and analysing costs to enable the effective use of financial resources. develops and implements cost management processes and procedures for a department or function.x000d monitors actual performance against budget and identifies variances.x000d analyses costs, identifies trends and recommends corrective actions.x000d provides guidance and advice on cost management techniques and tools.</t>
+          <t>planning, controlling and analysing costs to enable the effective use of financial resources. develops and implements cost management processes and procedures for a department or function. monitors actual performance against budget and identifies variances. analyses costs, identifies trends and recommends corrective actions. provides guidance and advice on cost management techniques and tools.</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>planning, controlling and analysing costs to enable the effective use of financial resources. leads the development and implementation of cost management strategies, policies and procedures for a significant area of the organisation.x000d provides authoritative advice and guidance on cost optimisation techniques and recognised good practices. oversees the development of complex cost models and reporting frameworks.x000d presents cost management insights to senior stakeholders and facilitates datadriven decisionmaking. promotes a culture of cost consciousness and continuous improvement.</t>
+          <t>planning, controlling and analysing costs to enable the effective use of financial resources. leads the development and implementation of cost management strategies, policies and procedures for a significant area of the organisation. provides authoritative advice and guidance on cost optimisation techniques and recognised good practices. oversees the development of complex cost models and reporting frameworks. presents cost management insights to senior stakeholders and facilitates datadriven decisionmaking. promotes a culture of cost consciousness and continuous improvement.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>planning, controlling and analysing costs to enable the effective use of financial resources. defines and leads the organisations overall approach to cost management, aligning it with strategic objectives and financial goals.x000d develops and implements enterprisewide cost management policies, standards and processes. collaborates with senior leaders to identify and drive cost optimisation initiatives.x000d provides strategic insights and recommendations to optimise cost performance and drive longterm value creation. sets the vision and direction for cost management across the organisation.</t>
+          <t>planning, controlling and analysing costs to enable the effective use of financial resources. defines and leads the organisations overall approach to cost management, aligning it with strategic objectives and financial goals. develops and implements enterprisewide cost management policies, standards and processes. collaborates with senior leaders to identify and drive cost optimisation initiatives. provides strategic insights and recommendations to optimise cost performance and drive longterm value creation. sets the vision and direction for cost management across the organisation.</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. performs demand management analysis and planning activities within a specific business or operational area. x000d monitors patterns of demand and identifies insights and proposals to improve business value. x000d identifies and assesses opportunities to prioritise or improve alignment between business demand and capacity to deliver. x000d engages stakeholders to communicate insights, plans and decisions regarding business demand.</t>
+          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. performs demand management analysis and planning activities within a specific business or operational area. monitors patterns of demand and identifies insights and proposals to improve business value. identifies and assesses opportunities to prioritise or improve alignment between business demand and capacity to deliver. engages stakeholders to communicate insights, plans and decisions regarding business demand.</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. implements demand management analysis and planning activities. x000d provides advice to help stakeholders adopt and adhere to the agreed demand management approach. manages the process of integrating demand management with complementary strategic, operational and change management processes. x000d maintains a register of business requests and routes requests to the right place. reports on the status of each request.x000d reviews new business proposals and provides advice on demand issues. works with business representatives to agree and implement shortterm and mediumterm modifications to demand.</t>
+          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. implements demand management analysis and planning activities. provides advice to help stakeholders adopt and adhere to the agreed demand management approach. manages the process of integrating demand management with complementary strategic, operational and change management processes. maintains a register of business requests and routes requests to the right place. reports on the status of each request. reviews new business proposals and provides advice on demand issues. works with business representatives to agree and implement shortterm and mediumterm modifications to demand.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. defines the approach and sets policies for discovering, analysing, planning, controlling and documenting demand for services and products. x000d organises scoping and business priority setting for strategic business changes involving business policymakers and direction setters. x000d engages with and influences senior stakeholders to improve the business value delivered from new or existing services and products. x000d leads the development of demand management capabilities. leads the integration of demand management with complementary strategic, operational and change management processes.</t>
+          <t>analysing and proactively managing business demand for new services or modifications to existing service features or volumes. defines the approach and sets policies for discovering, analysing, planning, controlling and documenting demand for services and products. organises scoping and business priority setting for strategic business changes involving business policymakers and direction setters. engages with and influences senior stakeholders to improve the business value delivered from new or existing services and products. leads the development of demand management capabilities. leads the integration of demand management with complementary strategic, operational and change management processes.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>developing and operating a measurement capability to support agreed organisational information needs. assists in the collection and maintenance of data for measurement purposes under routine supervision.x000d uses standard procedures for measuring attributes of processes, products and services. x000d helps generate and distribute measurement reports.</t>
+          <t>developing and operating a measurement capability to support agreed organisational information needs. assists in the collection and maintenance of data for measurement purposes under routine supervision. uses standard procedures for measuring attributes of processes, products and services. helps generate and distribute measurement reports.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>developing and operating a measurement capability to support agreed organisational information needs. applies standard techniques to support the specification of measures and the collection and maintenance of data for measurement. x000d generates, produces and distributes reports. x000d uses measurement tools for routine analysis of data. x000d identifies and implements improvements to data collection methods.</t>
+          <t>developing and operating a measurement capability to support agreed organisational information needs. applies standard techniques to support the specification of measures and the collection and maintenance of data for measurement. generates, produces and distributes reports. uses measurement tools for routine analysis of data. identifies and implements improvements to data collection methods.</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>developing and operating a measurement capability to support agreed organisational information needs. identifies and prioritises appropriate measures, scales and targets. x000d supports projects, functions or teams in the development of measurement methods. x000d specifies base and derived measures which support agreed information needs. specifies how to collect and store the data for each required measure. provides guidance on collection of data. x000d designs reports and reporting formats.</t>
+          <t>developing and operating a measurement capability to support agreed organisational information needs. identifies and prioritises appropriate measures, scales and targets. supports projects, functions or teams in the development of measurement methods. specifies base and derived measures which support agreed information needs. specifies how to collect and store the data for each required measure. provides guidance on collection of data. designs reports and reporting formats.</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>developing and operating a measurement capability to support agreed organisational information needs. establishes measurement objectives and the scope of measurement for functions, teams and projects. x000d plans and implements improvements to measurement capability. provides advice and guidance for effective use of measures and measurement. x000d selects measures appropriate to the context and organisational objectives. reviews data collection and storage mechanisms to support measurement.x000d contributes to organisational policies, standards and guidelines for measurement.</t>
+          <t>developing and operating a measurement capability to support agreed organisational information needs. establishes measurement objectives and the scope of measurement for functions, teams and projects. plans and implements improvements to measurement capability. provides advice and guidance for effective use of measures and measurement. selects measures appropriate to the context and organisational objectives. reviews data collection and storage mechanisms to support measurement. contributes to organisational policies, standards and guidelines for measurement.</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>developing and operating a measurement capability to support agreed organisational information needs. leads the development of organisational capabilities for measurement including automation. x000d creates the measurement framework and aligns measurement objectives with business objectives. x000d develops organisational policies, standards and guidelines for measurement. x000d provides resources to ensure adoption and adherence to policies and standards.</t>
+          <t>developing and operating a measurement capability to support agreed organisational information needs. leads the development of organisational capabilities for measurement including automation. creates the measurement framework and aligns measurement objectives with business objectives. develops organisational policies, standards and guidelines for measurement. provides resources to ensure adoption and adherence to policies and standards.</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. assists with implementing and monitoring security policies and protocols across different systems.x000d contributes to identifying and addressing potential risks in security governance and compliance.x000d supports the analysis of documented security incidents, escalating where appropriate.x000d assists in the review of access controls and permissions, ensuring adherence to security policies.</t>
+          <t>defining and operating a framework of security controls and security management strategies. assists with implementing and monitoring security policies and protocols across different systems. contributes to identifying and addressing potential risks in security governance and compliance. supports the analysis of documented security incidents, escalating where appropriate. assists in the review of access controls and permissions, ensuring adherence to security policies.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. applies and maintains specific security controls as required by organisational policy and local risk assessments.x000d communicates security risks and issues to business managers and others. performs basic risk assessments for small information systems. x000d contributes to the identification of risks that arise from potential technical solution architectures. suggests alternate solutions or countermeasures to mitigate risks. defines secure systems configurations in compliance with intended architectures.x000d supports investigation of suspected attacks and security breaches.</t>
+          <t>defining and operating a framework of security controls and security management strategies. applies and maintains specific security controls as required by organisational policy and local risk assessments. communicates security risks and issues to business managers and others. performs basic risk assessments for small information systems. contributes to the identification of risks that arise from potential technical solution architectures. suggests alternate solutions or countermeasures to mitigate risks. defines secure systems configurations in compliance with intended architectures. supports investigation of suspected attacks and security breaches.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. provides guidance on the application and operation of elementary physical, procedural and technical security controls. x000d explains the purpose of security controls and performs security risk and business impact analysis for medium complexity information systems. x000d identifies risks that arise from potential technical solution architectures. designs alternate solutions or countermeasures and ensures they manage identified risks. x000d investigates suspected attacks and supports security incident management.</t>
+          <t>defining and operating a framework of security controls and security management strategies. provides guidance on the application and operation of elementary physical, procedural and technical security controls. explains the purpose of security controls and performs security risk and business impact analysis for medium complexity information systems. identifies risks that arise from potential technical solution architectures. designs alternate solutions or countermeasures and ensures they manage identified risks. investigates suspected attacks and supports security incident management.</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. provides advice and guidance on security strategies to manage identified risks and ensure adoption and adherence to standards. x000d contributes to development of information security policy, standards and guidelines. x000d obtains and acts on vulnerability information and conducts security risk assessments, business impact analysis and accreditation on complex information systems. investigates major breaches of security and recommends appropriate control improvements. x000d develops new architectures that manage the risks posed by new technologies and business practices.</t>
+          <t>defining and operating a framework of security controls and security management strategies. provides advice and guidance on security strategies to manage identified risks and ensure adoption and adherence to standards. contributes to development of information security policy, standards and guidelines. obtains and acts on vulnerability information and conducts security risk assessments, business impact analysis and accreditation on complex information systems. investigates major breaches of security and recommends appropriate control improvements. develops new architectures that manage the risks posed by new technologies and business practices.</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. develops and communicates corporate information security policy, standards and guidelines. x000d ensures architectural principles are applied during design to reduce risk. drives adoption and adherence to policy, standards and guidelines. x000d contributes to the development of organisational strategies that address information control requirements. identifies and monitors environmental and market trends and proactively assesses impact on business strategies, benefits and risks. x000d leads the provision of authoritative advice and guidance on the requirements for security controls in collaboration with subject matter experts.</t>
+          <t>defining and operating a framework of security controls and security management strategies. develops and communicates corporate information security policy, standards and guidelines. ensures architectural principles are applied during design to reduce risk. drives adoption and adherence to policy, standards and guidelines. contributes to the development of organisational strategies that address information control requirements. identifies and monitors environmental and market trends and proactively assesses impact on business strategies, benefits and risks. leads the provision of authoritative advice and guidance on the requirements for security controls in collaboration with subject matter experts.</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>defining and operating a framework of security controls and security management strategies. directs the development, implementation, delivery and support of an enterprise information security strategy aligned with the business strategy. x000d ensures compliance between business strategies and information security. x000d leads the provision of information security expertise, guidance and systems needed to execute strategic and operational plans.x000d secures organisational resources to execute the information security strategy.</t>
+          <t>defining and operating a framework of security controls and security management strategies. directs the development, implementation, delivery and support of an enterprise information security strategy aligned with the business strategy. ensures compliance between business strategies and information security. leads the provision of information security expertise, guidance and systems needed to execute strategic and operational plans. secures organisational resources to execute the information security strategy.</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. assists with information assurance activities under routine supervision.x000d helps perform basic risk assessments and supports the implementation of information assurance measures.x000d assists in maintaining records and documentation related to information assurance.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. assists with information assurance activities under routine supervision. helps perform basic risk assessments and supports the implementation of information assurance measures. assists in maintaining records and documentation related to information assurance.</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. follows standard approaches for the technical assessment of information systems against information assurance policies and business objectives. x000d makes routine accreditation decisions. recognises decisions that are beyond their scope and responsibility level and escalates according.x000d reviews and performs risk assessments and risk treatment plans. identifies typical risk indicators and explains prevention measures.x000d maintains integrity of records to support and justify decisions.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. follows standard approaches for the technical assessment of information systems against information assurance policies and business objectives. makes routine accreditation decisions. recognises decisions that are beyond their scope and responsibility level and escalates according. reviews and performs risk assessments and risk treatment plans. identifies typical risk indicators and explains prevention measures. maintains integrity of records to support and justify decisions.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. performs technical assessments andor accreditation of complex or higherrisk information systems. x000d identifies risk mitigation measures required in addition to the standard organisation or domain measures. x000d establishes the requirement for accreditation evidence from delivery partners and communicates accreditation requirements to stakeholders. x000d contributes to planning and organisation of information assurance and accreditation activities. contributes to development of and implementation of information assurance processes.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. performs technical assessments andor accreditation of complex or higherrisk information systems. identifies risk mitigation measures required in addition to the standard organisation or domain measures. establishes the requirement for accreditation evidence from delivery partners and communicates accreditation requirements to stakeholders. contributes to planning and organisation of information assurance and accreditation activities. contributes to development of and implementation of information assurance processes.</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. interprets information assurance and security policies and applies these to manage risks. x000d provides advice and guidance to ensure adoption of and adherence to information assurance architectures, strategies, policies, standards and guidelines. x000d plans, organises and conducts information assurance and accreditation of complex domains areas, crossfunctional areas and across the supply chain. x000d contributes to the development of policies, standards and guidelines.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. interprets information assurance and security policies and applies these to manage risks. provides advice and guidance to ensure adoption of and adherence to information assurance architectures, strategies, policies, standards and guidelines. plans, organises and conducts information assurance and accreditation of complex domains areas, crossfunctional areas and across the supply chain. contributes to the development of policies, standards and guidelines.</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. develops information assurance policy, standards and guidelines. x000d contributes to the development of organisational strategies that address the evolving business risk and information control requirements. x000d drives adoption of and adherence to policies and standards. ensures architectural principles are followed, requirements are defined and rigorous security testing is applied. ensures accreditation processes support and enable organisational objectives.x000d monitors environmental and market trends and assesses any impact on organisational strategies, benefits and risks.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. develops information assurance policy, standards and guidelines. contributes to the development of organisational strategies that address the evolving business risk and information control requirements. drives adoption of and adherence to policies and standards. ensures architectural principles are followed, requirements are defined and rigorous security testing is applied. ensures accreditation processes support and enable organisational objectives. monitors environmental and market trends and assesses any impact on organisational strategies, benefits and risks.</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. directs the creation and review of an enterprise information assurance strategy to support the strategic requirements of the business.x000d ensures compliance between business strategies and information assurance by setting strategies, policies, standards and practices. x000d leads the provision of information assurance expertise, advice and guidance across all of the organisations information and information systems.</t>
+          <t>protecting against and managing risks related to the use, storage and transmission of data and information systems. directs the creation and review of an enterprise information assurance strategy to support the strategic requirements of the business. ensures compliance between business strategies and information assurance by setting strategies, policies, standards and practices. leads the provision of information assurance expertise, advice and guidance across all of the organisations information and information systems.</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>implementing and promoting compliance with information and data management legislation. supports the implementation of policy, standards and guidelines related to information and data legislation and compliance requirements.x000d monitors the implementation of effective controls for internal delegation, audit and control relating to information management.x000d reports on the consolidated status of information controls to inform effective decisionmaking.x000d identifies risks around the use of information and data that is subject to specific legislation. recommends remediation actions as required.</t>
+          <t>implementing and promoting compliance with information and data management legislation. supports the implementation of policy, standards and guidelines related to information and data legislation and compliance requirements. monitors the implementation of effective controls for internal delegation, audit and control relating to information management. reports on the consolidated status of information controls to inform effective decisionmaking. identifies risks around the use of information and data that is subject to specific legislation. recommends remediation actions as required.</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>implementing and promoting compliance with information and data management legislation. contributes to policies, standards and guidelines for information and data compliance. x000d provides authoritative advice on implementing compliance controls in products, services and systems. x000d investigates breaches and recommends control improvements. maintains an inventory of legislated data, conducts risk assessments and specifies necessary changes. x000d ensures formal requests and complaints are handled following procedures. prepares and submits reports to relevant authorities, ensuring all compliance requirements are met.</t>
+          <t>implementing and promoting compliance with information and data management legislation. contributes to policies, standards and guidelines for information and data compliance. provides authoritative advice on implementing compliance controls in products, services and systems. investigates breaches and recommends control improvements. maintains an inventory of legislated data, conducts risk assessments and specifies necessary changes. ensures formal requests and complaints are handled following procedures. prepares and submits reports to relevant authorities, ensuring all compliance requirements are met.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>implementing and promoting compliance with information and data management legislation. develops strategies for compliance with information and data legislation. x000d ensures that the policy and standards for compliance with information and data legislation are fit for purpose, current and correctly implemented. x000d acts as the organisations contact for the regulatory authorities. x000d operates as a focus for information and data legislation for the organisation, working with specialists to provide authoritative advice and guidance.</t>
+          <t>implementing and promoting compliance with information and data management legislation. develops strategies for compliance with information and data legislation. ensures that the policy and standards for compliance with information and data legislation are fit for purpose, current and correctly implemented. acts as the organisations contact for the regulatory authorities. operates as a focus for information and data legislation for the organisation, working with specialists to provide authoritative advice and guidance.</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. assists with vulnerability research tasks under routine supervision.x000d helps document and report findings from vulnerability research activities.</t>
+          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. assists with vulnerability research tasks under routine supervision. helps document and report findings from vulnerability research activities.</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. applies standard techniques and tools for vulnerability research. x000d uses available resources to update knowledge of relevant specialism. x000d participates in research communities. x000d analyses and reports on activities and results.</t>
+          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. applies standard techniques and tools for vulnerability research. uses available resources to update knowledge of relevant specialism. participates in research communities. analyses and reports on activities and results.</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. designs and executes complex vulnerability research activities. x000d specifies requirements for environment, data, resources and tools to perform assessments. x000d reviews test results and modifies tests if necessary. creates reports to communicate methodology, findings and conclusions. advises on deception methods by exploiting identified patterns. x000d makes an active contribution to research communities.</t>
+          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. designs and executes complex vulnerability research activities. specifies requirements for environment, data, resources and tools to perform assessments. reviews test results and modifies tests if necessary. creates reports to communicate methodology, findings and conclusions. advises on deception methods by exploiting identified patterns. makes an active contribution to research communities.</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. plans and manages vulnerability research activities. x000d maintains a strong external network for vulnerability research. gathers information on new and emerging threats and vulnerabilities. x000d assesses and documents the impacts and threats to the organisation. creates reports and shares knowledge and insights with stakeholders. x000d provides expert advice and guidance to support the adoption of tools and techniques for vulnerability research. contributes to the development of organisational policies, standards and guidelines for vulnerability research and assessment.</t>
+          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. plans and manages vulnerability research activities. maintains a strong external network for vulnerability research. gathers information on new and emerging threats and vulnerabilities. assesses and documents the impacts and threats to the organisation. creates reports and shares knowledge and insights with stakeholders. provides expert advice and guidance to support the adoption of tools and techniques for vulnerability research. contributes to the development of organisational policies, standards and guidelines for vulnerability research and assessment.</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. plans and leads the organisations approach to vulnerability research.x000d identifies new and emerging threats and vulnerabilities. maintains a strong external network. takes a leading part in externalfacing professional activities to facilitate information gathering and set the scope of research work. x000d engages with and influences relevant stakeholders to communicate results of research and the required response. x000d develops organisational policies and guidelines for monitoring emerging threats and vulnerabilities.</t>
+          <t>conducting applied research to discover, evaluate and mitigate new or unknown security vulnerabilities and weaknesses. plans and leads the organisations approach to vulnerability research. identifies new and emerging threats and vulnerabilities. maintains a strong external network. takes a leading part in externalfacing professional activities to facilitate information gathering and set the scope of research work. engages with and influences relevant stakeholders to communicate results of research and the required response. develops organisational policies and guidelines for monitoring emerging threats and vulnerabilities.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. contributes to routine threat intelligence gathering tasks. x000d monitors and detects potential security threats and escalates in accordance with relevant procedures and standards.</t>
+          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. contributes to routine threat intelligence gathering tasks. monitors and detects potential security threats and escalates in accordance with relevant procedures and standards.</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. performs routine threat intelligence gathering tasks. x000d transforms collected information into a data format that can be used for operational security activities.x000d cleans and converts quantitative information into consistent formats.</t>
+          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. performs routine threat intelligence gathering tasks. transforms collected information into a data format that can be used for operational security activities. cleans and converts quantitative information into consistent formats.</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. collates and analyses information for threat intelligence requirements from a variety of sources.x000d contributes to reviewing, ranking and categorising qualitative threat intelligence information. x000d creates threat intelligence reports. x000d evaluates the value, usefulness and impact of threat intelligence sources.</t>
+          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. collates and analyses information for threat intelligence requirements from a variety of sources. contributes to reviewing, ranking and categorising qualitative threat intelligence information. creates threat intelligence reports. evaluates the value, usefulness and impact of threat intelligence sources.</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. plans and manages threat intelligence activities. x000d identifies the most impactful threat categories and types of information that can help defend against them. reviews, ranks and categorises qualitative threat intelligence information.x000d provides expert advice on threat intelligence activities. x000d leads the production and editing of threat intelligence reports that enhance the intelligence production workflow. distributes information and obtains feedback about the value, usefulness and impact of the data.</t>
+          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. plans and manages threat intelligence activities. identifies the most impactful threat categories and types of information that can help defend against them. reviews, ranks and categorises qualitative threat intelligence information. provides expert advice on threat intelligence activities. leads the production and editing of threat intelligence reports that enhance the intelligence production workflow. distributes information and obtains feedback about the value, usefulness and impact of the data.</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. sets direction, plans and leads the organisations approach to threat intelligence, including the use of suppliers.x000d identifies requirements for threat intelligence based on the assets to be protected and the types of intelligence that can help protect those assets. x000d engages with and influences relevant stakeholders to communicate results of research and the required response. x000d ensures quality and accuracy of threat intelligence information. reviews threat intelligence capabilities.</t>
+          <t>developing and sharing actionable insights on current and potential security threats to the success or integrity of an organisation. sets direction, plans and leads the organisations approach to threat intelligence, including the use of suppliers. identifies requirements for threat intelligence based on the assets to be protected and the types of intelligence that can help protect those assets. engages with and influences relevant stakeholders to communicate results of research and the required response. ensures quality and accuracy of threat intelligence information. reviews threat intelligence capabilities.</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>defining and operating frameworks for decisionmaking, risk management, stakeholder relationships and compliance with organisational and regulatory obligations. implements the governance framework to enable governance activity to be conducted. x000d within a defined area of accountability, determines the requirements for appropriate governance reflecting the organisations values, ethics, risk appetite and wider governance frameworks. communicates delegated authority, benefits, opportunities, costs and risks. x000d leads reviews of governance practices with appropriate and sufficient independence from management activity. x000d acts as the organisations contact for relevant regulatory authorities and ensures proper relationships between the organisation and external stakeholders.</t>
+          <t>defining and operating frameworks for decisionmaking, risk management, stakeholder relationships and compliance with organisational and regulatory obligations. implements the governance framework to enable governance activity to be conducted. within a defined area of accountability, determines the requirements for appropriate governance reflecting the organisations values, ethics, risk appetite and wider governance frameworks. communicates delegated authority, benefits, opportunities, costs and risks. leads reviews of governance practices with appropriate and sufficient independence from management activity. acts as the organisations contact for relevant regulatory authorities and ensures proper relationships between the organisation and external stakeholders.</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>defining and operating frameworks for decisionmaking, risk management, stakeholder relationships and compliance with organisational and regulatory obligations. directs the definition, implementation and monitoring of the governance framework to meet organisational obligations under regulation, law, or contracts. x000d provides leadership, direction and oversight for governance activities. integrates risk management into frameworks, aligning with strategic objectives and risk appetite.x000d secures resources required to execute activities to achieve the organisations governance goals with effective transparency. x000d provides assurance to stakeholders that the organisation can deliver its obligations with an agreed balance of benefits, opportunities, costs and risks.</t>
+          <t>defining and operating frameworks for decisionmaking, risk management, stakeholder relationships and compliance with organisational and regulatory obligations. directs the definition, implementation and monitoring of the governance framework to meet organisational obligations under regulation, law, or contracts. provides leadership, direction and oversight for governance activities. integrates risk management into frameworks, aligning with strategic objectives and risk appetite. secures resources required to execute activities to achieve the organisations governance goals with effective transparency. provides assurance to stakeholders that the organisation can deliver its obligations with an agreed balance of benefits, opportunities, costs and risks.</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. assists in collecting and reporting data to support risk management activities under routine supervision. x000d helps create and maintain documentation of risks and risk management activities. x000d helps identify and report issues and discrepancies.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. assists in collecting and reporting data to support risk management activities under routine supervision. helps create and maintain documentation of risks and risk management activities. helps identify and report issues and discrepancies.</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. undertakes basic risk management activities. x000d maintains documentation of risks, threats, vulnerabilities and mitigation actions.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. undertakes basic risk management activities. maintains documentation of risks, threats, vulnerabilities and mitigation actions.</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. carries out risk management activities within a specific function, technical area or project of medium complexity. x000d identifies risks and vulnerabilities, assesses their impact and probability, develops mitigation strategies and reports to the business. x000d involves specialists and domain experts as necessary.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. carries out risk management activities within a specific function, technical area or project of medium complexity. identifies risks and vulnerabilities, assesses their impact and probability, develops mitigation strategies and reports to the business. involves specialists and domain experts as necessary.</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. plans and implements complex and substantial risk management activities within a specific function, technical area, project or programme. x000d establishes consistent risk management processes and reporting mechanisms aligned with governance frameworks.x000d engages specialists and domain experts as necessary. x000d advises on the organisations approach to risk management.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. plans and implements complex and substantial risk management activities within a specific function, technical area, project or programme. establishes consistent risk management processes and reporting mechanisms aligned with governance frameworks. engages specialists and domain experts as necessary. advises on the organisations approach to risk management.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. plans and manages the implementation of organisationwide risk management processes, integrating tools and techniques aligned with governance frameworks.x000d considers organisationwide risk and mitigation activities within the context of business risk as a whole and the organisations appetite for risk.x000d provides leadership on risk management, ensuring practices support strategic decisionmaking and compliance with organisational policies.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. plans and manages the implementation of organisationwide risk management processes, integrating tools and techniques aligned with governance frameworks. considers organisationwide risk and mitigation activities within the context of business risk as a whole and the organisations appetite for risk. provides leadership on risk management, ensuring practices support strategic decisionmaking and compliance with organisational policies.</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. establishes the organisations risk management strategy, defining and communicating the risk appetite in alignment with governance and strategic objectives.x000d defines and communicates the organisations appetite for risk. x000d provides resources to implement the organisations risk strategy. x000d delegates authority for detailed planning and execution of risk management activities across the organisation.</t>
+          <t>planning and implementing processes for managing risk across the enterprise, aligned with organisational strategy and governance frameworks. establishes the organisations risk management strategy, defining and communicating the risk appetite in alignment with governance and strategic objectives. defines and communicates the organisations appetite for risk. provides resources to implement the organisations risk strategy. delegates authority for detailed planning and execution of risk management activities across the organisation.</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. supports ethical reviews and conducts basic impact assessments under direction. x000d gathers and analyses information for assessments. reports on ethical issues and compliance with guidance from others. documents findings from audits and reviews. x000d assists with documentation and communication of ethical policies. x000d supports others in responding to incidents.</t>
+          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. supports ethical reviews and conducts basic impact assessments under direction. gathers and analyses information for assessments. reports on ethical issues and compliance with guidance from others. documents findings from audits and reviews. assists with documentation and communication of ethical policies. supports others in responding to incidents.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. engages stakeholders to communicate ethical considerations and influence design decisions. x000d conducts detailed impact assessments and makes recommendations. manages ethical reviews to ensure compliance with standards. x000d evaluates risks and proposes measures to address ethical concerns. leads discussions with stakeholders on ethical issues. x000d designs and executes ethical impact assessments. prepares reports based on audit findings.</t>
+          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. engages stakeholders to communicate ethical considerations and influence design decisions. conducts detailed impact assessments and makes recommendations. manages ethical reviews to ensure compliance with standards. evaluates risks and proposes measures to address ethical concerns. leads discussions with stakeholders on ethical issues. designs and executes ethical impact assessments. prepares reports based on audit findings.</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. provides expert advice to integrate ethics into ai and data projects and programmes. x000d oversees governance and assurance activities. reviews and approves impact assessments and audits. x000d promotes awareness of ethical principles and their application across the organisation. x000d contributes to the development of policy, standards and guidelines related to ai and data ethics.</t>
+          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. provides expert advice to integrate ethics into ai and data projects and programmes. oversees governance and assurance activities. reviews and approves impact assessments and audits. promotes awareness of ethical principles and their application across the organisation. contributes to the development of policy, standards and guidelines related to ai and data ethics.</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. sets direction for ethics in ai and data initiatives. defines governance processes to ensure compliance with ethical standards. x000d engages with industry bodies and experts to develop and drive industry recommended practices. x000d develops and implements strategic ethical frameworks. leads highlevel reviews and decisionmaking processes. x000d allocates resources to support the organisations commitment to ethical practices. ensures the organisation has resources and skills for ethical assurance.</t>
+          <t>implementing and promoting ethical practices in the design, development, deployment and use of ai and data technologies. sets direction for ethics in ai and data initiatives. defines governance processes to ensure compliance with ethical standards. engages with industry bodies and experts to develop and drive industry recommended practices. develops and implements strategic ethical frameworks. leads highlevel reviews and decisionmaking processes. allocates resources to support the organisations commitment to ethical practices. ensures the organisation has resources and skills for ethical assurance.</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. assists in collecting evidence and conducting audit activities under routine supervision. x000d maintains documentation and audit trails. x000d helps identify and report issues and discrepancies.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. assists in collecting evidence and conducting audit activities under routine supervision. maintains documentation and audit trails. helps identify and report issues and discrepancies.</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. adopts a structured approach to executing and documenting audit fieldwork, following agreed standards. x000d maintains integrity of records to support and satisfy audit trails.x000d identifies typical risk indicators and explains prevention measures.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. adopts a structured approach to executing and documenting audit fieldwork, following agreed standards. maintains integrity of records to support and satisfy audit trails. identifies typical risk indicators and explains prevention measures.</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. contributes to planning and executing of riskbased audit of existing and planned processes, products, systems and services.x000d identifies and documents risks in detail.x000d identifies the root cause of issues during an audit and communicates these effectively as risk insights.x000d collates evidence regarding the interpretation and implementation of control measures. prepares and communicates reports to stakeholders, providing a factual basis for findings.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. contributes to planning and executing of riskbased audit of existing and planned processes, products, systems and services. identifies and documents risks in detail. identifies the root cause of issues during an audit and communicates these effectively as risk insights. collates evidence regarding the interpretation and implementation of control measures. prepares and communicates reports to stakeholders, providing a factual basis for findings.</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. plans, organises and conducts audits of complex domains areas, crossfunctional areas and across the supply chain.x000d confirms the scope and objectives of specific audit activities with management. aligns with the scope of the audit programme and organisational policies.x000d determines appropriate methods of investigation to achieve the audit objectives. presents audit findings to management describing the effectiveness and efficiency of control mechanisms.x000d provides general and specific audit advice. collaborates with professionals in related specialisms to develop and integrate findings.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. plans, organises and conducts audits of complex domains areas, crossfunctional areas and across the supply chain. confirms the scope and objectives of specific audit activities with management. aligns with the scope of the audit programme and organisational policies. determines appropriate methods of investigation to achieve the audit objectives. presents audit findings to management describing the effectiveness and efficiency of control mechanisms. provides general and specific audit advice. collaborates with professionals in related specialisms to develop and integrate findings.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. leads and manages complex audits and programmes of audit activity.x000d obtains and manages appropriate specialist expertise to contribute highly specialised technical knowledge and experience.x000d develops organisational policies, standards and guidelines for the conduct of audits. ensures the objectivity and impartiality of the audit process.x000d identifies areas of risk and specifies audit programmes. ensures audit coverage is sufficient to provide the business with assurance of adequacy and integrity. authorises the issue of formal reports to management on the effectiveness and efficiency of control mechanisms.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. leads and manages complex audits and programmes of audit activity. obtains and manages appropriate specialist expertise to contribute highly specialised technical knowledge and experience. develops organisational policies, standards and guidelines for the conduct of audits. ensures the objectivity and impartiality of the audit process. identifies areas of risk and specifies audit programmes. ensures audit coverage is sufficient to provide the business with assurance of adequacy and integrity. authorises the issue of formal reports to management on the effectiveness and efficiency of control mechanisms.</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. directs the definition and implementation of the organisations audit function, and oversees its communication to stakeholders.x000d defines audit strategy, plans audit cycles and ensures appropriate coverage across the organisation. ensures the audit function adds value. liaises with stakeholders to ensure audit coverage is relevant and understood.x000d directs use of risk analysis to identify areas for review. ensures appropriate resources are available to deliver organisational requirements for audits.x000d reports to the most senior level on findings, relevance and recommendations for improvement of audit activity.</t>
+          <t>delivering independent, riskbased assessments of the effectiveness of processes, the controls and the compliance environment of an organisation. directs the definition and implementation of the organisations audit function, and oversees its communication to stakeholders. defines audit strategy, plans audit cycles and ensures appropriate coverage across the organisation. ensures the audit function adds value. liaises with stakeholders to ensure audit coverage is relevant and understood. directs use of risk analysis to identify areas for review. ensures appropriate resources are available to deliver organisational requirements for audits. reports to the most senior level on findings, relevance and recommendations for improvement of audit activity.</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. assists with quality management tasks under routine supervision.x000d supports the development, maintenance and distribution of quality standards.x000d helps document and track updates to quality management processes and standards.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. assists with quality management tasks under routine supervision. supports the development, maintenance and distribution of quality standards. helps document and track updates to quality management processes and standards.</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. uses appropriate methods and a systematic approach to developing, maintaining, controlling and distributing quality and environmental standards. x000d makes technical changes to and controls the updates and distribution of quality standards. x000d distributes new and revised standards.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. uses appropriate methods and a systematic approach to developing, maintaining, controlling and distributing quality and environmental standards. makes technical changes to and controls the updates and distribution of quality standards. distributes new and revised standards.</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. assists in the development of new or improved practices and organisational processes or standards. x000d assists projects, functions or teams in planning the quality management for their area of responsibility. x000d facilitates localised improvements to the quality system or services.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. assists in the development of new or improved practices and organisational processes or standards. assists projects, functions or teams in planning the quality management for their area of responsibility. facilitates localised improvements to the quality system or services.</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. ensures projects, teams and functions have appropriate practices in place and are meeting required organisational quality levels. x000d advises on the application of appropriate quality management techniques and standards. x000d determines areas where existing processes should change after analysing audit findings. facilitates improvements to processes by changing approaches and working practices, typically using recognised models. x000d takes responsibility for controlling updating and distributing organisational standards.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. ensures projects, teams and functions have appropriate practices in place and are meeting required organisational quality levels. advises on the application of appropriate quality management techniques and standards. determines areas where existing processes should change after analysing audit findings. facilitates improvements to processes by changing approaches and working practices, typically using recognised models. takes responsibility for controlling updating and distributing organisational standards.</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. achieves and maintains compliance against national and international standards, as appropriate. x000d prioritises areas for quality improvement by considering strategy, business objectives and results from internal and external audits. initiates the application of appropriate quality management techniques in these areas. x000d initiates improvements to processes by changing approaches and working practices, typically using recognised models. x000d identifies and plans systematic corrective action to reduce errors and improve the quality of the systems and services.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. achieves and maintains compliance against national and international standards, as appropriate. prioritises areas for quality improvement by considering strategy, business objectives and results from internal and external audits. initiates the application of appropriate quality management techniques in these areas. initiates improvements to processes by changing approaches and working practices, typically using recognised models. identifies and plans systematic corrective action to reduce errors and improve the quality of the systems and services.</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. determines the quality strategy and secures commitment from executive leadership. x000d develops policies for approval and adoption by organisational management. ensures adequate technology, procedures and resources are in place to support the quality system. x000d plans and monitors the performance of the quality management system and the internal quality audit schedule. x000d determines the extent to which quality policies and quality systems meet organisational needs and reviews as necessary.</t>
+          <t>defining and operating a management framework of processes and working practices to deliver the organisations quality objectives. determines the quality strategy and secures commitment from executive leadership. develops policies for approval and adoption by organisational management. ensures adequate technology, procedures and resources are in place to support the quality system. plans and monitors the performance of the quality management system and the internal quality audit schedule. determines the extent to which quality policies and quality systems meet organisational needs and reviews as necessary.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. assists with quality assurance tasks under routine supervision.x000d supports the collection of data and evidence related to quality assurance. x000d assists in reviewing records to ensure compliance with quality standards.x000d helps identify and report quality issues and discrepancies.</t>
+          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. assists with quality assurance tasks under routine supervision. supports the collection of data and evidence related to quality assurance. assists in reviewing records to ensure compliance with quality standards. helps identify and report quality issues and discrepancies.</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. contributes to the collection of evidence and the conduct of formal audits or reviews of activities.x000d examines records for evidence that appropriate testing and other quality control activities have taken place. x000d determines compliance with organisational directives, standards and procedures and identifies noncompliances, nonconformances and abnormal occurrences.</t>
+          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. contributes to the collection of evidence and the conduct of formal audits or reviews of activities. examines records for evidence that appropriate testing and other quality control activities have taken place. determines compliance with organisational directives, standards and procedures and identifies noncompliances, nonconformances and abnormal occurrences.</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. plans, organises and conducts assessment activity and determines whether appropriate quality control has been applied.x000d conducts formal assessments or reviews for given domain areas, suppliers or parts of the supply chain. collates, collects and examines records, analyses the evidence and drafts all or part of formal compliance reports.x000d determines the risks associated with findings and noncompliance and proposes corrective actions.x000d provides advice and guidance in the use of organisational standards.</t>
+          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. plans, organises and conducts assessment activity and determines whether appropriate quality control has been applied. conducts formal assessments or reviews for given domain areas, suppliers or parts of the supply chain. collates, collects and examines records, analyses the evidence and drafts all or part of formal compliance reports. determines the risks associated with findings and noncompliance and proposes corrective actions. provides advice and guidance in the use of organisational standards.</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. plans, organises and conducts formal reviews and assessments of complex domains areas, crossfunctional areas and across the supply chain.x000d evaluates, appraises and identifies noncompliances with organisational standards and determines the underlying reasons for noncompliance.x000d prepares and reports on assessment findings and associated risks. ensures appropriate owners for corrective actions are identified. identifies opportunities to improve organisational control mechanisms.x000d oversees the assurance activities of others, providing advice and expertise to support assurance activity.</t>
+          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. plans, organises and conducts formal reviews and assessments of complex domains areas, crossfunctional areas and across the supply chain. evaluates, appraises and identifies noncompliances with organisational standards and determines the underlying reasons for noncompliance. prepares and reports on assessment findings and associated risks. ensures appropriate owners for corrective actions are identified. identifies opportunities to improve organisational control mechanisms. oversees the assurance activities of others, providing advice and expertise to support assurance activity.</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. leads, develops and is accountable for an organisational approach and commitment to quality assurance.x000d ensures quality assurance processes and activities are robust and reliable, and appropriately tailored to the organisations quality objectives. plans and resources the organisational quality assurance activities, using internal or thirdparty resources.x000d considers the implications of emerging technology, approaches, trends, regulations and legislation.x000d monitors and reports on quality assurance activities, levels of compliance and improvement opportunities.</t>
+          <t>assuring, through ongoing and periodic assessments and reviews, that the organisations quality objectives are being met. leads, develops and is accountable for an organisational approach and commitment to quality assurance. ensures quality assurance processes and activities are robust and reliable, and appropriately tailored to the organisations quality objectives. plans and resources the organisational quality assurance activities, using internal or thirdparty resources. considers the implications of emerging technology, approaches, trends, regulations and legislation. monitors and reports on quality assurance activities, levels of compliance and improvement opportunities.</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>providing advice and recommendations, based on expertise and experience, to address client needs. takes responsibility for specific elements of a consulting engagement within a defined scope.x000d collaborates with clients as part of formal or informal consultancy engagements. understands client requirements by collecting data and delivering analysis. x000d ensures proposed solutions are correctly understood and effectively applied.x000d supports the broader consultancy engagement by contributing insights and assisting with problemsolving, always within the established boundaries of responsibility.</t>
+          <t>providing advice and recommendations, based on expertise and experience, to address client needs. takes responsibility for specific elements of a consulting engagement within a defined scope. collaborates with clients as part of formal or informal consultancy engagements. understands client requirements by collecting data and delivering analysis. ensures proposed solutions are correctly understood and effectively applied. supports the broader consultancy engagement by contributing insights and assisting with problemsolving, always within the established boundaries of responsibility.</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>providing advice and recommendations, based on expertise and experience, to address client needs. takes full responsibility for understanding client requirements including data collection, analysis and resolving issues.x000d manages the scope and delivery of consultancy engagements to meet agreed objectives. identifies, evaluates and recommends options. x000d collaborates with, and facilitates, stakeholder groups, as part of formal or informal consultancy agreements. seeks to fully address client needs and implements solutions if required. x000d enhances the capabilities and effectiveness of clients by ensuring proposed solutions are fully understood and appropriately exploited.</t>
+          <t>providing advice and recommendations, based on expertise and experience, to address client needs. takes full responsibility for understanding client requirements including data collection, analysis and resolving issues. manages the scope and delivery of consultancy engagements to meet agreed objectives. identifies, evaluates and recommends options. collaborates with, and facilitates, stakeholder groups, as part of formal or informal consultancy agreements. seeks to fully address client needs and implements solutions if required. enhances the capabilities and effectiveness of clients by ensuring proposed solutions are fully understood and appropriately exploited.</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>providing advice and recommendations, based on expertise and experience, to address client needs. leads and manages the provision of consultancy services andor a team of consultants. x000d provides expert advice and guidance in own areas of expertise to both consultants and clients.x000d engages with clients at a strategic level, establishing consultancy agreements or contracts and maintaining longterm relationships. manages the completion of engagements, ensuring strategic alignment with client needs and overseeing the transition from consultancy delivery to operational adoption. x000d oversees the development and delivery of consultancy services within the agreed strategic framework.</t>
+          <t>providing advice and recommendations, based on expertise and experience, to address client needs. leads and manages the provision of consultancy services andor a team of consultants. provides expert advice and guidance in own areas of expertise to both consultants and clients. engages with clients at a strategic level, establishing consultancy agreements or contracts and maintaining longterm relationships. manages the completion of engagements, ensuring strategic alignment with client needs and overseeing the transition from consultancy delivery to operational adoption. oversees the development and delivery of consultancy services within the agreed strategic framework.</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>providing advice and recommendations, based on expertise and experience, to address client needs. directs the strategic direction and operations of a significant consultancy practice. x000d engages with key stakeholders at the highest levels to ensure consultancy services drive strategic outcomes. x000d manages overall client relationships and the development of longterm consultancy partnerships, maintaining high standards of service delivery and ethical practice.x000d oversees practice development, proposals, sales, account management and the delivery of consultancy services across diverse topics.</t>
+          <t>providing advice and recommendations, based on expertise and experience, to address client needs. directs the strategic direction and operations of a significant consultancy practice. engages with key stakeholders at the highest levels to ensure consultancy services drive strategic outcomes. manages overall client relationships and the development of longterm consultancy partnerships, maintaining high standards of service delivery and ethical practice. oversees practice development, proposals, sales, account management and the delivery of consultancy services across diverse topics.</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>providing authoritative, professional advice and direction in a specialist area. provides detailed and specific advice to support the organisations planning and operations, typically related to the immediate area of responsibility.x000d actively maintains recognised expert level knowledge in one or more identifiable specialisms. x000d recognises and identifies the boundaries of their own specialist knowledge. x000d where appropriate, collaborates with other specialists to ensure advice given is professionally sound and appropriate to the organisations needs.</t>
+          <t>providing authoritative, professional advice and direction in a specialist area. provides detailed and specific advice to support the organisations planning and operations, typically related to the immediate area of responsibility. actively maintains recognised expert level knowledge in one or more identifiable specialisms. recognises and identifies the boundaries of their own specialist knowledge. where appropriate, collaborates with other specialists to ensure advice given is professionally sound and appropriate to the organisations needs.</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>providing authoritative, professional advice and direction in a specialist area. provides professional advice that informs operational leadership and influences the translation of strategy into operations in their specialist area.x000d oversees the provision of specialist advice by others. consolidates expertise from multiple sources, including thirdparty experts, to provide coherent and professionally sound advice to further organisational objectives.x000d supports and promotes the development and sharing of specialist knowledge within the organisation.</t>
+          <t>providing authoritative, professional advice and direction in a specialist area. provides professional advice that informs operational leadership and influences the translation of strategy into operations in their specialist area. oversees the provision of specialist advice by others. consolidates expertise from multiple sources, including thirdparty experts, to provide coherent and professionally sound advice to further organisational objectives. supports and promotes the development and sharing of specialist knowledge within the organisation.</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>providing authoritative, professional advice and direction in a specialist area. leads and promotes the development and application of specialist knowledge across the organisation, delivering professional advice that shapes direction and highlevel decisions.x000d maintains a network of recognised experts inside andor outside the organisation who can deliver expert advice in relevant areas. x000d actively influences professional development planning across a significant part of the organisation to further the development of appropriate expertise and provision of highquality professional advice.</t>
+          <t>providing authoritative, professional advice and direction in a specialist area. leads and promotes the development and application of specialist knowledge across the organisation, delivering professional advice that shapes direction and highlevel decisions. maintains a network of recognised experts inside andor outside the organisation who can deliver expert advice in relevant areas. actively influences professional development planning across a significant part of the organisation to further the development of appropriate expertise and provision of highquality professional advice.</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provide routine support using agreed guidelines on the use of wellestablished methods and tools. x000d assists in configuring and maintaining methods and tools under routine supervision. x000d supports the creation and updating of documentation related to methods and tools.</t>
+          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provide routine support using agreed guidelines on the use of wellestablished methods and tools. assists in configuring and maintaining methods and tools under routine supervision. supports the creation and updating of documentation related to methods and tools.</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provides support on the use of existing methods and tools. x000d configures and maintains methods and tools within a known context. x000d creates and updates the documentation of methods and tools.x000d identifies and resolves basic issues related to tool usage.</t>
+          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provides support on the use of existing methods and tools. configures and maintains methods and tools within a known context. creates and updates the documentation of methods and tools. identifies and resolves basic issues related to tool usage.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. engages with stakeholders to understand requirements and recommends appropriate solutions. x000d provides advice and guidance to support the adoption of methods and tools and adherence to policies and standards. x000d tailors processes to meet specific needs while ensuring they align with established standards and are informed by evaluations of methods and tools.x000d reviews and improves usage and application of methods and tools.</t>
+          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. engages with stakeholders to understand requirements and recommends appropriate solutions. provides advice and guidance to support the adoption of methods and tools and adherence to policies and standards. tailors processes to meet specific needs while ensuring they align with established standards and are informed by evaluations of methods and tools. reviews and improves usage and application of methods and tools.</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provides authoritative advice and leadership to promote adoption of methods and tools and adherence to policies and standards. x000d evaluates and selects appropriate methods and tools in line with agreed policies and standards. contributes to organisational policies, standards and guidelines for methods and tools.x000d implements methods and tools at programme, project and team levels including selection and tailoring in line with agreed standards. x000d manages reviews of the benefits and value of methods and tools. identifies and recommends improvements that support broader organisational goals.</t>
+          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. provides authoritative advice and leadership to promote adoption of methods and tools and adherence to policies and standards. evaluates and selects appropriate methods and tools in line with agreed policies and standards. contributes to organisational policies, standards and guidelines for methods and tools. implements methods and tools at programme, project and team levels including selection and tailoring in line with agreed standards. manages reviews of the benefits and value of methods and tools. identifies and recommends improvements that support broader organisational goals.</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. develops organisational policies, standards and guidelines for methods and tools. x000d sets direction and leads in the introduction and use of techniques, methodologies and tools, to meet business requirements. x000d leads the development of organisational capabilities for methods and tools to ensure consistent adoption and adherence to policies and standards.x000d secures organisational commitment and resources to methods and tools. drives continuous improvement and innovation in methods and tools.</t>
+          <t>leads the adoption, management and optimisation of methods and tools, ensuring effective use and alignment with organisational objectives. develops organisational policies, standards and guidelines for methods and tools. sets direction and leads in the introduction and use of techniques, methodologies and tools, to meet business requirements. leads the development of organisational capabilities for methods and tools to ensure consistent adoption and adherence to policies and standards. secures organisational commitment and resources to methods and tools. drives continuous improvement and innovation in methods and tools.</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. ensures programmeproject leads andor service owners adhere to the agreed portfolio management and governance frameworks.x000d explains what information is needed and ensures they provide this information to agreed targets of timelines and accuracy. x000d produces reports as appropriate for portfolio governance, including making recommendations for changes to the portfolio.</t>
+          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. ensures programmeproject leads andor service owners adhere to the agreed portfolio management and governance frameworks. explains what information is needed and ensures they provide this information to agreed targets of timelines and accuracy. produces reports as appropriate for portfolio governance, including making recommendations for changes to the portfolio.</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. engages and influences senior managers to ensure the portfolio will deliver the agreed business objectives. x000d leads the definition, planning, scheduling and monitoring of portfolio activities, ensuring alignment with governance standards. x000d ensures each portfolio component contributes to the overall objectives. identifies and addresses portfoliorelated issues, recommending and monitoring corrective actions. x000d collects and summarises portfolio measures, reporting on status and ensuring compliance with governance frameworks.</t>
+          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. engages and influences senior managers to ensure the portfolio will deliver the agreed business objectives. leads the definition, planning, scheduling and monitoring of portfolio activities, ensuring alignment with governance standards. ensures each portfolio component contributes to the overall objectives. identifies and addresses portfoliorelated issues, recommending and monitoring corrective actions. collects and summarises portfolio measures, reporting on status and ensuring compliance with governance frameworks.</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. authorises the structure of portfolios and aligns the portfolio with strategies, objectives, governance frameworks and emerging opportunities. x000d leads the definition, implementation and review of the organisations portfolio management framework. sets parameters for the prioritisation of resources and the changes to be implemented. x000d recommends and implements corrective action by engaging and influencing senior management. x000d leads the ongoing monitoring and review of portfolios for impact on current business activities and the strategic benefits to be realised. implements portfolio governance arrangements and effective reporting.</t>
+          <t>developing and applying a management framework to define and deliver a portfolio of programmes, projects andor ongoing services. authorises the structure of portfolios and aligns the portfolio with strategies, objectives, governance frameworks and emerging opportunities. leads the definition, implementation and review of the organisations portfolio management framework. sets parameters for the prioritisation of resources and the changes to be implemented. recommends and implements corrective action by engaging and influencing senior management. leads the ongoing monitoring and review of portfolios for impact on current business activities and the strategic benefits to be realised. implements portfolio governance arrangements and effective reporting.</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>identifying, planning and coordinating a set of related projects and activities in support of specific business strategies and objectives. plans, directs and coordinates activities to manage and implement a programme from initiation to final transition into operational, businessasusual management. x000d plans, schedules, monitors and reports on programmerelated activities. establishes and maintains appropriate and effective governance and risk management frameworks. x000d ensures comprehensive reporting and communication policies are in place and followed. maintains an awareness of current technical developments that may provide opportunities to the programmes. x000d ensures programmes are managed to realise agreed business benefits within agreed timescales.</t>
+          <t>identifying, planning and coordinating a set of related projects and activities in support of specific business strategies and objectives. plans, directs and coordinates activities to manage and implement a programme from initiation to final transition into operational, businessasusual management. plans, schedules, monitors and reports on programmerelated activities. establishes and maintains appropriate and effective governance and risk management frameworks. ensures comprehensive reporting and communication policies are in place and followed. maintains an awareness of current technical developments that may provide opportunities to the programmes. ensures programmes are managed to realise agreed business benefits within agreed timescales.</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>identifying, planning and coordinating a set of related projects and activities in support of specific business strategies and objectives. sets organisational strategy governing programme management, including the application of appropriate methodologies. x000d plans, directs and coordinates activities to manage and implement complex programmes from initiation to full integration with operational, businessasusual management. aligns programme objectives with business goals and authorises related projects and activities. x000d plans, schedules, monitors and reports on programme activities, supported by comprehensive reporting and communication strategies.x000d ensures governance and risk management frameworks are in place to support strategic decisionmaking and programme execution.</t>
+          <t>identifying, planning and coordinating a set of related projects and activities in support of specific business strategies and objectives. sets organisational strategy governing programme management, including the application of appropriate methodologies. plans, directs and coordinates activities to manage and implement complex programmes from initiation to full integration with operational, businessasusual management. aligns programme objectives with business goals and authorises related projects and activities. plans, schedules, monitors and reports on programme activities, supported by comprehensive reporting and communication strategies. ensures governance and risk management frameworks are in place to support strategic decisionmaking and programme execution.</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. defines, documents and executes small projects or subprojects. x000d works independently or with a small team, actively participating in all project phases. applies appropriate project management methods and tools. identifies, assesses and manages risks effectively. x000d prepares realistic project plans including scope, schedule, quality, risk and communication plans, ensuring stakeholder involvement and alignment with organisational governance standards. x000d tracks activities against the project schedule, managing stakeholder involvement as appropriate. monitors costs, times, quality and resources used. takes action where these exceed agreed tolerances.</t>
+          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. defines, documents and executes small projects or subprojects. works independently or with a small team, actively participating in all project phases. applies appropriate project management methods and tools. identifies, assesses and manages risks effectively. prepares realistic project plans including scope, schedule, quality, risk and communication plans, ensuring stakeholder involvement and alignment with organisational governance standards. tracks activities against the project schedule, managing stakeholder involvement as appropriate. monitors costs, times, quality and resources used. takes action where these exceed agreed tolerances.</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. takes full responsibility for the definition, approach, facilitation and satisfactory completion of mediumscale projects. x000d provides effective leadership to the project team, adopting suitable project management methods and tools. manages change control processes and assesses risks, ensuring projects align with governance frameworks and business priorities.x000d communicates regularly with stakeholders, ensuring project deliverables meet agreed standards, budgets and timelines. ensures project and product quality reviews occur on schedule and according to procedure. x000d proactively monitors performance metrics, implementing preventive and corrective actions as needed.</t>
+          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. takes full responsibility for the definition, approach, facilitation and satisfactory completion of mediumscale projects. provides effective leadership to the project team, adopting suitable project management methods and tools. manages change control processes and assesses risks, ensuring projects align with governance frameworks and business priorities. communicates regularly with stakeholders, ensuring project deliverables meet agreed standards, budgets and timelines. ensures project and product quality reviews occur on schedule and according to procedure. proactively monitors performance metrics, implementing preventive and corrective actions as needed.</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. takes full responsibility for the definition, documentation and successful completion of complex projects. x000d adopts and adapts project management methods and tools suited to the projects needs. ensures effective monitoring and control of resources, budgets and timelines. x000d integrates robust risk management within governance frameworks to align decisions with the organisations risk appetite and standards. x000d manages expectations of key stakeholders, ensuring all activities align with organisational goals, deliver agreed outcomes and provide business value.</t>
+          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. takes full responsibility for the definition, documentation and successful completion of complex projects. adopts and adapts project management methods and tools suited to the projects needs. ensures effective monitoring and control of resources, budgets and timelines. integrates robust risk management within governance frameworks to align decisions with the organisations risk appetite and standards. manages expectations of key stakeholders, ensuring all activities align with organisational goals, deliver agreed outcomes and provide business value.</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. sets organisational strategy governing the direction and conduct of project management, ensuring projects align with strategic objectives and governance frameworks. x000d authorises the management of largescale projects. leads project planning, scheduling, controlling and reporting activities for strategic, high impact, high risk projects. x000d oversees the selection and application of project methodologies. directs the approach to risk management for projects, ensuring risks and issues are managed in line with organisational policies. x000d ensures projects deliver their intended benefits and contribute to longterm goals.</t>
+          <t>delivering agreed project outcomes by aligning appropriate management techniques, collaboration, leadership and governance to specific project and organisational contexts. sets organisational strategy governing the direction and conduct of project management, ensuring projects align with strategic objectives and governance frameworks. authorises the management of largescale projects. leads project planning, scheduling, controlling and reporting activities for strategic, high impact, high risk projects. oversees the selection and application of project methodologies. directs the approach to risk management for projects, ensuring risks and issues are managed in line with organisational policies. ensures projects deliver their intended benefits and contribute to longterm goals.</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. assists with the compilation of reports for projects, programmes, or portfolios. x000d maintains programme and project files from supplied actual and forecast data.x000d works under supervision to support the administrative needs of project teams, contributing to routine project activities.</t>
+          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. assists with the compilation of reports for projects, programmes, or portfolios. maintains programme and project files from supplied actual and forecast data. works under supervision to support the administrative needs of project teams, contributing to routine project activities.</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. provides foundational support for projects, programmes, or portfolios. x000d assists with planning, scheduling, tracking and reporting using established tools and processes. follows recommended solutions to ensure accurate documentation and communication of project progress. x000d collaborates closely with project teams and stakeholders, gathering updates and information to maintain project records and ensure alignment with project objectives.x000d participates in project boards, assurance teams and quality review meetings when necessary.</t>
+          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. provides foundational support for projects, programmes, or portfolios. assists with planning, scheduling, tracking and reporting using established tools and processes. follows recommended solutions to ensure accurate documentation and communication of project progress. collaborates closely with project teams and stakeholders, gathering updates and information to maintain project records and ensure alignment with project objectives. participates in project boards, assurance teams and quality review meetings when necessary.</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. supports programme or project control boards, project assurance teams and quality review meetings.x000d takes responsibility for the provision of support services to projects. uses project control solutions for planning, scheduling and tracking. sets up and provides guidance on project management software, procedures, processes, tools and techniques.x000d provides basic guidance on project proposals. may provide views across projects on topics such as risk, quality, finance, or configuration management.x000d works closely with project boards and review meetings, contributing actively to discussions and decisions.</t>
+          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. supports programme or project control boards, project assurance teams and quality review meetings. takes responsibility for the provision of support services to projects. uses project control solutions for planning, scheduling and tracking. sets up and provides guidance on project management software, procedures, processes, tools and techniques. provides basic guidance on project proposals. may provide views across projects on topics such as risk, quality, finance, or configuration management. works closely with project boards and review meetings, contributing actively to discussions and decisions.</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. takes responsibility for the provision of portfolio, programme and project support. x000d advises on the available standards, procedures, methods, tools and techniques. x000d evaluates project andor programme performance and recommends changes where necessary. x000d contributes to reviews and audits of project and programme management to ensure conformance to standards.</t>
+          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. takes responsibility for the provision of portfolio, programme and project support. advises on the available standards, procedures, methods, tools and techniques. evaluates project andor programme performance and recommends changes where necessary. contributes to reviews and audits of project and programme management to ensure conformance to standards.</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. leads implementation and delivery of portfolio, programme and project office services. x000d defines the approachpolicy and sets standards for the support provided for managing and monitoring portfolios, programmes, and projects. x000d manages resources to ensure delivery of effective servicesresources in line with current and planned demand. x000d reviews and improves the delivery portfolio, programme and project office services.</t>
+          <t>providing support and guidance on portfolio, programme and project management processes, procedures, tools and techniques. leads implementation and delivery of portfolio, programme and project office services. defines the approachpolicy and sets standards for the support provided for managing and monitoring portfolios, programmes, and projects. manages resources to ensure delivery of effective servicesresources in line with current and planned demand. reviews and improves the delivery portfolio, programme and project office services.</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. manages the routine delivery of small products or services, or specific parts of a larger product or service.x000d follows delivery methodologies, tools, and quality processes. monitors the teams adherence to these practices.x000d coordinates team planning processes based on the established priorities of work items. tracks and reports on delivery progress, risks and issues.x000d supports a collaborative and productive working environment, demonstrating appropriate behaviours. contributes to continuous improvement of delivery processes within the team.</t>
+          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. manages the routine delivery of small products or services, or specific parts of a larger product or service. follows delivery methodologies, tools, and quality processes. monitors the teams adherence to these practices. coordinates team planning processes based on the established priorities of work items. tracks and reports on delivery progress, risks and issues. supports a collaborative and productive working environment, demonstrating appropriate behaviours. contributes to continuous improvement of delivery processes within the team.</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. manages the delivery of products or services for small to mediumsized initiatives.x000d applies appropriate delivery methodologies and tools. establishes and leads delivery teams, creating a collaborative and productive working environment.x000d manages the prioritisation of work items, leads iteration planning processes and ensures value is delivered incrementally throughout the delivery cycle. communicates delivery progress, risks and issues to stakeholders.x000d ensures the quality of deliverables. participates in reviews and contributes to the continuous improvement of delivery processes within the scope of the team or initiative.</t>
+          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. manages the delivery of products or services for small to mediumsized initiatives. applies appropriate delivery methodologies and tools. establishes and leads delivery teams, creating a collaborative and productive working environment. manages the prioritisation of work items, leads iteration planning processes and ensures value is delivered incrementally throughout the delivery cycle. communicates delivery progress, risks and issues to stakeholders. ensures the quality of deliverables. participates in reviews and contributes to the continuous improvement of delivery processes within the scope of the team or initiative.</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. leads delivery of products or services for large or complex initiatives.x000d adapts delivery approaches based on the context and complexity of the initiative. provides leadership and guidance to multiple delivery teams. collaborates with stakeholders to align delivery objectives with business goals. proactively manages risks, dependencies and changes that may impact delivery.x000d ensures optimal allocation of resources and skills across teams. monitors key delivery metrics, ensuring transparency and visibility.x000d drives the continuous improvement of delivery processes and practices across the organisation.</t>
+          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. leads delivery of products or services for large or complex initiatives. adapts delivery approaches based on the context and complexity of the initiative. provides leadership and guidance to multiple delivery teams. collaborates with stakeholders to align delivery objectives with business goals. proactively manages risks, dependencies and changes that may impact delivery. ensures optimal allocation of resources and skills across teams. monitors key delivery metrics, ensuring transparency and visibility. drives the continuous improvement of delivery processes and practices across the organisation.</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. defines and oversees the delivery strategy for multiple products or services.x000d aligns delivery strategy with organisational goals and customer needs. ensures effective allocation of resources and budget.x000d monitors and reports on performance of product and service delivery, ensuring alignment with objectives. identifies and mitigates systemic risks and issues.x000d sets the direction and standards for delivery management across the organisation. leads the development of a culture focused on continuous improvement and customercentricity.</t>
+          <t>ensuring successful delivery of new or updated products and services through effective leadership and collaboration within defined delivery cycles. defines and oversees the delivery strategy for multiple products or services. aligns delivery strategy with organisational goals and customer needs. ensures effective allocation of resources and budget. monitors and reports on performance of product and service delivery, ensuring alignment with objectives. identifies and mitigates systemic risks and issues. sets the direction and standards for delivery management across the organisation. leads the development of a culture focused on continuous improvement and customercentricity.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>investigating business situations to define recommendations for improvement action. assists in investigating business situations to help identify and analyse problems and opportunities, under routine supervision. x000d helps collect and organise data and information to support recommendations.</t>
+          <t>investigating business situations to define recommendations for improvement action. assists in investigating business situations to help identify and analyse problems and opportunities, under routine supervision. helps collect and organise data and information to support recommendations.</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>investigating business situations to define recommendations for improvement action. investigates straightforward business situations to identify and analyse problems and opportunities. x000d contributes to the recommendation of improvements. x000d follows agreed standards and techniques to investigate, analyse and document business situations. x000d engages with stakeholders under direction.</t>
+          <t>investigating business situations to define recommendations for improvement action. investigates straightforward business situations to identify and analyse problems and opportunities. contributes to the recommendation of improvements. follows agreed standards and techniques to investigate, analyse and document business situations. engages with stakeholders under direction.</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>investigating business situations to define recommendations for improvement action. investigates business situations where there is some complexity and ambiguity. x000d adopts holistic view to identify and analyse problems and opportunities. x000d contributes to the selection of the approach and techniques to be used for business situation analysis. x000d conducts root cause analysis and identifies recommendations for improvements. engages and collaborates with operational stakeholders.</t>
+          <t>investigating business situations to define recommendations for improvement action. investigates business situations where there is some complexity and ambiguity. adopts holistic view to identify and analyse problems and opportunities. contributes to the selection of the approach and techniques to be used for business situation analysis. conducts root cause analysis and identifies recommendations for improvements. engages and collaborates with operational stakeholders.</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>investigating business situations to define recommendations for improvement action. plans, manages and investigates business situation analysis where there is significant ambiguity and complexity. x000d advises on the approach and techniques to be used for business situation analysis. ensures holistic view adopted to identify and analyse wideranging problems and opportunities. x000d engages and collaborates with a wide range of stakeholders, including those at the management level. gains agreement from stakeholders to conclusions and recommendations. x000d contributes to definition of organisational standards and guidelines for business situation analysis.</t>
+          <t>investigating business situations to define recommendations for improvement action. plans, manages and investigates business situation analysis where there is significant ambiguity and complexity. advises on the approach and techniques to be used for business situation analysis. ensures holistic view adopted to identify and analyse wideranging problems and opportunities. engages and collaborates with a wide range of stakeholders, including those at the management level. gains agreement from stakeholders to conclusions and recommendations. contributes to definition of organisational standards and guidelines for business situation analysis.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>investigating business situations to define recommendations for improvement action. initiates and leads business situation analysis where there is extensive ambiguity, complexity and potentially significant organisational impacts. x000d establishes and promotes the need for holistic business situation analysis prior to change programme initiation. x000d engages with stakeholders at executive level and advises on recommended change initiatives. x000d defines organisational policies, standards and techniques for business situation analysis.</t>
+          <t>investigating business situations to define recommendations for improvement action. initiates and leads business situation analysis where there is extensive ambiguity, complexity and potentially significant organisational impacts. establishes and promotes the need for holistic business situation analysis prior to change programme initiation. engages with stakeholders at executive level and advises on recommended change initiatives. defines organisational policies, standards and techniques for business situation analysis.</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. assists in feasibility assessment tasks under routine supervision. x000d helps gather information required for feasibility assessments. x000d supports the identification and documentation of options for business change.</t>
+          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. assists in feasibility assessment tasks under routine supervision. helps gather information required for feasibility assessments. supports the identification and documentation of options for business change.</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. supports option identification and feasibility assessment.x000d selects and employs standard techniques to get the information required for feasibility assessment. x000d supports identification of tangible costs and benefits, and development of business cases.</t>
+          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. supports option identification and feasibility assessment. selects and employs standard techniques to get the information required for feasibility assessment. supports identification of tangible costs and benefits, and development of business cases.</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. selects relevant feasibility assessment approaches and techniques. x000d identifies the range of possible options. undertakes shortlisting of options and feasibility assessment. x000d engages with internal and external stakeholders to get the information required for feasibility assessment. x000d supports preparation of business cases including costbenefit, impact and risk analysis for each option.</t>
+          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. selects relevant feasibility assessment approaches and techniques. identifies the range of possible options. undertakes shortlisting of options and feasibility assessment. engages with internal and external stakeholders to get the information required for feasibility assessment. supports preparation of business cases including costbenefit, impact and risk analysis for each option.</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. manages investigative work to enable feasibility assessments. x000d collaborates with stakeholders and specialists to get the information required for feasibility assessment. x000d advises on the selection of feasibility assessment approaches and techniques relevant to the business situation and options. x000d prepares business cases, including costbenefit, impact and risk analysis for each option.</t>
+          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. manages investigative work to enable feasibility assessments. collaborates with stakeholders and specialists to get the information required for feasibility assessment. advises on the selection of feasibility assessment approaches and techniques relevant to the business situation and options. prepares business cases, including costbenefit, impact and risk analysis for each option.</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. establishes an organisational framework and standards for feasibility assessment and business case development. x000d directs and leads feasibility assessments for initiatives that will have a significant impact on the organisation. x000d engages with senior stakeholders to clarify the strategic context for investment options. directs and leads the selection of feasibility assessment approaches and techniques that are relevant to the business situation and options. x000d presents feasibility assessments and business cases to senior stakeholders and supports decisionmaking regarding investment options.</t>
+          <t>defining, evaluating and describing business change options for financial, technical and business feasibility and strategic alignment. establishes an organisational framework and standards for feasibility assessment and business case development. directs and leads feasibility assessments for initiatives that will have a significant impact on the organisation. engages with senior stakeholders to clarify the strategic context for investment options. directs and leads the selection of feasibility assessment approaches and techniques that are relevant to the business situation and options. presents feasibility assessments and business cases to senior stakeholders and supports decisionmaking regarding investment options.</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>managing requirements through the entire delivery and operational lifecycle. uses standard techniques to elicit, specify and document requirements for simple subject areas with clearlydefined boundaries. x000d assists in the definition and management of requirements. x000d assists in the creation of a requirements baselinebacklog.x000d assists in investigating and applying changes to requirements.</t>
+          <t>managing requirements through the entire delivery and operational lifecycle. uses standard techniques to elicit, specify and document requirements for simple subject areas with clearlydefined boundaries. assists in the definition and management of requirements. assists in the creation of a requirements baselinebacklog. assists in investigating and applying changes to requirements.</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>managing requirements through the entire delivery and operational lifecycle. defines and manages scoping, requirements definition and prioritisation activities for smallscale changes and assists with more complex change initiatives.x000d follows agreed standards and applies appropriate techniques to elicit and document detailed requirements. provides constructive challenge to stakeholders as required. reviews requirements for errors and omissions. x000d prioritises requirements and documents traceability to source. x000d provides input to the requirements baselinebacklog. investigates, manages and applies requests for changes to requirements, in line with change management policy.</t>
+          <t>managing requirements through the entire delivery and operational lifecycle. defines and manages scoping, requirements definition and prioritisation activities for smallscale changes and assists with more complex change initiatives. follows agreed standards and applies appropriate techniques to elicit and document detailed requirements. provides constructive challenge to stakeholders as required. reviews requirements for errors and omissions. prioritises requirements and documents traceability to source. provides input to the requirements baselinebacklog. investigates, manages and applies requests for changes to requirements, in line with change management policy.</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>managing requirements through the entire delivery and operational lifecycle. defines and manages scoping, requirements definition and prioritisation activities for initiatives of medium size and complexity. x000d contributes to selecting the requirements approach. x000d facilitates input from stakeholders, provides constructive challenge and enables effective prioritisation of requirements. x000d establishes requirements baselines or backlogs, obtains appropriate agreement to requirements and ensures traceability to source.</t>
+          <t>managing requirements through the entire delivery and operational lifecycle. defines and manages scoping, requirements definition and prioritisation activities for initiatives of medium size and complexity. contributes to selecting the requirements approach. facilitates input from stakeholders, provides constructive challenge and enables effective prioritisation of requirements. establishes requirements baselines or backlogs, obtains appropriate agreement to requirements and ensures traceability to source.</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>managing requirements through the entire delivery and operational lifecycle. plans and drives scoping, requirements definition and prioritisation activities for large, complex initiatives. x000d selects, adopts and adapts appropriate requirements definition and management methods, tools and techniques. contributes to the development of organisational methods and standards for requirements management.x000d obtains input and agreement to requirements from a diverse range of stakeholders. negotiates with stakeholders to manage competing priorities and conflicts. x000d establishes requirements baselines or backlogs. ensures changes to requirements are investigated and managed.</t>
+          <t>managing requirements through the entire delivery and operational lifecycle. plans and drives scoping, requirements definition and prioritisation activities for large, complex initiatives. selects, adopts and adapts appropriate requirements definition and management methods, tools and techniques. contributes to the development of organisational methods and standards for requirements management. obtains input and agreement to requirements from a diverse range of stakeholders. negotiates with stakeholders to manage competing priorities and conflicts. establishes requirements baselines or backlogs. ensures changes to requirements are investigated and managed.</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>managing requirements through the entire delivery and operational lifecycle. champions the importance and value of requirements management principles and selecting effective requirements management lifecycle models. x000d develops organisational policies, standards and guidelines for requirements definition and management. x000d plans and leads scoping, requirements definition and priority setting for complex, strategic programmes.x000d drives adoption of, and adherence to, policies and standards. develops new methods and organisational capabilities for requirements management.</t>
+          <t>managing requirements through the entire delivery and operational lifecycle. champions the importance and value of requirements management principles and selecting effective requirements management lifecycle models. develops organisational policies, standards and guidelines for requirements definition and management. plans and leads scoping, requirements definition and priority setting for complex, strategic programmes. drives adoption of, and adherence to, policies and standards. develops new methods and organisational capabilities for requirements management.</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. assists in creating models for simple, welldefined business scenarios under guidance. x000d uses established techniques, as directed, to model simple subject areas with clearlydefined boundaries.x000d supports more complex modelling activities under the guidance of others by organising information and helping to apply relevant techniques.</t>
+          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. assists in creating models for simple, welldefined business scenarios under guidance. uses established techniques, as directed, to model simple subject areas with clearlydefined boundaries. supports more complex modelling activities under the guidance of others by organising information and helping to apply relevant techniques.</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. produces models for straightforward business scenarios with clear boundaries, selecting suitable techniques to meet assigned objectives. x000d engages with subject matter experts to ensure models are accurate and meet business requirements. applies established techniques to meet objectives, modelling business processes, roles and data.x000d collaborates with stakeholders to address issues and ensure models provide clarity and insight. x000d tests models and makes improvements as needed, ensuring accuracy and relevance to the business context.</t>
+          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. produces models for straightforward business scenarios with clear boundaries, selecting suitable techniques to meet assigned objectives. engages with subject matter experts to ensure models are accurate and meet business requirements. applies established techniques to meet objectives, modelling business processes, roles and data. collaborates with stakeholders to address issues and ensure models provide clarity and insight. tests models and makes improvements as needed, ensuring accuracy and relevance to the business context.</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. develops models for complex and ambiguous business scenarios. x000d selects appropriate techniques and approaches to ensure models capture the necessary business elements. independently plans modelling activities, ensuring alignment with business objectives.x000d collaborates with operational stakeholders to validate and refine models based on feedback, and to gain agreement on modelling results and their implications. x000d advises stakeholders interpreting and applying models for decisionmaking and business improvements.</t>
+          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. develops models for complex and ambiguous business scenarios. selects appropriate techniques and approaches to ensure models capture the necessary business elements. independently plans modelling activities, ensuring alignment with business objectives. collaborates with operational stakeholders to validate and refine models based on feedback, and to gain agreement on modelling results and their implications. advises stakeholders interpreting and applying models for decisionmaking and business improvements.</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. manages the development of models that support strategic business objectives.x000d works on complex and ambiguous scenarios, applying advanced techniques and methods. creates bespoke models for nonstandard contexts and ensures their alignment with overall business strategy.x000d ensures the quality of business modelling work. x000d engages and collaborates with a wide range of stakeholders providing guidance on selecting and applying appropriate modelling techniques. influences decisionmaking by presenting models that highlight key business insights.</t>
+          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. manages the development of models that support strategic business objectives. works on complex and ambiguous scenarios, applying advanced techniques and methods. creates bespoke models for nonstandard contexts and ensures their alignment with overall business strategy. ensures the quality of business modelling work. engages and collaborates with a wide range of stakeholders providing guidance on selecting and applying appropriate modelling techniques. influences decisionmaking by presenting models that highlight key business insights.</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. defines organisational standards for business modelling, ensuring models align with strategic business objectives. x000d oversees the creation and maintenance of models across multiple functions and departments, ensuring they are used effectively.x000d leads organisationwide initiatives to improve business modelling, introducing new techniques where necessary. x000d engages with senior stakeholders to gain agreement on strategic models and the decisions they inform.</t>
+          <t>creating abstract or distilled models of business scenarios, representing processes, data and roles to support decisionmaking and analysis. defines organisational standards for business modelling, ensuring models align with strategic business objectives. oversees the creation and maintenance of models across multiple functions and departments, ensuring they are used effectively. leads organisationwide initiatives to improve business modelling, introducing new techniques where necessary. engages with senior stakeholders to gain agreement on strategic models and the decisions they inform.</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. assists in planning and preparing acceptance tests for systems, products, business processes or services.x000d assists in collecting feedback from acceptance testing.</t>
+          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. assists in planning and preparing acceptance tests for systems, products, business processes or services. assists in collecting feedback from acceptance testing.</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. follows agreed standards and techniques to devise test cases and scenarios based on predefined acceptance criteria. x000d analyses and reports on test activities, results, issues and risks.</t>
+          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. follows agreed standards and techniques to devise test cases and scenarios based on predefined acceptance criteria. analyses and reports on test activities, results, issues and risks.</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. develops acceptance criteria related to functional and nonfunctional requirements, business processes, features, user stories and business rules. x000d designs and specifies test cases and scenarios to test that systems, products and services fulfil the acceptance criteria and deliver the predicted business benefits. x000d collaborates with project colleagues and stakeholders involved in the analysis, development and operation of products, systems or services to ensure accuracy and comprehensive test coverage. x000d analyses and reports on test activities, results, issues and risks including the work of others.</t>
+          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. develops acceptance criteria related to functional and nonfunctional requirements, business processes, features, user stories and business rules. designs and specifies test cases and scenarios to test that systems, products and services fulfil the acceptance criteria and deliver the predicted business benefits. collaborates with project colleagues and stakeholders involved in the analysis, development and operation of products, systems or services to ensure accuracy and comprehensive test coverage. analyses and reports on test activities, results, issues and risks including the work of others.</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. plans and manages user acceptance testing activity.x000d specifies the testing environment. manages the creation of test cases and scenarios, ensuring they reflect realistic operational conditions and coverage needs. x000d ensures entry and exit criteria are set and met before user acceptance testing starts or ends. specifies required user resources. ensures users receive appropriate training and support.x000d ensures tests and results are documented, analysed and reported, highlighting issues and risks to stakeholders. provides authoritative advice on acceptance testing planning and execution.</t>
+          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. plans and manages user acceptance testing activity. specifies the testing environment. manages the creation of test cases and scenarios, ensuring they reflect realistic operational conditions and coverage needs. ensures entry and exit criteria are set and met before user acceptance testing starts or ends. specifies required user resources. ensures users receive appropriate training and support. ensures tests and results are documented, analysed and reported, highlighting issues and risks to stakeholders. provides authoritative advice on acceptance testing planning and execution.</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. leads the organisations approach to user acceptance testing.x000d engages senior stakeholders to secure organisational commitment and resources for effective acceptance testing. x000d integrates entry and exit criteria into user acceptance testing planning and execution. provides input on required resources, including skills and availability, for user acceptance testing activities. reports on any significant risks and issues, recommending actions as needed. x000d develops organisational policies, standards and guidelines for acceptance testing. develops acceptance testing capabilities and methods for the organisation.</t>
+          <t>validating systems, products, business processes or services to determine whether the acceptance criteria have been satisfied. leads the organisations approach to user acceptance testing. engages senior stakeholders to secure organisational commitment and resources for effective acceptance testing. integrates entry and exit criteria into user acceptance testing planning and execution. provides input on required resources, including skills and availability, for user acceptance testing activities. reports on any significant risks and issues, recommending actions as needed. develops organisational policies, standards and guidelines for acceptance testing. develops acceptance testing capabilities and methods for the organisation.</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. assists in gathering data and documenting current business processes under routine supervision. x000d participates in process mapping exercises and helps identify areas for potential improvement.x000d assists in creating process documentation.x000d supports the implementation of minor process changes and improvements.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. assists in gathering data and documenting current business processes under routine supervision. participates in process mapping exercises and helps identify areas for potential improvement. assists in creating process documentation. supports the implementation of minor process changes and improvements.</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. applies standard techniques to analyse existing business processes and identifies opportunities for improvement. x000d collaborates with stakeholders to ensure process changes align with business objectives. proposes and implements process improvements that enhance efficiency, effectiveness and quality. x000d develops and maintains process documentation. x000d supports the adoption of new technologies and tools to enable process automation and optimisation.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. applies standard techniques to analyse existing business processes and identifies opportunities for improvement. collaborates with stakeholders to ensure process changes align with business objectives. proposes and implements process improvements that enhance efficiency, effectiveness and quality. develops and maintains process documentation. supports the adoption of new technologies and tools to enable process automation and optimisation.</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. analyses and designs business processes to identify alternative solutions to improve efficiency, effectiveness and exploit new technologies and automation.x000d develops graphical models of business processes to facilitate understanding and decisionmaking.x000d recommends implementation approaches for process improvement initiatives.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. analyses and designs business processes to identify alternative solutions to improve efficiency, effectiveness and exploit new technologies and automation. develops graphical models of business processes to facilitate understanding and decisionmaking. recommends implementation approaches for process improvement initiatives.</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. manages the execution of business process improvements. x000d assesses the feasibility of business process changes and recommends alternative approaches. x000d selects, tailors and implements methods and tools for improving business processes at programme, project or team level. x000d contributes to the definition of organisational policies, standards and guidelines for business process improvement.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. manages the execution of business process improvements. assesses the feasibility of business process changes and recommends alternative approaches. selects, tailors and implements methods and tools for improving business processes at programme, project or team level. contributes to the definition of organisational policies, standards and guidelines for business process improvement.</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. plans and leads strategic, large and complex business process improvement activities aligned with automation, or exploiting existing or new technologies.x000d develops organisational policies, standards and guidelines for business process improvement. x000d leads the introduction of techniques, methodologies and tools to meet business requirements, ensuring consistency across all user groups.x000d leads the development of organisational capabilities for business process improvement and ensures adoption and adherence to policies and standards.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. plans and leads strategic, large and complex business process improvement activities aligned with automation, or exploiting existing or new technologies. develops organisational policies, standards and guidelines for business process improvement. leads the introduction of techniques, methodologies and tools to meet business requirements, ensuring consistency across all user groups. leads the development of organisational capabilities for business process improvement and ensures adoption and adherence to policies and standards.</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>creating new and potentially disruptive approaches to performing business activities. directs the identification, evaluation and adoption of new or existing technologies to improve business processes. x000d aligns business strategies, enterprise transformation and technology strategies. x000d embeds strategic business process improvement into the governance and leadership of the organisation. x000d directs the creation and review of a crossfunctional, enterprisewide approach and culture for embracing business process management.</t>
+          <t>creating new and potentially disruptive approaches to performing business activities. directs the identification, evaluation and adoption of new or existing technologies to improve business processes. aligns business strategies, enterprise transformation and technology strategies. embeds strategic business process improvement into the governance and leadership of the organisation. directs the creation and review of a crossfunctional, enterprisewide approach and culture for embracing business process management.</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. contributes to identifying new areas of capability improvement within the organisation which may be enhancements to skills, technology or processes. x000d develops and maintains a detailed knowledge of capability improvement approaches and techniques and selects appropriate approaches for the organisation. x000d conducts capability improvement assignments, such as maturity or performance assessments, to identify strengths and weaknesses. selects and prioritises improvement opportunities, generates buyin and plans improvement activities justified by measurable organisational benefits. x000d offers support, guidance, advice and suggestions to help continual improvement activities.</t>
+          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. contributes to identifying new areas of capability improvement within the organisation which may be enhancements to skills, technology or processes. develops and maintains a detailed knowledge of capability improvement approaches and techniques and selects appropriate approaches for the organisation. conducts capability improvement assignments, such as maturity or performance assessments, to identify strengths and weaknesses. selects and prioritises improvement opportunities, generates buyin and plans improvement activities justified by measurable organisational benefits. offers support, guidance, advice and suggestions to help continual improvement activities.</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. seeks out, identifies, proposes and initiates capability improvement activities within the organisation. x000d leads substantial improvement programmes. plans and manages the evaluation or assessment of organisational capabilities. selects frameworks, approaches and techniques for use. x000d takes action to exploit opportunities to deliver measurable, beneficial impacts upon operational effectiveness. devises solutions and leads change initiatives, including communication, transition and implementation activities. x000d monitors international, national and sector trends to establish the needed capability.</t>
+          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. seeks out, identifies, proposes and initiates capability improvement activities within the organisation. leads substantial improvement programmes. plans and manages the evaluation or assessment of organisational capabilities. selects frameworks, approaches and techniques for use. takes action to exploit opportunities to deliver measurable, beneficial impacts upon operational effectiveness. devises solutions and leads change initiatives, including communication, transition and implementation activities. monitors international, national and sector trends to establish the needed capability.</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. represents and leads organisational capability improvement at the highest level. x000d determines the need for strategic organisationlevel capability improvement to satisfy the organisations strategic goals and longterm objectives.x000d liaises with the organisations functions to establish requirements and identifies, proposes, initiates and leads significant organisational capability improvement programmes.x000d manages the quality and appropriateness of the work performed and delivers measurable business benefits. adopts andor modifies existing capability improvement approaches as necessary.</t>
+          <t>providing leadership, advice and implementation support to assess organisational capabilities and to identify, prioritise and implement improvements. represents and leads organisational capability improvement at the highest level. determines the need for strategic organisationlevel capability improvement to satisfy the organisations strategic goals and longterm objectives. liaises with the organisations functions to establish requirements and identifies, proposes, initiates and leads significant organisational capability improvement programmes. manages the quality and appropriateness of the work performed and delivers measurable business benefits. adopts andor modifies existing capability improvement approaches as necessary.</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. gathers data regarding job roles and responsibilities from various sources. x000d assists in mapping tasks and competencies using established skillsbased frameworks. contributes to the creation of preliminary job descriptions and performance metrics. x000d works under direction to align job roles with organisational strategies, workplace practices and evolving requirements. x000d provides support in the assessment of job changes and their impact on workflows and employee satisfaction. participates in the process of revising job documentation to reflect updated role definitions and responsibilities.</t>
+          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. gathers data regarding job roles and responsibilities from various sources. assists in mapping tasks and competencies using established skillsbased frameworks. contributes to the creation of preliminary job descriptions and performance metrics. works under direction to align job roles with organisational strategies, workplace practices and evolving requirements. provides support in the assessment of job changes and their impact on workflows and employee satisfaction. participates in the process of revising job documentation to reflect updated role definitions and responsibilities.</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. performs detailed job analyses, breaking down roles using datadriven insights. x000d creates or revises job descriptions with consideration of required skills, competencies and organisational culture. x000d evaluates the impact of job role changes on workflows, employee engagement and overall workplace practices. x000d provides insights into aligning job roles with emerging organisational needs, including technology integration and adaptive strategies. collaborates with stakeholders to ensure job designs are effective, responsive to changing business needs and aligned with skillsbased approaches.</t>
+          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. performs detailed job analyses, breaking down roles using datadriven insights. creates or revises job descriptions with consideration of required skills, competencies and organisational culture. evaluates the impact of job role changes on workflows, employee engagement and overall workplace practices. provides insights into aligning job roles with emerging organisational needs, including technology integration and adaptive strategies. collaborates with stakeholders to ensure job designs are effective, responsive to changing business needs and aligned with skillsbased approaches.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. leads job architecture and design initiatives, ensuring alignment with organisational strategies and evolving workplace practices. x000d develops comprehensive role definitions that encompass necessary skills, competencies and alignment with the organisations culture and goals.x000d assesses and suggests modifications to existing roles to improve effectiveness and address new challenges. x000d provides authoritative advice on the adaptation of job architecture and job design to reflect changes in organisational strategy, technology, workplace practices and skillsbased approaches.</t>
+          <t>planning, analysing and designing job roles and structures to align with organisational requirements, goals and culture. leads job architecture and design initiatives, ensuring alignment with organisational strategies and evolving workplace practices. develops comprehensive role definitions that encompass necessary skills, competencies and alignment with the organisations culture and goals. assesses and suggests modifications to existing roles to improve effectiveness and address new challenges. provides authoritative advice on the adaptation of job architecture and job design to reflect changes in organisational strategy, technology, workplace practices and skillsbased approaches.</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>planning, designing and implementing an integrated organisation structure and culture. assists in designing team structures and workflows under guidance, following standard modelling techniques and tools.x000d helps develop visual representations of organisational models to aid understanding. assists in preparing and updating organisational charts, role descriptions and other documentation.x000d supports evaluation of design options by gathering and analysing data. participates in creating design views to address stakeholder concerns and perspectives.</t>
+          <t>planning, designing and implementing an integrated organisation structure and culture. assists in designing team structures and workflows under guidance, following standard modelling techniques and tools. helps develop visual representations of organisational models to aid understanding. assists in preparing and updating organisational charts, role descriptions and other documentation. supports evaluation of design options by gathering and analysing data. participates in creating design views to address stakeholder concerns and perspectives.</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>planning, designing and implementing an integrated organisation structure and culture. designs team structures and workflows using modelling techniques, following agreed architectures, design standards and methodologies. x000d develops visual representations of organisational models and structures to facilitate understanding and decisionmaking. supports the identification and evaluation of alternative design options and tradeoffs.x000d creates multiple design views to address the concerns of different stakeholders and to present different perspectives. develops representations of team dynamics and workflows to aid stakeholder understanding and approval.x000d reviews and refines designs to ensure they meet specifications.</t>
+          <t>planning, designing and implementing an integrated organisation structure and culture. designs team structures and workflows using modelling techniques, following agreed architectures, design standards and methodologies. develops visual representations of organisational models and structures to facilitate understanding and decisionmaking. supports the identification and evaluation of alternative design options and tradeoffs. creates multiple design views to address the concerns of different stakeholders and to present different perspectives. develops representations of team dynamics and workflows to aid stakeholder understanding and approval. reviews and refines designs to ensure they meet specifications.</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>planning, designing and implementing an integrated organisation structure and culture. leads the design and implementation of organisational structures for significant teams, departments or divisions.x000d conducts impact analyses on major design options and tradeoffs to inform strategic decisionmaking.x000d aligns existing organisational structures, roles, jobs and career paths to new processes and strategies. ensures that the organisational design balances organisational performance and cultural requirements.x000d reviews organisational designs and ensures that appropriate methods, tools and techniques are applied effectively. contributes to development of organisational design policies, processes and standards.</t>
+          <t>planning, designing and implementing an integrated organisation structure and culture. leads the design and implementation of organisational structures for significant teams, departments or divisions. conducts impact analyses on major design options and tradeoffs to inform strategic decisionmaking. aligns existing organisational structures, roles, jobs and career paths to new processes and strategies. ensures that the organisational design balances organisational performance and cultural requirements. reviews organisational designs and ensures that appropriate methods, tools and techniques are applied effectively. contributes to development of organisational design policies, processes and standards.</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>planning, designing and implementing an integrated organisation structure and culture. champions the value of new ways of working to address internal and external opportunities and threats. x000d sets direction and leads in selecting and using organisation design techniques, methodologies and tools. x000d plans and leads organisation design activities, identifies alternatives, assesses feasibility and recommends solutions. identifies major changes affecting the organisation and mobilises resources to implement changes. x000d initiates the definition of new organisation boundaries and creates future organisation design. outlines performance measurement objectives and the highlevel implementation approach.</t>
+          <t>planning, designing and implementing an integrated organisation structure and culture. champions the value of new ways of working to address internal and external opportunities and threats. sets direction and leads in selecting and using organisation design techniques, methodologies and tools. plans and leads organisation design activities, identifies alternatives, assesses feasibility and recommends solutions. identifies major changes affecting the organisation and mobilises resources to implement changes. initiates the definition of new organisation boundaries and creates future organisation design. outlines performance measurement objectives and the highlevel implementation approach.</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>planning, designing and implementing an integrated organisation structure and culture. establishes and communicates the need and rationale for organisational structure and culture change. x000d secures organisational commitment and resources needed for organisational and culture change. x000d leads organisational change by removing obstacles, advocating and lobbying for change at the highest levels. x000d puts in place mechanisms to reinforce and embed organisational and culture change. acts as a role model for desired behaviours and sets consistent standards and expectations.</t>
+          <t>planning, designing and implementing an integrated organisation structure and culture. establishes and communicates the need and rationale for organisational structure and culture change. secures organisational commitment and resources needed for organisational and culture change. leads organisational change by removing obstacles, advocating and lobbying for change at the highest levels. puts in place mechanisms to reinforce and embed organisational and culture change. acts as a role model for desired behaviours and sets consistent standards and expectations.</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. assists with organisational change management tasks under routine supervision.x000d supports the collection and analysis of data related to change readiness and impact.x000d helps document and communicate change management plans and activities.</t>
+          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. assists with organisational change management tasks under routine supervision. supports the collection and analysis of data related to change readiness and impact. helps document and communicate change management plans and activities.</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. follows standard techniques to investigate and analyse the size, nature and impact of changes to operational activities. x000d contributes to change management plans and actions, focusing on the procedural execution of change. x000d supports implementation and engages with stakeholders under direction.</t>
+          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. follows standard techniques to investigate and analyse the size, nature and impact of changes to operational activities. contributes to change management plans and actions, focusing on the procedural execution of change. supports implementation and engages with stakeholders under direction.</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. conducts readiness assessments to assess the size, nature and impact of organisational change. x000d defines tactics to use considering the challenges to be addressed. provides guidance and makes suggestions to support individuals responsible for operational implementation of change management activities.x000d gathers feedback to analyse the impact and effectiveness of the change management activities being deployed. takes corrective action as required.x000d develops and communicates tailored change management plans. establishes and builds relationships with the project sponsors and key stakeholders.</t>
+          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. conducts readiness assessments to assess the size, nature and impact of organisational change. defines tactics to use considering the challenges to be addressed. provides guidance and makes suggestions to support individuals responsible for operational implementation of change management activities. gathers feedback to analyse the impact and effectiveness of the change management activities being deployed. takes corrective action as required. develops and communicates tailored change management plans. establishes and builds relationships with the project sponsors and key stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. develops the change management approach and a change management plan in collaboration with sponsors, users and project teams. x000d creates and implements action plans to ensure readiness for change before going live. acquires change management resources and develops their capabilities to deliver the required changes.x000d gathers feedback to allow timely improvements to the change management plan and approach. assesses risks and takes preventative action. x000d develops and communicates tailored change management plans for senior stakeholder groups. provides guidance to support change sponsors.</t>
+          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. develops the change management approach and a change management plan in collaboration with sponsors, users and project teams. creates and implements action plans to ensure readiness for change before going live. acquires change management resources and develops their capabilities to deliver the required changes. gathers feedback to allow timely improvements to the change management plan and approach. assesses risks and takes preventative action. develops and communicates tailored change management plans for senior stakeholder groups. provides guidance to support change sponsors.</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. defines and communicates the approach for change management for a significant part of the organisation. x000d initiates, plans and leads strategic, large and complex change management initiatives. provides guidance to change leaders, emphasising the technical and procedural aspects of change.x000d establishes feedback processes and leads analyses of change management successes. x000d enables continual improvements to change management methodology, tools and training necessary to enhance the maturity across the organisation.</t>
+          <t>planning, designing and implementing activities to transition the organisation and people to the required future state. defines and communicates the approach for change management for a significant part of the organisation. initiates, plans and leads strategic, large and complex change management initiatives. provides guidance to change leaders, emphasising the technical and procedural aspects of change. establishes feedback processes and leads analyses of change management successes. enables continual improvements to change management methodology, tools and training necessary to enhance the maturity across the organisation.</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. supports teams in adopting new practices, providing ongoing resources and guidance. x000d facilitates a safe environment for exploring challenges related to change. x000d assists with engagement sessions to secure leadership commitment, focusing on the behavioural aspects of change.x000d addresses issues that arise during implementation, ensuring minimal disruption.</t>
+          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. supports teams in adopting new practices, providing ongoing resources and guidance. facilitates a safe environment for exploring challenges related to change. assists with engagement sessions to secure leadership commitment, focusing on the behavioural aspects of change. addresses issues that arise during implementation, ensuring minimal disruption.</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. develops and implements cultural change plans across teams, ensuring alignment with longterm success. x000d coordinates crossfunctional teams to support the adoption of new behaviours. communicates how changes align with business goals and longterm success, focusing on emotional and behavioural impacts. supports leaders and employees in exploring challenges associated with adopting new practices. x000d enables employees to develop the necessary skills and behaviours for sustained change.</t>
+          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. develops and implements cultural change plans across teams, ensuring alignment with longterm success. coordinates crossfunctional teams to support the adoption of new behaviours. communicates how changes align with business goals and longterm success, focusing on emotional and behavioural impacts. supports leaders and employees in exploring challenges associated with adopting new practices. enables employees to develop the necessary skills and behaviours for sustained change.</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. champions new ways of working that align with strategic opportunities. x000d influences and engages with senior executives to gain their support for change initiatives. x000d guides the development of strategies and roadmaps to drive longterm behavioural change. reviews progress, addresses challenges and ensures the sustainability of change initiatives.x000d provides guidance to change leaders, focusing on the human aspects of organisational change.</t>
+          <t>facilitates cultural and behavioural change by enabling individuals and teams to embed new ways of working and adapt to changes. champions new ways of working that align with strategic opportunities. influences and engages with senior executives to gain their support for change initiatives. guides the development of strategies and roadmaps to drive longterm behavioural change. reviews progress, addresses challenges and ensures the sustainability of change initiatives. provides guidance to change leaders, focusing on the human aspects of organisational change.</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. assists with product management tasks under routine supervision. x000d helps create and curate content to support product usage.x000d assists in monitoring results and feedback from product activities.x000d supports problem resolution by collecting and reporting on feedback and usage data.</t>
+          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. assists with product management tasks under routine supervision. helps create and curate content to support product usage. assists in monitoring results and feedback from product activities. supports problem resolution by collecting and reporting on feedback and usage data.</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. creates and curates various content to support the adoption and usage of products or services. x000d monitors results and feedback from product campaigns. x000d applies standard techniques and tools to carry out analysis and performance monitoring activities for specified products. x000d supports problem resolution, resolves issues and acts on feedback for products in use.</t>
+          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. creates and curates various content to support the adoption and usage of products or services. monitors results and feedback from product campaigns. applies standard techniques and tools to carry out analysis and performance monitoring activities for specified products. supports problem resolution, resolves issues and acts on feedback for products in use.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. manages one or more lowervalue products or services. x000d prioritises product requirements and develops product roadmaps. owns the product backlog. manages elements of the product lifecycle to meet customeruser needs and achieve financial or other targets. x000d uses insights from market andor user research, feedback, expert opinion and usage data to understand needs and opportunities. x000d facilitates uptake of products by developing content, supporting and evaluating campaigns and monitoring product performance. rolls out product trials and product launches.</t>
+          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. manages one or more lowervalue products or services. prioritises product requirements and develops product roadmaps. owns the product backlog. manages elements of the product lifecycle to meet customeruser needs and achieve financial or other targets. uses insights from market andor user research, feedback, expert opinion and usage data to understand needs and opportunities. facilitates uptake of products by developing content, supporting and evaluating campaigns and monitoring product performance. rolls out product trials and product launches.</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. manages the full product lifecycle to meet customeruser needs and achieve targets. x000d selects and adapts appropriate product development methods, tools and techniques. x000d uses insights from market andor user research, feedback and usage data to understand needs and opportunities. develops product propositions and determines positioning and variants for different segments. prioritises requirements and develops product roadmaps. x000d coordinates customer testing, product launches and supports communications and training. adapts products based on changing customeruser needs and creates retirement and transition plans.</t>
+          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. manages the full product lifecycle to meet customeruser needs and achieve targets. selects and adapts appropriate product development methods, tools and techniques. uses insights from market andor user research, feedback and usage data to understand needs and opportunities. develops product propositions and determines positioning and variants for different segments. prioritises requirements and develops product roadmaps. coordinates customer testing, product launches and supports communications and training. adapts products based on changing customeruser needs and creates retirement and transition plans.</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. oversees the organisations product and services portfolio and the delivery of customer value andor user satisfaction. x000d creates the product lifecycle management framework for internal and external customers and users. champions the value of product management principles and appropriate product development models. x000d aligns the product management objectives with business objectives and authorises the selection and planning of all product management activities. x000d initiates the creation of new products and services. identifies how developing new products or adapting existing products can create new opportunities.</t>
+          <t>managing and developing products or services throughout their full lifecycle, from inception through growth, maturity, and decline, to retirement. oversees the organisations product and services portfolio and the delivery of customer value andor user satisfaction. creates the product lifecycle management framework for internal and external customers and users. champions the value of product management principles and appropriate product development models. aligns the product management objectives with business objectives and authorises the selection and planning of all product management activities. initiates the creation of new products and services. identifies how developing new products or adapting existing products can create new opportunities.</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>planning, estimating and executing systems development work to time, budget and quality targets. contributes to the planning and management of systems development work.x000d adopts and applies appropriate systems development methods, tools and techniques in line with agreed standards. x000d engages with stakeholders to ensure systems development deliverables meet requirements and quality expectations. manages risks and issues related to systems development activities, escalating as needed. x000d contributes to the continuous improvement of systems development processes and practices.</t>
+          <t>planning, estimating and executing systems development work to time, budget and quality targets. contributes to the planning and management of systems development work. adopts and applies appropriate systems development methods, tools and techniques in line with agreed standards. engages with stakeholders to ensure systems development deliverables meet requirements and quality expectations. manages risks and issues related to systems development activities, escalating as needed. contributes to the continuous improvement of systems development processes and practices.</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>planning, estimating and executing systems development work to time, budget and quality targets. plans and drives systems development work to deliver the organisations objectives and plans. x000d selects, adopts and adapts appropriate systems development methods, tools and techniques. ensures stakeholders are aware of required resources and that they are made available. facilitates availability and optimum utilisation of resources. x000d monitors and reports on the progress of development projects. ensures projects are carried out in accordance with agreed architectures, standards, methods and tools and addresses security and privacy requirements. x000d develops roadmaps to communicate future development activity.</t>
+          <t>planning, estimating and executing systems development work to time, budget and quality targets. plans and drives systems development work to deliver the organisations objectives and plans. selects, adopts and adapts appropriate systems development methods, tools and techniques. ensures stakeholders are aware of required resources and that they are made available. facilitates availability and optimum utilisation of resources. monitors and reports on the progress of development projects. ensures projects are carried out in accordance with agreed architectures, standards, methods and tools and addresses security and privacy requirements. develops roadmaps to communicate future development activity.</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>planning, estimating and executing systems development work to time, budget and quality targets. sets policy and drives adherence to standards for systems development. x000d leads activities to make security and privacy integral to systems development. x000d identifies and manages the resources necessary for all stages of systems development projects. x000d ensures technical, financial and quality targets are met.</t>
+          <t>planning, estimating and executing systems development work to time, budget and quality targets. sets policy and drives adherence to standards for systems development. leads activities to make security and privacy integral to systems development. identifies and manages the resources necessary for all stages of systems development projects. ensures technical, financial and quality targets are met.</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>planning, estimating and executing systems development work to time, budget and quality targets. directs the definition, implementation and continual improvement of the organisations systems development management framework. x000d aligns systems development to business strategies and objectives and with emerging technology and digital opportunities. maintains an overview of the contribution of systems development programmes to organisational success.x000d authorises the structure of systems development functions and platforms. x000d sets strategy for resource management within systems development and authorises the allocation of resources for systems development programmes.</t>
+          <t>planning, estimating and executing systems development work to time, budget and quality targets. directs the definition, implementation and continual improvement of the organisations systems development management framework. aligns systems development to business strategies and objectives and with emerging technology and digital opportunities. maintains an overview of the contribution of systems development programmes to organisational success. authorises the structure of systems development functions and platforms. sets strategy for resource management within systems development and authorises the allocation of resources for systems development programmes.</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. provides support for implementing systems and software lifecycle practices by applying established methods and procedures. x000d supports automation and continuous integration processes under direction. x000d monitors and reports on the effectiveness of lifecycle management activities. x000d contributes to the documentation and maintenance of lifecycle tools and practices.</t>
+          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. provides support for implementing systems and software lifecycle practices by applying established methods and procedures. supports automation and continuous integration processes under direction. monitors and reports on the effectiveness of lifecycle management activities. contributes to the documentation and maintenance of lifecycle tools and practices.</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. elicits requirements for systems and software lifecycle working practices and automation.x000d prepares design options for the working environment of methods, procedures, techniques, tools and people. x000d selects systems and software lifecycle working practices for software components and microservices. x000d deploys automation to achieve wellengineered and secure outcomes.</t>
+          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. elicits requirements for systems and software lifecycle working practices and automation. prepares design options for the working environment of methods, procedures, techniques, tools and people. selects systems and software lifecycle working practices for software components and microservices. deploys automation to achieve wellengineered and secure outcomes.</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. collaborates with those responsible for ongoing systems and software lifecycle management to select, adopt and adapt working practices.x000d supports deployment of the working environment for systems and software lifecycle working practices.x000d provides effective feedback to encourage development of the individuals and teams responsible for systems and software lifecycle working practices. provides guidance and makes suggestions to support continual improvement and learning approach.x000d contributes to identifying new domains within the organisation where systems and software lifecycle working practices can be deployed.</t>
+          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. collaborates with those responsible for ongoing systems and software lifecycle management to select, adopt and adapt working practices. supports deployment of the working environment for systems and software lifecycle working practices. provides effective feedback to encourage development of the individuals and teams responsible for systems and software lifecycle working practices. provides guidance and makes suggestions to support continual improvement and learning approach. contributes to identifying new domains within the organisation where systems and software lifecycle working practices can be deployed.</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. obtains organisational commitment to strategies to deliver systems and software lifecycle working practices to achieve business objectives. x000d works with others to integrate organisational policies, standards and techniques across the full software and systems lifecycle. x000d develops and deploys the working environment supporting systems and software lifecycle practices for strategic, large and complex products and services. x000d leads activities to manage risks associated with systems and software lifecycle working practices. plans and manages the evaluation or assessment of systems and software lifecycle working practices</t>
+          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. obtains organisational commitment to strategies to deliver systems and software lifecycle working practices to achieve business objectives. works with others to integrate organisational policies, standards and techniques across the full software and systems lifecycle. develops and deploys the working environment supporting systems and software lifecycle practices for strategic, large and complex products and services. leads activities to manage risks associated with systems and software lifecycle working practices. plans and manages the evaluation or assessment of systems and software lifecycle working practices</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. represents and leads systems and software lifecycle working practices at the highest level in the organisation.x000d identifies opportunities for innovation in systems and software lifecycle working practices to achieve organisational goals and objectives. x000d leads the essential cultural and environmental changes and communicates the benefits to all stakeholders. x000d oversees the quality of the work performed and delivers measurable business benefits.</t>
+          <t>establishing and deploying an environment for developing, continually improving and securely operating software and systems products and services. represents and leads systems and software lifecycle working practices at the highest level in the organisation. identifies opportunities for innovation in systems and software lifecycle working practices to achieve organisational goals and objectives. leads the essential cultural and environmental changes and communicates the benefits to all stakeholders. oversees the quality of the work performed and delivers measurable business benefits.</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>designing systems to meet specified requirements and agreed systems architectures. assists in the creation and documentation of system design elements under routine supervision. x000d follows established procedures and guidelines. x000d helps create and maintain documentation.</t>
+          <t>designing systems to meet specified requirements and agreed systems architectures. assists in the creation and documentation of system design elements under routine supervision. follows established procedures and guidelines. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>designing systems to meet specified requirements and agreed systems architectures. follows standard approaches and established design patterns to create new designs for simple systems or system components.x000d identifies and resolves minor design issues. x000d identifies alternative design options and seeks guidance when deviating from established design patterns.</t>
+          <t>designing systems to meet specified requirements and agreed systems architectures. follows standard approaches and established design patterns to create new designs for simple systems or system components. identifies and resolves minor design issues. identifies alternative design options and seeks guidance when deviating from established design patterns.</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>designing systems to meet specified requirements and agreed systems architectures. designs system components using appropriate modelling techniques following agreed architectures, design standards, patterns and methodology. x000d identifies and evaluates alternative design options and tradeoffs. creates multiple design views to address the concerns of the different stakeholders and to handle functional and nonfunctional requirements. x000d models, simulates or prototypes the behaviour of proposed system components to enable approval by stakeholders. x000d produces detailed design specifications to form the basis for the construction of systems. reviews, verifies and improves own designs against specifications.</t>
+          <t>designing systems to meet specified requirements and agreed systems architectures. designs system components using appropriate modelling techniques following agreed architectures, design standards, patterns and methodology. identifies and evaluates alternative design options and tradeoffs. creates multiple design views to address the concerns of the different stakeholders and to handle functional and nonfunctional requirements. models, simulates or prototypes the behaviour of proposed system components to enable approval by stakeholders. produces detailed design specifications to form the basis for the construction of systems. reviews, verifies and improves own designs against specifications.</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>designing systems to meet specified requirements and agreed systems architectures. designs large or complex systems and undertakes impact analysis on major design options and tradeoffs. x000d ensures the system design balances functional and nonfunctional requirements. x000d reviews systems designs and ensures appropriate methods, tools and techniques are applied effectively. makes recommendations and assesses and manages associated risks. x000d adopts and adapts system design methods, tools and techniques. contributes to development of system design policies, standards and selection of architecture components.</t>
+          <t>designing systems to meet specified requirements and agreed systems architectures. designs large or complex systems and undertakes impact analysis on major design options and tradeoffs. ensures the system design balances functional and nonfunctional requirements. reviews systems designs and ensures appropriate methods, tools and techniques are applied effectively. makes recommendations and assesses and manages associated risks. adopts and adapts system design methods, tools and techniques. contributes to development of system design policies, standards and selection of architecture components.</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>designing systems to meet specified requirements and agreed systems architectures. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for system design. x000d champions the importance and value of system design principles and the selection of appropriate systems design lifecycle models. x000d leads system design activities for strategic, large and complex systems development programmes. develops effective implementation strategies consistent with specified requirements, architectures and constraints of performance and feasibility. x000d develops system design requiring the introduction of new technologies or new uses for existing technologies.</t>
+          <t>designing systems to meet specified requirements and agreed systems architectures. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for system design. champions the importance and value of system design principles and the selection of appropriate systems design lifecycle models. leads system design activities for strategic, large and complex systems development programmes. develops effective implementation strategies consistent with specified requirements, architectures and constraints of performance and feasibility. develops system design requiring the introduction of new technologies or new uses for existing technologies.</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. creates and documents detailed designs for simple software applications or components. x000d applies agreed modelling techniques, standards, patterns and tools. x000d contributes to the design of components of larger software systems, ensuring alignment with overall design requirements, including security.x000d reviews own work.</t>
+          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. creates and documents detailed designs for simple software applications or components. applies agreed modelling techniques, standards, patterns and tools. contributes to the design of components of larger software systems, ensuring alignment with overall design requirements, including security. reviews own work.</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. undertakes complete design of moderately complex software applications or components.x000d applies agreed standards, guidelines, patterns and tools. assists as part of a team in the design of components of larger software systems. specifies user andor system interfaces. x000d creates multiple design views to address the different stakeholders concerns and to handle functional and nonfunctional requirements, considering all relevant factors, including security. assists in the evaluation of options and tradeoffs. x000d collaborates in reviews of work with others as appropriate.</t>
+          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. undertakes complete design of moderately complex software applications or components. applies agreed standards, guidelines, patterns and tools. assists as part of a team in the design of components of larger software systems. specifies user andor system interfaces. creates multiple design views to address the different stakeholders concerns and to handle functional and nonfunctional requirements, considering all relevant factors, including security. assists in the evaluation of options and tradeoffs. collaborates in reviews of work with others as appropriate.</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. designs and architects complex software applications, components and modules.x000d uses appropriate modelling techniques in line with agreed software design standards, guidelines, patterns and methodologies. produces and communicates multiple design views to address stakeholder concerns and meet both functional and nonfunctional requirements including security.x000d identifies, evaluates and recommends design alternatives and tradeoffs. models, simulates or prototypes proposed software behaviours to secure stakeholder approval and facilitate effective software construction. x000d reviews, verifies and enhances own designs against specifications and leads reviews of others designs.</t>
+          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. designs and architects complex software applications, components and modules. uses appropriate modelling techniques in line with agreed software design standards, guidelines, patterns and methodologies. produces and communicates multiple design views to address stakeholder concerns and meet both functional and nonfunctional requirements including security. identifies, evaluates and recommends design alternatives and tradeoffs. models, simulates or prototypes proposed software behaviours to secure stakeholder approval and facilitate effective software construction. reviews, verifies and enhances own designs against specifications and leads reviews of others designs.</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. specifies, designs and architects large or complex software applications, components and modules. x000d adopts and adapts software design methods, tools and techniques. undertakes impact analysis on major design options, makes recommendations and assesses and manages associated risks. specifies prototypessimulations to enable informed decisionmaking. x000d evaluates software designs to ensure adherence to standards and identifies corrective action. ensures the software design balances functional, quality, security and systems management requirements. x000d contributes to the development of organisational software design and architecture policies and standards.</t>
+          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. specifies, designs and architects large or complex software applications, components and modules. adopts and adapts software design methods, tools and techniques. undertakes impact analysis on major design options, makes recommendations and assesses and manages associated risks. specifies prototypessimulations to enable informed decisionmaking. evaluates software designs to ensure adherence to standards and identifies corrective action. ensures the software design balances functional, quality, security and systems management requirements. contributes to the development of organisational software design and architecture policies and standards.</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. leads the selection and development of software design and architectural methods, tools and techniques. x000d defines and maintains architectural principles, patterns and frameworks to guide software design and development across the organisation.x000d ensures adherence to technical strategies and systems architectures including security.</t>
+          <t>architecting and designing software to meet specified requirements, ensuring adherence to established standards and principles. leads the selection and development of software design and architectural methods, tools and techniques. defines and maintains architectural principles, patterns and frameworks to guide software design and development across the organisation. ensures adherence to technical strategies and systems architectures including security.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. assists with defining configurations for networks and network components under routine supervision. x000d follows established network architectures, standards, and security protocols.x000d assists in documenting network configurations and producing detailed network specifications under guidance, incorporating relevant security aspects.</t>
+          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. assists with defining configurations for networks and network components under routine supervision. follows established network architectures, standards, and security protocols. assists in documenting network configurations and producing detailed network specifications under guidance, incorporating relevant security aspects.</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. specifies the technical configurations and components required for a small network or a network segment in a more complex infrastructure.x000d follows organisational architectures, standards, and security guidelines.</t>
+          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. specifies the technical configurations and components required for a small network or a network segment in a more complex infrastructure. follows organisational architectures, standards, and security guidelines.</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. designs specific network components using agreed architectures, design standards, patterns and methodology.x000d translates logical designs into physical designs that meet specified operational parameters for capacity and performance.x000d reviews and verifies network designs against nonfunctional requirements, including validation and error correction procedures, access, security and audit controls.x000d contributes to the development of recovery routines and contingency procedures. contributes to alternative network architectures, networking topologies and design options.</t>
+          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. designs specific network components using agreed architectures, design standards, patterns and methodology. translates logical designs into physical designs that meet specified operational parameters for capacity and performance. reviews and verifies network designs against nonfunctional requirements, including validation and error correction procedures, access, security and audit controls. contributes to the development of recovery routines and contingency procedures. contributes to alternative network architectures, networking topologies and design options.</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. produces, or approves network providers, network architectures, topologies and configuration databases for own area of responsibility.x000d specifies design parameters for network connectivity, capacity, speed, interfacing, security and access, in line with business requirements.x000d assesses networkrelated risks and specifies recovery routines and contingency procedures.x000d creates multiple design views to address the different stakeholders concerns and to handle both functional and nonfunctional requirements.</t>
+          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. produces, or approves network providers, network architectures, topologies and configuration databases for own area of responsibility. specifies design parameters for network connectivity, capacity, speed, interfacing, security and access, in line with business requirements. assesses networkrelated risks and specifies recovery routines and contingency procedures. creates multiple design views to address the different stakeholders concerns and to handle both functional and nonfunctional requirements.</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. takes responsibility for major aspects of network specification, standards, technologies and overall network design models within the organisation.x000d produces network design policies, principles and criteria covering connectivity, capacity, interfacing, security, resilience, recovery and access.x000d develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for network design.</t>
+          <t>designing communication networks to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. takes responsibility for major aspects of network specification, standards, technologies and overall network design models within the organisation. produces network design policies, principles and criteria covering connectivity, capacity, interfacing, security, resilience, recovery and access. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for network design.</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. assists in developing preliminary infrastructure design specifications under routine supervision. x000d uses established standards and security protocols to contribute to infrastructure design activities. x000d helps draft design documents and diagrams. documents designrelated issues.</t>
+          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. assists in developing preliminary infrastructure design specifications under routine supervision. uses established standards and security protocols to contribute to infrastructure design activities. helps draft design documents and diagrams. documents designrelated issues.</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. performs varied infrastructure design tasks, including complex and nonroutine assignments, using standard methods. x000d develops design specifications and diagrams for infrastructure components, integrating hardware, software, network elements, and cloud services, and addressing security requirements.x000d collaborates with others to align infrastructure design with organisational objectives and resolve design issues. x000d suggests improvements to enhance infrastructure performance and reliability.</t>
+          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. performs varied infrastructure design tasks, including complex and nonroutine assignments, using standard methods. develops design specifications and diagrams for infrastructure components, integrating hardware, software, network elements, and cloud services, and addressing security requirements. collaborates with others to align infrastructure design with organisational objectives and resolve design issues. suggests improvements to enhance infrastructure performance and reliability.</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. leads the design of complex infrastructure systems to deliver comprehensive design solutions. x000d develops detailed architectural frameworks and ensures integration of all infrastructure components, including cloud services.x000d provides guidance on recommended practices and design standards. reviews and validates design specifications and documentation. x000d checks that designs are scalable, reliable and secure, aligning with business and technical requirements.</t>
+          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. leads the design of complex infrastructure systems to deliver comprehensive design solutions. develops detailed architectural frameworks and ensures integration of all infrastructure components, including cloud services. provides guidance on recommended practices and design standards. reviews and validates design specifications and documentation. checks that designs are scalable, reliable and secure, aligning with business and technical requirements.</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. manages the design of infrastructure from analysis to execution and evaluation. x000d accountable for achieving design objectives and ensuring alignment with organisational goals and the effective integration of infrastructure components and systems. provides authoritative guidance on design practices and methodologies.x000d evaluates new technologies and their applicability to the organisations needs. develops and enforces design standards and recommended practices, ensuring consistent and highquality design outcomes.</t>
+          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. manages the design of infrastructure from analysis to execution and evaluation. accountable for achieving design objectives and ensuring alignment with organisational goals and the effective integration of infrastructure components and systems. provides authoritative guidance on design practices and methodologies. evaluates new technologies and their applicability to the organisations needs. develops and enforces design standards and recommended practices, ensuring consistent and highquality design outcomes.</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for infrastructure design.x000d collaborates with senior stakeholders to align design projects with organisational objectives. x000d provides strategic oversight and guidance, ensuring infrastructure designs are forwardlooking, scalable and secure. x000d accountable for the overall success of infrastructure design initiatives.</t>
+          <t>designing technology infrastructure to meet business requirements, ensuring scalability, reliability, security and alignment with strategic objectives. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for infrastructure design. collaborates with senior stakeholders to align design projects with organisational objectives. provides strategic oversight and guidance, ensuring infrastructure designs are forwardlooking, scalable and secure. accountable for the overall success of infrastructure design initiatives.</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. assists in designing simple hardware components or subsystems under guidance.x000d follows established design principles, patterns and methodologies as directed. participates in translating logical designs into physical implementations.x000d tests hardware components or subsystems against provided specifications and documents results. contributes to the documentation of hardware designs using required standards, methods and tools.x000d seeks guidance and support for deviations from standard practices or when facing unfamiliar scenarios.</t>
+          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. assists in designing simple hardware components or subsystems under guidance. follows established design principles, patterns and methodologies as directed. participates in translating logical designs into physical implementations. tests hardware components or subsystems against provided specifications and documents results. contributes to the documentation of hardware designs using required standards, methods and tools. seeks guidance and support for deviations from standard practices or when facing unfamiliar scenarios.</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. follows selected standard approaches and design patterns to design simple hardware components. x000d seeks guidance when deviating from established design patterns. takes account of target environment, performance, security, safety, reliability and sustainability requirements.x000d translates logical designs into physical designs. tests the performance of prototypes and production output against specification.x000d submits hardware designs for approval. documents all work using required standards, methods and tools.</t>
+          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. follows selected standard approaches and design patterns to design simple hardware components. seeks guidance when deviating from established design patterns. takes account of target environment, performance, security, safety, reliability and sustainability requirements. translates logical designs into physical designs. tests the performance of prototypes and production output against specification. submits hardware designs for approval. documents all work using required standards, methods and tools.</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. designs hardware components, taking account of target environment, performance, security, safety, reliability and sustainability requirements. x000d translates logical designs into physical designs and delivers technical prototypes of proposed components for approval and production. x000d designs the tests to measure the performance of prototypes and production output against specification and inform iterative development.</t>
+          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. designs hardware components, taking account of target environment, performance, security, safety, reliability and sustainability requirements. translates logical designs into physical designs and delivers technical prototypes of proposed components for approval and production. designs the tests to measure the performance of prototypes and production output against specification and inform iterative development.</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. specifies and designs complex hardware componentssystems. x000d selects appropriate design standards, methods and tools, consistent with agreed policies and ensures they are applied effectively. x000d undertakes impact analysis on major design options. assesses and manages associated risks. ensures hardware designs balance functional, quality, safety, security, systems management, reliability and sustainability requirements. x000d reviews designs created by others to ensure selection of appropriate technology, efficient use of resources and effective integration of multiple systems and technology. contributes to policy for selection of components.</t>
+          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. specifies and designs complex hardware componentssystems. selects appropriate design standards, methods and tools, consistent with agreed policies and ensures they are applied effectively. undertakes impact analysis on major design options. assesses and manages associated risks. ensures hardware designs balance functional, quality, safety, security, systems management, reliability and sustainability requirements. reviews designs created by others to ensure selection of appropriate technology, efficient use of resources and effective integration of multiple systems and technology. contributes to policy for selection of components.</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. provides overall direction and leadership in the hardware design practice within an organisation. x000d influences industrybased models for the development of new technology and components. x000d develops effective procurement strategies, consistent with business needs. x000d develops, drives adoption and ensures adherence to organisational policies, strategies and standards for hardware design.</t>
+          <t>specifying and designing hardware systems and components to meet defined requirements by following agreed design principles and standards. provides overall direction and leadership in the hardware design practice within an organisation. influences industrybased models for the development of new technology and components. develops effective procurement strategies, consistent with business needs. develops, drives adoption and ensures adherence to organisational policies, strategies and standards for hardware design.</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors simple programsscripts. x000d applies agreed standards, tools and basic security practices to achieve a wellengineered result.x000d reviews own work.</t>
+          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors simple programsscripts. applies agreed standards, tools and basic security practices to achieve a wellengineered result. reviews own work.</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors moderately complex programsscripts. x000d applies agreed standards, tools and security measures to achieve a wellengineered result.x000d monitors and reports on progress. identifies issues related to software development activities. proposes practical solutions to resolve issues.x000d collaborates in reviews of work with others as appropriate.</t>
+          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors moderately complex programsscripts. applies agreed standards, tools and security measures to achieve a wellengineered result. monitors and reports on progress. identifies issues related to software development activities. proposes practical solutions to resolve issues. collaborates in reviews of work with others as appropriate.</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors complex programsscripts and integration software services. x000d contributes to the selection of the software development methods, tools, techniques, and security practices.x000d applies agreed standards, tools, and security measures to achieve wellengineered outcomes.x000d participates in reviews of own work and leads reviews of colleagues work.</t>
+          <t>developing software components to deliver value to stakeholders. designs, codes, verifies, tests, documents, amends and refactors complex programsscripts and integration software services. contributes to the selection of the software development methods, tools, techniques, and security practices. applies agreed standards, tools, and security measures to achieve wellengineered outcomes. participates in reviews of own work and leads reviews of colleagues work.</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>developing software components to deliver value to stakeholders. takes technical responsibility across all stages and iterations of software development. x000d plans and drives software construction activities. adopts and adapts appropriate software development methods, tools and techniques. x000d measures and monitors applications of projectteam standards for software construction, including software security. x000d contributes to the development of organisational policies, standards and guidelines for software development.</t>
+          <t>developing software components to deliver value to stakeholders. takes technical responsibility across all stages and iterations of software development. plans and drives software construction activities. adopts and adapts appropriate software development methods, tools and techniques. measures and monitors applications of projectteam standards for software construction, including software security. contributes to the development of organisational policies, standards and guidelines for software development.</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>developing software components to deliver value to stakeholders. develops organisational policies, standards and guidelines for software construction and refactoring. x000d plans and leads software construction activities for strategic, large and complex development projects. x000d adapts or develops new methods and organisational capabilities and drives adoption of, and adherence to, policies and standards.</t>
+          <t>developing software components to deliver value to stakeholders. develops organisational policies, standards and guidelines for software construction and refactoring. plans and leads software construction activities for strategic, large and complex development projects. adapts or develops new methods and organisational capabilities and drives adoption of, and adherence to, policies and standards.</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. produces builds from system components using appropriate build automation tools and processes.x000d conducts tests as defined in an integration test specification and records the details of any failures.x000d analyses and reports on integration test activities and results. identifies and reports issues and risks.</t>
+          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. produces builds from system components using appropriate build automation tools and processes. conducts tests as defined in an integration test specification and records the details of any failures. analyses and reports on integration test activities and results. identifies and reports issues and risks.</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. defines the modules and components and dependencies needed for an integration build and produces a build definition. accepts completed modules and components, checking that they meet defined criteria.x000d produces builds from system components for loading onto target environments. x000d configures the hardware, software and infrastructure environment as required by the system being integrated. x000d produces integration test specifications, conducts tests and records and reports on outcomes. diagnoses faults and documents the results of tests. produces system integration reports.</t>
+          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. defines the modules and components and dependencies needed for an integration build and produces a build definition. accepts completed modules and components, checking that they meet defined criteria. produces builds from system components for loading onto target environments. configures the hardware, software and infrastructure environment as required by the system being integrated. produces integration test specifications, conducts tests and records and reports on outcomes. diagnoses faults and documents the results of tests. produces system integration reports.</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. provides technical expertise to enable the configuration of system components and equipment for systems testing.x000d collaborates with technical teams to develop and agree system integration plans and report on progress. defines complexnew integration builds. ensures integration test environments are correctly configured.x000d designs, performs and reports results of tests of the integration build. identifies and documents system integration components for recording in the configuration management system.x000d recommends and implements improvements to processes and tools.</t>
+          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. provides technical expertise to enable the configuration of system components and equipment for systems testing. collaborates with technical teams to develop and agree system integration plans and report on progress. defines complexnew integration builds. ensures integration test environments are correctly configured. designs, performs and reports results of tests of the integration build. identifies and documents system integration components for recording in the configuration management system. recommends and implements improvements to processes and tools.</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. plans and drives activities to develop organisational systems integration and build capabilities including automation and continuous integration.x000d identifies, evaluates and manages the adoption of tools, techniques and processes to create a robust integration framework. provides authoritative advice and guidance on any aspect of systems integration.x000d leads integration work in line with the agreed system and service design. assesses risks and takes preventative action. measures and monitors applications of standards.x000d contributes to the development of organisational policies, standards and guidelines for systems integration.</t>
+          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. plans and drives activities to develop organisational systems integration and build capabilities including automation and continuous integration. identifies, evaluates and manages the adoption of tools, techniques and processes to create a robust integration framework. provides authoritative advice and guidance on any aspect of systems integration. leads integration work in line with the agreed system and service design. assesses risks and takes preventative action. measures and monitors applications of standards. contributes to the development of organisational policies, standards and guidelines for systems integration.</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. leads the development of organisational systems integration and build capabilities including automation and continuous integration.x000d develops organisational policies, standards and guidelines for systems integration and build.x000d provides resources to ensure systems integration and build can operate effectively and ensures adoption and adherence to policies and standards.</t>
+          <t>planning, implementing and controlling activities to integrate system elements, subsystems and interfaces to create operational systems, products or services. leads the development of organisational systems integration and build capabilities including automation and continuous integration. develops organisational policies, standards and guidelines for systems integration and build. provides resources to ensure systems integration and build can operate effectively and ensures adoption and adherence to policies and standards.</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. executes given manual functional test scripts under supervision to verify basic software capabilities.x000d configures test environments, uses basic automated tools for functionality verification, records results and reports issues.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. executes given manual functional test scripts under supervision to verify basic software capabilities. configures test environments, uses basic automated tools for functionality verification, records results and reports issues.</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. assists in designing functional test cases and creating test scripts. x000d supports the preparation of test data for functional testing under supervision.x000d configures test environments to reflect realistic use cases.x000d executes and records manual and automated functional tests, analysing results and reporting on findings, issues and risks.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. assists in designing functional test cases and creating test scripts. supports the preparation of test data for functional testing under supervision. configures test environments to reflect realistic use cases. executes and records manual and automated functional tests, analysing results and reporting on findings, issues and risks.</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. designs detailed functional test cases and scripts, covering various scenarios and boundary values.x000d actively participates in requirement and design reviews, refining test plans based on insights gained. x000d undertakes structured exploratory testing to investigate and verify functionality. x000d prepares test data, configures environments and automates repeatable tests. executes tests, logs defects with detailed information and analyses results to assess system functionality.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. designs detailed functional test cases and scripts, covering various scenarios and boundary values. actively participates in requirement and design reviews, refining test plans based on insights gained. undertakes structured exploratory testing to investigate and verify functionality. prepares test data, configures environments and automates repeatable tests. executes tests, logs defects with detailed information and analyses results to assess system functionality.</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. selects appropriate functional testing approaches, considering risk, criticality and complexity. x000d develops, automates and executes comprehensive test plans and cases. x000d configures environments to mirror realworld usage, collaborates with stakeholders to refine requirements and manages scalable automated testing frameworks. x000d identifies and mitigates risks during testing, provides detailed analysis and reports on functional test activities and results, including work done by others.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. selects appropriate functional testing approaches, considering risk, criticality and complexity. develops, automates and executes comprehensive test plans and cases. configures environments to mirror realworld usage, collaborates with stakeholders to refine requirements and manages scalable automated testing frameworks. identifies and mitigates risks during testing, provides detailed analysis and reports on functional test activities and results, including work done by others.</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. leads functional testing efforts across all development stages, ensuring alignment with functional requirements and focusing on riskbased prioritisation.x000d provides authoritative advice on testing methods, tools and frameworks.x000d monitors and improves test coverage, collaborates with teams to address challenges and ensures compliance with standards.x000d leads efforts to improve the efficiency and reliability of functional testing. identifies improvements and contributes to organisational policies, standards and guidelines for functional testing.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. leads functional testing efforts across all development stages, ensuring alignment with functional requirements and focusing on riskbased prioritisation. provides authoritative advice on testing methods, tools and frameworks. monitors and improves test coverage, collaborates with teams to address challenges and ensures compliance with standards. leads efforts to improve the efficiency and reliability of functional testing. identifies improvements and contributes to organisational policies, standards and guidelines for functional testing.</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. develops organisational policies, standards and guidelines for functional testing, ensuring they align with business strategy and incorporate a riskbased approach.x000d plans and leads complex testing initiatives, ensuring alignment with strategic objectives and incorporating a riskbased approach.x000d manages risks and opportunities, coordinates with other testing activities and drives improvements in functional testing capabilities.x000d promotes a culture of quality in functional testing, driving adherence to organisational standards and proactive risk mitigation.</t>
+          <t>assessing specified or unspecified functional requirements and characteristics of products, systems and services through investigation and testing. develops organisational policies, standards and guidelines for functional testing, ensuring they align with business strategy and incorporate a riskbased approach. plans and leads complex testing initiatives, ensuring alignment with strategic objectives and incorporating a riskbased approach. manages risks and opportunities, coordinates with other testing activities and drives improvements in functional testing capabilities. promotes a culture of quality in functional testing, driving adherence to organisational standards and proactive risk mitigation.</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. executes given nonfunctional test scripts under supervision, focusing on system qualities and characteristics such as performance.x000d sets up basic test environments and uses standard tools to execute prescribed tests.x000d records results and reports issues.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. executes given nonfunctional test scripts under supervision, focusing on system qualities and characteristics such as performance. sets up basic test environments and uses standard tools to execute prescribed tests. records results and reports issues.</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. assists in designing nonfunctional test cases and creating test scripts. x000d supports the preparation of test data for nonfunctional testing under supervision. configures test environments. executes both manual and automated nonfunctional testing.x000d implements appropriate test tools based on given nonfunctional requirements or specifications. defines test conditions for given nonfunctional requirements. x000d analyses and reports on test activities, results, issues and risks.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. assists in designing nonfunctional test cases and creating test scripts. supports the preparation of test data for nonfunctional testing under supervision. configures test environments. executes both manual and automated nonfunctional testing. implements appropriate test tools based on given nonfunctional requirements or specifications. defines test conditions for given nonfunctional requirements. analyses and reports on test activities, results, issues and risks.</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. designs nonfunctional test cases and scripts, mapping to preset criteria for system qualities and characteristics.x000d prepares and manages test data to reflect realworld scenarios. configures test environments, collaborates with stakeholders to clarify requirements and automates repeatable tests. x000d participates in requirement reviews to refine comprehensive test plans. undertakes exploratory tests to investigate unusual behaviours. x000d executes tests, troubleshooting issues as they arise. analyses and reports on test activities, providing thorough coverage of nonfunctional attributes.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. designs nonfunctional test cases and scripts, mapping to preset criteria for system qualities and characteristics. prepares and manages test data to reflect realworld scenarios. configures test environments, collaborates with stakeholders to clarify requirements and automates repeatable tests. participates in requirement reviews to refine comprehensive test plans. undertakes exploratory tests to investigate unusual behaviours. executes tests, troubleshooting issues as they arise. analyses and reports on test activities, providing thorough coverage of nonfunctional attributes.</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. selects suitable nonfunctional testing approaches, considering system criticality and complexity. x000d develops, automates and executes test plans for endtoend system attributes. configures and manages complex, test environments, ensuring alignment with production conditions. x000d applies riskbased strategies to prioritise test efforts and collaborates across teams to ensure comprehensive automated test coverage. troubleshoots issues in realtime, ensuring prompt resolution. x000d analyses and reports on test activities, results and risks, including the work of others.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. selects suitable nonfunctional testing approaches, considering system criticality and complexity. develops, automates and executes test plans for endtoend system attributes. configures and manages complex, test environments, ensuring alignment with production conditions. applies riskbased strategies to prioritise test efforts and collaborates across teams to ensure comprehensive automated test coverage. troubleshoots issues in realtime, ensuring prompt resolution. analyses and reports on test activities, results and risks, including the work of others.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. plans and drives nonfunctional testing across all stages, ensuring alignment with requirements and prioritising riskbased strategies. x000d provides expert advice on nonfunctional methods, tools and frameworks. leads the setup and maintenance of advanced test environments. x000d monitors the application of testing standards, ensuring they reflect realworld conditions. troubleshoots and resolves complex issues, working closely with stakeholders.x000d leads efforts to improve the efficiency and reliability of nonfunctional testing. identifies improvements and contributes to organisational policies, standards and guidelines for nonfunctional testing.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. plans and drives nonfunctional testing across all stages, ensuring alignment with requirements and prioritising riskbased strategies. provides expert advice on nonfunctional methods, tools and frameworks. leads the setup and maintenance of advanced test environments. monitors the application of testing standards, ensuring they reflect realworld conditions. troubleshoots and resolves complex issues, working closely with stakeholders. leads efforts to improve the efficiency and reliability of nonfunctional testing. identifies improvements and contributes to organisational policies, standards and guidelines for nonfunctional testing.</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. develops organisational policies, standards and guidelines for process testing, ensuring they align with business strategy and incorporate a riskbased approach.x000d plans and leads strategic, complex testing activities, ensuring they align with overall system quality goals. manages risks and opportunities, coordinating with other types of testing.x000d develops organisational capabilities to address complex quality validation challenges. drives continuous automation and improvements in test environments.x000d promotes a culture of quality in nonfunctional testing, driving adherence to organisational standards and proactive risk mitigation.</t>
+          <t>assessing systems and services to evaluate performance, security, scalability and other nonfunctional qualities against requirements or expected standards. develops organisational policies, standards and guidelines for process testing, ensuring they align with business strategy and incorporate a riskbased approach. plans and leads strategic, complex testing activities, ensuring they align with overall system quality goals. manages risks and opportunities, coordinating with other types of testing. develops organisational capabilities to address complex quality validation challenges. drives continuous automation and improvements in test environments. promotes a culture of quality in nonfunctional testing, driving adherence to organisational standards and proactive risk mitigation.</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. executes given process test scripts under supervision to verify business workflows and user journeys. x000d configures basic test environments to simulate business processes.x000d uses standard testing tools for process validation, records results and reports issues.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. executes given process test scripts under supervision to verify business workflows and user journeys. configures basic test environments to simulate business processes. uses standard testing tools for process validation, records results and reports issues.</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. designs test cases and scripts to validate key business scenarios and workflows.x000d supports the preparation and management of test data under supervision to align with business processes configures test environments to reflect realworld business processes.x000d executes and records manual and automated process tests in line with test plans.x000d analyses and reports on test activities, identifying issues and risks related to business process validation.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. designs test cases and scripts to validate key business scenarios and workflows. supports the preparation and management of test data under supervision to align with business processes configures test environments to reflect realworld business processes. executes and records manual and automated process tests in line with test plans. analyses and reports on test activities, identifying issues and risks related to business process validation.</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. designs process test cases and scripts that cover endtoend business scenarios. x000d actively participates in requirement and design reviews to refine test plans. prepares and manages test data that accurately mirrors business processes. x000d configures test environments, executes tests and addresses issues as they arise. undertakes structured exploratory testing to assess alternative business flows. x000d automates repeatable tests for efficiency. analyses and reports on outcomes, focusing on impacts to business processes.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. designs process test cases and scripts that cover endtoend business scenarios. actively participates in requirement and design reviews to refine test plans. prepares and manages test data that accurately mirrors business processes. configures test environments, executes tests and addresses issues as they arise. undertakes structured exploratory testing to assess alternative business flows. automates repeatable tests for efficiency. analyses and reports on outcomes, focusing on impacts to business processes.</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. selects and applies appropriate testing approaches based on business criticality, risk and process complexity. x000d develops, automates and executes detailed test plans focusing on endtoend process validation. ensures automated test environments accurately simulate real business processes and workflows. x000d collaborates closely with stakeholders to refine business requirements and ensure full coverage. identifies and mitigates risks throughout the testing process and addresses issues.x000d provides detailed analysis and reports on the impact of test results on business operations, including work done by others.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. selects and applies appropriate testing approaches based on business criticality, risk and process complexity. develops, automates and executes detailed test plans focusing on endtoend process validation. ensures automated test environments accurately simulate real business processes and workflows. collaborates closely with stakeholders to refine business requirements and ensure full coverage. identifies and mitigates risks throughout the testing process and addresses issues. provides detailed analysis and reports on the impact of test results on business operations, including work done by others.</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. leads process testing activities across all stages of development, ensuring alignment with business objectives and prioritising key workflows based on risk.x000d ensures test environments are robust and reflective of actual business operations.x000d provides expert advice on process testing, ensuring tests are effective and align with business needs.x000d leads efforts to improve the efficiency and reliability of process testing. identifies gaps and risks and contributes to the development of policies and standards that support comprehensive and riskbased process testing.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. leads process testing activities across all stages of development, ensuring alignment with business objectives and prioritising key workflows based on risk. ensures test environments are robust and reflective of actual business operations. provides expert advice on process testing, ensuring tests are effective and align with business needs. leads efforts to improve the efficiency and reliability of process testing. identifies gaps and risks and contributes to the development of policies and standards that support comprehensive and riskbased process testing.</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. develops organisational policies, standards and guidelines for process testing, ensuring they align with business strategy and incorporate a riskbased approach.x000d plans and leads largescale process testing initiatives, focusing on validating complex and critical processes.x000d leads efforts to optimise and innovate process testing methodologies, integrating them with overall business goals and risk management strategies.x000d promotes a culture of quality in process testing, driving adherence to organisational standards and proactive risk mitigation.</t>
+          <t>assessing documented and undocumented process flows within a product, system or service against business needs through investigation and testing. develops organisational policies, standards and guidelines for process testing, ensuring they align with business strategy and incorporate a riskbased approach. plans and leads largescale process testing initiatives, focusing on validating complex and critical processes. leads efforts to optimise and innovate process testing methodologies, integrating them with overall business goals and risk management strategies. promotes a culture of quality in process testing, driving adherence to organisational standards and proactive risk mitigation.</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>designing and deploying software product configurations into software environments or platforms. assists with software configuration tasks.x000d supports the setup and customisation of software environments and platforms.x000d helps document and report on configuration changes and deployments.x000d reviews own work.</t>
+          <t>designing and deploying software product configurations into software environments or platforms. assists with software configuration tasks. supports the setup and customisation of software environments and platforms. helps document and report on configuration changes and deployments. reviews own work.</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>designing and deploying software product configurations into software environments or platforms. designs, verifies, documents, amends and refactors moderately complex software configurations for deployment. x000d applies agreed standards and tools, to achieve a wellengineered result. x000d collaborates in reviews of work with others as appropriate.</t>
+          <t>designing and deploying software product configurations into software environments or platforms. designs, verifies, documents, amends and refactors moderately complex software configurations for deployment. applies agreed standards and tools, to achieve a wellengineered result. collaborates in reviews of work with others as appropriate.</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>designing and deploying software product configurations into software environments or platforms. designs, verifies, documents, amends and refactors complex software configurations for deployment. x000d contributes to the selection of the software configuration methods, tools and techniques.x000d applies agreed standards and tools, to achieve wellengineered outcomes. x000d participates in reviews of own work and leads reviews of colleagues work.</t>
+          <t>designing and deploying software product configurations into software environments or platforms. designs, verifies, documents, amends and refactors complex software configurations for deployment. contributes to the selection of the software configuration methods, tools and techniques. applies agreed standards and tools, to achieve wellengineered outcomes. participates in reviews of own work and leads reviews of colleagues work.</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>designing and deploying software product configurations into software environments or platforms. takes technical responsibility across all stages and iterations of configuration development and deployment. x000d plans and drives software configuration activities. adopts and adapts appropriate software configuration methods, tools and techniques. x000d measures and monitors the application of standards for configuration design and deployment including software security. x000d contributes to the development of organisational policies, standards and guidelines for software configuration design and deployment.</t>
+          <t>designing and deploying software product configurations into software environments or platforms. takes technical responsibility across all stages and iterations of configuration development and deployment. plans and drives software configuration activities. adopts and adapts appropriate software configuration methods, tools and techniques. measures and monitors the application of standards for configuration design and deployment including software security. contributes to the development of organisational policies, standards and guidelines for software configuration design and deployment.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>designing and deploying software product configurations into software environments or platforms. develops organisational policies, standards and guidelines for software configuration design, deployment and refactoring. x000d plans and leads software configuration and deployment activities for strategic, large and complex deployment projects. x000d develops new methods and organisational capabilities and drives adoption of and adherence to policies and standards.</t>
+          <t>designing and deploying software product configurations into software environments or platforms. develops organisational policies, standards and guidelines for software configuration design, deployment and refactoring. plans and leads software configuration and deployment activities for strategic, large and complex deployment projects. develops new methods and organisational capabilities and drives adoption of and adherence to policies and standards.</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and tests simple realtimeembedded components as part of an overall larger systems design. x000d uses appropriate programming languages to drive simple sensors and actuators. x000d applies specialised tools for realtime program analysis and system debugging.</t>
+          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and tests simple realtimeembedded components as part of an overall larger systems design. uses appropriate programming languages to drive simple sensors and actuators. applies specialised tools for realtime program analysis and system debugging.</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and integrates mediumcomplexity realtimeembedded components as part of an overall larger systems design. x000d follows agreed standards and uses specialised tools for system analysis and optimisation.x000d drives specialist hardware, typically sensors and actuators, and optimises component code for performance. x000d applies a range of approaches to the verification and testing of realtime components.</t>
+          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and integrates mediumcomplexity realtimeembedded components as part of an overall larger systems design. follows agreed standards and uses specialised tools for system analysis and optimisation. drives specialist hardware, typically sensors and actuators, and optimises component code for performance. applies a range of approaches to the verification and testing of realtime components.</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and integrates complex realtimeembedded components and subsystems.x000d designs physical layouts that reflect the connection between system components to test and optimise performance. x000d builds system prototypes and simulations to aid development and enable debugging, testing and troubleshooting of embedded software. x000d applies a range of approaches to the validation, verification, and testing of realtime components and subsystems, using a variety of specialist tools for system analysis and optimisation.</t>
+          <t>designing and developing reliable realtime software typically within embedded systems. designs, builds and integrates complex realtimeembedded components and subsystems. designs physical layouts that reflect the connection between system components to test and optimise performance. builds system prototypes and simulations to aid development and enable debugging, testing and troubleshooting of embedded software. applies a range of approaches to the validation, verification, and testing of realtime components and subsystems, using a variety of specialist tools for system analysis and optimisation.</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>designing and developing reliable realtime software typically within embedded systems. designs and develops realtimeembedded architectures and systems to meet agreed system requirements.x000d plans and manages the development of complex realtimeembedded systems and selects the approaches and techniques to be used. x000d analyses design options and tradeoffs between hardware and software, makes recommendations and assesses and manages associated risks. ensures effective validation, verification and testing is undertaken throughout development.x000d oversees the integration of multiple subsystems into the overall system.</t>
+          <t>designing and developing reliable realtime software typically within embedded systems. designs and develops realtimeembedded architectures and systems to meet agreed system requirements. plans and manages the development of complex realtimeembedded systems and selects the approaches and techniques to be used. analyses design options and tradeoffs between hardware and software, makes recommendations and assesses and manages associated risks. ensures effective validation, verification and testing is undertaken throughout development. oversees the integration of multiple subsystems into the overall system.</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>designing and developing reliable realtime software typically within embedded systems. provides overall direction and leadership in the development of realtimeembedded systems. x000d develops organisational policies, standards and guidelines for realtimeembedded systems architectures and designs. x000d plans and leads strategic, large and complex realtimeembedded system developments. identifies opportunities to exploit new technologies and improve existing technologies and practices. x000d drives adherence to technical strategies, systems architectures and the implementation of riskbased verification, validation and testing. develops effective implementation and procurement strategies.</t>
+          <t>designing and developing reliable realtime software typically within embedded systems. provides overall direction and leadership in the development of realtimeembedded systems. develops organisational policies, standards and guidelines for realtimeembedded systems architectures and designs. plans and leads strategic, large and complex realtimeembedded system developments. identifies opportunities to exploit new technologies and improve existing technologies and practices. drives adherence to technical strategies, systems architectures and the implementation of riskbased verification, validation and testing. develops effective implementation and procurement strategies.</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. assists with safety engineering tasks under routine supervision.x000d supports the documentation of hazard and risk analysis activities.x000d helps collect safety assurance evidence using agreed methods and procedures.</t>
+          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. assists with safety engineering tasks under routine supervision. supports the documentation of hazard and risk analysis activities. helps collect safety assurance evidence using agreed methods and procedures.</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. contributes to hazard and risk analysis during system development and implementation using agreed methods and procedures. x000d documents the results of hazard and risk analysis activities.x000d contributes to the collection of safety assurance evidence using appropriate methods and tools. x000d undertakes all work in accordance with agreed safety, technical and quality standards.</t>
+          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. contributes to hazard and risk analysis during system development and implementation using agreed methods and procedures. documents the results of hazard and risk analysis activities. contributes to the collection of safety assurance evidence using appropriate methods and tools. undertakes all work in accordance with agreed safety, technical and quality standards.</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. contributes to identifying, analysing and documenting hazards and safety risks using agreed methods and procedures.x000d contributes to the specification of safety requirements. x000d analyses and documents safety validation results during system development and implementation.x000d contributes to developing and maintaining project safety assurance plans. gathers safety assurance evidence for safety case preparation.</t>
+          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. contributes to identifying, analysing and documenting hazards and safety risks using agreed methods and procedures. contributes to the specification of safety requirements. analyses and documents safety validation results during system development and implementation. contributes to developing and maintaining project safety assurance plans. gathers safety assurance evidence for safety case preparation.</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. identifies and analyses hazards and contributes to identifying and evaluating risk reduction measures, ensuring these are adequately documented. x000d specifies safetyrelated systems architectures for defined safety levels. x000d develops and maintains project safety assurance plans. monitors implementation and compliance. ensures safety assurance evidence is gathered for safety case preparation.x000d works with system architects, designers and developers to assure safety requirements implementation.</t>
+          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. identifies and analyses hazards and contributes to identifying and evaluating risk reduction measures, ensuring these are adequately documented. specifies safetyrelated systems architectures for defined safety levels. develops and maintains project safety assurance plans. monitors implementation and compliance. ensures safety assurance evidence is gathered for safety case preparation. works with system architects, designers and developers to assure safety requirements implementation.</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. takes full responsibility for hazard analysis and risk evaluation, safetyrelated systems architectural design and safety compliance planning.x000d leads the definition and allocation of safety requirements for the system, according to the systems nature and required safety level. x000d takes responsibility for the safetyrelated aspects of multiple complex or high safety integrity level projects.</t>
+          <t>applying appropriate methods to assure safety during all lifecycle phases of safetyrelated systems developments. takes full responsibility for hazard analysis and risk evaluation, safetyrelated systems architectural design and safety compliance planning. leads the definition and allocation of safety requirements for the system, according to the systems nature and required safety level. takes responsibility for the safetyrelated aspects of multiple complex or high safety integrity level projects.</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. collects safety assurance evidence using appropriate methods and tools. x000d undertakes all work in accordance with agreed safety, technical and quality standards.</t>
+          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. collects safety assurance evidence using appropriate methods and tools. undertakes all work in accordance with agreed safety, technical and quality standards.</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. undertakes safety analyses using agreed techniques to verify or validate that safety requirements are implemented. x000d participates in system safety assessments.x000d creates safety assessment reports and recommends and defines how a systems safety requirements can be satisfied.</t>
+          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. undertakes safety analyses using agreed techniques to verify or validate that safety requirements are implemented. participates in system safety assessments. creates safety assessment reports and recommends and defines how a systems safety requirements can be satisfied.</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. champions and promotes safety practices in the organisation. x000d leads safety assessments according to organisational safety policies and standards.x000d defines and implements organisational policies and standards for system safety assessment.x000d assures compliance with defined standards and policies and oversees overall safety lifecycle assessment activities.</t>
+          <t>assessing safetyrelated software and hardware systems to determine compliance with standards and required levels of safety integrity. champions and promotes safety practices in the organisation. leads safety assessments according to organisational safety policies and standards. defines and implements organisational policies and standards for system safety assessment. assures compliance with defined standards and policies and oversees overall safety lifecycle assessment activities.</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>designing, installing and maintaining radio frequency based devices and software. assists with setting up, tuning and functional checks of radio frequency devices and software. x000d resolves faults down to line replaceable unit level or escalates according to given procedures. x000d carries out user confidence checks and escalates faults according to given procedures. x000d integrates rf devices with software applications using static configurations.</t>
+          <t>designing, installing and maintaining radio frequency based devices and software. assists with setting up, tuning and functional checks of radio frequency devices and software. resolves faults down to line replaceable unit level or escalates according to given procedures. carries out user confidence checks and escalates faults according to given procedures. integrates rf devices with software applications using static configurations.</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>designing, installing and maintaining radio frequency based devices and software. deploys, sets up, tunes and calibrates rf devices and software following maintenance schedules and using appropriate tools and test equipment. x000d incorporates hardwarefirmware modifications. interprets automatic faultperformance indications and resolves faults down to discrete component level or escalates according to given procedures. x000d implements communication protocols between system elements in accordance with defined standards. x000d integrates rf devices with software applications, incorporating dynamic reconfiguration of elements under software control to optimise their operational performance.</t>
+          <t>designing, installing and maintaining radio frequency based devices and software. deploys, sets up, tunes and calibrates rf devices and software following maintenance schedules and using appropriate tools and test equipment. incorporates hardwarefirmware modifications. interprets automatic faultperformance indications and resolves faults down to discrete component level or escalates according to given procedures. implements communication protocols between system elements in accordance with defined standards. integrates rf devices with software applications, incorporating dynamic reconfiguration of elements under software control to optimise their operational performance.</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>designing, installing and maintaining radio frequency based devices and software. investigates and resolves systemwide fault conditions using a wide range of diagnostic tools and techniques. x000d reconfigures equipment to circumvent temporary outages. specifies, selects and integrates rf devices in a system. x000d defines internal communication protocols for transmission over the available frequencies. x000d reconfigures devices and software to optimise performance.</t>
+          <t>designing, installing and maintaining radio frequency based devices and software. investigates and resolves systemwide fault conditions using a wide range of diagnostic tools and techniques. reconfigures equipment to circumvent temporary outages. specifies, selects and integrates rf devices in a system. defines internal communication protocols for transmission over the available frequencies. reconfigures devices and software to optimise performance.</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>designing, installing and maintaining radio frequency based devices and software. monitors system performance, recommends equipment modifications and changes to operating procedures, servicing methods and schedules. x000d develops maintenance schedules and procedures. approves equipment upgrades and modifications. x000d reviews industry and national standards on relevant rf protocols and regulations. x000d measures and evaluates the effectiveness of rf devices and software.</t>
+          <t>designing, installing and maintaining radio frequency based devices and software. monitors system performance, recommends equipment modifications and changes to operating procedures, servicing methods and schedules. develops maintenance schedules and procedures. approves equipment upgrades and modifications. reviews industry and national standards on relevant rf protocols and regulations. measures and evaluates the effectiveness of rf devices and software.</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>designing, installing and maintaining radio frequency based devices and software. provides overall direction and leadership for the use of rf based devices and software. x000d specifies requirements for radio frequency equipment performance and sets maintenance policy. x000d identifies opportunities to exploit new technologies and improve existing technologies and practices.x000d develops effective implementation and procurement strategies.</t>
+          <t>designing, installing and maintaining radio frequency based devices and software. provides overall direction and leadership for the use of rf based devices and software. specifies requirements for radio frequency equipment performance and sets maintenance policy. identifies opportunities to exploit new technologies and improve existing technologies and practices. develops effective implementation and procurement strategies.</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. assists in the creation of basic visual and audio components for animations under routine supervision. x000d follows established procedures and guidelines and contributes to the development of simple animations using standard tools. x000d helps create and maintain documentation.</t>
+          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. assists in the creation of basic visual and audio components for animations under routine supervision. follows established procedures and guidelines and contributes to the development of simple animations using standard tools. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. builds visual and audio components using animation software. x000d uses design tools to evolve rapid prototypes of interactive systems and user interfaces.x000d uses visual design tools and organic modelling techniques to create and animate virtual characters within a game or system design.</t>
+          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. builds visual and audio components using animation software. uses design tools to evolve rapid prototypes of interactive systems and user interfaces. uses visual design tools and organic modelling techniques to create and animate virtual characters within a game or system design.</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. builds visual and audio components and integrates them into the system structure.x000d uses design tools to evolve rapid prototypes and assess the viability of design concepts for interactive systems and user interfaces. x000d uses complex visual design tools and organic modelling techniques to create and animate virtual characters within a game or system design.</t>
+          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. builds visual and audio components and integrates them into the system structure. uses design tools to evolve rapid prototypes and assess the viability of design concepts for interactive systems and user interfaces. uses complex visual design tools and organic modelling techniques to create and animate virtual characters within a game or system design.</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. manages iterations of level design and storytelling, documenting the overall flow and architecture of a game or similar system. x000d develops conceptual structures into design blueprints to create highlevel structures and runtime architectures for websites and virtual environments.x000d oversees the integration of animations with game logic, physics and artificial intelligence systems.</t>
+          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. manages iterations of level design and storytelling, documenting the overall flow and architecture of a game or similar system. develops conceptual structures into design blueprints to create highlevel structures and runtime architectures for websites and virtual environments. oversees the integration of animations with game logic, physics and artificial intelligence systems.</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. provides overall creative direction in the conception and design of animation products such as games and simulations.x000d establishes animation development strategies, pipelines and quality assurance processes. x000d adapts or develops new methods and organisational capabilities and drives adoption of, and adherence to, policies and standards.</t>
+          <t>designing and developing animated and interactive systems such as games, simulations and virtual environments. provides overall creative direction in the conception and design of animation products such as games and simulations. establishes animation development strategies, pipelines and quality assurance processes. adapts or develops new methods and organisational capabilities and drives adoption of, and adherence to, policies and standards.</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. assists in implementing data management activities under close guidance and supervision.x000d helps create and maintain documentation of data management activities. x000d helps identify and report issues and discrepancies.</t>
+          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. assists in implementing data management activities under close guidance and supervision. helps create and maintain documentation of data management activities. helps identify and report issues and discrepancies.</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. implements standard data management practices based on detailed organisational requirements.x000d monitors and maintains data quality through regular reviews and validation checks. x000d communicates the details of data management procedures to others, helping with their understanding and compliance.</t>
+          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. implements standard data management practices based on detailed organisational requirements. monitors and maintains data quality through regular reviews and validation checks. communicates the details of data management procedures to others, helping with their understanding and compliance.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. devises and implements data governance and master data management processes for specific subsets of data. x000d assesses the integrity of data from multiple sources. x000d advises on transformation of data between formats or media. maintains and implements data handling procedures. x000d enables data availability, integrity and searchability through formal data and metadata structures and protection measures.</t>
+          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. devises and implements data governance and master data management processes for specific subsets of data. assesses the integrity of data from multiple sources. advises on transformation of data between formats or media. maintains and implements data handling procedures. enables data availability, integrity and searchability through formal data and metadata structures and protection measures.</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. devises and implements data governance and master data management processes. x000d derives data management structures and metadata to support consistent data retrieval, integration, analysis, pattern recognition and interpretation across the organisation.x000d independently validates external information from multiple sources. plans effective data storage, sharing and publishing practices within the organisation.x000d identifies and addresses issues preventing optimal use of information assets. provides expert advice to maximise data asset value, ensuring data quality and compliance.</t>
+          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. devises and implements data governance and master data management processes. derives data management structures and metadata to support consistent data retrieval, integration, analysis, pattern recognition and interpretation across the organisation. independently validates external information from multiple sources. plans effective data storage, sharing and publishing practices within the organisation. identifies and addresses issues preventing optimal use of information assets. provides expert advice to maximise data asset value, ensuring data quality and compliance.</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. leads the strategic direction for data management and data governance, establishing policies and frameworks that align with business and regulatory requirements. derives an overall strategy of master data management that supports the development and secure operation of data and digital services. x000d creates organisational policies, standards and guidelines for data management, ensuring ethical principles are applied.x000d plans, establishes and manages processes for regular and consistent access to external data sources, ensuring their validation and integration.</t>
+          <t>developing and implementing plans, policies and practices that control, protect and optimise the value and governance of data assets. leads the strategic direction for data management and data governance, establishing policies and frameworks that align with business and regulatory requirements. derives an overall strategy of master data management that supports the development and secure operation of data and digital services. creates organisational policies, standards and guidelines for data management, ensuring ethical principles are applied. plans, establishes and manages processes for regular and consistent access to external data sources, ensuring their validation and integration.</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. establishes, modifies or maintains simple data structures and associated components. x000d uses specific data modelling and design techniques under guidance.</t>
+          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. establishes, modifies or maintains simple data structures and associated components. uses specific data modelling and design techniques under guidance.</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. applies standard data modelling and design techniques based upon a detailed understanding of organisational requirements. x000d establishes, modifies and maintains data structures and associated components. x000d communicates and explain the details of data structures and components to others.</t>
+          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. applies standard data modelling and design techniques based upon a detailed understanding of organisational requirements. establishes, modifies and maintains data structures and associated components. communicates and explain the details of data structures and components to others.</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. investigates enterprise data requirements where there is some complexity and ambiguity. x000d plans data modelling and design activities, selecting appropriate techniques and levels of detail to meet objectives. x000d provides advice and guidance to others using the data structures and associated components.</t>
+          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. investigates enterprise data requirements where there is some complexity and ambiguity. plans data modelling and design activities, selecting appropriate techniques and levels of detail to meet objectives. provides advice and guidance to others using the data structures and associated components.</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. sets standards for data modelling and design tools and techniques, advises on their application and ensures compliance. x000d manages the investigation of enterprise data requirements based on a detailed understanding of information requirements. x000d coordinates the application of analysis, design and modelling techniques to establish, modify or maintain data structures and their associated components. x000d manages the iteration, review and maintenance of data requirements and data models.</t>
+          <t>developing models and diagrams to represent, communicate and manage data requirements and data assets. sets standards for data modelling and design tools and techniques, advises on their application and ensures compliance. manages the investigation of enterprise data requirements based on a detailed understanding of information requirements. coordinates the application of analysis, design and modelling techniques to establish, modify or maintain data structures and their associated components. manages the iteration, review and maintenance of data requirements and data models.</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. assists in creating and documenting detailed database designs under routine supervision. x000d follows established procedures and guidelines. x000d helps create and maintain documentation.</t>
+          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. assists in creating and documenting detailed database designs under routine supervision. follows established procedures and guidelines. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. interprets installation standards to meet project needs and produces database or data warehouse component specifications. x000d develops physical database or data warehouse design elements, within set policies, to meet data requirements.</t>
+          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. interprets installation standards to meet project needs and produces database or data warehouse component specifications. develops physical database or data warehouse design elements, within set policies, to meet data requirements.</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. implements physical database designs to support transactional data requirements for performance and availability. x000d develops and maintains specialist knowledge of database and data warehouse concepts, design principles, architectures, software and facilities. x000d assesses proposed changes to objectdata structures and evaluates alternative options. x000d implements data warehouse designs that support business intelligence and data analytics.</t>
+          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. implements physical database designs to support transactional data requirements for performance and availability. develops and maintains specialist knowledge of database and data warehouse concepts, design principles, architectures, software and facilities. assesses proposed changes to objectdata structures and evaluates alternative options. implements data warehouse designs that support business intelligence and data analytics.</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. provides specialist expertise in the design characteristics of database management systems or data warehouse productsservices. x000d provides expert guidance in the selection, provision and use of database and data warehouse architectures, software and facilities. x000d ensures design policies optimise transactional data systems for performance and availability while meeting the needs of business intelligence and analytics platforms.</t>
+          <t>specifying, designing and maintaining mechanisms for storing and accessing data across various environments and platforms. provides specialist expertise in the design characteristics of database management systems or data warehouse productsservices. provides expert guidance in the selection, provision and use of database and data warehouse architectures, software and facilities. ensures design policies optimise transactional data systems for performance and availability while meeting the needs of business intelligence and analytics platforms.</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. assists in data preparation and analysis activities under direction. x000d processes and validates data to support analytics. x000d generates standard reports and insights using established tools and methods.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. assists in data preparation and analysis activities under direction. processes and validates data to support analytics. generates standard reports and insights using established tools and methods.</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. supports data analytics by gathering and preparing data from multiple sources. x000d applies analytical and statistical methods and software tools to analyse data and develop reports. x000d assists in identifying trends, patterns and insights that inform business decisions. x000d collaborates with team members to refine analysis techniques and maintain data quality.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. supports data analytics by gathering and preparing data from multiple sources. applies analytical and statistical methods and software tools to analyse data and develop reports. assists in identifying trends, patterns and insights that inform business decisions. collaborates with team members to refine analysis techniques and maintain data quality.</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. conducts endtoend data analysis, defining data requirements and ensuring data integrity. x000d applies advanced analytical and statistical techniques to extract meaningful insights and develop predictive models.x000d communicates complex findings to stakeholders in an understandable manner. x000d contributes to the development of data analytics processes and standards. identifies opportunities for improving data analytics practices.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. conducts endtoend data analysis, defining data requirements and ensuring data integrity. applies advanced analytical and statistical techniques to extract meaningful insights and develop predictive models. communicates complex findings to stakeholders in an understandable manner. contributes to the development of data analytics processes and standards. identifies opportunities for improving data analytics practices.</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. manages data analytics activities, establishing frameworks and methodologies aligned with business objectives and data governance policies. x000d leads the implementation of data analytics solutions. translates business needs into analytics requirements and identifies datadriven solutions. x000d guides the selection and application of advanced analytical techniques. x000d communicates insights and recommendations to senior stakeholders, influencing strategic decisions.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. manages data analytics activities, establishing frameworks and methodologies aligned with business objectives and data governance policies. leads the implementation of data analytics solutions. translates business needs into analytics requirements and identifies datadriven solutions. guides the selection and application of advanced analytical techniques. communicates insights and recommendations to senior stakeholders, influencing strategic decisions.</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. develops organisational strategies and roadmaps for data analytics. x000d sets policies, standards and recommended practices for the use of data and data analytical techniques.x000d leads initiatives to build data analytics capabilities and develop a datadriven culture.x000d oversees the delivery of analytics projects and programmes. promotes the ethical use of data and data analytics.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. develops organisational strategies and roadmaps for data analytics. sets policies, standards and recommended practices for the use of data and data analytical techniques. leads initiatives to build data analytics capabilities and develop a datadriven culture. oversees the delivery of analytics projects and programmes. promotes the ethical use of data and data analytics.</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. directs the creation and review of a crossfunctional, enterprisewide approach and culture for generating value from data analytics and data science. x000d drives the identification, evaluation and adoption of data analytics and data science capabilities to transform organisational performance. leads the provision of the organisations data analytics and data science capabilities.x000d ensures the strategic application of data analytics and data science is embedded in the governance and leadership of the organisation. x000d aligns business strategies, enterprise transformation and data analytics and data science strategies.</t>
+          <t>enabling datadriven decision making by extracting, analysing and communicating insights from structured and unstructured data. directs the creation and review of a crossfunctional, enterprisewide approach and culture for generating value from data analytics and data science. drives the identification, evaluation and adoption of data analytics and data science capabilities to transform organisational performance. leads the provision of the organisations data analytics and data science capabilities. ensures the strategic application of data analytics and data science is embedded in the governance and leadership of the organisation. aligns business strategies, enterprise transformation and data analytics and data science strategies.</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. under routine supervision, applies specified data science techniques to data.x000d analyses and reports findings and addresses simple issues, using algorithms included within standard software frameworks and tools.</t>
+          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. under routine supervision, applies specified data science techniques to data. analyses and reports findings and addresses simple issues, using algorithms included within standard software frameworks and tools.</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. applies standard data science techniques to new problems and datasets using specialised programming techniques.x000d identifies and selects appropriate data sources and prepares data to be used by data science models.x000d evaluates the outcomes and performance of data science models. identifies and implements opportunities to train and improve models and the data they use. x000d publishes and reports on model outputs to meet customer needs and conform to agreed standards.</t>
+          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. applies standard data science techniques to new problems and datasets using specialised programming techniques. identifies and selects appropriate data sources and prepares data to be used by data science models. evaluates the outcomes and performance of data science models. identifies and implements opportunities to train and improve models and the data they use. publishes and reports on model outputs to meet customer needs and conform to agreed standards.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. investigates problems and datasets to assess the usefulness of data science solutions. x000d applies diverse data science techniques and specialised programming languages. understands and applies rules and guidelines specific to the industry and business, and anticipates risks and other implications of modelling.x000d selects, acquires and integrates data for analysis. formulates hypotheses and evaluates data science models. advises on the effectiveness of specific techniques based on analysis findings and research. x000d contributes to the development, evaluation, monitoring and deployment of data science solutions.</t>
+          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. investigates problems and datasets to assess the usefulness of data science solutions. applies diverse data science techniques and specialised programming languages. understands and applies rules and guidelines specific to the industry and business, and anticipates risks and other implications of modelling. selects, acquires and integrates data for analysis. formulates hypotheses and evaluates data science models. advises on the effectiveness of specific techniques based on analysis findings and research. contributes to the development, evaluation, monitoring and deployment of data science solutions.</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. plans, coordinates and drives all stages of the development of data science solutions. x000d provides expert advice to evaluate the problems to be solved and the need for data science solutions. identifies and justifies what data sources to use or acquire. x000d specifies and applies appropriate data science techniques and specialised programming languages.x000d critically reviews the benefits and value of data science techniques and tools and recommends improvements. contributes to developing policy, standards and guidelines for developing, evaluating, monitoring and deploying data science solutions.</t>
+          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. plans, coordinates and drives all stages of the development of data science solutions. provides expert advice to evaluate the problems to be solved and the need for data science solutions. identifies and justifies what data sources to use or acquire. specifies and applies appropriate data science techniques and specialised programming languages. critically reviews the benefits and value of data science techniques and tools and recommends improvements. contributes to developing policy, standards and guidelines for developing, evaluating, monitoring and deploying data science solutions.</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. champions and leads the introduction and use of data science to drive innovation and business value. x000d develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for data science.x000d sets direction and leads in the introduction and use of data science techniques, methodologies and tools. leads the development of organisational capabilities for data science. x000d plans and leads strategic, large and complex data science initiatives to generate insights, create value and drive decisionmaking.</t>
+          <t>applying mathematics, statistics, data mining and predictive modelling techniques to gain insights, predict behaviours and generate value from data. champions and leads the introduction and use of data science to drive innovation and business value. develops and drives adoption of and adherence to organisational policies, standards, guidelines and methods for data science. sets direction and leads in the introduction and use of data science techniques, methodologies and tools. leads the development of organisational capabilities for data science. plans and leads strategic, large and complex data science initiatives to generate insights, create value and drive decisionmaking.</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. assists in data preparation, model training and evaluation tasks under routine supervision. x000d uses standard machine learning frameworks and tools to develop basic models for welldefined problems. x000d documents results and contributes to maintaining machine learning solutions.</t>
+          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. assists in data preparation, model training and evaluation tasks under routine supervision. uses standard machine learning frameworks and tools to develop basic models for welldefined problems. documents results and contributes to maintaining machine learning solutions.</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. applies established machine learning techniques and algorithms to solve business problems. x000d selects and prepares data for model training and evaluation. x000d trains, optimises and validates machine learning models using standard tools and frameworks. x000d deploys models into production and monitors their performance. communicates results and limitations to stakeholders.</t>
+          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. applies established machine learning techniques and algorithms to solve business problems. selects and prepares data for model training and evaluation. trains, optimises and validates machine learning models using standard tools and frameworks. deploys models into production and monitors their performance. communicates results and limitations to stakeholders.</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. assesses the suitability of machine learning and designs and develops solutions for a range of business problems.x000d selects and applies appropriate techniques and algorithms based on data characteristics and business requirements. provides guidance to others.x000d engineers features and optimises model performance. implements algorithms and contributes to development, evaluation, monitoring and deployment. applies industryspecific rules and guidelines, anticipating risks and implications.x000d collaborates with crossfunctional teams to integrate machine learning models into production systems. conducts indepth performance analysis and troubleshoots issues.</t>
+          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. assesses the suitability of machine learning and designs and develops solutions for a range of business problems. selects and applies appropriate techniques and algorithms based on data characteristics and business requirements. provides guidance to others. engineers features and optimises model performance. implements algorithms and contributes to development, evaluation, monitoring and deployment. applies industryspecific rules and guidelines, anticipating risks and implications. collaborates with crossfunctional teams to integrate machine learning models into production systems. conducts indepth performance analysis and troubleshoots issues.</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. leads the development and implementation of machine learning solutions for complex, highimpact business problems.x000d architects endtoend machine learning pipelines and systems, incorporating mlops practices. evaluates and selects tools, frameworks and infrastructure for machine learning projects. x000d establishes practices and standards for machine learning development and operations. provides expert advice and guidance on machine learning techniques and applications.x000d collaborates with stakeholders to align machine learning initiatives with organisational goals.</t>
+          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. leads the development and implementation of machine learning solutions for complex, highimpact business problems. architects endtoend machine learning pipelines and systems, incorporating mlops practices. evaluates and selects tools, frameworks and infrastructure for machine learning projects. establishes practices and standards for machine learning development and operations. provides expert advice and guidance on machine learning techniques and applications. collaborates with stakeholders to align machine learning initiatives with organisational goals.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. sets the strategic direction and roadmap for machine learning adoption and innovation within the organisation. x000d establishes governance frameworks and recommended protocols for responsible, ethical and sustainable development and use of machine learning. x000d leads the development of organisational capabilities, policies, standards and guidelines in machine learning. x000d collaborates with senior stakeholders to identify highimpact opportunities for machine learning and drives their implementation. follows research and industry trends and integrates them into organisational practices.</t>
+          <t>developing systems that learn from data and experience, improving performance, accuracy and adaptability in dynamic environments. sets the strategic direction and roadmap for machine learning adoption and innovation within the organisation. establishes governance frameworks and recommended protocols for responsible, ethical and sustainable development and use of machine learning. leads the development of organisational capabilities, policies, standards and guidelines in machine learning. collaborates with senior stakeholders to identify highimpact opportunities for machine learning and drives their implementation. follows research and industry trends and integrates them into organisational practices.</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. assists with the creation of regular business intelligence reports using standard tools. x000d supports data preparation from existing sources.</t>
+          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. assists with the creation of regular business intelligence reports using standard tools. supports data preparation from existing sources.</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. sources and prepares data for analysis and performs standard business intelligence analysis activities. x000d checks the integrity and validity of data sources. creates and delivers standard reports in accordance with stakeholder needs and conforming to agreed standards. x000d investigates the need for new or revised business intelligence analysis. x000d contributes to the recommendation of improvements. engages with stakeholders under direction.</t>
+          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. sources and prepares data for analysis and performs standard business intelligence analysis activities. checks the integrity and validity of data sources. creates and delivers standard reports in accordance with stakeholder needs and conforming to agreed standards. investigates the need for new or revised business intelligence analysis. contributes to the recommendation of improvements. engages with stakeholders under direction.</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. supports business intelligence needs of specific management or governance processes or operational areas. x000d investigates the need for business intelligence reporting and analysis where there is some complexity and ambiguity. x000d selects and applies nonstandard business intelligence tools and techniques to provide insights and aid decisionmaking. selects, acquires and integrates data for analysis and verifies the datas quality and integrity.x000d identifies opportunities to digitise and streamline operational data handling and optimise business intelligence capabilities.</t>
+          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. supports business intelligence needs of specific management or governance processes or operational areas. investigates the need for business intelligence reporting and analysis where there is some complexity and ambiguity. selects and applies nonstandard business intelligence tools and techniques to provide insights and aid decisionmaking. selects, acquires and integrates data for analysis and verifies the datas quality and integrity. identifies opportunities to digitise and streamline operational data handling and optimise business intelligence capabilities.</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. plans and manages business intelligence activities. x000d ensures business intelligence processes, procedures and practices are robust, efficient and fit for purpose, focusing on automation, key controls and data quality. advises on the available standards, procedures, methods, tools and techniques.x000d manages reviews of the benefits and value of business intelligence techniques and tools and recommends improvements. x000d contributes to the development of analytics policies, standards and guidelines.</t>
+          <t>developing, producing and delivering regular and oneoff management information to provide insights and aid decisionmaking. plans and manages business intelligence activities. ensures business intelligence processes, procedures and practices are robust, efficient and fit for purpose, focusing on automation, key controls and data quality. advises on the available standards, procedures, methods, tools and techniques. manages reviews of the benefits and value of business intelligence techniques and tools and recommends improvements. contributes to the development of analytics policies, standards and guidelines.</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. assists in developing and implementing data pipelines and data stores. x000d performs administrative tasks to provide data accessibility, retrievability, security and protection.x000d supports the monitoring of data pipeline operations, identifying issues and escalating as needed. x000d participates in data migration and conversion tasks under routine supervision.</t>
+          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. assists in developing and implementing data pipelines and data stores. performs administrative tasks to provide data accessibility, retrievability, security and protection. supports the monitoring of data pipeline operations, identifying issues and escalating as needed. participates in data migration and conversion tasks under routine supervision.</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. follows standard approaches and established design patterns to create and implement simple data pipelines and data stores to acquire and prepare data. x000d applies data engineering standards and tools to create and maintain data pipelines and perform extract, transform and load etl processes, incorporating security and data integrity practices.x000d contributes to data migration and conversion projects, ensuring data integrity and consistency.x000d conducts routine data quality checks and remediation.</t>
+          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. follows standard approaches and established design patterns to create and implement simple data pipelines and data stores to acquire and prepare data. applies data engineering standards and tools to create and maintain data pipelines and perform extract, transform and load etl processes, incorporating security and data integrity practices. contributes to data migration and conversion projects, ensuring data integrity and consistency. conducts routine data quality checks and remediation.</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. designs, implements and maintains complex data engineering solutions to acquire and prepare data. x000d creates and maintains data pipelines to connect data across data stores, applications and organisations. builds in compliance with data governance and security standards.x000d supports the development of continuous integration and deployment practices. monitors and optimises pipeline performance and scalability. x000d conducts complex data quality checking and remediation. leads data migration and data conversion activities.</t>
+          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. designs, implements and maintains complex data engineering solutions to acquire and prepare data. creates and maintains data pipelines to connect data across data stores, applications and organisations. builds in compliance with data governance and security standards. supports the development of continuous integration and deployment practices. monitors and optimises pipeline performance and scalability. conducts complex data quality checking and remediation. leads data migration and data conversion activities.</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. plans and drives the development of data engineering solutions, balancing functional and nonfunctional requirements. x000d monitors application of data standards, architectures and security, ensuring compliance and scalability.x000d develops and promotes continuous integration, deployment and monitoring practices.x000d contributes to organisational policies, standards and guidelines for data engineering.</t>
+          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. plans and drives the development of data engineering solutions, balancing functional and nonfunctional requirements. monitors application of data standards, architectures and security, ensuring compliance and scalability. develops and promotes continuous integration, deployment and monitoring practices. contributes to organisational policies, standards and guidelines for data engineering.</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. leads the selection and development of data engineering methods, tools and techniques. x000d develops organisational policies, standards and guidelines for the development and secure operation of data services and products. x000d ensures adherence to technical strategies and architectures. x000d plans and leads data engineering for strategic, highimpact, large and complex programmes ensuring alignment with organisational objectives and industry practices.</t>
+          <t>designing, building, operationalising, securing and monitoring data pipelines, stores and realtime processing systems for scalable and reliable data management. leads the selection and development of data engineering methods, tools and techniques. develops organisational policies, standards and guidelines for the development and secure operation of data services and products. ensures adherence to technical strategies and architectures. plans and leads data engineering for strategic, highimpact, large and complex programmes ensuring alignment with organisational objectives and industry practices.</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. creates standard data visuals using established products, tools and techniques, under routine supervision.x000d assists in updating and refining existing data visualisations to maintain effective representation of concepts, ideas and facts.</t>
+          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. creates standard data visuals using established products, tools and techniques, under routine supervision. assists in updating and refining existing data visualisations to maintain effective representation of concepts, ideas and facts.</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. uses visualisation products, as guided, to design and create data visuals. x000d selects appropriate visualisation techniques from the options available. x000d engages with the target user to prototype and refine specified visualisations.x000d assists in developing narratives around data sets to support understanding and decisionmaking.</t>
+          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. uses visualisation products, as guided, to design and create data visuals. selects appropriate visualisation techniques from the options available. engages with the target user to prototype and refine specified visualisations. assists in developing narratives around data sets to support understanding and decisionmaking.</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. applies a variety of visualisation techniques and designs the content and appearance of data visuals. x000d operationalises and automates activities for efficient and timely production of data visuals. x000d selects appropriate visualisation approaches from a range of applicable options. develops narratives around data sets to guide decisionmaking processes and enhance understanding of key insights.x000d contributes to exploration and experimentation in data visualisation.</t>
+          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. applies a variety of visualisation techniques and designs the content and appearance of data visuals. operationalises and automates activities for efficient and timely production of data visuals. selects appropriate visualisation approaches from a range of applicable options. develops narratives around data sets to guide decisionmaking processes and enhance understanding of key insights. contributes to exploration and experimentation in data visualisation.</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. leads exploration of new approaches for data visualisation. establishes the purpose and parameters of the data visualisation. x000d oversees the use of data visualisation tools and techniques. communicates results using appropriate methods for the target audience.x000d advises on the use of data visualisation approaches for different purposes and contexts to satisfy requirements. develops plans to meet user needs.x000d collaborates with stakeholders to identify key insights and create compelling narratives that effectively communicate the story behind the data to drive decisionmaking processes.</t>
+          <t>facilitating understanding of data by displaying concepts, ideas and facts using graphical representations. leads exploration of new approaches for data visualisation. establishes the purpose and parameters of the data visualisation. oversees the use of data visualisation tools and techniques. communicates results using appropriate methods for the target audience. advises on the use of data visualisation approaches for different purposes and contexts to satisfy requirements. develops plans to meet user needs. collaborates with stakeholders to identify key insights and create compelling narratives that effectively communicate the story behind the data to drive decisionmaking processes.</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>identifying users behaviours, needs and motivations using observational research methods. assists with user research tasks under routine supervision.x000d supports the collection and documentation of user research.x000d helps organise and share the outcomes of user research activities.x000d participates in basic usercentred design activities as directed.</t>
+          <t>identifying users behaviours, needs and motivations using observational research methods. assists with user research tasks under routine supervision. supports the collection and documentation of user research. helps organise and share the outcomes of user research activities. participates in basic usercentred design activities as directed.</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>identifying users behaviours, needs and motivations using observational research methods. applies standard methods to support user research initiatives.x000d engages effectively with users and customer representatives to generate highquality research. x000d documents and shares the outcomes of user research.x000d contributes to research design and analysis tasks under guidance.</t>
+          <t>identifying users behaviours, needs and motivations using observational research methods. applies standard methods to support user research initiatives. engages effectively with users and customer representatives to generate highquality research. documents and shares the outcomes of user research. contributes to research design and analysis tasks under guidance.</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>identifying users behaviours, needs and motivations using observational research methods. conducts generative research for the development of systems, products, services or devices. x000d plans own user research activities. facilitates input from users and stakeholders. x000d identifies appropriate user research methods for specific questions and contexts. x000d collects and analyses user research data. supports synthesis of research and the creation of insights, reports and presentations.</t>
+          <t>identifying users behaviours, needs and motivations using observational research methods. conducts generative research for the development of systems, products, services or devices. plans own user research activities. facilitates input from users and stakeholders. identifies appropriate user research methods for specific questions and contexts. collects and analyses user research data. supports synthesis of research and the creation of insights, reports and presentations.</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>identifying users behaviours, needs and motivations using observational research methods. plans and drives user research activities providing expert advice and guidance to support the adoption of agreed approaches. x000d selects and implements appropriate methods for engaging users in generative research activities.x000d leads the collection and analysis of user research data. synthesises research, develops insights and presents conclusions to inform decisionmaking and drive actions. x000d leads complex user research initiatives and identifies emerging user needs and trends. contributes to the development of organisational methods and standards for user research.</t>
+          <t>identifying users behaviours, needs and motivations using observational research methods. plans and drives user research activities providing expert advice and guidance to support the adoption of agreed approaches. selects and implements appropriate methods for engaging users in generative research activities. leads the collection and analysis of user research data. synthesises research, develops insights and presents conclusions to inform decisionmaking and drive actions. leads complex user research initiatives and identifies emerging user needs and trends. contributes to the development of organisational methods and standards for user research.</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>identifying users behaviours, needs and motivations using observational research methods. sets the overall vision and direction for user research activities.x000d champions usercentred design and secures organisational commitment to the significant involvement of users in research. x000d develops organisational policies, standards and guidelines for user research. x000d develops or sources organisational resources and capabilities to facilitate the adoption and exploitation of user research. collaborates with internal and external partners to facilitate effective user research.</t>
+          <t>identifying users behaviours, needs and motivations using observational research methods. sets the overall vision and direction for user research activities. champions usercentred design and secures organisational commitment to the significant involvement of users in research. develops organisational policies, standards and guidelines for user research. develops or sources organisational resources and capabilities to facilitate the adoption and exploitation of user research. collaborates with internal and external partners to facilitate effective user research.</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. assists in the creation of customer journey maps and identifies key touchpoints for improvement.x000d follows established procedures to document customer feedback and support the implementation of minor improvements.</t>
+          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. assists in the creation of customer journey maps and identifies key touchpoints for improvement. follows established procedures to document customer feedback and support the implementation of minor improvements.</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. analyses research to gather detailed insights into customer needs and preferences. x000d uses appropriate tools and methods for data collection. participates in the design and optimisation of customer journeys. x000d collaborates with team members to implement customer experience improvements. x000d documents findings and supports the analysis process.</t>
+          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. analyses research to gather detailed insights into customer needs and preferences. uses appropriate tools and methods for data collection. participates in the design and optimisation of customer journeys. collaborates with team members to implement customer experience improvements. documents findings and supports the analysis process.</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. uses customer research findings to gain a comprehensive understanding of customer needs and expectations.x000d enables the creation of visual representations of customer journeys to enhance crossfunctional collaboration. designs and refines customer journeys, working with crossfunctional teams to enhance touchpoints and interactions. x000d develops and implements designs to improve customer experience. recommends and applies appropriate technologies and segmentation insights to enhance customer experiences.x000d monitors metrics and feedback to assess effectiveness and drive continuous improvement.</t>
+          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. uses customer research findings to gain a comprehensive understanding of customer needs and expectations. enables the creation of visual representations of customer journeys to enhance crossfunctional collaboration. designs and refines customer journeys, working with crossfunctional teams to enhance touchpoints and interactions. develops and implements designs to improve customer experience. recommends and applies appropriate technologies and segmentation insights to enhance customer experiences. monitors metrics and feedback to assess effectiveness and drive continuous improvement.</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. plans and oversees customer experience initiatives. x000d ensures alignment with business goals and customer expectations.x000d establishes frameworks for monitoring and measuring customer experience. uses datadriven insights to guide improvements.x000d ensures customer experience designs leverage customer insights and emerging technologies for personalised experiences. works with senior stakeholders to develop and implement customer experience strategies. drives collaboration across teams to ensure a consistent experience.</t>
+          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. plans and oversees customer experience initiatives. ensures alignment with business goals and customer expectations. establishes frameworks for monitoring and measuring customer experience. uses datadriven insights to guide improvements. ensures customer experience designs leverage customer insights and emerging technologies for personalised experiences. works with senior stakeholders to develop and implement customer experience strategies. drives collaboration across teams to ensure a consistent experience.</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. champions customer experience at an organisational level. x000d leads strategic initiatives to enhance customer experience, including the evaluation and adoption of innovative technologies and approaches. aligns efforts with business objectives and customer needs.x000d monitors industry trends and innovations in customer experience. x000d develops policies and standards to guide customer experience practices. ensures adoption of good practices and continuous improvement within the organisation.</t>
+          <t>ensuring the delivery of highquality interactions and experiences that meet customer expectations across all touchpoints and channels. champions customer experience at an organisational level. leads strategic initiatives to enhance customer experience, including the evaluation and adoption of innovative technologies and approaches. aligns efforts with business objectives and customer needs. monitors industry trends and innovations in customer experience. develops policies and standards to guide customer experience practices. ensures adoption of good practices and continuous improvement within the organisation.</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>driving accessibility and inclusion in services and products. assists with basic accessibility testing and gathering information for accessibility reviews. x000d supports team members in executing predefined accessibility tests. x000d documents test results and contributes to accessibility audit reports.</t>
+          <t>driving accessibility and inclusion in services and products. assists with basic accessibility testing and gathering information for accessibility reviews. supports team members in executing predefined accessibility tests. documents test results and contributes to accessibility audit reports.</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>driving accessibility and inclusion in services and products. analyses accessibility requirements and technical information. x000d designs and executes accessibility tests under direction. reports findings in a structured way and makes initial recommendations for compliance. x000d supports accessibility reviews and audits.x000d escalates complex issues to senior colleagues.</t>
+          <t>driving accessibility and inclusion in services and products. analyses accessibility requirements and technical information. designs and executes accessibility tests under direction. reports findings in a structured way and makes initial recommendations for compliance. supports accessibility reviews and audits. escalates complex issues to senior colleagues.</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>driving accessibility and inclusion in services and products. engages with stakeholders to explain accessibility factors. influences designs to improve accessibility. x000d provides detailed accessibility analysis to inform decisions throughout the product or service lifecycle.x000d plans and manages accessibility testing to meet agreed standards. x000d evaluates compliance with accessibility regulations. assesses risks based on test outcomes.</t>
+          <t>driving accessibility and inclusion in services and products. engages with stakeholders to explain accessibility factors. influences designs to improve accessibility. provides detailed accessibility analysis to inform decisions throughout the product or service lifecycle. plans and manages accessibility testing to meet agreed standards. evaluates compliance with accessibility regulations. assesses risks based on test outcomes.</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>driving accessibility and inclusion in services and products. leads accessibility governance and assurance activities. x000d interprets complex systems to identify opportunities for improved accessibility. provides expert advice to drive accessibility compliance across products, services and projects. x000d defines organisational accessibility testing approaches, aligned with regulations and standards. x000d promotes awareness of accessibility and inclusion principles.</t>
+          <t>driving accessibility and inclusion in services and products. leads accessibility governance and assurance activities. interprets complex systems to identify opportunities for improved accessibility. provides expert advice to drive accessibility compliance across products, services and projects. defines organisational accessibility testing approaches, aligned with regulations and standards. promotes awareness of accessibility and inclusion principles.</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>driving accessibility and inclusion in services and products. sets the organisations strategic direction for accessibility and inclusion in products and services. x000d defines and oversees governance processes to ensure compliance. leads the development of accessibility policies, standards and guidelines. x000d engages with industry bodies and experts to develop and implement good working practices.x000d drives a culture of proactive accessibility consideration in design and development. ensures adequate resources and skills for accessibility assurance.</t>
+          <t>driving accessibility and inclusion in services and products. sets the organisations strategic direction for accessibility and inclusion in products and services. defines and oversees governance processes to ensure compliance. leads the development of accessibility policies, standards and guidelines. engages with industry bodies and experts to develop and implement good working practices. drives a culture of proactive accessibility consideration in design and development. ensures adequate resources and skills for accessibility assurance.</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. assists with user experience analysis tasks under routine supervision.x000d supports the collection and documentation of user requirements.x000d helps organise and structure user experience data for analysis.</t>
+          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. assists with user experience analysis tasks under routine supervision. supports the collection and documentation of user requirements. helps organise and structure user experience data for analysis.</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. applies standard techniques and tools for developing user stories and eliciting user experience requirements. x000d organises and structures user experience analysis. x000d works with stakeholders to prioritise requirements and resolve conflicts.</t>
+          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. applies standard techniques and tools for developing user stories and eliciting user experience requirements. organises and structures user experience analysis. works with stakeholders to prioritise requirements and resolve conflicts.</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. selects appropriate techniques and tools to develop user stories and elicit user experience requirements in complex situations. x000d identifies and describes the design goals for systems, products, services and devices. x000d identifies the roles of affected stakeholder groups. resolves potential conflicts between differing user requirements. x000d specifies measurable criteria for the required usability and accessibility of systems, products, services and devices.</t>
+          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. selects appropriate techniques and tools to develop user stories and elicit user experience requirements in complex situations. identifies and describes the design goals for systems, products, services and devices. identifies the roles of affected stakeholder groups. resolves potential conflicts between differing user requirements. specifies measurable criteria for the required usability and accessibility of systems, products, services and devices.</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. determines the approaches to be used for user experience analysis. x000d plans and manages user experience and accessibility analysis activities. x000d provides expert advice and guidance to support the adoption and adaptation of agreed approaches. x000d develops user experience tools, techniques and standards as part of the organisations framework for usercentred design</t>
+          <t>understanding the context of use for systems, products and services and specifying user experience requirements and design goals. determines the approaches to be used for user experience analysis. plans and manages user experience and accessibility analysis activities. provides expert advice and guidance to support the adoption and adaptation of agreed approaches. develops user experience tools, techniques and standards as part of the organisations framework for usercentred design</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. assists in creating user experience elements under routine supervision. x000d follows established procedures and guidelines. x000d helps create and maintain documentation.</t>
+          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. assists in creating user experience elements under routine supervision. follows established procedures and guidelines. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. applies standard techniques and tools for designing user interactions with and experiences of selected system, product or service components. x000d reviews design goals and agreed security, usability and accessibility requirements. creates design artefacts to communicate ideas. x000d contributes to overall user experience design as part of a team.x000d assists in evaluating design options and tradeoffs. considers and applies visual design and branding guidelines consistently when appropriate.</t>
+          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. applies standard techniques and tools for designing user interactions with and experiences of selected system, product or service components. reviews design goals and agreed security, usability and accessibility requirements. creates design artefacts to communicate ideas. contributes to overall user experience design as part of a team. assists in evaluating design options and tradeoffs. considers and applies visual design and branding guidelines consistently when appropriate.</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. selects appropriate tools, methods and design patterns to design user interactions with and experiences of a product, system or service.x000d translates concepts into outputs and prototypes for user feedback and evaluation.x000d evaluates alternative design options and recommends designs taking into account performance, security, usability and accessibility requirements. x000d considers and integrates appropriate visual design and branding elements in user experience designs.</t>
+          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. selects appropriate tools, methods and design patterns to design user interactions with and experiences of a product, system or service. translates concepts into outputs and prototypes for user feedback and evaluation. evaluates alternative design options and recommends designs taking into account performance, security, usability and accessibility requirements. considers and integrates appropriate visual design and branding elements in user experience designs.</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. plans and drives user experience design activities.x000d provides expert advice and guidance to support the adoption of agreed approaches. determines the approaches to be used to design user experiences. x000d uses iterative approaches to incorporate user feedback or evaluation rapidly into designs. x000d ensures appropriate consideration and integration of visual design and branding elements into user experience design.</t>
+          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. plans and drives user experience design activities. provides expert advice and guidance to support the adoption of agreed approaches. determines the approaches to be used to design user experiences. uses iterative approaches to incorporate user feedback or evaluation rapidly into designs. ensures appropriate consideration and integration of visual design and branding elements into user experience design.</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. obtains organisational commitment to strategies to deliver required user experience, usability, accessibility and security. x000d defines organisational policies, standards and techniques for user experience design. x000d plans and leads user experience design activities for strategic, large or complex programmes.x000d promotes the value of usercentred design across the organisation.</t>
+          <t>producing design concepts and prototypes for user interactions and experiences of a product, system or service. obtains organisational commitment to strategies to deliver required user experience, usability, accessibility and security. defines organisational policies, standards and techniques for user experience design. plans and leads user experience design activities for strategic, large or complex programmes. promotes the value of usercentred design across the organisation.</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>validating systems, products or services against user experience goals, metrics and targets. assists in preparing and operating the environment, facilities and tools needed to evaluate systems, products, services or devices. x000d assists in the collection of feedback on prototypes and designs from users and others.</t>
+          <t>validating systems, products or services against user experience goals, metrics and targets. assists in preparing and operating the environment, facilities and tools needed to evaluate systems, products, services or devices. assists in the collection of feedback on prototypes and designs from users and others.</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>validating systems, products or services against user experience goals, metrics and targets. evaluates design options and prototypes to obtain user feedback on requirements of developing systems, products, services or devices.x000d tests the usability and accessibility of components and alternative designs. administers a range of evaluations, recording data and feedback. analyses evaluation data and recommends actions. identifies areas for future user research.x000d checks systems, products, services or devices for adherence to applicable standards, guidelines, style guides and legislation. x000d evaluates the usability of existing or competitor systems to provide benchmark values and as input to design.</t>
+          <t>validating systems, products or services against user experience goals, metrics and targets. evaluates design options and prototypes to obtain user feedback on requirements of developing systems, products, services or devices. tests the usability and accessibility of components and alternative designs. administers a range of evaluations, recording data and feedback. analyses evaluation data and recommends actions. identifies areas for future user research. checks systems, products, services or devices for adherence to applicable standards, guidelines, style guides and legislation. evaluates the usability of existing or competitor systems to provide benchmark values and as input to design.</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>validating systems, products or services against user experience goals, metrics and targets. selects appropriate tools and techniques to evaluate user experiences of systems, products, services or devices.x000d validates that security, usability and accessibility requirements have been met. x000d checks operational systems, products, services or devices for changes in usability and accessibility needs. x000d interprets and presents results of evaluations, prioritises issues and reports on remedial actions. collates input for future user research.</t>
+          <t>validating systems, products or services against user experience goals, metrics and targets. selects appropriate tools and techniques to evaluate user experiences of systems, products, services or devices. validates that security, usability and accessibility requirements have been met. checks operational systems, products, services or devices for changes in usability and accessibility needs. interprets and presents results of evaluations, prioritises issues and reports on remedial actions. collates input for future user research.</t>
         </is>
       </c>
     </row>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>validating systems, products or services against user experience goals, metrics and targets. manages user experience evaluation of systems, products, services or devices.x000d assures that the security, usability and accessibility requirements are met and required practices have been followed.x000d advises on what to evaluate, type of evaluation to use and the extent of user involvement required. works iteratively with design teams to ensure feedback from the evaluation is understood and acted upon. x000d advises on the achievement of required usability and accessibility levels of specific designs or prototypes. prioritises input for future user research.</t>
+          <t>validating systems, products or services against user experience goals, metrics and targets. manages user experience evaluation of systems, products, services or devices. assures that the security, usability and accessibility requirements are met and required practices have been followed. advises on what to evaluate, type of evaluation to use and the extent of user involvement required. works iteratively with design teams to ensure feedback from the evaluation is understood and acted upon. advises on the achievement of required usability and accessibility levels of specific designs or prototypes. prioritises input for future user research.</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>validating systems, products or services against user experience goals, metrics and targets. champions high standards in user interaction with the organisations systems, products and services including involvement of users in evaluation activities. x000d specifies standards and methods for security, usability and accessibility and ensure this is addressed in future designs. x000d develops or sources resources and capabilities to conduct effective user experience evaluation, including specialist usercentred facilities and communities of users. leads the provision of input and resources for future user research.x000d collaborates with internal and external partners to facilitate an effective evaluation of systems, products and services.</t>
+          <t>validating systems, products or services against user experience goals, metrics and targets. champions high standards in user interaction with the organisations systems, products and services including involvement of users in evaluation activities. specifies standards and methods for security, usability and accessibility and ensure this is addressed in future designs. develops or sources resources and capabilities to conduct effective user experience evaluation, including specialist usercentred facilities and communities of users. leads the provision of input and resources for future user research. collaborates with internal and external partners to facilitate an effective evaluation of systems, products and services.</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. contributes, under instruction, to the generation of content and the configuration of content items and files. x000d executes preplanned testing activities under supervision and records findings.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. contributes, under instruction, to the generation of content and the configuration of content items and files. executes preplanned testing activities under supervision and records findings.</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. works with colleagues and stakeholders to understand audience needs and to assimilate source material. x000d creates draft content to meet the requirements of the audience as clearly, simply and quickly as possible. x000d applies guidelines and standards to moderate content from others, escalating where appropriate.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. works with colleagues and stakeholders to understand audience needs and to assimilate source material. creates draft content to meet the requirements of the audience as clearly, simply and quickly as possible. applies guidelines and standards to moderate content from others, escalating where appropriate.</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. produces information artefacts that are accurate, current, relevant and easily understood by the intended audience. x000d clarifies detailed content requirements with clients and representatives of the intended audience. x000d designs, creates, controls and evaluates moderately complex subject matter. x000d makes informed decisions about the best way to present information to an audience. applies moderation and editing processes to content supplied by others.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. produces information artefacts that are accurate, current, relevant and easily understood by the intended audience. clarifies detailed content requirements with clients and representatives of the intended audience. designs, creates, controls and evaluates moderately complex subject matter. makes informed decisions about the best way to present information to an audience. applies moderation and editing processes to content supplied by others.</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. designs the content and appearance of complex information artefacts. x000d controls, monitors and evaluates content to ensure quality, consistency and accessibility of messages and optimal use of chosen media. understands and manages risks associated with publishing content.x000d moderates content and ensures content can be repurposed appropriately. x000d reviews work of others and takes responsibility for ensuring appropriate publication.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. designs the content and appearance of complex information artefacts. controls, monitors and evaluates content to ensure quality, consistency and accessibility of messages and optimal use of chosen media. understands and manages risks associated with publishing content. moderates content and ensures content can be repurposed appropriately. reviews work of others and takes responsibility for ensuring appropriate publication.</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. provides overall editorial control across the team or teams of content designers and authors. x000d advises on appropriate content formats and mediums. x000d develops and maintains content plans showing how the identified audience needs will be met. x000d oversees the review and approval of materials to enable requirements to be satisfied.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. provides overall editorial control across the team or teams of content designers and authors. advises on appropriate content formats and mediums. develops and maintains content plans showing how the identified audience needs will be met. oversees the review and approval of materials to enable requirements to be satisfied.</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. obtains organisational commitment to policies, standards and strategies to create required content. x000d specifies design standards and methods to meet organisational objectives for content creation. x000d plans and leads content creation for strategic, large and complex programmes.</t>
+          <t>planning, designing and creating content that meets usercentred and organisational needs, encompassing textual information, graphical content and multimedia elements. obtains organisational commitment to policies, standards and strategies to create required content. specifies design standards and methods to meet organisational objectives for content creation. plans and leads content creation for strategic, large and complex programmes.</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. contributes, under instruction, to publication support activities. x000d supports the collation of data. x000d uses established publishing processes and procedures following appropriate guidelines.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. contributes, under instruction, to publication support activities. supports the collation of data. uses established publishing processes and procedures following appropriate guidelines.</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. uses technical publication concepts, tools, and methods to publish content following agreed procedures and guidelines. x000d prepares and formats content to meet the needs of the target audience and platform.x000d obtains and analyses usage data and presents it effectively. x000d applies principles of usability and accessibility to published information.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. uses technical publication concepts, tools, and methods to publish content following agreed procedures and guidelines. prepares and formats content to meet the needs of the target audience and platform. obtains and analyses usage data and presents it effectively. applies principles of usability and accessibility to published information.</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. coordinates content management processes and procedures to meet the needs of users. x000d uses content publishing systems to manage published content across different channels. x000d assists in identifying and working with content creators.x000d considers all legal issues related to publishing.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. coordinates content management processes and procedures to meet the needs of users. uses content publishing systems to manage published content across different channels. assists in identifying and working with content creators. considers all legal issues related to publishing.</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. applies organisational guidelines and uses appropriate tools and techniques to provide publishing interfaces to new or existing platforms and applications. x000d maintains and updates content management processes and practices to meet the needs of users. selects appropriate channels through which content should be published. x000d collaborates with and provides guidance to content creators. provides advice to users and content authors to leverage the features of the relevant channels and tools used. x000d identifies the legal implications associated with publishing.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. applies organisational guidelines and uses appropriate tools and techniques to provide publishing interfaces to new or existing platforms and applications. maintains and updates content management processes and practices to meet the needs of users. selects appropriate channels through which content should be published. collaborates with and provides guidance to content creators. provides advice to users and content authors to leverage the features of the relevant channels and tools used. identifies the legal implications associated with publishing.</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. plans and manages content publishing activities and assignments. x000d develops standards, processes and practices for consistent content publishing across one or more platformschannels. advises on the approach and techniques to be used for content publishing. x000d advises on approaches for content publishing and creator collaborations. assures design of the overall content structure and style. x000d ensures publication processes comply with agreed policies and strategies and legal requirements.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. plans and manages content publishing activities and assignments. develops standards, processes and practices for consistent content publishing across one or more platformschannels. advises on the approach and techniques to be used for content publishing. advises on approaches for content publishing and creator collaborations. assures design of the overall content structure and style. ensures publication processes comply with agreed policies and strategies and legal requirements.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. obtains organisational commitment and resources to ensure the appropriate quality of material published by or on behalf of the organisation. x000d defines organisational policies, standards, processes and practices for content publishing, including creator partnerships. x000d plans and leads content publishing activities for strategic, large and complex programmes. x000d ensures policies are implemented and any legal issues related to publishing are adequately managed.</t>
+          <t>managing processes to collect, assemble and publish content across various channels to meet organisational and audience needs. obtains organisational commitment and resources to ensure the appropriate quality of material published by or on behalf of the organisation. defines organisational policies, standards, processes and practices for content publishing, including creator partnerships. plans and leads content publishing activities for strategic, large and complex programmes. ensures policies are implemented and any legal issues related to publishing are adequately managed.</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. maintains a knowledge management database. x000d leverages knowledge of a specialism to capture and classify content, taking expert advice when required.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. maintains a knowledge management database. leverages knowledge of a specialism to capture and classify content, taking expert advice when required.</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. maintains knowledge management systems and content to meet business needs.x000d supports others to enable them to complete knowledge management activities and form knowledge management habits. supports changes to work practices to enable capture and use of knowledge.x000d reports on the progress of knowledge management activities. x000d configures and develops knowledge management systems and standards.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. maintains knowledge management systems and content to meet business needs. supports others to enable them to complete knowledge management activities and form knowledge management habits. supports changes to work practices to enable capture and use of knowledge. reports on the progress of knowledge management activities. configures and develops knowledge management systems and standards.</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. organises knowledge assets and oversees the lifecycle of identifying, capturing, classifying, storing and maintaining assets. x000d facilitates sharing, collaboration and communication of knowledge. implements specific knowledge management initiatives.x000d monitors the use and impact of knowledge. x000d interrogates existing knowledge content to identify issues, risks and opportunities.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. organises knowledge assets and oversees the lifecycle of identifying, capturing, classifying, storing and maintaining assets. facilitates sharing, collaboration and communication of knowledge. implements specific knowledge management initiatives. monitors the use and impact of knowledge. interrogates existing knowledge content to identify issues, risks and opportunities.</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops and implements knowledge management processes, practices and behaviours. x000d provides advice, guidance and support to help people to adopt and embed knowledge management. contributes to the definition of policies, standards and guidelines for knowledge management.x000d evaluates and selects knowledge management methods and tools. promotes collaborative technologies, processes and behaviours to facilitate sharing of ideas and workknowledge. x000d shares ideas and examples of existing practices. implements knowledge management at programme, project and team level.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops and implements knowledge management processes, practices and behaviours. provides advice, guidance and support to help people to adopt and embed knowledge management. contributes to the definition of policies, standards and guidelines for knowledge management. evaluates and selects knowledge management methods and tools. promotes collaborative technologies, processes and behaviours to facilitate sharing of ideas and workknowledge. shares ideas and examples of existing practices. implements knowledge management at programme, project and team level.</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops organisational policies, standards and guidelines for knowledge management. x000d champions and leads in the development of an organisational knowledge management approach. shares different approaches for knowledge sharing across communities of practice, business units and networks.x000d promotes knowledgesharing through operational business processes and systems. monitors and evaluates knowledgesharing initiatives. x000d manages reviews of the benefits and value of knowledge management. identifies and recommends improvements.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops organisational policies, standards and guidelines for knowledge management. champions and leads in the development of an organisational knowledge management approach. shares different approaches for knowledge sharing across communities of practice, business units and networks. promotes knowledgesharing through operational business processes and systems. monitors and evaluates knowledgesharing initiatives. manages reviews of the benefits and value of knowledge management. identifies and recommends improvements.</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops an organisationwide knowledge management strategy and leads the creation of a knowledge management culture. x000d embeds knowledge management across business units and develops strategic knowledge management capabilities. x000d reinforces the importance of knowledge sharing by aligning individual and organisational objectives and rewards. x000d identifies opportunities for strategic relationships or partnerships with customers, suppliers and partners.</t>
+          <t>systematically capturing, developing and leveraging vital knowledge to create value and enhance organisational performance. develops an organisationwide knowledge management strategy and leads the creation of a knowledge management culture. embeds knowledge management across business units and develops strategic knowledge management capabilities. reinforces the importance of knowledge sharing by aligning individual and organisational objectives and rewards. identifies opportunities for strategic relationships or partnerships with customers, suppliers and partners.</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. creates simple visual elements under supervision. x000d applies basic design principles. uses design software to produce simple graphics. supports the maintenance of design assets and libraries. x000d participates in design reviews and incorporates feedback. x000d helps with routine tasks such as resizing images, preparing files for print or digital use and organising design assets.</t>
+          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. creates simple visual elements under supervision. applies basic design principles. uses design software to produce simple graphics. supports the maintenance of design assets and libraries. participates in design reviews and incorporates feedback. helps with routine tasks such as resizing images, preparing files for print or digital use and organising design assets.</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. assists the creation of visual elements and layouts for digital and print media under routine supervision. x000d applies design principles to produce consistent and effective visuals. uses design software to create and edit graphics, preparing mockups and prototypes. conforms to brand guidelines and assignment specifications. x000d responds to feedback and research findings to revise designs. x000d participates in research activities to inform design decisions and understand user needs.</t>
+          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. assists the creation of visual elements and layouts for digital and print media under routine supervision. applies design principles to produce consistent and effective visuals. uses design software to create and edit graphics, preparing mockups and prototypes. conforms to brand guidelines and assignment specifications. responds to feedback and research findings to revise designs. participates in research activities to inform design decisions and understand user needs.</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. designs visual concepts and layouts for a range of media. x000d works with stakeholders to understand design requirements. x000d produces highquality graphics and visual elements using design software. develops prototypes and iterates based on feedback. applies brand guidelines and assignment specifications. x000d contributes to the development of design standards and recognised good practices.</t>
+          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. designs visual concepts and layouts for a range of media. works with stakeholders to understand design requirements. produces highquality graphics and visual elements using design software. develops prototypes and iterates based on feedback. applies brand guidelines and assignment specifications. contributes to the development of design standards and recognised good practices.</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. designs visual concepts and comprehensive designs for complex assignments.x000d engages with clients and stakeholders to elicit and document design requirements and goals. manages design assignments from concept to final delivery. x000d creates detailed design mockups and interactive prototypes. reviews and approves design work, ensuring alignment with brand standards and evidencebased practices. x000d develops and implements design processes, guidelines and recognised good practices to enhance design quality and effectiveness.</t>
+          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. designs visual concepts and comprehensive designs for complex assignments. engages with clients and stakeholders to elicit and document design requirements and goals. manages design assignments from concept to final delivery. creates detailed design mockups and interactive prototypes. reviews and approves design work, ensuring alignment with brand standards and evidencebased practices. develops and implements design processes, guidelines and recognised good practices to enhance design quality and effectiveness.</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. manages graphic design activities for the organisation, ensuring designs are researchdriven and aligned with business objectives. x000d oversees multiple design initiatives, ensuring highquality, consistent output. engages with senior stakeholders to align design goals with business objectives and user needs. x000d develops researchinformed visual solutions to strengthen brand identity and user experience. x000d leads the creation and adoption of design standards, processes and recognised good practices. provides authoritative advice on visual design trends and evidencebased practices, ensuring designs meet all required specifications and brand guidelines.</t>
+          <t>creating and applying visual concepts to communicate ideas, enhance aesthetics and improve user experience across digital and print media. manages graphic design activities for the organisation, ensuring designs are researchdriven and aligned with business objectives. oversees multiple design initiatives, ensuring highquality, consistent output. engages with senior stakeholders to align design goals with business objectives and user needs. develops researchinformed visual solutions to strengthen brand identity and user experience. leads the creation and adoption of design standards, processes and recognised good practices. provides authoritative advice on visual design trends and evidencebased practices, ensuring designs meet all required specifications and brand guidelines.</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. analyses the realworld problem, then selects appropriate physical and mathematical models to approximate the phenomena under investigation. x000d applies relevant mathematical techniques to simulate the problem. x000d conducts quality and performance assessments on computational model outputs and makes improvements to the models. x000d provides advice and guidance to the users of these models.</t>
+          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. analyses the realworld problem, then selects appropriate physical and mathematical models to approximate the phenomena under investigation. applies relevant mathematical techniques to simulate the problem. conducts quality and performance assessments on computational model outputs and makes improvements to the models. provides advice and guidance to the users of these models.</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. investigates realworld problems to assess whether existing scientific models provide effective solutions.x000d creates new mathematical representations of the underlying science that can be implemented in a computational model. applies advanced programming techniques to implement scientific models and apply these for problemsolving. x000d analyses the functioning of existing computational models to improve accuracy and performance. x000d communicates limitations such as uncertainty and systematic errors. ensures appropriate usage of computational models.</t>
+          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. investigates realworld problems to assess whether existing scientific models provide effective solutions. creates new mathematical representations of the underlying science that can be implemented in a computational model. applies advanced programming techniques to implement scientific models and apply these for problemsolving. analyses the functioning of existing computational models to improve accuracy and performance. communicates limitations such as uncertainty and systematic errors. ensures appropriate usage of computational models.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. initiates the creation, testing, improvement and application of mathematical model frameworks representing realworld systems and scientific theories. x000d sets standards and approaches for the application of scientific modelling. x000d oversees the representation of science and mathematics principles and theories in models to ensure appropriate, consistent and effective usage. x000d develops or introduces new mathematical techniques where necessary.</t>
+          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. initiates the creation, testing, improvement and application of mathematical model frameworks representing realworld systems and scientific theories. sets standards and approaches for the application of scientific modelling. oversees the representation of science and mathematics principles and theories in models to ensure appropriate, consistent and effective usage. develops or introduces new mathematical techniques where necessary.</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. directs the creation and review of a crossfunctional, enterprisewide approach and culture for scientific modelling. x000d leads the development of the organisations scientific modelling capabilities and champions its use in solving realworld problems.</t>
+          <t>applying computer simulation and other forms of computation to solve realworld problems in scientific disciplines. directs the creation and review of a crossfunctional, enterprisewide approach and culture for scientific modelling. leads the development of the organisations scientific modelling capabilities and champions its use in solving realworld problems.</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. creates moderately complex algorithms using a range of mathematical techniques and with sensitivity to the limitations of the techniques. x000d uses sophisticated scientific computing and visualisation environments. x000d assesses the stability, accuracy and efficiency of algorithms and makes or recommends improvements to them. x000d iterates and improves models using feedback from experts as appropriate.</t>
+          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. creates moderately complex algorithms using a range of mathematical techniques and with sensitivity to the limitations of the techniques. uses sophisticated scientific computing and visualisation environments. assesses the stability, accuracy and efficiency of algorithms and makes or recommends improvements to them. iterates and improves models using feedback from experts as appropriate.</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. creates, tests and improves complex algorithms that numerically solve realworld problems. x000d develops mathematical and computational techniques to assist with numerical analysis. x000d communicates limitations such as uncertainty and systematic errors. x000d reviews algorithms for their conformance to design and performance standards.</t>
+          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. creates, tests and improves complex algorithms that numerically solve realworld problems. develops mathematical and computational techniques to assist with numerical analysis. communicates limitations such as uncertainty and systematic errors. reviews algorithms for their conformance to design and performance standards.</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. initiates the creation, testing, improvement and application of numerical algorithms that solve realworld mathematical problems. x000d sets standards and strategies for the application of numerical analysis. x000d leads the implementation of numerical analyses capabilities to ensure appropriate, consistent and effective usage across the organisation.</t>
+          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. initiates the creation, testing, improvement and application of numerical algorithms that solve realworld mathematical problems. sets standards and strategies for the application of numerical analysis. leads the implementation of numerical analyses capabilities to ensure appropriate, consistent and effective usage across the organisation.</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. directs the creation and review of a crossfunctional, enterprisewide approach and culture for numerical analysis. x000d leads the development of the organisations numerical analysis capabilities and champions its use in solving realworld problems.</t>
+          <t>creating, analysing, implementing, testing and improving algorithms for numerically solving mathematical problems. directs the creation and review of a crossfunctional, enterprisewide approach and culture for numerical analysis. leads the development of the organisations numerical analysis capabilities and champions its use in solving realworld problems.</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>using advanced computer systems and special programming techniques to solve complex computational problems. develops moderately complex solutions that use highperformance computing environments to address realworld problems. x000d applies a range of highperformance computing techniques with sensitivity to the limitations of the techniques. uses input and feedback from experts as appropriate. x000d analyses the complexity, scalability and performance of algorithms, including massively parallel implementations, and makes or recommends improvements.</t>
+          <t>using advanced computer systems and special programming techniques to solve complex computational problems. develops moderately complex solutions that use highperformance computing environments to address realworld problems. applies a range of highperformance computing techniques with sensitivity to the limitations of the techniques. uses input and feedback from experts as appropriate. analyses the complexity, scalability and performance of algorithms, including massively parallel implementations, and makes or recommends improvements.</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>using advanced computer systems and special programming techniques to solve complex computational problems. creates, tests and improves complex highperformance computing solutions to address realworld problems. x000d collaborates with stakeholders to ensure highperformance computing solutions are effective at addressing their problems. x000d guides development teams in the appropriate and effective use of highperformance computing resources</t>
+          <t>using advanced computer systems and special programming techniques to solve complex computational problems. creates, tests and improves complex highperformance computing solutions to address realworld problems. collaborates with stakeholders to ensure highperformance computing solutions are effective at addressing their problems. guides development teams in the appropriate and effective use of highperformance computing resources</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>using advanced computer systems and special programming techniques to solve complex computational problems. initiates the creation, testing, improvement and application of algorithms that solve realworld problems in highperformance computing environments. x000d sets standards and strategies for the use of highperformance computing. x000d leads the implementation of organisational capabilities to ensure appropriate, consistent and effective usage of highperformance computing.</t>
+          <t>using advanced computer systems and special programming techniques to solve complex computational problems. initiates the creation, testing, improvement and application of algorithms that solve realworld problems in highperformance computing environments. sets standards and strategies for the use of highperformance computing. leads the implementation of organisational capabilities to ensure appropriate, consistent and effective usage of highperformance computing.</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>using advanced computer systems and special programming techniques to solve complex computational problems. directs the creation and review of a crossfunctional, enterprisewide approach and culture for highperformance computing.x000d leads the development of the organisations highperformance computing capabilities and champions its use in solving realworld problems.</t>
+          <t>using advanced computer systems and special programming techniques to solve complex computational problems. directs the creation and review of a crossfunctional, enterprisewide approach and culture for highperformance computing. leads the development of the organisations highperformance computing capabilities and champions its use in solving realworld problems.</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>managing the provision of technologybased services to meet defined organisational needs. takes responsibility for managing the design, procurement, installation, upgrading, operation, control, maintenance and effective use of specific technology services.x000d leads service delivery, ensuring agreed service levels, security requirements and other quality standards are met. ensures adherence to relevant policies and procedures.x000d ensures processes, procedures and practices are aligned across teams and providers to operate effectively and efficiently. x000d monitors technology services performance. provides appropriate status and other reports to managers and senior users.</t>
+          <t>managing the provision of technologybased services to meet defined organisational needs. takes responsibility for managing the design, procurement, installation, upgrading, operation, control, maintenance and effective use of specific technology services. leads service delivery, ensuring agreed service levels, security requirements and other quality standards are met. ensures adherence to relevant policies and procedures. ensures processes, procedures and practices are aligned across teams and providers to operate effectively and efficiently. monitors technology services performance. provides appropriate status and other reports to managers and senior users.</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>managing the provision of technologybased services to meet defined organisational needs. manages and allocates resources for budgeting, estimating, planning, developing and delivering a portfolio of technology services and systems. x000d engages and influences stakeholders to ensure services are developed and managed to meet agreed service levels, security requirements and quality standards. x000d plans and implements processes, procedures, tools and practices for monitoring and managing the performance of technology services. x000d aligns the contribution of specified systems and services with organisational and financial goals. recommends sourcing options, whether inhouse, outsourced, or a combination, ensuring optimal service delivery.</t>
+          <t>managing the provision of technologybased services to meet defined organisational needs. manages and allocates resources for budgeting, estimating, planning, developing and delivering a portfolio of technology services and systems. engages and influences stakeholders to ensure services are developed and managed to meet agreed service levels, security requirements and quality standards. plans and implements processes, procedures, tools and practices for monitoring and managing the performance of technology services. aligns the contribution of specified systems and services with organisational and financial goals. recommends sourcing options, whether inhouse, outsourced, or a combination, ensuring optimal service delivery.</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>managing the provision of technologybased services to meet defined organisational needs. sets the strategic direction for managing the technology services portfolio, ensuring alignment with organisational strategies, objectives and emerging opportunities. x000d promotes and assesses technologys potential to drive change, evaluating feasibility and impact.x000d authorises the establishment and integration of new or modified service delivery capabilities, balancing inhouse and outsourced options. oversees resource allocation for planning, developing and delivering technical services and products.x000d maintains a strategic overview of how technology services contribute to organisational success.</t>
+          <t>managing the provision of technologybased services to meet defined organisational needs. sets the strategic direction for managing the technology services portfolio, ensuring alignment with organisational strategies, objectives and emerging opportunities. promotes and assesses technologys potential to drive change, evaluating feasibility and impact. authorises the establishment and integration of new or modified service delivery capabilities, balancing inhouse and outsourced options. oversees resource allocation for planning, developing and delivering technical services and products. maintains a strategic overview of how technology services contribute to organisational success.</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>delivering management, technical and administrative services to support and maintain live applications. assists with specified maintenance procedures. x000d assists in the investigation and resolution of issues relating to applications.</t>
+          <t>delivering management, technical and administrative services to support and maintain live applications. assists with specified maintenance procedures. assists in the investigation and resolution of issues relating to applications.</t>
         </is>
       </c>
     </row>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>delivering management, technical and administrative services to support and maintain live applications. follows agreed procedures to identify and resolve issues with applications. x000d uses application management software and tools to collect agreed performance statistics. x000d carries out agreed applications maintenance tasks.</t>
+          <t>delivering management, technical and administrative services to support and maintain live applications. follows agreed procedures to identify and resolve issues with applications. uses application management software and tools to collect agreed performance statistics. carries out agreed applications maintenance tasks.</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>delivering management, technical and administrative services to support and maintain live applications. maintains application support processes and checks that all requests for support are dealt with according to agreed procedures. x000d uses application management software and tools to investigate issues, collect performance statistics and create reports.</t>
+          <t>delivering management, technical and administrative services to support and maintain live applications. maintains application support processes and checks that all requests for support are dealt with according to agreed procedures. uses application management software and tools to investigate issues, collect performance statistics and create reports.</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>delivering management, technical and administrative services to support and maintain live applications. ensures all requests for support are dealt with according to set standards and procedures. x000d drafts and maintains procedures and documentation for applications support, incorporating security considerations.x000d manages application enhancements to improve business performance. x000d advises on application security, licensing, upgrades, backups and disaster recovery needs.</t>
+          <t>delivering management, technical and administrative services to support and maintain live applications. ensures all requests for support are dealt with according to set standards and procedures. drafts and maintains procedures and documentation for applications support, incorporating security considerations. manages application enhancements to improve business performance. advises on application security, licensing, upgrades, backups and disaster recovery needs.</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. supports routine infrastructure tasks and basic troubleshooting under close supervision.x000d monitors infrastructure health and reports on component status to support operational continuity.</t>
+          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. supports routine infrastructure tasks and basic troubleshooting under close supervision. monitors infrastructure health and reports on component status to support operational continuity.</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. executes operational procedures, runs automation scripts and performs routine maintenance, installation and monitoring of infrastructure components. x000d adjusts automation tasks as instructed to meet operational standards.x000d reports on infrastructure performance and security events, addressing issues directly when possible or escalating them to others for resolution.</t>
+          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. executes operational procedures, runs automation scripts and performs routine maintenance, installation and monitoring of infrastructure components. adjusts automation tasks as instructed to meet operational standards. reports on infrastructure performance and security events, addressing issues directly when possible or escalating them to others for resolution.</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. provisions, deploys and configures infrastructure services and components.x000d monitors infrastructure for load, performance and security events. reports metrics and resolves operational issues.x000d executes standard operational procedures, including backups and restorations. x000d carries out agreed system software maintenance tasks. automates routine system administration tasks to specifications using standard tools and basic scripting.</t>
+          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. provisions, deploys and configures infrastructure services and components. monitors infrastructure for load, performance and security events. reports metrics and resolves operational issues. executes standard operational procedures, including backups and restorations. carries out agreed system software maintenance tasks. automates routine system administration tasks to specifications using standard tools and basic scripting.</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. applies technical expertise to maintain and optimise technology infrastructure, executing updates and employing automation tools. configures tools andor creates scripts to automate infrastructure tasks. x000d maintains operational procedures and checks that they are followed, including adherence to security policies. uses infrastructure management tools to monitor load, performance, and security metrics.x000d investigates and enables the resolution of operational and securityrelated issues. provides reports and proposals for improvement to stakeholders.x000d contributes to the planning and implementation of infrastructure maintenance and updates. implements agreed infrastructure changes and maintenance routines.</t>
+          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. applies technical expertise to maintain and optimise technology infrastructure, executing updates and employing automation tools. configures tools andor creates scripts to automate infrastructure tasks. maintains operational procedures and checks that they are followed, including adherence to security policies. uses infrastructure management tools to monitor load, performance, and security metrics. investigates and enables the resolution of operational and securityrelated issues. provides reports and proposals for improvement to stakeholders. contributes to the planning and implementation of infrastructure maintenance and updates. implements agreed infrastructure changes and maintenance routines.</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. provides technical leadership to optimise the performance of the technology infrastructure. x000d drives the adoption of tools and automated processes for effective operational management and delivery.x000d oversees the planning, installation, maintenance and acceptance of new and updated infrastructure components and infrastructurebased services. aligns to service expectations, security requirements and other quality standards. x000d ensures operational procedures and documentation are current and effective, tracks and addresses operational issues and reports to stakeholders.</t>
+          <t>provisioning, deploying, configuring, operating and optimising technology infrastructure across physical, virtual and cloudbased environments. provides technical leadership to optimise the performance of the technology infrastructure. drives the adoption of tools and automated processes for effective operational management and delivery. oversees the planning, installation, maintenance and acceptance of new and updated infrastructure components and infrastructurebased services. aligns to service expectations, security requirements and other quality standards. ensures operational procedures and documentation are current and effective, tracks and addresses operational issues and reports to stakeholders.</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. assists with system software administration tasks under routine supervision.x000d supports the installation and configuration of system software.x000d helps monitor system performance and resource usage.x000d assists in documenting system software settings and updates.</t>
+          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. assists with system software administration tasks under routine supervision. supports the installation and configuration of system software. helps monitor system performance and resource usage. assists in documenting system software settings and updates.</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. monitors operational systems for resource usage and failure rates, to inform and facilitate system software tuning.x000d applies system software settings to optimise performance, enabling maximum throughput and efficient resource utilisation.x000d installs and tests new versions of system software. x000d assists in creating software implementation procedures, including fallback contingency plans.</t>
+          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. monitors operational systems for resource usage and failure rates, to inform and facilitate system software tuning. applies system software settings to optimise performance, enabling maximum throughput and efficient resource utilisation. installs and tests new versions of system software. assists in creating software implementation procedures, including fallback contingency plans.</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. monitors system software metrics and adjusts configurations for optimum availability and performance.x000d applies technical expertise to investigates and resolve complex system software issues, requesting action from supplier if required. x000d analyses system software updates and determines which ones require actions. x000d develops comprehensive software implementation procedures with robust contingency plans.</t>
+          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. monitors system software metrics and adjusts configurations for optimum availability and performance. applies technical expertise to investigates and resolve complex system software issues, requesting action from supplier if required. analyses system software updates and determines which ones require actions. develops comprehensive software implementation procedures with robust contingency plans.</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. ensures system software is provisioned and configured to support the achievement of service objectives. x000d develops and maintains diagnostic tools and processes for troubleshooting and performance analysis. x000d evaluates new system software and recommends adoption if appropriate. plans the provisioning and testing of new versions of system software. x000d ensures operational procedures and diagnostics for system software are current, accessible and well understood. investigates and coordinates the resolution of potential and actual service problems.</t>
+          <t>installing, managing and maintaining operating systems, data management, office automation and utility software across various infrastructure environments. ensures system software is provisioned and configured to support the achievement of service objectives. develops and maintains diagnostic tools and processes for troubleshooting and performance analysis. evaluates new system software and recommends adoption if appropriate. plans the provisioning and testing of new versions of system software. ensures operational procedures and diagnostics for system software are current, accessible and well understood. investigates and coordinates the resolution of potential and actual service problems.</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>providing maintenance and support services for communications networks. supports routine network tasks under close supervision. x000d monitors basic network health and reports on the status of network components. x000d assists with straightforward troubleshooting and follows established procedures to maintain operational continuity. x000d escalates issues as necessary to higher levels of support</t>
+          <t>providing maintenance and support services for communications networks. supports routine network tasks under close supervision. monitors basic network health and reports on the status of network components. assists with straightforward troubleshooting and follows established procedures to maintain operational continuity. escalates issues as necessary to higher levels of support</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>providing maintenance and support services for communications networks. assists in the operational configuration of network components and the investigation and resolution of network problems.x000d assists in the implementation of basic scripting and automation tools to streamline network support tasks.x000d assists with specified maintenance procedures and follows established safety, security and quality standards.x000d provides firstline support and guidance to network users, escalating issues as necessary.</t>
+          <t>providing maintenance and support services for communications networks. assists in the operational configuration of network components and the investigation and resolution of network problems. assists in the implementation of basic scripting and automation tools to streamline network support tasks. assists with specified maintenance procedures and follows established safety, security and quality standards. provides firstline support and guidance to network users, escalating issues as necessary.</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>providing maintenance and support services for communications networks. executes agreed network maintenance tasks and specified operational configuration of network components.x000d identifies and diagnoses network problemsfaults using the required troubleshooting tools and network management software, including addressing securityrelated issues.x000d implements and maintains scripts, automation tools and orchestration platforms to optimise network support processes.x000d collects performance and traffic statistics and collaborates with others to ensure network effectiveness and resolve issues</t>
+          <t>providing maintenance and support services for communications networks. executes agreed network maintenance tasks and specified operational configuration of network components. identifies and diagnoses network problemsfaults using the required troubleshooting tools and network management software, including addressing securityrelated issues. implements and maintains scripts, automation tools and orchestration platforms to optimise network support processes. collects performance and traffic statistics and collaborates with others to ensure network effectiveness and resolve issues</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>providing maintenance and support services for communications networks. applies technical expertise to maintain and optimise network infrastructure, executing updates and employing automation tools. x000d uses network management tools to monitor load, performance, and security statistics. investigates and enables the resolution of networkrelated operational and security issues. configures tools andor creates scripts to automate network tasks. x000d maintains operational procedures and checks that they are followed. provides reports and proposals for improvement to stakeholders.x000d contributes to the planning and implementation of network maintenance, updates, and security enhancements. implements agreed network changes and maintenance routines.</t>
+          <t>providing maintenance and support services for communications networks. applies technical expertise to maintain and optimise network infrastructure, executing updates and employing automation tools. uses network management tools to monitor load, performance, and security statistics. investigates and enables the resolution of networkrelated operational and security issues. configures tools andor creates scripts to automate network tasks. maintains operational procedures and checks that they are followed. provides reports and proposals for improvement to stakeholders. contributes to the planning and implementation of network maintenance, updates, and security enhancements. implements agreed network changes and maintenance routines.</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>providing maintenance and support services for communications networks. leads network operations to optimise performance. x000d oversees planning, installation, maintenance, and acceptance of network components and services, aligning with service expectations, standards, and security requirements.x000d ensures network support requests are handled according to set standards and procedures.x000d drives the adoption of tools and processes for effective operational management and delivery, ensuring security considerations are addressed. maintains procedures and documentation. investigates and resolves complex network problems. tracks operational issues and reports to stakeholders.</t>
+          <t>providing maintenance and support services for communications networks. leads network operations to optimise performance. oversees planning, installation, maintenance, and acceptance of network components and services, aligning with service expectations, standards, and security requirements. ensures network support requests are handled according to set standards and procedures. drives the adoption of tools and processes for effective operational management and delivery, ensuring security considerations are addressed. maintains procedures and documentation. investigates and resolves complex network problems. tracks operational issues and reports to stakeholders.</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>installing and testing, or decommissioning and removing, systems or system components. follows agreed procedures to perform simple installations, replace consumable items and check the correct working of installations. x000d documents and reports on work done.</t>
+          <t>installing and testing, or decommissioning and removing, systems or system components. follows agreed procedures to perform simple installations, replace consumable items and check the correct working of installations. documents and reports on work done.</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>installing and testing, or decommissioning and removing, systems or system components. installs or removes system components using supplied installation instructions and tools. x000d conducts standard tests and contributes to investigations of problems and faults.x000d confirms the correct working of installations. x000d documents results in accordance with agreed procedures.</t>
+          <t>installing and testing, or decommissioning and removing, systems or system components. installs or removes system components using supplied installation instructions and tools. conducts standard tests and contributes to investigations of problems and faults. confirms the correct working of installations. documents results in accordance with agreed procedures.</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>installing and testing, or decommissioning and removing, systems or system components. installs or removes hardware andor software, using supplied installation instructions and tools, including handover to the client. x000d uses standard procedures and diagnostic tools to test installations, correct problems, and document results. x000d records details of all components that have been installed and removed. assists users and follows agreed procedures for further help or escalation.x000d contributes to the development of installation procedures and standards.</t>
+          <t>installing and testing, or decommissioning and removing, systems or system components. installs or removes hardware andor software, using supplied installation instructions and tools, including handover to the client. uses standard procedures and diagnostic tools to test installations, correct problems, and document results. records details of all components that have been installed and removed. assists users and follows agreed procedures for further help or escalation. contributes to the development of installation procedures and standards.</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>installing and testing, or decommissioning and removing, systems or system components. undertakes or supervises complex installations and deinstallations of systems or components, including handover to the client. x000d develops procedures and standards for installation and handover to maintain and improve the installation service. x000d schedules installation work around client priorities and resource availability. x000d ensures adherence to established safety and quality procedures.</t>
+          <t>installing and testing, or decommissioning and removing, systems or system components. undertakes or supervises complex installations and deinstallations of systems or components, including handover to the client. develops procedures and standards for installation and handover to maintain and improve the installation service. schedules installation work around client priorities and resource availability. ensures adherence to established safety and quality procedures.</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>installing and testing, or decommissioning and removing, systems or system components. takes responsibility for installation andor decommissioning projects. x000d provides effective team leadership, including information flow to and from the customer during project work. x000d develops and implements quality plans and method statements. x000d monitors the effectiveness of installations and ensures appropriate recommendations for change are made.</t>
+          <t>installing and testing, or decommissioning and removing, systems or system components. takes responsibility for installation andor decommissioning projects. provides effective team leadership, including information flow to and from the customer during project work. develops and implements quality plans and method statements. monitors the effectiveness of installations and ensures appropriate recommendations for change are made.</t>
         </is>
       </c>
     </row>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. applies tools, techniques and processes to administer, track, log, report on and correct configuration items, components and changes. x000d assists with audits to check the accuracy of the information and undertakes any necessary corrective action under direction.</t>
+          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. applies tools, techniques and processes to administer, track, log, report on and correct configuration items, components and changes. assists with audits to check the accuracy of the information and undertakes any necessary corrective action under direction.</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. applies tools, techniques and processes to track, log and correct information related to configuration items. x000d verifies and approves changes to protect assets and components from unauthorised change, diversion and inappropriate use. x000d supports user compliance with identification standards for object types, environments, processes, lifecycles, documentation, versions, formats, baselines, releases and templates. x000d performs audits to check the accuracy of the information and undertakes any necessary corrective action under direction.</t>
+          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. applies tools, techniques and processes to track, log and correct information related to configuration items. verifies and approves changes to protect assets and components from unauthorised change, diversion and inappropriate use. supports user compliance with identification standards for object types, environments, processes, lifecycles, documentation, versions, formats, baselines, releases and templates. performs audits to check the accuracy of the information and undertakes any necessary corrective action under direction.</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. proposes and agrees the configuration items cis to be uniquely identified with naming conventions. x000d puts in place operational processes for secure configuration, classification and management of cis and for verifying and auditing configuration records. x000d develops, configures and maintains tools including automation to identify, track, log and maintain accurate, complete and current information. x000d reports on the status of configuration management. identifies problems and issues and recommend corrective actions.</t>
+          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. proposes and agrees the configuration items cis to be uniquely identified with naming conventions. puts in place operational processes for secure configuration, classification and management of cis and for verifying and auditing configuration records. develops, configures and maintains tools including automation to identify, track, log and maintain accurate, complete and current information. reports on the status of configuration management. identifies problems and issues and recommend corrective actions.</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. plans the capture and management of cis and related information. x000d agrees scope of configuration management processes and the configuration items cis and related information to be controlled. x000d identifies, evaluates and manages the adoption of appropriate tools, techniques and processes including automation for configuration management. x000d contributes to the development of configuration management strategies, policies, standards and guidelines.</t>
+          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. plans the capture and management of cis and related information. agrees scope of configuration management processes and the configuration items cis and related information to be controlled. identifies, evaluates and manages the adoption of appropriate tools, techniques and processes including automation for configuration management. contributes to the development of configuration management strategies, policies, standards and guidelines.</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. develops configuration management strategies, policies, standards and guidelines. x000d champions the importance and value of configuration management and develops new methods and organisational capabilities including automation for configuration management. x000d provides resources to drive adoption of, and adherence to, policies and standards. x000d measures and monitors adherence to standards and ensures consistent execution of the process across the organisation.</t>
+          <t>planning, identifying, controlling, accounting for and auditing of configuration items cis and their interrelationships. develops configuration management strategies, policies, standards and guidelines. champions the importance and value of configuration management and develops new methods and organisational capabilities including automation for configuration management. provides resources to drive adoption of, and adherence to, policies and standards. measures and monitors adherence to standards and ensures consistent execution of the process across the organisation.</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. assists with release management tasks under routine supervision.x000d supports the collection of data and information for release planning and scheduling.x000d assists in the preparation of release materials and resources. helps document and maintain records of release activities.x000d participates in basic testing and quality assurance tasks and issue resolution.</t>
+          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. assists with release management tasks under routine supervision. supports the collection of data and information for release planning and scheduling. assists in the preparation of release materials and resources. helps document and maintain records of release activities. participates in basic testing and quality assurance tasks and issue resolution.</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. supports the planning and scheduling of releases.x000d coordinates release activities with relevant teams. follows defined release processes and procedures.x000d participates in testing and quality assurance activities to ensure releases meet standards. identifies and resolves issues related to the release process.x000d documents and reports on release outcomes and communicates findings to stakeholders.</t>
+          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. supports the planning and scheduling of releases. coordinates release activities with relevant teams. follows defined release processes and procedures. participates in testing and quality assurance activities to ensure releases meet standards. identifies and resolves issues related to the release process. documents and reports on release outcomes and communicates findings to stakeholders.</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. plans and schedules releases in line with business requirements and objectives.x000d coordinates release activities across multiple teams and stakeholders. manages the release lifecycle, ensuring timely and quality deliverables.x000d ensures releases meet defined quality, security and compliance standards.x000d communicates release plans, progress and outcomes to stakeholders. conducts postrelease reviews and identifies areas for improvement.</t>
+          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. plans and schedules releases in line with business requirements and objectives. coordinates release activities across multiple teams and stakeholders. manages the release lifecycle, ensuring timely and quality deliverables. ensures releases meet defined quality, security and compliance standards. communicates release plans, progress and outcomes to stakeholders. conducts postrelease reviews and identifies areas for improvement.</t>
         </is>
       </c>
     </row>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. develops and maintains release approaches, processes and automation tools.x000d oversees the planning and scheduling of complex, largescale releases. coordinates release activities across multiple projects and programmes.x000d ensures release processes and procedures are applied and that releases can be rolled back as needed. x000d communicates release approaches and outcomes. conducts postrelease analysis and drives continuous improvement.</t>
+          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. develops and maintains release approaches, processes and automation tools. oversees the planning and scheduling of complex, largescale releases. coordinates release activities across multiple projects and programmes. ensures release processes and procedures are applied and that releases can be rolled back as needed. communicates release approaches and outcomes. conducts postrelease analysis and drives continuous improvement.</t>
         </is>
       </c>
     </row>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. defines organisational release management strategies, policies and standards.x000d aligns release management with overall business strategies and objectives. ensures the availability of resources and tools for effective release management.x000d communicates release strategies and outcomes to stakeholders.x000d drives the adoption of new release management techniques and technologies.</t>
+          <t>managing the release of new and updated services into production, ensuring alignment with business objectives and compliance standards. defines organisational release management strategies, policies and standards. aligns release management with overall business strategies and objectives. ensures the availability of resources and tools for effective release management. communicates release strategies and outcomes to stakeholders. drives the adoption of new release management techniques and technologies.</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. assists in deploying software releases and updates under routine supervision.x000d executes defined deployment processes and procedures using deployment tools and techniques.x000d monitors deployed applications and reports issues. assists in rolling back deployments when necessary.</t>
+          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. assists in deploying software releases and updates under routine supervision. executes defined deployment processes and procedures using deployment tools and techniques. monitors deployed applications and reports issues. assists in rolling back deployments when necessary.</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. deploys software releases and updates to production environments.x000d uses deployment tools and techniques to ensure consistent deployments. monitors and troubleshoots deployment processes.x000d performs rollbacks of deployments in case of issues or failures.x000d collaborates with release management and operations teams.</t>
+          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. deploys software releases and updates to production environments. uses deployment tools and techniques to ensure consistent deployments. monitors and troubleshoots deployment processes. performs rollbacks of deployments in case of issues or failures. collaborates with release management and operations teams.</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. plans and executes deployments of complex software releases and updates.x000d manages continuous deployment using automation tools and techniques. develops and maintains deployment processes, procedures and scripts.x000d monitors and optimises deployment processes for efficiency and reliability. ensures the availability, performance and security of deployed applications.x000d collaborates with crossfunctional teams.</t>
+          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. plans and executes deployments of complex software releases and updates. manages continuous deployment using automation tools and techniques. develops and maintains deployment processes, procedures and scripts. monitors and optimises deployment processes for efficiency and reliability. ensures the availability, performance and security of deployed applications. collaborates with crossfunctional teams.</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. designs and implements deployment approaches, processes and automation tools for the organisation.x000d oversees the deployment of critical and largescale software. ensures deployment processes align with organisational standards and recommended practices.x000d continuously improves deployment processes and automation capabilities.x000d defines monitoring and alert strategies for deployed applications.</t>
+          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. designs and implements deployment approaches, processes and automation tools for the organisation. oversees the deployment of critical and largescale software. ensures deployment processes align with organisational standards and recommended practices. continuously improves deployment processes and automation capabilities. defines monitoring and alert strategies for deployed applications.</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. defines organisational deployment strategies, policies and standards.x000d aligns deployment practices with overall operations and service delivery goals.x000d ensures the availability of resources and tools for effective deployment.x000d drives the adoption of new deployment techniques and technologies. collaborates with senior stakeholders to ensure deployments meet business strategies and objectives.</t>
+          <t>transitioning software from development to live usage, managing risks and ensuring it works as intended. defines organisational deployment strategies, policies and standards. aligns deployment practices with overall operations and service delivery goals. ensures the availability of resources and tools for effective deployment. drives the adoption of new deployment techniques and technologies. collaborates with senior stakeholders to ensure deployments meet business strategies and objectives.</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. assists with storage management tasks such as provisioning.x000d supports the setup and configuration of storage systems, incorporating standard security practices.x000d helps monitor storage performance and capacity, and documents storage utilisation.</t>
+          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. assists with storage management tasks such as provisioning. supports the setup and configuration of storage systems, incorporating standard security practices. helps monitor storage performance and capacity, and documents storage utilisation.</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. executes routine storage management tasks following established procedures and using standard tools.x000d implements documented configurations for allocation of storage, installation and maintenance of secure storage systems using the agreed operational procedures.x000d identifies operational problems, including securityrelated issues, and contributes to their resolution.x000d uses standard management and reporting tools to collect and report on storage utilisation, performance and backup statistics.</t>
+          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. executes routine storage management tasks following established procedures and using standard tools. implements documented configurations for allocation of storage, installation and maintenance of secure storage systems using the agreed operational procedures. identifies operational problems, including securityrelated issues, and contributes to their resolution. uses standard management and reporting tools to collect and report on storage utilisation, performance and backup statistics.</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. prepares and maintains operational procedures for storage management. x000d monitors capacity, performance, availability and other operational metrics. takes appropriate action to ensure corrective and proactive maintenance of storage and backup systems to protect and secure business information. x000d creates reports and proposals for improvement. x000d contributes to the planning and implementation of new installations and scheduled maintenance and changes of existing systems.</t>
+          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. prepares and maintains operational procedures for storage management. monitors capacity, performance, availability and other operational metrics. takes appropriate action to ensure corrective and proactive maintenance of storage and backup systems to protect and secure business information. creates reports and proposals for improvement. contributes to the planning and implementation of new installations and scheduled maintenance and changes of existing systems.</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. develops standards and guidelines for implementing data protection and disaster recovery functionality for all business applications and business data. x000d provides authoritative advice and guidance to implement and improve storage management. x000d manages storage and backup systems to provide agreed service levels. x000d creates, improves and supports storage management services with optimal utilisation of storage resources, ensuring security, availability and integrity of data.</t>
+          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. develops standards and guidelines for implementing data protection and disaster recovery functionality for all business applications and business data. provides authoritative advice and guidance to implement and improve storage management. manages storage and backup systems to provide agreed service levels. creates, improves and supports storage management services with optimal utilisation of storage resources, ensuring security, availability and integrity of data.</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. develops organisational policies, standards and guidelines for storage management.x000d develops strategies for managing storage and data based on the level of criticality of the information. x000d ensures compliance with regulatory and security requirements. x000d aligns investments in storage management with business goals and data management policies.</t>
+          <t>provisioning, configuring and optimising onpremises and cloudbased storage solutions, ensuring data availability, security and alignment with business objectives. develops organisational policies, standards and guidelines for storage management. develops strategies for managing storage and data based on the level of criticality of the information. ensures compliance with regulatory and security requirements. aligns investments in storage management with business goals and data management policies.</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. assists with the tasks related to granting, monitoring and reporting on physical access controls under routine supervision. x000d follows established procedures and guidelines to support the maintenance of the physical environment. x000d helps create and maintain documentation.</t>
+          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. assists with the tasks related to granting, monitoring and reporting on physical access controls under routine supervision. follows established procedures and guidelines to support the maintenance of the physical environment. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. monitors compliance against agreed processes and investigates, assesses and resolves incidents of noncompliance, escalating where necessary. x000d processes physical access requests, monitors access control systems and reports on accessrelated activities.</t>
+          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. monitors compliance against agreed processes and investigates, assesses and resolves incidents of noncompliance, escalating where necessary. processes physical access requests, monitors access control systems and reports on accessrelated activities.</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. uses data centre management tools to produce management information on power, cooling and space and investigate issues where necessary. x000d carries out routine audit and checks to ensure adherence to policies and procedures. x000d facilitates the implementation of mandatory electrical safety testing.</t>
+          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. uses data centre management tools to produce management information on power, cooling and space and investigate issues where necessary. carries out routine audit and checks to ensure adherence to policies and procedures. facilitates the implementation of mandatory electrical safety testing.</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. develops and maintains the standards, processes and documentation for data centres. x000d optimises efficiency in the population of data centre space. ensures adherence to all relevant policies and processes. x000d uses data centre management tools to plan, record and manage installed infrastructure, power, space and cooling capabilities. x000d monitors usage and actions to meet sustainability targets.</t>
+          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. develops and maintains the standards, processes and documentation for data centres. optimises efficiency in the population of data centre space. ensures adherence to all relevant policies and processes. uses data centre management tools to plan, record and manage installed infrastructure, power, space and cooling capabilities. monitors usage and actions to meet sustainability targets.</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. sets organisational policies for managing the it estate, ensuring alignment with recognised industry practices. x000d develops strategies to forecast and fulfil future data centre space requirements.x000d takes overall responsibility for adherence to health and safety regulations and electrical safety policies.x000d identifies and implements recognised industry practices to align future plans with corporate sustainability targets.</t>
+          <t>planning, designing and managing the buildings, space and facilities which, collectively, make up the it estate. sets organisational policies for managing the it estate, ensuring alignment with recognised industry practices. develops strategies to forecast and fulfil future data centre space requirements. takes overall responsibility for adherence to health and safety regulations and electrical safety policies. identifies and implements recognised industry practices to align future plans with corporate sustainability targets.</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. monitors and logs the actual service provided. x000d compares delivered service to service level agreements, identifying any deviations or areas for improvement.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. monitors and logs the actual service provided. compares delivered service to service level agreements, identifying any deviations or areas for improvement.</t>
         </is>
       </c>
     </row>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. monitors service delivery performance metrics. x000d liaises with stakeholders to help them plan for a deterioration in service andor breaches of service level agreements.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. monitors service delivery performance metrics. liaises with stakeholders to help them plan for a deterioration in service andor breaches of service level agreements.</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. performs defined tasks to monitor service delivery against service level agreements and maintains records of relevant information. x000d analyses service delivery performance to identify actions required to maintain or improve levels of service.x000d initiates and reports on actions to maintain or improve levels of service.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. performs defined tasks to monitor service delivery against service level agreements and maintains records of relevant information. analyses service delivery performance to identify actions required to maintain or improve levels of service. initiates and reports on actions to maintain or improve levels of service.</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. ensures service delivery meets agreed service levels. x000d negotiates service level requirements and agreed service levels with customers. x000d diagnoses service delivery problems and initiates actions to maintain or improve levels of service. x000d establishes and maintains operational methods, procedures and facilities and reviews them regularly for effectiveness and efficiency.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. ensures service delivery meets agreed service levels. negotiates service level requirements and agreed service levels with customers. diagnoses service delivery problems and initiates actions to maintain or improve levels of service. establishes and maintains operational methods, procedures and facilities and reviews them regularly for effectiveness and efficiency.</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. ensures service delivery is monitored effectively and that identified actions to maintain or improve levels of service are implemented. x000d ensures service level agreements are complete and costeffective across the catalogue of available services. ensures operational methods, procedures, facilities and tools are established, reviewed and maintained. prepares proposals to meet forecast changes in the levels or types of services.x000d reviews service delivery to ensure agreed targets are met. x000d negotiates with relevant parties in respect of disruptions and major amendments to the provision of services.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. ensures service delivery is monitored effectively and that identified actions to maintain or improve levels of service are implemented. ensures service level agreements are complete and costeffective across the catalogue of available services. ensures operational methods, procedures, facilities and tools are established, reviewed and maintained. prepares proposals to meet forecast changes in the levels or types of services. reviews service delivery to ensure agreed targets are met. negotiates with relevant parties in respect of disruptions and major amendments to the provision of services.</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. sets strategies for service delivery that support the strategic needs of the client organisation. x000d authorises allocation of resources for monitoring service delivery arrangements. x000d develops relationships with customers at the highest level to identify potential areas of mutual commercial interest for future development. x000d maintains an overview of the contribution of service delivery arrangements to organisational success. provides leadership within the industry on the identification of future trends.</t>
+          <t>agreeing targets for service levels and assessing, monitoring and managing the delivery of services against the targets. sets strategies for service delivery that support the strategic needs of the client organisation. authorises allocation of resources for monitoring service delivery arrangements. develops relationships with customers at the highest level to identify potential areas of mutual commercial interest for future development. maintains an overview of the contribution of service delivery arrangements to organisational success. provides leadership within the industry on the identification of future trends.</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>providing a source of consistent information about available services and products to customers and users. assists with service catalogue management tasks under routine supervision.x000d supports the collection and updating of service and product information.x000d helps maintain the accuracy and relevance of the service catalogue.</t>
+          <t>providing a source of consistent information about available services and products to customers and users. assists with service catalogue management tasks under routine supervision. supports the collection and updating of service and product information. helps maintain the accuracy and relevance of the service catalogue.</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>providing a source of consistent information about available services and products to customers and users. collates information needed to populate the service catalogue. x000d edits and maintains service and product descriptions and keeps the list of available services up to date. x000d acts as a contact point, receiving and handling routine updates to the service catalogue. x000d identifies opportunities to improve service catalogue management processes.</t>
+          <t>providing a source of consistent information about available services and products to customers and users. collates information needed to populate the service catalogue. edits and maintains service and product descriptions and keeps the list of available services up to date. acts as a contact point, receiving and handling routine updates to the service catalogue. identifies opportunities to improve service catalogue management processes.</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>providing a source of consistent information about available services and products to customers and users. contributes to the design and implementation of a service catalogue.x000d enables automation of service requests and order fulfilment. x000d provides advice and guidance on the information to be included in the service catalogue. x000d contributes to reviews and improvement of the catalogue and of service catalogue management processes.</t>
+          <t>providing a source of consistent information about available services and products to customers and users. contributes to the design and implementation of a service catalogue. enables automation of service requests and order fulfilment. provides advice and guidance on the information to be included in the service catalogue. contributes to reviews and improvement of the catalogue and of service catalogue management processes.</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>providing a source of consistent information about available services and products to customers and users. manages the creation and maintenance of a catalogue of services. x000d ensures the service catalogue is complete and current. works with service owners to ensure consistency and accuracy of the service catalogue entries. x000d completes regular reviews of the catalogue with stakeholders to ensure relevance to business needs and requirements. x000d manages the service catalogue management processes.</t>
+          <t>providing a source of consistent information about available services and products to customers and users. manages the creation and maintenance of a catalogue of services. ensures the service catalogue is complete and current. works with service owners to ensure consistency and accuracy of the service catalogue entries. completes regular reviews of the catalogue with stakeholders to ensure relevance to business needs and requirements. manages the service catalogue management processes.</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. performs defined availability management tasks, such as routine monitoring and data collection.x000d tests disaster recovery procedures under direction and contributes to the documentation of recovery plans.x000d assists with the operation of availability management tools and processes.x000d monitors service components against agreed performance standards and reports any deviations.</t>
+          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. performs defined availability management tasks, such as routine monitoring and data collection. tests disaster recovery procedures under direction and contributes to the documentation of recovery plans. assists with the operation of availability management tools and processes. monitors service components against agreed performance standards and reports any deviations.</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. analyses service and component availability, reliability, maintainability and serviceability. x000d contributes to the availability management process and its operation. x000d monitors and maintains services and components to ensure ongoing compliance with agreed performance targets and service levels.x000d implements disaster recovery arrangements and documents recovery procedures. conducts testing of recovery procedures.</t>
+          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. analyses service and component availability, reliability, maintainability and serviceability. contributes to the availability management process and its operation. monitors and maintains services and components to ensure ongoing compliance with agreed performance targets and service levels. implements disaster recovery arrangements and documents recovery procedures. conducts testing of recovery procedures.</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. provides advice and guidance on the planning, design and improvement of service and component availability. x000d investigates all breaches of availability targets and service nonavailability and initiates remedial activities. x000d develops plans for disaster recovery together with supporting processes. x000d manages the testing of disaster recovery plans.</t>
+          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. provides advice and guidance on the planning, design and improvement of service and component availability. investigates all breaches of availability targets and service nonavailability and initiates remedial activities. develops plans for disaster recovery together with supporting processes. manages the testing of disaster recovery plans.</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. sets policy and develops strategies, plans and processes to ensure services deliver agreed levels of availability. x000d develops and implements new availability tools and techniques.</t>
+          <t>ensuring services deliver agreed levels of availability to meet the current and future needs of the business. sets policy and develops strategies, plans and processes to ensure services deliver agreed levels of availability. develops and implements new availability tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>developing, implementing and testing a business continuity framework. maintains records of all related testing and training and ensures the availability of all documentation.x000d records the actions taken and the consequences following an incident or live testing of a continuity plan for a lessonslearned report.</t>
+          <t>developing, implementing and testing a business continuity framework. maintains records of all related testing and training and ensures the availability of all documentation. records the actions taken and the consequences following an incident or live testing of a continuity plan for a lessonslearned report.</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>developing, implementing and testing a business continuity framework. applies a structured approach to develop and document the detail for a continuity plan. x000d maintains documentation of business continuity and disaster recovery plans. x000d supports the development of a test plan and implementation of continuity management exercises.</t>
+          <t>developing, implementing and testing a business continuity framework. applies a structured approach to develop and document the detail for a continuity plan. maintains documentation of business continuity and disaster recovery plans. supports the development of a test plan and implementation of continuity management exercises.</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>developing, implementing and testing a business continuity framework. contributes to the development of continuity management plans. x000d identifies information and communication systems that support critical business processes. x000d coordinates the business impact analysis and the assessment of risks. x000d coordinates the planning, designing and testing of contingency plans.</t>
+          <t>developing, implementing and testing a business continuity framework. contributes to the development of continuity management plans. identifies information and communication systems that support critical business processes. coordinates the business impact analysis and the assessment of risks. coordinates the planning, designing and testing of contingency plans.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>developing, implementing and testing a business continuity framework. manages the development, implementation and testing of continuity management plans. x000d manages the relationship with individuals and teams who have authority for critical business processes and supporting systems. x000d evaluates the critical risks and identifies priority areas for improvement. x000d tests continuity management plans and procedures to ensure they address exposure to risk and that agreed levels of continuity can be maintained.</t>
+          <t>developing, implementing and testing a business continuity framework. manages the development, implementation and testing of continuity management plans. manages the relationship with individuals and teams who have authority for critical business processes and supporting systems. evaluates the critical risks and identifies priority areas for improvement. tests continuity management plans and procedures to ensure they address exposure to risk and that agreed levels of continuity can be maintained.</t>
         </is>
       </c>
     </row>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>developing, implementing and testing a business continuity framework. sets the strategy for continuity management across the organisation. x000d secures organisational commitment, funding and resources for continuity management. x000d leads continuity management exercises. x000d communicates the policy, governance, scope and roles involved in continuity management. has defined authority and accountability for the actions and decisions for continuity management</t>
+          <t>developing, implementing and testing a business continuity framework. sets the strategy for continuity management across the organisation. secures organisational commitment, funding and resources for continuity management. leads continuity management exercises. communicates the policy, governance, scope and roles involved in continuity management. has defined authority and accountability for the actions and decisions for continuity management</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>ensuring service components have the capacity and performance to meet current and planned business needs. assists in monitoring service component capacity and performance under routine guidance and supervision.x000d collects and reports data on resource utilisation and capacity metrics. x000d supports the implementation of capacity management procedures and practices.</t>
+          <t>ensuring service components have the capacity and performance to meet current and planned business needs. assists in monitoring service component capacity and performance under routine guidance and supervision. collects and reports data on resource utilisation and capacity metrics. supports the implementation of capacity management procedures and practices.</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>ensuring service components have the capacity and performance to meet current and planned business needs. monitors service component capacity and performance, identifying potential issues and escalating as necessary. x000d applies standard procedures to manage demand and capacity. x000d participates in capacity modelling and forecasting activities, providing input and recommendations. x000d supports the implementation of capacity management tools and techniques.</t>
+          <t>ensuring service components have the capacity and performance to meet current and planned business needs. monitors service component capacity and performance, identifying potential issues and escalating as necessary. applies standard procedures to manage demand and capacity. participates in capacity modelling and forecasting activities, providing input and recommendations. supports the implementation of capacity management tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>ensuring service components have the capacity and performance to meet current and planned business needs. monitors service component capacity and initiates actions to resolve any shortfalls according to agreed procedures. x000d applies techniques to control the demand upon a particular resource or service. x000d contributes to capacity modelling and planning using datadriven insights.x000d supports the design of service component capacity.</t>
+          <t>ensuring service components have the capacity and performance to meet current and planned business needs. monitors service component capacity and initiates actions to resolve any shortfalls according to agreed procedures. applies techniques to control the demand upon a particular resource or service. contributes to capacity modelling and planning using datadriven insights. supports the design of service component capacity.</t>
         </is>
       </c>
     </row>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>ensuring service components have the capacity and performance to meet current and planned business needs. manages capacity modelling and forecasting activities, using datadriven insights.x000d proactively reviews information in conjunction with service level agreements to identify any capacity issues and specifies any required changes. provides advice to support the design of service components, including designing in flexible and scalable capacity. x000d works with business representatives to agree and implement short and mediumterm modifications to capacity. x000d drafts and maintains standards and procedures for service component capacity management. ensures the correct implementation of standards and procedures.</t>
+          <t>ensuring service components have the capacity and performance to meet current and planned business needs. manages capacity modelling and forecasting activities, using datadriven insights. proactively reviews information in conjunction with service level agreements to identify any capacity issues and specifies any required changes. provides advice to support the design of service components, including designing in flexible and scalable capacity. works with business representatives to agree and implement short and mediumterm modifications to capacity. drafts and maintains standards and procedures for service component capacity management. ensures the correct implementation of standards and procedures.</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>ensuring service components have the capacity and performance to meet current and planned business needs. leads the development and implementation of policy and strategies for capacity and performance management to meet business needs. x000d leads capacity modelling and forecasting over the organisations planning or budgeting cycle using datadriven insights. considers external factors and industry trends.x000d ensures policies and standards for capacity management are fit for purpose, current and correctly implemented. drives continuous improvement in capacity management practices, focusing on costeffectiveness and resource optimisation.x000d reviews new business proposals and provides specialist advice on capacity issues.</t>
+          <t>ensuring service components have the capacity and performance to meet current and planned business needs. leads the development and implementation of policy and strategies for capacity and performance management to meet business needs. leads capacity modelling and forecasting over the organisations planning or budgeting cycle using datadriven insights. considers external factors and industry trends. ensures policies and standards for capacity management are fit for purpose, current and correctly implemented. drives continuous improvement in capacity management practices, focusing on costeffectiveness and resource optimisation. reviews new business proposals and provides specialist advice on capacity issues.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. follows agreed procedures to identify, register and categorise incidents.x000d uses provided tools and technologies to support the incident management process.x000d collects information as instructed to assist in incident resolution and allocates incidents as directed.x000d assists in monitoring incident queues and escalates issues according to procedures.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. follows agreed procedures to identify, register and categorise incidents. uses provided tools and technologies to support the incident management process. collects information as instructed to assist in incident resolution and allocates incidents as directed. assists in monitoring incident queues and escalates issues according to procedures.</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. provides first line investigation and gathers information to enable incident resolution and allocate incidents. x000d gathers information to enable incident resolution and allocates incidents according to established procedures. escalates incidents as necessary. x000d advises relevant people of actions taken. communicates with users and stakeholders to provide updates on incident status. x000d assists in maintaining records and documentation related to incidents.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. provides first line investigation and gathers information to enable incident resolution and allocate incidents. gathers information to enable incident resolution and allocates incidents according to established procedures. escalates incidents as necessary. advises relevant people of actions taken. communicates with users and stakeholders to provide updates on incident status. assists in maintaining records and documentation related to incidents.</t>
         </is>
       </c>
     </row>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. prioritises and diagnoses incidents applying agreed procedures and tools.x000d investigates causes of incidents and seeks resolution. x000d escalates unresolved incidents to higher levels or specialist teams. coordinates with stakeholders to ensure timely resolution.x000d facilitates recovery, following resolution of incidents. documents, communicates outcomes and closes resolved incidents.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. prioritises and diagnoses incidents applying agreed procedures and tools. investigates causes of incidents and seeks resolution. escalates unresolved incidents to higher levels or specialist teams. coordinates with stakeholders to ensure timely resolution. facilitates recovery, following resolution of incidents. documents, communicates outcomes and closes resolved incidents.</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. monitors and manages incident queues to ensure incidents are handled according to procedures and service levels. x000d contributes to developing, testing and improving incident management procedures. uses analytics tools to track trends.x000d ensures resolved incidents are properly documented and closed. x000d supports team members in the correct use of the incident process.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. monitors and manages incident queues to ensure incidents are handled according to procedures and service levels. contributes to developing, testing and improving incident management procedures. uses analytics tools to track trends. ensures resolved incidents are properly documented and closed. supports team members in the correct use of the incident process.</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. responsible for the operation of the incident management process. x000d manages incident communications, ensuring al parties are aware of incidents and their role in the process. x000d leads the review of major incidents and informs service owners of outcomes. ensures incident resolution within service targets. analyses metrics and reports on the performance of the incident management process. x000d develops, maintains and tests incident management policy and procedures. ensures compliance with regulatory requirements.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. responsible for the operation of the incident management process. manages incident communications, ensuring al parties are aware of incidents and their role in the process. leads the review of major incidents and informs service owners of outcomes. ensures incident resolution within service targets. analyses metrics and reports on the performance of the incident management process. develops, maintains and tests incident management policy and procedures. ensures compliance with regulatory requirements.</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. shapes and directs the organisations incident management strategy. establishes policies and standards for incident management aligned with organisational goals.x000d provides leadership during major incidents, coordinating crossfunctional teams and external partners. makes highlevel decisions to minimise impact and ensure swift recovery.x000d leads the development of organisational capabilities for incident management.x000d promotes organisational collaboration and ensures that incident management processes are understood and adopted across the organisation.</t>
+          <t>coordinating responses to a diverse range of incidents to minimise negative impacts and quickly restore services. shapes and directs the organisations incident management strategy. establishes policies and standards for incident management aligned with organisational goals. provides leadership during major incidents, coordinating crossfunctional teams and external partners. makes highlevel decisions to minimise impact and ensure swift recovery. leads the development of organisational capabilities for incident management. promotes organisational collaboration and ensures that incident management processes are understood and adopted across the organisation.</t>
         </is>
       </c>
     </row>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. assists with problem management tasks under routine supervision.x000d helps document problems and maintain relevant records.x000d assists in detecting, logging, classifying, and prioritising problems in systems, processes, and services.</t>
+          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. assists with problem management tasks under routine supervision. helps document problems and maintain relevant records. assists in detecting, logging, classifying, and prioritising problems in systems, processes, and services.</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13767,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. investigates problems in systems, processes and services. x000d contributes to the implementation of agreed remedies and preventative measures.</t>
+          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. investigates problems in systems, processes and services. contributes to the implementation of agreed remedies and preventative measures.</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. initiates and monitors actions to investigate and resolve problems in systems, processes and services.x000d determines problem fixes and remedies. x000d collaborates with others to implement agreed remedies and preventative measures.x000d supports analysis of patterns and trends to improve problem management processes.</t>
+          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. initiates and monitors actions to investigate and resolve problems in systems, processes and services. determines problem fixes and remedies. collaborates with others to implement agreed remedies and preventative measures. supports analysis of patterns and trends to improve problem management processes.</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. ensures appropriate action is taken to anticipate, investigate and resolve problems in systems and services. x000d ensures problems are fully documented within the relevant reporting systems. x000d enables development of problem solutions. coordinates the implementation of agreed remedies and preventative measures.x000d analyses patterns and trends and improves problem management processes.</t>
+          <t>managing the lifecycle of all problems that have occurred or could occur in delivering a service. ensures appropriate action is taken to anticipate, investigate and resolve problems in systems and services. ensures problems are fully documented within the relevant reporting systems. enables development of problem solutions. coordinates the implementation of agreed remedies and preventative measures. analyses patterns and trends and improves problem management processes.</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. administers, tracks, logs, reports on change requests, using appropriate tools, techniques and processes.x000d provides assistance to implement standard lowrisk changes, in accordance with defined change control procedures.</t>
+          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. administers, tracks, logs, reports on change requests, using appropriate tools, techniques and processes. provides assistance to implement standard lowrisk changes, in accordance with defined change control procedures.</t>
         </is>
       </c>
     </row>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. develops, documents and implements changes based on requests for change. x000d applies change control processes and procedures. x000d applies tools, techniques and processes to manage and report on change requests.</t>
+          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. develops, documents and implements changes based on requests for change. applies change control processes and procedures. applies tools, techniques and processes to manage and report on change requests.</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. assesses, analyses, develops, documents and implements changes based on requests for change. x000d ensures operational processes and procedures are in place for effective change control. x000d develops, configures and maintains tools to manage and report on the lifecycle of change requests. x000d identifies problems and issues and recommend corrective actions.</t>
+          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. assesses, analyses, develops, documents and implements changes based on requests for change. ensures operational processes and procedures are in place for effective change control. develops, configures and maintains tools to manage and report on the lifecycle of change requests. identifies problems and issues and recommend corrective actions.</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. leads the assessment, analysis, development, documentation and implementation of changes.x000d develops implementation plans for complex requests for change. x000d reviews proposed implementations and evaluates the risks to the integrity of the product and service environment. ensures appropriate change approval is applied to changes. x000d reviews the effectiveness of change implementation. identifies, evaluates and manages the adoption of appropriate tools, techniques and processes for change control.</t>
+          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. leads the assessment, analysis, development, documentation and implementation of changes. develops implementation plans for complex requests for change. reviews proposed implementations and evaluates the risks to the integrity of the product and service environment. ensures appropriate change approval is applied to changes. reviews the effectiveness of change implementation. identifies, evaluates and manages the adoption of appropriate tools, techniques and processes for change control.</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. sets the organisations policy for the management of change in live services and test environments.x000d ensures effective control and treatment of risk. x000d leads the development of new and improved practices for change control. x000d measures and monitors adherence to standards and ensures consistent execution of the process across the organisation.</t>
+          <t>assessing risks associated with proposed changes and ensuring changes to products, services or systems are controlled and coordinated. sets the organisations policy for the management of change in live services and test environments. ensures effective control and treatment of risk. leads the development of new and improved practices for change control. measures and monitors adherence to standards and ensures consistent execution of the process across the organisation.</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. uses agreed procedures to create and maintain an accurate register of assets. x000d performs activities related to the administration of assets. x000d produces routine reports to assist asset management activities and decisionmaking.</t>
+          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. uses agreed procedures to create and maintain an accurate register of assets. performs activities related to the administration of assets. produces routine reports to assist asset management activities and decisionmaking.</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. applies tools, techniques and processes to create and maintain an accurate asset register. x000d produces reports and analysis to support asset management activities and aid decisionmaking.</t>
+          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. applies tools, techniques and processes to create and maintain an accurate asset register. produces reports and analysis to support asset management activities and aid decisionmaking.</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. controls assets in one or more significant areas ensuring administration of full lifecycle of assets is carried out. x000d produces and analyses registers and histories of authorised assets and verifies that all of these assets are in a known state and location. x000d acts to highlight and resolve potential instances of unauthorised assets.</t>
+          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. controls assets in one or more significant areas ensuring administration of full lifecycle of assets is carried out. produces and analyses registers and histories of authorised assets and verifies that all of these assets are in a known state and location. acts to highlight and resolve potential instances of unauthorised assets.</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. manages and maintains the service compliance of it and service assets in line with business and regulatory requirements. x000d identifies, assesses and communicates associated risks. x000d ensures asset controllers, infrastructure teams and the business coordinate and optimise value, maintain control and maintain appropriate legal compliance.</t>
+          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. manages and maintains the service compliance of it and service assets in line with business and regulatory requirements. identifies, assesses and communicates associated risks. ensures asset controllers, infrastructure teams and the business coordinate and optimise value, maintain control and maintain appropriate legal compliance.</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. sets the strategy for asset management across the organisation. x000d communicates the policy, governance, scope and roles involved in asset management. x000d promotes awareness of and commitment to the role of asset management in the continuing economic and effective provision of services. provides information and advice on complex asset management issues.x000d initiates impact assessment arising from decisions to obtain, change or continue the possession or use of an asset, system or service.</t>
+          <t>managing the full lifecycle of assets from acquisition, operation, maintenance to disposal. sets the strategy for asset management across the organisation. communicates the policy, governance, scope and roles involved in asset management. promotes awareness of and commitment to the role of asset management in the continuing economic and effective provision of services. provides information and advice on complex asset management issues. initiates impact assessment arising from decisions to obtain, change or continue the possession or use of an asset, system or service.</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. applies standard service acceptance criteria and participates in service acceptance testing. x000d collaborates with delivery teams to ensure service deliverables meet the required standards. x000d documents and communicates the outcomes of service acceptance activities. x000d identifies and reports issues or nonconformances, assisting with their resolution.</t>
+          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. applies standard service acceptance criteria and participates in service acceptance testing. collaborates with delivery teams to ensure service deliverables meet the required standards. documents and communicates the outcomes of service acceptance activities. identifies and reports issues or nonconformances, assisting with their resolution.</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. engages with delivery teams to confirm that products developed meet the service acceptance criteria and are to the required standard. x000d assesses risks related to service acceptance and suggests actions to address identified risks. x000d facilitates the communication of acceptance criteria across teams to maintain alignment and consistency throughout the process.x000d provides input into change control processes.</t>
+          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. engages with delivery teams to confirm that products developed meet the service acceptance criteria and are to the required standard. assesses risks related to service acceptance and suggests actions to address identified risks. facilitates the communication of acceptance criteria across teams to maintain alignment and consistency throughout the process. provides input into change control processes.</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. engages with delivery teams to ensure correct products are produced in a timely fashion. x000d leads the assessment of complex or critical service deliverables, ensuring they meet both current and future operational needs. leads comprehensive risk evaluations identifying and prioritising risks that may impact service readiness. x000d provides authoritative advice on service acceptance practices. provides recommendations for enhancing service readiness and improving service acceptance processes.x000d evaluates the quality of project outputs against agreed service acceptance criteria.</t>
+          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. engages with delivery teams to ensure correct products are produced in a timely fashion. leads the assessment of complex or critical service deliverables, ensuring they meet both current and future operational needs. leads comprehensive risk evaluations identifying and prioritising risks that may impact service readiness. provides authoritative advice on service acceptance practices. provides recommendations for enhancing service readiness and improving service acceptance processes. evaluates the quality of project outputs against agreed service acceptance criteria.</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. develops the organisations approach for service acceptance, owns the transition process and defines the acceptance criteria for service transitions.x000d ensures risk management activities are aligned with the organisations broader risk management framework. promotes and monitors project quality outputs to ensure they are fit for purpose and fit for use within operational services. x000d actively engages with stakeholders to promote awareness and compliance with service transition quality plans and processes. x000d agrees the service acceptance criteria with delivery teams.</t>
+          <t>managing the process to obtain formal confirmation that service acceptance criteria have been met. develops the organisations approach for service acceptance, owns the transition process and defines the acceptance criteria for service transitions. ensures risk management activities are aligned with the organisations broader risk management framework. promotes and monitors project quality outputs to ensure they are fit for purpose and fit for use within operational services. actively engages with stakeholders to promote awareness and compliance with service transition quality plans and processes. agrees the service acceptance criteria with delivery teams.</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. performs simple security administration tasks. x000d maintains relevant records and documentation, contributing to overall data integrity.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. performs simple security administration tasks. maintains relevant records and documentation, contributing to overall data integrity.</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. receives and responds to routine requests for security support. maintains records and effectively communicates actions taken.x000d assists in the investigation and resolution of issues relating to security systems using basic diagnostic tools and techniques.x000d documents incident and event information and generates reports on exceptions and security events. contributes to management reporting processes.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. receives and responds to routine requests for security support. maintains records and effectively communicates actions taken. assists in the investigation and resolution of issues relating to security systems using basic diagnostic tools and techniques. documents incident and event information and generates reports on exceptions and security events. contributes to management reporting processes.</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. investigates minor security breaches using established procedures, incorporating analytical tools and techniques.x000d performs nonstandard operational security tasks adapting to evolving technologies and threat landscapes.x000d addresses and resolves a variety of security events to maintain system integrity and operational continuity.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. investigates minor security breaches using established procedures, incorporating analytical tools and techniques. performs nonstandard operational security tasks adapting to evolving technologies and threat landscapes. addresses and resolves a variety of security events to maintain system integrity and operational continuity.</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. maintains and optimises operational security processes. checks that all requests for support are dealt with according to established protocols, including for cloudbased and automated systems.x000d provides advice on implementing and managing physical, procedural and technical security encompassing both physical and digital assets.x000d investigates security breaches in accordance with established procedures using advanced tools and techniques and recommends necessary corrective actions. x000d enables effective implementation of recommended security measures and monitors their performance.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. maintains and optimises operational security processes. checks that all requests for support are dealt with according to established protocols, including for cloudbased and automated systems. provides advice on implementing and managing physical, procedural and technical security encompassing both physical and digital assets. investigates security breaches in accordance with established procedures using advanced tools and techniques and recommends necessary corrective actions. enables effective implementation of recommended security measures and monitors their performance.</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. oversees security operations procedures, ensuring adherence and effectiveness, including cloud security practices and automated threat responses.x000d reviews actual or potential security breaches and vulnerabilities and ensures they are promptly and thoroughly investigated. recommends actions and appropriate control improvements.x000d ensures the integrity and completeness of security records, ensuring timely support and adherence to established procedures.x000d contributes to the creation and maintenance of security policies, standards and procedures integrating new compliance requirements and technology advances.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. oversees security operations procedures, ensuring adherence and effectiveness, including cloud security practices and automated threat responses. reviews actual or potential security breaches and vulnerabilities and ensures they are promptly and thoroughly investigated. recommends actions and appropriate control improvements. ensures the integrity and completeness of security records, ensuring timely support and adherence to established procedures. contributes to the creation and maintenance of security policies, standards and procedures integrating new compliance requirements and technology advances.</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. develops comprehensive policies, standards, processes and guidelines for organisational security across the entire digital landscape.x000d ensures the ongoing relevance and effective implementation of security policies and standards, adapting to emerging technologies and threats.x000d reviews and advises on security aspects of new business initiatives considering implications in the evolving digital landscape.x000d leads strategic planning for security operations, integrating advanced threat intelligence and automation to enhance organisational resilience.</t>
+          <t>manages and administers security measures, using tools and intelligence to protect assets, ensuring compliance and operational integrity. develops comprehensive policies, standards, processes and guidelines for organisational security across the entire digital landscape. ensures the ongoing relevance and effective implementation of security policies and standards, adapting to emerging technologies and threats. reviews and advises on security aspects of new business initiatives considering implications in the evolving digital landscape. leads strategic planning for security operations, integrating advanced threat intelligence and automation to enhance organisational resilience.</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. performs basic identity and access management tasks, including user account lifecycle management, under supervision.x000d maintains accurate records and follows established identity and access management protocols.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. performs basic identity and access management tasks, including user account lifecycle management, under supervision. maintains accurate records and follows established identity and access management protocols.</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. provides assistance for identity and access management operations, including automated role allocation and access control management.x000d engages in user identity lifecycle management, including account creation and deletion.x000d facilitates operation of identity and access management tools and selfservice portals.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. provides assistance for identity and access management operations, including automated role allocation and access control management. engages in user identity lifecycle management, including account creation and deletion. facilitates operation of identity and access management tools and selfservice portals.</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. administers standard identity and access management services, implementing policies and resolving related issues. x000d manages monitoring, audits and logging for identity and access management systems. investigates minor security breaches in accordance with established procedures related to identity and access management.x000d assists users in defining their access rights and privileges. designs and implements simple identity and access management solutions, enhancing user access security. contributes to the enhancement and optimisation of existing identity and access management processes and systems.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. administers standard identity and access management services, implementing policies and resolving related issues. manages monitoring, audits and logging for identity and access management systems. investigates minor security breaches in accordance with established procedures related to identity and access management. assists users in defining their access rights and privileges. designs and implements simple identity and access management solutions, enhancing user access security. contributes to the enhancement and optimisation of existing identity and access management processes and systems.</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. designs and implements complex identity and access management solutions, focusing on automated access control and role allocation. x000d oversees the integration of identity and access management services with new technologies.x000d provides specialised support for complex identity and access management operations and supports implementation of policies and standards.x000d collaborates with stakeholders to align identity and access management with business objectives and emerging security trends.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. designs and implements complex identity and access management solutions, focusing on automated access control and role allocation. oversees the integration of identity and access management services with new technologies. provides specialised support for complex identity and access management operations and supports implementation of policies and standards. collaborates with stakeholders to align identity and access management with business objectives and emerging security trends.</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. offers authoritative advice on identity and access management, ensuring services align with and support evolving business needs and security protocols.x000d manages largescale identity and access management initiatives and oversees the integration of identity and access management services with new technologies, enhancing security and operational efficiency.x000d leads operational planning for identity and access management, anticipating future trends and preparing the organisation for scalable growth.x000d ensures compliance of identity and access management systems and oversees advanced monitoring and audit processes.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. offers authoritative advice on identity and access management, ensuring services align with and support evolving business needs and security protocols. manages largescale identity and access management initiatives and oversees the integration of identity and access management services with new technologies, enhancing security and operational efficiency. leads operational planning for identity and access management, anticipating future trends and preparing the organisation for scalable growth. ensures compliance of identity and access management systems and oversees advanced monitoring and audit processes.</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14535,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>manages identity verification and access permissions within organisational systems and environments. shapes and defines organisationwide identity and access management policies, ensuring alignment with business strategies and security requirements.x000d champions good practices, advocating for robust and innovative identity and access management solutions across the organisation.x000d influences and guides organisational governance, integrating emerging technologies and regulatory compliance into identity and access management strategies.x000d reviews and advises on identity and access management aspects and implications of new business initiatives.</t>
+          <t>manages identity verification and access permissions within organisational systems and environments. shapes and defines organisationwide identity and access management policies, ensuring alignment with business strategies and security requirements. champions good practices, advocating for robust and innovative identity and access management solutions across the organisation. influences and guides organisational governance, integrating emerging technologies and regulatory compliance into identity and access management strategies. reviews and advises on identity and access management aspects and implications of new business initiatives.</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. undertakes lowcomplexity routine vulnerability assessments using automated and semiautomated tools. x000d escalates issues where appropriate.x000d contributes to documenting the scope and evaluating the results of vulnerability assessments.</t>
+          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. undertakes lowcomplexity routine vulnerability assessments using automated and semiautomated tools. escalates issues where appropriate. contributes to documenting the scope and evaluating the results of vulnerability assessments.</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. follows standard approaches to perform basic vulnerability assessments for small information systems. x000d supports creation of catalogues of information and technology assets for vulnerability assessment.</t>
+          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. follows standard approaches to perform basic vulnerability assessments for small information systems. supports creation of catalogues of information and technology assets for vulnerability assessment.</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. collates and analyses catalogues of information and technology assets for vulnerability assessment. x000d performs vulnerability assessments and business impact analysis for medium complexity information systems. x000d contributes to selection and deployment of vulnerability assessment tools and techniques.</t>
+          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. collates and analyses catalogues of information and technology assets for vulnerability assessment. performs vulnerability assessments and business impact analysis for medium complexity information systems. contributes to selection and deployment of vulnerability assessment tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. plans and manages vulnerability assessment activities within the organisation.x000d evaluates, selects and reviews vulnerability assessment tools and techniques.x000d provides expert advice and guidance to support the adoption of agreed approaches.x000d obtains and acts on vulnerability information and conducts security risk assessments, business impact analysis and accreditation on complex information systems.</t>
+          <t>identifying and classifying security vulnerabilities in networks, systems and applications and mitigating or eliminating their impact. plans and manages vulnerability assessment activities within the organisation. evaluates, selects and reviews vulnerability assessment tools and techniques. provides expert advice and guidance to support the adoption of agreed approaches. obtains and acts on vulnerability information and conducts security risk assessments, business impact analysis and accreditation on complex information systems.</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>recovering and investigating material found in digital devices. assists with digital forensic investigations under routine supervision. x000d supports the recovery of damaged, deleted or hidden data from digital devices.x000d helps collect and preserve digital information and evidence according to established protocols.</t>
+          <t>recovering and investigating material found in digital devices. assists with digital forensic investigations under routine supervision. supports the recovery of damaged, deleted or hidden data from digital devices. helps collect and preserve digital information and evidence according to established protocols.</t>
         </is>
       </c>
     </row>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>recovering and investigating material found in digital devices. applies standard forensic tools and techniques to examine digital devices. x000d recovers and analyses damaged, deleted or hidden data from various digital sources and devices. x000d maintains the integrity of digital evidence and ensures its collection adheres to legal admissibility standards.</t>
+          <t>recovering and investigating material found in digital devices. applies standard forensic tools and techniques to examine digital devices. recovers and analyses damaged, deleted or hidden data from various digital sources and devices. maintains the integrity of digital evidence and ensures its collection adheres to legal admissibility standards.</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>recovering and investigating material found in digital devices. designs and executes complex digital forensic examinations. x000d specifies requirements for specialised forensic tools and resources. provides guidance on advanced data recovery techniques and artefact analysis. x000d processes and analyses digital evidence in line with organisational policies and industry standards. develops procedures for handling emerging technologies in forensic contexts.x000d contributes to forensic reports detailing technical findings.</t>
+          <t>recovering and investigating material found in digital devices. designs and executes complex digital forensic examinations. specifies requirements for specialised forensic tools and resources. provides guidance on advanced data recovery techniques and artefact analysis. processes and analyses digital evidence in line with organisational policies and industry standards. develops procedures for handling emerging technologies in forensic contexts. contributes to forensic reports detailing technical findings.</t>
         </is>
       </c>
     </row>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>recovering and investigating material found in digital devices. leads investigations to correctly gather, analyse and present findings, including digital evidence, to both business and legal audiences.x000d collates conclusions and recommendations and presents forensic findings to stakeholders.x000d plans and manages digital forensics activities within the organisation. provides expert advice on digital forensics.x000d contributes to the development of digital forensics policies, standards and guidelines. evaluates and selects digital forensics tools and techniques.</t>
+          <t>recovering and investigating material found in digital devices. leads investigations to correctly gather, analyse and present findings, including digital evidence, to both business and legal audiences. collates conclusions and recommendations and presents forensic findings to stakeholders. plans and manages digital forensics activities within the organisation. provides expert advice on digital forensics. contributes to the development of digital forensics policies, standards and guidelines. evaluates and selects digital forensics tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -14781,7 +14781,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>recovering and investigating material found in digital devices. plans and leads the organisations approach to digital forensics.x000d sets policies, standards and guidelines for how the organisation conducts digital forensic investigations.x000d leads and manages high risk, large or wideranging digital forensics investigations engaging additional specialists if required.x000d authorises the release of formal forensic reports. engages with external stakeholders on forensic matters.</t>
+          <t>recovering and investigating material found in digital devices. plans and leads the organisations approach to digital forensics. sets policies, standards and guidelines for how the organisation conducts digital forensic investigations. leads and manages high risk, large or wideranging digital forensics investigations engaging additional specialists if required. authorises the release of formal forensic reports. engages with external stakeholders on forensic matters.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. assists in cybercrime investigations under routine supervision. x000d supports the collection of evidence related to cybercrime investigations. x000d participates in monitoring suspicious activities.x000d helps maintain evidence integrity and assists in preliminary interviews. follows established protocols and guidelines.</t>
+          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. assists in cybercrime investigations under routine supervision. supports the collection of evidence related to cybercrime investigations. participates in monitoring suspicious activities. helps maintain evidence integrity and assists in preliminary interviews. follows established protocols and guidelines.</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. conducts cybercrime investigations using standard procedures. x000d collects and preserves various forms of evidence in cybercrime cases. assesses credibility and checks for compliance with relevant investigative standards. x000d analyses basic cyber threats and incidents, and prepares investigative reports. identifies incidents that may have legal implications. x000d conducts interviews and assists in interrogations.</t>
+          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. conducts cybercrime investigations using standard procedures. collects and preserves various forms of evidence in cybercrime cases. assesses credibility and checks for compliance with relevant investigative standards. analyses basic cyber threats and incidents, and prepares investigative reports. identifies incidents that may have legal implications. conducts interviews and assists in interrogations.</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. oversees midlevel investigations, coordinating evidence collection and forensic analyses.x000d assesses target vulnerabilities and operational impacts of cyber incidents.x000d provides comprehensive reports and expert analysis for stakeholders. x000d conducts interviews and interrogations, identifying potential legal implications and collaborating with legal professionals.</t>
+          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. oversees midlevel investigations, coordinating evidence collection and forensic analyses. assesses target vulnerabilities and operational impacts of cyber incidents. provides comprehensive reports and expert analysis for stakeholders. conducts interviews and interrogations, identifying potential legal implications and collaborating with legal professionals.</t>
         </is>
       </c>
     </row>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. manages complex cybercrime investigations, overseeing all stages from detection to resolution. x000d evaluates incidents involving advanced threats or significant breaches. x000d develops and implements procedures for evidence handling and documentation. collaborates with legal teams to ensure evidence supports potential legal proceedings. x000d leads the development of response strategies, assessing vulnerabilities and operational capabilities. oversees the implementation of tools and automation to enhance investigative processes.</t>
+          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. manages complex cybercrime investigations, overseeing all stages from detection to resolution. evaluates incidents involving advanced threats or significant breaches. develops and implements procedures for evidence handling and documentation. collaborates with legal teams to ensure evidence supports potential legal proceedings. leads the development of response strategies, assessing vulnerabilities and operational capabilities. oversees the implementation of tools and automation to enhance investigative processes.</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. defines the organisational strategy for cybercrime investigations.x000d establishes policies and standards for handling various forms of evidence in cybercrime cases, including the adoption and integration of tools and automation to improve efficiency and accuracy.x000d oversees highrisk or sensitive investigations, managing crossdisciplinary teams. conducts highlevel interviews and interrogations, providing strategic insights on cybersecurity threats and vulnerabilities.x000d engages with external stakeholders, including regulatory bodies and legal entities, to ensure compliance with legal and ethical standards.</t>
+          <t>investigates cybercrimes, collects evidence, determines incident impacts and collaborates with legal teams to protect digital assets. defines the organisational strategy for cybercrime investigations. establishes policies and standards for handling various forms of evidence in cybercrime cases, including the adoption and integration of tools and automation to improve efficiency and accuracy. oversees highrisk or sensitive investigations, managing crossdisciplinary teams. conducts highlevel interviews and interrogations, providing strategic insights on cybersecurity threats and vulnerabilities. engages with external stakeholders, including regulatory bodies and legal entities, to ensure compliance with legal and ethical standards.</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. supports offensive cyber operations under supervision. x000d assists in creating electronic target folders based on provided intelligence. x000d participates in basic operational tasks, following established security protocols.x000d assists in documenting operations and outcomes, contributing to postoperation reviews.</t>
+          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. supports offensive cyber operations under supervision. assists in creating electronic target folders based on provided intelligence. participates in basic operational tasks, following established security protocols. assists in documenting operations and outcomes, contributing to postoperation reviews.</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. carries out specific tasks within offensive cyber operations, aligning operational tasks with broader objectives.x000d supports the creation and maintenance of electronic target folders, gathering and verifying target information. x000d assists in the execution of operations, maintaining operational security. x000d prepares detailed reports and participates in postoperation analysis.</t>
+          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. carries out specific tasks within offensive cyber operations, aligning operational tasks with broader objectives. supports the creation and maintenance of electronic target folders, gathering and verifying target information. assists in the execution of operations, maintaining operational security. prepares detailed reports and participates in postoperation analysis.</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. responsible for the execution of offensive cyber operations, including detailed planning and target selection. x000d manages the development and updating of electronic target folders, ensuring accuracy and comprehensiveness. coordinates operational teams, adapting actions based on realtime intelligence. x000d ensures compliance with legal and ethical standards during operations. evaluates collateral damage from targeting activities, including potential second and thirdorder effects.x000d conducts postoperation analyses, assessing impact and recommending improvements.</t>
+          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. responsible for the execution of offensive cyber operations, including detailed planning and target selection. manages the development and updating of electronic target folders, ensuring accuracy and comprehensiveness. coordinates operational teams, adapting actions based on realtime intelligence. ensures compliance with legal and ethical standards during operations. evaluates collateral damage from targeting activities, including potential second and thirdorder effects. conducts postoperation analyses, assessing impact and recommending improvements.</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. leads complex and highrisk offensive cyber operations, overseeing planning, execution and analysis. x000d integrates intelligence with operational planning, aligning all actions with organisational objectives. evaluates the intelligence cost against the operational benefit of engaging targets. assesses potential collateral damage, including second and thirdorder effects. x000d manages the creation and tactical use of electronic target folders, coordinating with external entities as necessary. x000d develops policies and standards for offensive operations, ensuring legal and ethical compliance. provides expert guidance on offensive capabilities and operational tactics.</t>
+          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. leads complex and highrisk offensive cyber operations, overseeing planning, execution and analysis. integrates intelligence with operational planning, aligning all actions with organisational objectives. evaluates the intelligence cost against the operational benefit of engaging targets. assesses potential collateral damage, including second and thirdorder effects. manages the creation and tactical use of electronic target folders, coordinating with external entities as necessary. develops policies and standards for offensive operations, ensuring legal and ethical compliance. provides expert guidance on offensive capabilities and operational tactics.</t>
         </is>
       </c>
     </row>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. sets the strategic direction and policies for offensive cyber operations within the organisation. x000d leads the development and deployment of advanced operational techniques and capabilities. oversees critical and sensitive operations, ensuring alignment with national or organisational security goals. x000d collaborates with senior leadership and external entities on offensive operations. evaluates intelligence cost versus operational benefit at a strategic level. assesses and mitigates potential collateral damage.x000d evaluates and refines the effectiveness of offensive operations, providing recommendations for future initiatives.</t>
+          <t>plans, executes and manages offensive cybersecurity operations, including target selection, electronic target folders and postoperation analysis. sets the strategic direction and policies for offensive cyber operations within the organisation. leads the development and deployment of advanced operational techniques and capabilities. oversees critical and sensitive operations, ensuring alignment with national or organisational security goals. collaborates with senior leadership and external entities on offensive operations. evaluates intelligence cost versus operational benefit at a strategic level. assesses and mitigates potential collateral damage. evaluates and refines the effectiveness of offensive operations, providing recommendations for future initiatives.</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. assists with penetration testing tasks under routine supervision.x000d supports the execution of standard penetration tests on systems, networks and applications.x000d helps document and report on test results, findings and potential security risks.</t>
+          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. assists with penetration testing tasks under routine supervision. supports the execution of standard penetration tests on systems, networks and applications. helps document and report on test results, findings and potential security risks.</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. follows standard approaches to design and execute penetration testing activities.x000d researches and investigates attack techniques and recommends ways to defend against them. x000d analyses and reports on penetration testing activities, results, issues and risks.</t>
+          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. follows standard approaches to design and execute penetration testing activities. researches and investigates attack techniques and recommends ways to defend against them. analyses and reports on penetration testing activities, results, issues and risks.</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. selects appropriate testing approaches using indepth technical analysis of risks and typical vulnerabilities. x000d produces test scripts, materials and test packs and tests new and existing networks, systems or applications. provides advice on penetration testing to support others.x000d records and analyses actions and results and modifies tests if necessary. x000d provides reports on progress, anomalies, risks and issues associated with the overall project.</t>
+          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. selects appropriate testing approaches using indepth technical analysis of risks and typical vulnerabilities. produces test scripts, materials and test packs and tests new and existing networks, systems or applications. provides advice on penetration testing to support others. records and analyses actions and results and modifies tests if necessary. provides reports on progress, anomalies, risks and issues associated with the overall project.</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. plans and drives penetration testing within a defined area of business activity. x000d delivers objective insights into the existence of vulnerabilities, the effectiveness of defences and mitigating controls. x000d takes responsibility for the integrity of testing activities and coordinates the execution of these activities. provides authoritative advice and guidance on all aspects of penetration testing. x000d identifies needs and implements new approaches for penetration testing. contributes to security testing standards.</t>
+          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. plans and drives penetration testing within a defined area of business activity. delivers objective insights into the existence of vulnerabilities, the effectiveness of defences and mitigating controls. takes responsibility for the integrity of testing activities and coordinates the execution of these activities. provides authoritative advice and guidance on all aspects of penetration testing. identifies needs and implements new approaches for penetration testing. contributes to security testing standards.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. determines penetration testing policy and owns the supporting processes. x000d manages all penetration testing activities within the organisation. assesses and advises on the practicality of testing process alternatives. x000d establishes capability for continual improvement and invention in penetration testing and leads the implementation of new approaches. x000d assesses suppliers development and testing capabilities. manages client relationships with respect to penetration testing.</t>
+          <t>testing the effectiveness of security controls by emulating the tools and techniques of likely attackers. determines penetration testing policy and owns the supporting processes. manages all penetration testing activities within the organisation. assesses and advises on the practicality of testing process alternatives. establishes capability for continual improvement and invention in penetration testing and leads the implementation of new approaches. assesses suppliers development and testing capabilities. manages client relationships with respect to penetration testing.</t>
         </is>
       </c>
     </row>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>planning, implementing and managing the full lifecycle of organisational records. follows detailed guidance to acknowledge receipt of records, including the capture of essential metadata.x000d delivers digital and physical records in line with agreed procedures.</t>
+          <t>planning, implementing and managing the full lifecycle of organisational records. follows detailed guidance to acknowledge receipt of records, including the capture of essential metadata. delivers digital and physical records in line with agreed procedures.</t>
         </is>
       </c>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>planning, implementing and managing the full lifecycle of organisational records. assists in the collection, delivery and retention of records. x000d identifies and applies appropriate metadata.x000d uses established methods to transform records between formats or media, following organisational policies and procedures. identifies and reports potential risks or issues related to information handling and security.x000d performs administrative tasks to maintain accessibility, retrievability, integrity, security and protection of records.</t>
+          <t>planning, implementing and managing the full lifecycle of organisational records. assists in the collection, delivery and retention of records. identifies and applies appropriate metadata. uses established methods to transform records between formats or media, following organisational policies and procedures. identifies and reports potential risks or issues related to information handling and security. performs administrative tasks to maintain accessibility, retrievability, integrity, security and protection of records.</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>planning, implementing and managing the full lifecycle of organisational records. maintains key metadata for records, including ownership and category information.x000d configures routine controls to restrict record operations to approved actions only. conducts routine searches for records required to support authorised requests. supports users in finding and accessing records.x000d uses ethical and reliable methods to transform data between formats or media, following organisational policies and being aware of potential issues when handling information.x000d transforms data between formats or media using ethical and reliable methods. follows organisational policies and actively identifies potential risks in information handling.</t>
+          <t>planning, implementing and managing the full lifecycle of organisational records. maintains key metadata for records, including ownership and category information. configures routine controls to restrict record operations to approved actions only. conducts routine searches for records required to support authorised requests. supports users in finding and accessing records. uses ethical and reliable methods to transform data between formats or media, following organisational policies and being aware of potential issues when handling information. transforms data between formats or media using ethical and reliable methods. follows organisational policies and actively identifies potential risks in information handling.</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>planning, implementing and managing the full lifecycle of organisational records. supports the implementation of records management policies and practices including the approved disposal of records.x000d conducts complex or sensitive searches for records to address authorised requests.x000d monitors and reports on the implementation of effective controls for records management including metadata and access controls. recommends remediation actions as required.x000d provides advice and guidance to enable appropriate records management practices to be adopted across the organisation.</t>
+          <t>planning, implementing and managing the full lifecycle of organisational records. supports the implementation of records management policies and practices including the approved disposal of records. conducts complex or sensitive searches for records to address authorised requests. monitors and reports on the implementation of effective controls for records management including metadata and access controls. recommends remediation actions as required. provides advice and guidance to enable appropriate records management practices to be adopted across the organisation.</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>planning, implementing and managing the full lifecycle of organisational records. ensures implementation of records management policies covering all aspects of retention and disposal.x000d manages access controls for records, including authorising access and approving the release of potentially sensitive information. conducts and oversees complex record searches, seeking legal guidance when necessary.x000d reviews new change proposals and provides specialist advice on records management. assesses and manages recordsrelated risks.x000d contributes to the development of policy, standards and procedures for compliance with recordsrelated legislation.</t>
+          <t>planning, implementing and managing the full lifecycle of organisational records. ensures implementation of records management policies covering all aspects of retention and disposal. manages access controls for records, including authorising access and approving the release of potentially sensitive information. conducts and oversees complex record searches, seeking legal guidance when necessary. reviews new change proposals and provides specialist advice on records management. assesses and manages recordsrelated risks. contributes to the development of policy, standards and procedures for compliance with recordsrelated legislation.</t>
         </is>
       </c>
     </row>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. accurately assigns classificationslabels to low complexity information under supervision. x000d understands and applies relevant classificationlabelling systems, standards and guidelines. x000d participates in quality assurance activities such as peer review or supervisor checks.</t>
+          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. accurately assigns classificationslabels to low complexity information under supervision. understands and applies relevant classificationlabelling systems, standards and guidelines. participates in quality assurance activities such as peer review or supervisor checks.</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. independently assigns accurate classificationslabels to a broad range of information. x000d interprets complex information and chooses appropriate classificationslabels. x000d participates in team quality improvement initiatives. x000d advises and guides others on classificationlabelling practices.</t>
+          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. independently assigns accurate classificationslabels to a broad range of information. interprets complex information and chooses appropriate classificationslabels. participates in team quality improvement initiatives. advises and guides others on classificationlabelling practices.</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. assigns classificationslabels to highly complex information. x000d performs quality assurance checks on the work of others. investigates and corrects complex classificationlabelling errors. x000d delivers training to team members. x000d contributes to the development of classificationlabelling processes and guidelines.</t>
+          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. assigns classificationslabels to highly complex information. performs quality assurance checks on the work of others. investigates and corrects complex classificationlabelling errors. delivers training to team members. contributes to the development of classificationlabelling processes and guidelines.</t>
         </is>
       </c>
     </row>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. leads team quality assurance and training for information classificationlabelling. x000d develops and implements audit methodologies for assessing classification and labelling accuracy and consistency.x000d collaborates with subject matter experts to improve source information quality. analyses and reports on classificationlabelling quality. x000d contributes to organisational information classificationlabelling strategy.</t>
+          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. leads team quality assurance and training for information classificationlabelling. develops and implements audit methodologies for assessing classification and labelling accuracy and consistency. collaborates with subject matter experts to improve source information quality. analyses and reports on classificationlabelling quality. contributes to organisational information classificationlabelling strategy.</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. sets organisational information classificationlabelling standards, policies and procedures. x000d designs and oversees quality audit programmes. x000d leads strategic interventions to improve information classificationlabelling. x000d engages with industry bodies and collaborates to define and improve standards and working practices.</t>
+          <t>interpreting information and assigning classifications or labels based on domainspecific knowledge, standards and guidelines to enable data analysis and use. sets organisational information classificationlabelling standards, policies and procedures. designs and oversees quality audit programmes. leads strategic interventions to improve information classificationlabelling. engages with industry bodies and collaborates to define and improve standards and working practices.</t>
         </is>
       </c>
     </row>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. executes operational procedures, runs automation scripts and performs routine maintenance and monitoring of databases.x000d adjusts automation tasks as instructed to meet operational standards for databases.x000d reports on database performance, addresses issues directly when possible, or escalates to others for resolution.</t>
+          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. executes operational procedures, runs automation scripts and performs routine maintenance and monitoring of databases. adjusts automation tasks as instructed to meet operational standards for databases. reports on database performance, addresses issues directly when possible, or escalates to others for resolution.</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. provisions, installs, configures and ensures the maintenance and reliability of databases.x000d monitors databases for load, performance and security events. reports metrics and resolves operational issues.x000d executes standard operational procedures, including database backups and restorations.x000d automates routine database administration tasks to specifications using standard scripts and tools.</t>
+          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. provisions, installs, configures and ensures the maintenance and reliability of databases. monitors databases for load, performance and security events. reports metrics and resolves operational issues. executes standard operational procedures, including database backups and restorations. automates routine database administration tasks to specifications using standard scripts and tools.</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. applies technical expertise to maintain and optimise databases, executing updates and employing automation tools. configures tools andor creates scripts to automate database tasks.x000d maintains operational procedures and checks that they are followed, including compliance with security policies. uses database management tools to monitor load and performance statistics. x000d investigates and enables the resolution of database operational and security issues. provides reports and proposals for improvement to stakeholders.x000d contributes to the planning and implementation of database maintenance and updates. implements agreed database changes and maintenance routines.</t>
+          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. applies technical expertise to maintain and optimise databases, executing updates and employing automation tools. configures tools andor creates scripts to automate database tasks. maintains operational procedures and checks that they are followed, including compliance with security policies. uses database management tools to monitor load and performance statistics. investigates and enables the resolution of database operational and security issues. provides reports and proposals for improvement to stakeholders. contributes to the planning and implementation of database maintenance and updates. implements agreed database changes and maintenance routines.</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. provides technical leadership to optimise the performance of databases.x000d drives the adoption of tools and automated processes for effective database management and delivery.x000d oversees the planning, installation, maintenance and acceptance of new and updated database components and databasebased services. ensures alignment to service expectations, security requirements and other quality standards.x000d ensures database operational procedures and documentation are current and effective, tracks and addresses operational issues and reports to stakeholders.</t>
+          <t>installing, configuring, monitoring, maintaining databases and data stores, ensuring performance and security and adapting to evolving technologies. provides technical leadership to optimise the performance of databases. drives the adoption of tools and automated processes for effective database management and delivery. oversees the planning, installation, maintenance and acceptance of new and updated database components and databasebased services. ensures alignment to service expectations, security requirements and other quality standards. ensures database operational procedures and documentation are current and effective, tracks and addresses operational issues and reports to stakeholders.</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. provides operational direction, support and guidance to assigned colleagues. x000d allocates routine tasks or project work, in line with team objectives and individual capabilities. monitors quality and performance against agreed criteria to make learning recommendations or to escalate concerns. x000d coaches colleagues in developing target skills and capabilities in line with team and personal goals. x000d facilitates effective working relationships between team members.</t>
+          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. provides operational direction, support and guidance to assigned colleagues. allocates routine tasks or project work, in line with team objectives and individual capabilities. monitors quality and performance against agreed criteria to make learning recommendations or to escalate concerns. coaches colleagues in developing target skills and capabilities in line with team and personal goals. facilitates effective working relationships between team members.</t>
         </is>
       </c>
     </row>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. forms, maintains and leads workgroups and individuals to achieve organisational objectives. x000d delegates objectives and responsibilities, including people management tasks. sets quality, performance and capability targets aligned with organisational goals. x000d monitors performance and working relationships and provides feedback to address individual issues. encourages skill development in line with team and personal goals. adjusts workload, targets and team capacity to support individual growth. x000d actively participates in formal processes such as recruitment, reward, promotion and disciplinary procedures.</t>
+          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. forms, maintains and leads workgroups and individuals to achieve organisational objectives. delegates objectives and responsibilities, including people management tasks. sets quality, performance and capability targets aligned with organisational goals. monitors performance and working relationships and provides feedback to address individual issues. encourages skill development in line with team and personal goals. adjusts workload, targets and team capacity to support individual growth. actively participates in formal processes such as recruitment, reward, promotion and disciplinary procedures.</t>
         </is>
       </c>
     </row>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. determines and delegates people management and functional management objectives and responsibilities. x000d creates and sets the direction for multiple workgroups to achieve strategic organisational objectives. sets strategy for quality and performance measurement in line with organisational goals. x000d provides a work environment and resources that allow individuals and workgroups to perform their tasks efficiently. x000d leads the implementation of formal organisational processes such as recruitment, reward, promotion and disciplinary procedures.</t>
+          <t>improving organisational performance by developing the performance of individuals and workgroups to meet agreed objectives with measurable results. determines and delegates people management and functional management objectives and responsibilities. creates and sets the direction for multiple workgroups to achieve strategic organisational objectives. sets strategy for quality and performance measurement in line with organisational goals. provides a work environment and resources that allow individuals and workgroups to perform their tasks efficiently. leads the implementation of formal organisational processes such as recruitment, reward, promotion and disciplinary procedures.</t>
         </is>
       </c>
     </row>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. supports assigned coworkers by providing guidance on areas such as organisational contacts, communication channels, processes, job expectations and manager relations.x000d helps individuals navigate areas of uncertainty, offering practical advice and connecting them with the appropriate resources when needed.</t>
+          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. supports assigned coworkers by providing guidance on areas such as organisational contacts, communication channels, processes, job expectations and manager relations. helps individuals navigate areas of uncertainty, offering practical advice and connecting them with the appropriate resources when needed.</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. implements working practices that motivate employees and support their health and wellbeing. x000d provides guidance to individuals on longterm development goals and career opportunities, considering an individuals strengths and preferences. x000d communicates business direction, policy and purpose where these may drive or affect employee engagement. ensures clear communication of delegated tasks and provides sufficient autonomy to motivate and empower individuals.x000d maintains awareness of the physical and emotional welfare of employees, and provides counselling when required.</t>
+          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. implements working practices that motivate employees and support their health and wellbeing. provides guidance to individuals on longterm development goals and career opportunities, considering an individuals strengths and preferences. communicates business direction, policy and purpose where these may drive or affect employee engagement. ensures clear communication of delegated tasks and provides sufficient autonomy to motivate and empower individuals. maintains awareness of the physical and emotional welfare of employees, and provides counselling when required.</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. leads on the implementation of organisational strategies for employee engagement.x000d ensures managers provide a productive working environment that motivates employees and supports their health and wellbeing. x000d initiates productive working practices for remote, virtual and onsite working and ensures the availability of support for employees. x000d communicates and promotes policies for employee health and wellbeing.</t>
+          <t>enhancing employee engagement and ways of working, empowering employees and supporting their health and wellbeing. leads on the implementation of organisational strategies for employee engagement. ensures managers provide a productive working environment that motivates employees and supports their health and wellbeing. initiates productive working practices for remote, virtual and onsite working and ensures the availability of support for employees. communicates and promotes policies for employee health and wellbeing.</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates a series of group activities or workshops in situations of complexity and ambiguity and competing stakeholder needs.x000d designs a structured sequence of meetings, events or workshops to solve complex problems.x000d understands required outcomes and outputs from teams and facilitates the team to deliver these.x000d helps to improve team processes and performance in meetings, events or workshops.</t>
+          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates a series of group activities or workshops in situations of complexity and ambiguity and competing stakeholder needs. designs a structured sequence of meetings, events or workshops to solve complex problems. understands required outcomes and outputs from teams and facilitates the team to deliver these. helps to improve team processes and performance in meetings, events or workshops.</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates workgroups to deliver defined goals and outcomes. x000d provides support, guidance and suggestions to workgroups and teams to learn collaborative problem solving and improve their team performance. creates shared responsibilities and sustainable agreements with the team.x000d implements and improves agreed team principles, practices, processes ceremonies.x000d recognises and works with the strengths and constraints of team dynamics.</t>
+          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates workgroups to deliver defined goals and outcomes. provides support, guidance and suggestions to workgroups and teams to learn collaborative problem solving and improve their team performance. creates shared responsibilities and sustainable agreements with the team. implements and improves agreed team principles, practices, processes ceremonies. recognises and works with the strengths and constraints of team dynamics.</t>
         </is>
       </c>
     </row>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates crossfunctional leadership teams to deliver organisational goals and outcomes.x000d designs repeatable, systematic or ad hoc team processes for decisionmaking, prioritisation and problemsolving at the highest level. guides leadership teams in developing shared responsibilities and making decisions that enable sustainable agreements.x000d asks questions and raises awareness of leadership team performance. provides suggestions to encourage teams to learn and improve how they work together.x000d champions the development of selforganising workgroups across the organisation.</t>
+          <t>supporting workgroups to implement principles and practices for effective teamwork across organisational boundaries and professional specialisms. facilitates crossfunctional leadership teams to deliver organisational goals and outcomes. designs repeatable, systematic or ad hoc team processes for decisionmaking, prioritisation and problemsolving at the highest level. guides leadership teams in developing shared responsibilities and making decisions that enable sustainable agreements. asks questions and raises awareness of leadership team performance. provides suggestions to encourage teams to learn and improve how they work together. champions the development of selforganising workgroups across the organisation.</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. assists practitioners with creating personal development plans. x000d advises on suitable development activities such as specific learning or experience to be gained. x000d monitors practitioners continuing professional development records. x000d ensures achievements and enhanced capabilities are recorded and referenced to personal and organisational objectives.</t>
+          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. assists practitioners with creating personal development plans. advises on suitable development activities such as specific learning or experience to be gained. monitors practitioners continuing professional development records. ensures achievements and enhanced capabilities are recorded and referenced to personal and organisational objectives.</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. determines development needs for a professional practice area. x000d aligns development activities with organisational priorities, learning and development strategies and career pathways. x000d guides practitioners in creating development plans. advises and supports assigned practitioners, ensuring alignment with professional development plans and career opportunities. x000d ensures practitioners record evidence of continuing professional development. contributes to practitioners performance appraisals, when required.</t>
+          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. determines development needs for a professional practice area. aligns development activities with organisational priorities, learning and development strategies and career pathways. guides practitioners in creating development plans. advises and supports assigned practitioners, ensuring alignment with professional development plans and career opportunities. ensures practitioners record evidence of continuing professional development. contributes to practitioners performance appraisals, when required.</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. develops and defines a professional development framework for one or more professional disciplines. x000d determines and maintains organisational development needs in line with business needs and strategic direction. generates development strategies to achieve required change. x000d develops and leads communities of practice, including defining career pathways. x000d defines the approach to identifying suitable individuals to provide career advice and support. monitors progress and evaluates business benefits achieved from continual professional development.</t>
+          <t>facilitating the professional development of individuals in line with their career goals and organisational requirements. develops and defines a professional development framework for one or more professional disciplines. determines and maintains organisational development needs in line with business needs and strategic direction. generates development strategies to achieve required change. develops and leads communities of practice, including defining career pathways. defines the approach to identifying suitable individuals to provide career advice and support. monitors progress and evaluates business benefits achieved from continual professional development.</t>
         </is>
       </c>
     </row>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. gathers, maintains and analyses organisationwide workforce capability data.x000d performs gap analysis to identify workforce strengths and shortfalls with reference to business strategy and specific future needs. x000d contributes to the development of organisationwide workforce plans to meet current and future demand. x000d coordinates and schedules ongoing workforce planning activities. assists in maintaining a skills and capability inventory.</t>
+          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. gathers, maintains and analyses organisationwide workforce capability data. performs gap analysis to identify workforce strengths and shortfalls with reference to business strategy and specific future needs. contributes to the development of organisationwide workforce plans to meet current and future demand. coordinates and schedules ongoing workforce planning activities. assists in maintaining a skills and capability inventory.</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. leads the development of workforce plans to ensure the availability of appropriately skilled resources to meet organisational objectives and commitments.x000d contributes to the development of the strategic workforce planning approach. oversees and reviews the implementation of workforce plans. x000d develops currentstate assessment of workforce skills, capabilities and potential. forecasts future workforce demand for skills based on broad organisationwide plans and external factors. x000d maintains a skills and capability inventory and identifies options for closing gaps.</t>
+          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. leads the development of workforce plans to ensure the availability of appropriately skilled resources to meet organisational objectives and commitments. contributes to the development of the strategic workforce planning approach. oversees and reviews the implementation of workforce plans. develops currentstate assessment of workforce skills, capabilities and potential. forecasts future workforce demand for skills based on broad organisationwide plans and external factors. maintains a skills and capability inventory and identifies options for closing gaps.</t>
         </is>
       </c>
     </row>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. defines an integrated strategic workforce planning approach connecting organisational business goals to future skill needs.x000d communicates the workforce planning approach and obtains organisational commitment. selects frameworks to be used for the organisations skills and capability inventory. x000d interprets business strategy to direct workforce demand forecasting skills and numbers for the organisation. monitors the external environment in relation to supply and emerging trends. x000d influences people management policies and practices to align with workforce plans. integrates with resourcing strategies and plans. monitors execution of workforce plans.</t>
+          <t>strategically projecting the demand for people and skills and proactively planning the workforce supply to meet organisational needs. defines an integrated strategic workforce planning approach connecting organisational business goals to future skill needs. communicates the workforce planning approach and obtains organisational commitment. selects frameworks to be used for the organisations skills and capability inventory. interprets business strategy to direct workforce demand forecasting skills and numbers for the organisation. monitors the external environment in relation to supply and emerging trends. influences people management policies and practices to align with workforce plans. integrates with resourcing strategies and plans. monitors execution of workforce plans.</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>acquiring, deploying and onboarding resources. assists with resourcing tasks under routine supervision.x000d helps with recruiting and onboarding new employees.x000d supports the documentation and tracking of resourcing activities.</t>
+          <t>acquiring, deploying and onboarding resources. assists with resourcing tasks under routine supervision. helps with recruiting and onboarding new employees. supports the documentation and tracking of resourcing activities.</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>acquiring, deploying and onboarding resources. supports managers and teams in resourcing and recruitment activities. x000d uses recommended tools for planning, scheduling and tracking resourcing activity. x000d provides guidance on resource management and recruitment software, procedures, processes, tools and techniques.</t>
+          <t>acquiring, deploying and onboarding resources. supports managers and teams in resourcing and recruitment activities. uses recommended tools for planning, scheduling and tracking resourcing activity. provides guidance on resource management and recruitment software, procedures, processes, tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>acquiring, deploying and onboarding resources. facilitates and supports the execution of resourcing activities in collaboration with managers and teams.x000d analyses resource requests to determine tasks, skills and effort required. creates and communicates open positions internally and externally. conducts interviews and assessments using a planned format and structure.x000d implements internal resource allocation matching skills to tasks. contributes to transitioning of resources, complying with relevant statutory or external regulations and codes of practice.</t>
+          <t>acquiring, deploying and onboarding resources. facilitates and supports the execution of resourcing activities in collaboration with managers and teams. analyses resource requests to determine tasks, skills and effort required. creates and communicates open positions internally and externally. conducts interviews and assessments using a planned format and structure. implements internal resource allocation matching skills to tasks. contributes to transitioning of resources, complying with relevant statutory or external regulations and codes of practice.</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>acquiring, deploying and onboarding resources. plans and manages the acquisition and deployment of resources to meet specific needs and ongoing demand.x000d defines and manages the implementation of resourcing processes and tools. advises on available options and customises resourcing approach to meet requirements. adheres to standards, statutory or external regulations and codes of practice and ensures compliance. x000d engages with external parties in support of resourcing plans.x000d measures effectiveness of resourcing processes and implements improvements.</t>
+          <t>acquiring, deploying and onboarding resources. plans and manages the acquisition and deployment of resources to meet specific needs and ongoing demand. defines and manages the implementation of resourcing processes and tools. advises on available options and customises resourcing approach to meet requirements. adheres to standards, statutory or external regulations and codes of practice and ensures compliance. engages with external parties in support of resourcing plans. measures effectiveness of resourcing processes and implements improvements.</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>acquiring, deploying and onboarding resources. defines resourcing approach for a significant part of the organisation in line with workforce plans and strategic business goals.x000d communicates resourcing approach and obtains organisational commitment. advises on standards, regulations and codes of practice and ensures compliance.x000d maintains a strong external network and supplier framework to support sourcing and acquiring resources.x000d leads development of plans and budget to ensure the organisation has appropriately skilled resources to meet organisational objectives and commitments. reviews the ongoing success and effectiveness of resource management processes.</t>
+          <t>acquiring, deploying and onboarding resources. defines resourcing approach for a significant part of the organisation in line with workforce plans and strategic business goals. communicates resourcing approach and obtains organisational commitment. advises on standards, regulations and codes of practice and ensures compliance. maintains a strong external network and supplier framework to support sourcing and acquiring resources. leads development of plans and budget to ensure the organisation has appropriately skilled resources to meet organisational objectives and commitments. reviews the ongoing success and effectiveness of resource management processes.</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. supports learning and development activities under routine supervision. x000d assists in maintaining training records and documenting learning and development activities. x000d helps organise learning events and track attendance.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. supports learning and development activities under routine supervision. assists in maintaining training records and documenting learning and development activities. helps organise learning events and track attendance.</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. contributes to the maintenance of training records and the catalogue of learning and development resources.x000d supports the organisation of learning events by helping to coordinate logistics, schedules, and communication with attendees.x000d supports the collection and organisation of data on learning and development activities to assist in evaluating their effectiveness.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. contributes to the maintenance of training records and the catalogue of learning and development resources. supports the organisation of learning events by helping to coordinate logistics, schedules, and communication with attendees. supports the collection and organisation of data on learning and development activities to assist in evaluating their effectiveness.</t>
         </is>
       </c>
     </row>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. contributes to the development and maintenance of a catalogue of learning and development resources. x000d uses data to analyse and evaluate the effectiveness of learningeducational activities. x000d books and organises learning events. x000d updates and controls training records, including attainment of certificates and accreditations.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. contributes to the development and maintenance of a catalogue of learning and development resources. uses data to analyse and evaluate the effectiveness of learningeducational activities. books and organises learning events. updates and controls training records, including attainment of certificates and accreditations.</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. manages the provision of learning and development, ensuring optimum use of resources. x000d maintains, publicises and promotes a catalogue of learning and development activities. ensures courses are up to date and accredited when required. x000d arranges facilities and schedules with learning and development providers as appropriate. x000d uses data to assess and improve the effectiveness of learning or educational activities.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. manages the provision of learning and development, ensuring optimum use of resources. maintains, publicises and promotes a catalogue of learning and development activities. ensures courses are up to date and accredited when required. arranges facilities and schedules with learning and development providers as appropriate. uses data to assess and improve the effectiveness of learning or educational activities.</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. determines the learning and development programme and delivery mechanisms needed to grow staff skills in line with business needs.x000d identifies appropriate accreditation and qualification paths applicable to individuals within the organisation.x000d evaluates learning outcomes. x000d manages the development and provision of all learning, taking account of the strategic aims of the employing organisation.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. determines the learning and development programme and delivery mechanisms needed to grow staff skills in line with business needs. identifies appropriate accreditation and qualification paths applicable to individuals within the organisation. evaluates learning outcomes. manages the development and provision of all learning, taking account of the strategic aims of the employing organisation.</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. directs the development and implementation of a learning and development strategy for the organisation aligned to business needs. x000d leads the provision of learning and development expertise, guidance and systems needed to execute strategic and operational plans. x000d secures organisational resources to execute the learning and development strategy. x000d identifies opportunities for strategic relationships with suppliers and partners.</t>
+          <t>delivering management, advisory and administrative services to support the development of knowledge, skills and competencies. directs the development and implementation of a learning and development strategy for the organisation aligned to business needs. leads the provision of learning and development expertise, guidance and systems needed to execute strategic and operational plans. secures organisational resources to execute the learning and development strategy. identifies opportunities for strategic relationships with suppliers and partners.</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. assists with learning design and development tasks under routine supervision.x000d supports the creation and maintenance of learning materials and resources.x000d helps document and organise learning content and environments.</t>
+          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. assists with learning design and development tasks under routine supervision. supports the creation and maintenance of learning materials and resources. helps document and organise learning content and environments.</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. designs, creates, customises and maintains learning materials and resources to deliver agreed outcomes, and meet accreditation requirements when appropriate. x000d contributes to the design, configuration and testing of learning environments.</t>
+          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. designs, creates, customises and maintains learning materials and resources to deliver agreed outcomes, and meet accreditation requirements when appropriate. contributes to the design, configuration and testing of learning environments.</t>
         </is>
       </c>
     </row>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. specifies the content and structure of learning and development materials. x000d takes responsibility for design, creation, packaging and maintenance. manages development to deliver agreed outcomes. x000d where required, designs, configures and tests learning environments. x000d secures external accreditations as appropriate.</t>
+          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. specifies the content and structure of learning and development materials. takes responsibility for design, creation, packaging and maintenance. manages development to deliver agreed outcomes. where required, designs, configures and tests learning environments. secures external accreditations as appropriate.</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. specifies solutions for use in learning and development programmes in the workplace or in compulsory, further or higher education.x000d commissions the development of learning materials, allocates resources to learning teams and defines learning outcomes. x000d leads learning programmes, recommends and specifies learning interventions for design, development and deployment according to agreed learning outcomes.</t>
+          <t>designing and developing resources to transfer knowledge, develop skills and change behaviours. specifies solutions for use in learning and development programmes in the workplace or in compulsory, further or higher education. commissions the development of learning materials, allocates resources to learning teams and defines learning outcomes. leads learning programmes, recommends and specifies learning interventions for design, development and deployment according to agreed learning outcomes.</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. performs a range of learning activities under direction to support the delivery of learning objectives. x000d assists in the preparation of learning environments. x000d observes learners performing practical activities and work, providing assistance with routine enquiries and escalating where needed.</t>
+          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. performs a range of learning activities under direction to support the delivery of learning objectives. assists in the preparation of learning environments. observes learners performing practical activities and work, providing assistance with routine enquiries and escalating where needed.</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. delivers learning activities to various audiences using prepared materials aligned with established learning objectives. x000d follows established guidelines to prepare the learning environment. assists in developing and maintaining relevant examples and case studies.x000d uses a range of delivery techniques to develop learner skills and knowledge. x000d observes learners performing practical activities and work. advises and assists where necessary. provides detailed instruction where necessary and responds to questions, seeking advice in exceptional conditions beyond own experience.</t>
+          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. delivers learning activities to various audiences using prepared materials aligned with established learning objectives. follows established guidelines to prepare the learning environment. assists in developing and maintaining relevant examples and case studies. uses a range of delivery techniques to develop learner skills and knowledge. observes learners performing practical activities and work. advises and assists where necessary. provides detailed instruction where necessary and responds to questions, seeking advice in exceptional conditions beyond own experience.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. prepares and delivers learning activities tailored to various audiences and specific learning objectives.x000d contributes to the design and selection of appropriate environments. uses a broad range of learning delivery techniques to build learner skills and knowledge. develops and updates examples and case study materials.x000d observes and evaluates learner performance, offering guidance and tailored instruction. x000d adjusts delivery approaches and materials to enhance learner experience, responding to specialised queries and ensuring objectives are met.</t>
+          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. prepares and delivers learning activities tailored to various audiences and specific learning objectives. contributes to the design and selection of appropriate environments. uses a broad range of learning delivery techniques to build learner skills and knowledge. develops and updates examples and case study materials. observes and evaluates learner performance, offering guidance and tailored instruction. adjusts delivery approaches and materials to enhance learner experience, responding to specialised queries and ensuring objectives are met.</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. manages the delivery of programmes of learning to ensure learning objectives are met. x000d plans and schedules the delivery of learning activities. leads the design and selection of appropriate environments to support and enhance the learning experience. customises learning activities incorporating relevant scenarios and case studies. x000d delivers learning activities to specialist audiences requiring the application of advanced technical and professional principles to unpredictable situations. advises others in learning delivery techniques and options.x000d evaluates and monitors the performance of learning delivery activities.</t>
+          <t>transferring knowledge, developing skills and changing behaviours using a range of techniques, resources and media. manages the delivery of programmes of learning to ensure learning objectives are met. plans and schedules the delivery of learning activities. leads the design and selection of appropriate environments to support and enhance the learning experience. customises learning activities incorporating relevant scenarios and case studies. delivers learning activities to specialist audiences requiring the application of advanced technical and professional principles to unpredictable situations. advises others in learning delivery techniques and options. evaluates and monitors the performance of learning delivery activities.</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. assists in the administration of competency assessments using standard tools and procedures under routine supervision. x000d supports the collection and organisation of assessment data and results using specified methods and tools. x000d helps create and maintain documentation.</t>
+          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. assists in the administration of competency assessments using standard tools and procedures under routine supervision. supports the collection and organisation of assessment data and results using specified methods and tools. helps create and maintain documentation.</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. performs routine assessments of knowledge, skills, competencies, or behaviours using specified tools and methods. x000d supports the collection, organisation, and review of assessment data to maintain accurate records.</t>
+          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. performs routine assessments of knowledge, skills, competencies, or behaviours using specified tools and methods. supports the collection, organisation, and review of assessment data to maintain accurate records.</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. performs routine and nonroutine assessments of knowledge, skill, competency or behaviour using specified methods. x000d provides advice and guidance to support the adoption of assessment methods and tools. x000d moderates assessments conducted by other assessors. x000d reviews and improves usage and application of assessment methods and tools.</t>
+          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. performs routine and nonroutine assessments of knowledge, skill, competency or behaviour using specified methods. provides advice and guidance to support the adoption of assessment methods and tools. moderates assessments conducted by other assessors. reviews and improves usage and application of assessment methods and tools.</t>
         </is>
       </c>
     </row>
@@ -16636,7 +16636,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. provides advice and guidance on selecting, adopting and adapting assessment methods, tools and techniques. x000d plans assessments based on the context of the assessment and how assessment results will be used. x000d manages execution of assessments to ensure they deliver the required outcomes with acceptable quality. monitors and moderates reviews performed by other assessors. x000d manages reviews of the benefits and value of assessment methods and tools. identifies and recommends improvements to assessment methods and tools.</t>
+          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. provides advice and guidance on selecting, adopting and adapting assessment methods, tools and techniques. plans assessments based on the context of the assessment and how assessment results will be used. manages execution of assessments to ensure they deliver the required outcomes with acceptable quality. monitors and moderates reviews performed by other assessors. manages reviews of the benefits and value of assessment methods and tools. identifies and recommends improvements to assessment methods and tools.</t>
         </is>
       </c>
     </row>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. champions the importance and value of assessment and appropriate assessment methods, tools and techniques. x000d develops organisational policies, standards and guidelines for assessments. x000d leads in the introduction and use of assessment methodologies and tools. establishes an assessment practice and pool of assessors within the organisation. x000d establishes quality assurance to ensure internal andor external consistency and reliability of assessment outcomes. ensures the quality of assessments across different user groups.</t>
+          <t>assessing knowledge, skills, competency and behaviours by any means, whether formal or informal, against frameworks such as sfia. champions the importance and value of assessment and appropriate assessment methods, tools and techniques. develops organisational policies, standards and guidelines for assessments. leads in the introduction and use of assessment methodologies and tools. establishes an assessment practice and pool of assessors within the organisation. establishes quality assurance to ensure internal andor external consistency and reliability of assessment outcomes. ensures the quality of assessments across different user groups.</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. processes applications for certification. x000d logs complaints.x000d assists with the preparation and organisation of credential materials.x000d supports the creation and maintenance of credentials or certificates and helps resolve routine problems during the certification lifecycle.</t>
+          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. processes applications for certification. logs complaints. assists with the preparation and organisation of credential materials. supports the creation and maintenance of credentials or certificates and helps resolve routine problems during the certification lifecycle.</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. issues certifications or credentials and maintains and retains certification records. x000d maintains information on the certification scheme and a general description of the certification process. x000d designs, creates, develops, customises and maintains credentials or certificates. x000d responds to public information requests. analyses and acts on complaints or issues.</t>
+          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. issues certifications or credentials and maintains and retains certification records. maintains information on the certification scheme and a general description of the certification process. designs, creates, develops, customises and maintains credentials or certificates. responds to public information requests. analyses and acts on complaints or issues.</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. documents instructions for all personnel involved in certification, including legally enforceable agreements with any third parties involved in the process. x000d identifies threats to impartiality by analysing, mitigating or eliminating potential conflict of interests arising from certification activities. x000d implements the procedures for certification of individuals for the delivery of training. x000d determines the merits of complaints and any remedial actions required.</t>
+          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. documents instructions for all personnel involved in certification, including legally enforceable agreements with any third parties involved in the process. identifies threats to impartiality by analysing, mitigating or eliminating potential conflict of interests arising from certification activities. implements the procedures for certification of individuals for the delivery of training. determines the merits of complaints and any remedial actions required.</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. defines a certification or accreditation scheme, including organisation structure, duties, responsibilities and authorities. x000d determines necessary competence to perform certification functions. designs and implements the examiner or assessor selection and approval process. x000d monitors performance and judgements, and agrees corrective actions. plans and provides adequate premises, equipment and resources. x000d documents policies and procedures for maintenance and release of information, including consideration of any legal agreements for confidentiality.</t>
+          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. defines a certification or accreditation scheme, including organisation structure, duties, responsibilities and authorities. determines necessary competence to perform certification functions. designs and implements the examiner or assessor selection and approval process. monitors performance and judgements, and agrees corrective actions. plans and provides adequate premises, equipment and resources. documents policies and procedures for maintenance and release of information, including consideration of any legal agreements for confidentiality.</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. sets policies and standards for the operation of a certification scheme, including segregation of duties and addressing impartiality. x000d develops and maintains a description of the code of ethics and professional practices required. x000d aligns certification schemes with relevant external standards, frameworks such as sfia and established industry practices. x000d obtains approval from accreditation scheme owners or governance bodies.</t>
+          <t>designing, developing and operating certification schemes, accreditations and credentials, including digital credentials or badges. sets policies and standards for the operation of a certification scheme, including segregation of duties and addressing impartiality. develops and maintains a description of the code of ethics and professional practices required. aligns certification schemes with relevant external standards, frameworks such as sfia and established industry practices. obtains approval from accreditation scheme owners or governance bodies.</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. contributes to the delivery of aspects of computing and it curricula in a formal educational context. x000d applies good practice in learning content design, development and delivery.x000d assesses student performance in aspects of a curriculum area, providing support to enhance student understanding as needed.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. contributes to the delivery of aspects of computing and it curricula in a formal educational context. applies good practice in learning content design, development and delivery. assesses student performance in aspects of a curriculum area, providing support to enhance student understanding as needed.</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. delivers the majority of a curriculum. x000d applies good practice in learning content design, development and delivery. maintains awareness of relevant pedagogical and domain research.x000d assesses student performance across a curriculum. provides feedback and support to help students improve their understanding.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. delivers the majority of a curriculum. applies good practice in learning content design, development and delivery. maintains awareness of relevant pedagogical and domain research. assesses student performance across a curriculum. provides feedback and support to help students improve their understanding.</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. delivers a curriculum. x000d applies good practice supported by pedagogical research to learning content design, development and delivery. x000d assesses student performance and reviews cohort performance. advises and assists students to enable the achievement of learning objectives.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. delivers a curriculum. applies good practice supported by pedagogical research to learning content design, development and delivery. assesses student performance and reviews cohort performance. advises and assists students to enable the achievement of learning objectives.</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. leads the teaching and assessment of a curriculum or learning pathway. x000d implements enhancement strategies for teaching and assessment. reviews pedagogical research and practices relevant to topics in the curricula. applies good teaching practices in learning content design, development and delivery.x000d contributes to the development and implementation of specialist teaching practices needed by the curriculum. x000d evaluates and monitors student achievements and the effectiveness of teaching activities across the curriculum. advises on the use of appropriate pedagogies and assessment approaches.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. leads the teaching and assessment of a curriculum or learning pathway. implements enhancement strategies for teaching and assessment. reviews pedagogical research and practices relevant to topics in the curricula. applies good teaching practices in learning content design, development and delivery. contributes to the development and implementation of specialist teaching practices needed by the curriculum. evaluates and monitors student achievements and the effectiveness of teaching activities across the curriculum. advises on the use of appropriate pedagogies and assessment approaches.</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. leads the teaching, assessment and enhancement of a range of curricula or learning pathways.x000d reviews and critically evaluates pedagogical research and practices relevant to the curricula. develops and leads the introduction of advanced or specialist teaching practices. x000d leads and supports others in the development of good practice in learning content design, development and delivery. x000d monitors, evaluates and reports the performance of teaching and assessment activities within their areas of responsibility.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. leads the teaching, assessment and enhancement of a range of curricula or learning pathways. reviews and critically evaluates pedagogical research and practices relevant to the curricula. develops and leads the introduction of advanced or specialist teaching practices. leads and supports others in the development of good practice in learning content design, development and delivery. monitors, evaluates and reports the performance of teaching and assessment activities within their areas of responsibility.</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>delivering and assessing curricula in a structured and systematic education environment. authorises teaching, assessment and enhancement strategies for a broad range of curricula or learning pathways.x000d directs the definition, implementation and monitoring of teaching to satisfy relevant statutory and professional benchmarks and frameworks.x000d secures resources to deliver the organisations teaching commitments.x000d monitors and evaluates relevant domain and pedagogical research to identify and implement improvements to the delivery of the curricula.</t>
+          <t>delivering and assessing curricula in a structured and systematic education environment. authorises teaching, assessment and enhancement strategies for a broad range of curricula or learning pathways. directs the definition, implementation and monitoring of teaching to satisfy relevant statutory and professional benchmarks and frameworks. secures resources to deliver the organisations teaching commitments. monitors and evaluates relevant domain and pedagogical research to identify and implement improvements to the delivery of the curricula.</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>specifying, designing and developing curricula within a structured and systematic education environment. leads the specification and development of curricula and assessment in an educational context or for an independent examination body. x000d contributes to the development of a strategy for curriculum evolution. x000d ensures relevant current domain research is represented in the curricula.</t>
+          <t>specifying, designing and developing curricula within a structured and systematic education environment. leads the specification and development of curricula and assessment in an educational context or for an independent examination body. contributes to the development of a strategy for curriculum evolution. ensures relevant current domain research is represented in the curricula.</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>specifying, designing and developing curricula within a structured and systematic education environment. authorises the curriculum and assessment strategies for a broad range of curricula or learning pathways.x000d directs the definition, implementation and monitoring of curricula to satisfy relevant statutory and professional benchmarks and frameworks.x000d develops strategies for the evolution of curricula over time. incorporates emerging domain and pedagogical themes into plans for future curricula.</t>
+          <t>specifying, designing and developing curricula within a structured and systematic education environment. authorises the curriculum and assessment strategies for a broad range of curricula or learning pathways. directs the definition, implementation and monitoring of curricula to satisfy relevant statutory and professional benchmarks and frameworks. develops strategies for the evolution of curricula over time. incorporates emerging domain and pedagogical themes into plans for future curricula.</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. assists in the preparation of prequalification questionnaires and tender invitations in response to business cases. x000d assembles relevant information for tenders. x000d produces detailed evaluation criteria for simple tender criteria. x000d assists in the evaluation of tenders.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. assists in the preparation of prequalification questionnaires and tender invitations in response to business cases. assembles relevant information for tenders. produces detailed evaluation criteria for simple tender criteria. assists in the evaluation of tenders.</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. prepares prequalification questionnaires and tender invitations in response to business cases. x000d recognises the difference between open source and proprietary systems options. x000d applies standard procedures and tools to produce detailed evaluation criteria for complex tenders and to evaluate tenders.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. prepares prequalification questionnaires and tender invitations in response to business cases. recognises the difference between open source and proprietary systems options. applies standard procedures and tools to produce detailed evaluation criteria for complex tenders and to evaluate tenders.</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. reviews business cases requirements, potential benefits and options and determines appropriate procurement routes. x000d using market knowledge to inform specifications, ensures detailed prequalification questionnaires and tender invitations are prepared. x000d collects and collates data to support collaboration and negotiates terms and conditions to reflect the scale of requirements and encourage optimal performance. x000d evaluates tenders based on specification and evaluation criteria, prepares acceptance documentation and advises on contracts and service level agreements.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. reviews business cases requirements, potential benefits and options and determines appropriate procurement routes. using market knowledge to inform specifications, ensures detailed prequalification questionnaires and tender invitations are prepared. collects and collates data to support collaboration and negotiates terms and conditions to reflect the scale of requirements and encourage optimal performance. evaluates tenders based on specification and evaluation criteria, prepares acceptance documentation and advises on contracts and service level agreements.</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. plans and manages procurement activities. x000d manages tender, evaluation and acquisition processes. researches suppliers and markets, and maintains a broad understanding of the commercial environment, to inform and develop commercial strategies and sourcing plans. x000d advises on the business case for alternative sourcing models. advises on policy and procedures covering tendering, the selection of suppliers and procurement. x000d negotiates with potential partners and suppliers, developing acceptance criteria and procedures. drafts and places contracts.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. plans and manages procurement activities. manages tender, evaluation and acquisition processes. researches suppliers and markets, and maintains a broad understanding of the commercial environment, to inform and develop commercial strategies and sourcing plans. advises on the business case for alternative sourcing models. advises on policy and procedures covering tendering, the selection of suppliers and procurement. negotiates with potential partners and suppliers, developing acceptance criteria and procedures. drafts and places contracts.</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. develops policy and procedures for sourcing and procurement activities. x000d establishes procurement strategies, standards, methods, processes and good practices that ensure compliance with legislation, regulation and information security requirements.x000d leads the procurement process, from clarifying requirements through to placing, monitoring and terminating contracts. conducts complex negotiations and sets parameters for routine negotiations. ensures terms and conditions align with organisational requirements, current legislation and policy.x000d identifies external partners, engaging with professionals in related disciplines as appropriate.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. develops policy and procedures for sourcing and procurement activities. establishes procurement strategies, standards, methods, processes and good practices that ensure compliance with legislation, regulation and information security requirements. leads the procurement process, from clarifying requirements through to placing, monitoring and terminating contracts. conducts complex negotiations and sets parameters for routine negotiations. ensures terms and conditions align with organisational requirements, current legislation and policy. identifies external partners, engaging with professionals in related disciplines as appropriate.</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>managing, or providing advice on, the procurement or commissioning of products and services. shapes and leads the organisations overarching sourcing and procurement strategies, ensuring alignment with the global business vision and longterm objectives.x000d assumes full accountability for all sourcing and procurement activities, guiding the organisations sourcing vision and strategic procurement decisions.x000d strategically develops, deploys and continually assesses procurement processes to align with dynamic market conditions and organisational goals.x000d leads highlevel negotiations for major, organisationdefining contracts, setting negotiation frameworks and strategies that significantly impact the organisations market position and success.</t>
+          <t>managing, or providing advice on, the procurement or commissioning of products and services. shapes and leads the organisations overarching sourcing and procurement strategies, ensuring alignment with the global business vision and longterm objectives. assumes full accountability for all sourcing and procurement activities, guiding the organisations sourcing vision and strategic procurement decisions. strategically develops, deploys and continually assesses procurement processes to align with dynamic market conditions and organisational goals. leads highlevel negotiations for major, organisationdefining contracts, setting negotiation frameworks and strategies that significantly impact the organisations market position and success.</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. assists in the collection and reporting of supplier performance data.x000d assists with the routine daytoday communication between the organisation and suppliers.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. assists in the collection and reporting of supplier performance data. assists with the routine daytoday communication between the organisation and suppliers.</t>
         </is>
       </c>
     </row>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. acts as the routine contact point between the organisation and suppliers.x000d supports resolution of supplierrelated incidents, problems, or unsatisfactory performance.x000d collects and reports on supplier performance data.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. acts as the routine contact point between the organisation and suppliers. supports resolution of supplierrelated incidents, problems, or unsatisfactory performance. collects and reports on supplier performance data.</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. collects supplier performance data and investigates problems. x000d monitors and reports on supplier performance, customer satisfaction, adherence to security requirements and market intelligence. validates that suppliers performance is in accordance with contract terms. x000d engages proactively and collaboratively with suppliers to resolve incidents, problems, or unsatisfactory performance. x000d implements supplier managementrelated service improvement initiatives and programmes.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. collects supplier performance data and investigates problems. monitors and reports on supplier performance, customer satisfaction, adherence to security requirements and market intelligence. validates that suppliers performance is in accordance with contract terms. engages proactively and collaboratively with suppliers to resolve incidents, problems, or unsatisfactory performance. implements supplier managementrelated service improvement initiatives and programmes.</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. manages suppliers to meet key performance indicators and agreed targets. x000d manages the operational relationships between suppliers and ensures potential disputes or conflicts are raised and resolved. x000d performs benchmarking and makes use of supplier performance data to ensure performance is adequately monitored and regularly reviewed. use suppliers expertise to support and inform development roadmaps.x000d manages implementation of supplier service improvement actions. identifies constraints and opportunities when negotiating or renegotiating contracts.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. manages suppliers to meet key performance indicators and agreed targets. manages the operational relationships between suppliers and ensures potential disputes or conflicts are raised and resolved. performs benchmarking and makes use of supplier performance data to ensure performance is adequately monitored and regularly reviewed. use suppliers expertise to support and inform development roadmaps. manages implementation of supplier service improvement actions. identifies constraints and opportunities when negotiating or renegotiating contracts.</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. develops organisational policies, standards and guidelines to ensure effective supplier management across the integrated supply chain. x000d defines the approach for commercial communications and the management of relationships with suppliers. establishes a positive and effective working environment with suppliers for mutual benefit. x000d ensures resources and tools are in place to conduct benchmarking. reviews supplier analysis and assesses effectiveness across the supply chain. x000d manages risks and assures the quality of the services delivered by suppliers.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. develops organisational policies, standards and guidelines to ensure effective supplier management across the integrated supply chain. defines the approach for commercial communications and the management of relationships with suppliers. establishes a positive and effective working environment with suppliers for mutual benefit. ensures resources and tools are in place to conduct benchmarking. reviews supplier analysis and assesses effectiveness across the supply chain. manages risks and assures the quality of the services delivered by suppliers.</t>
         </is>
       </c>
     </row>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. determines overall supplier management strategy, embracing effective management and operational relationships at all levels. x000d leads collaborative supplier partnerships. aligns supplier performance and relationship management with business objectives and sourcing strategies.x000d establishes frameworks for supplier governance and service monitoring.x000d ensures commercial value from contracts and represents the organisation in significant supplier disputes.</t>
+          <t>aligning the organisations supplier performance objectives and activities with sourcing strategies and plans, balancing costs, efficiencies and service quality. determines overall supplier management strategy, embracing effective management and operational relationships at all levels. leads collaborative supplier partnerships. aligns supplier performance and relationship management with business objectives and sourcing strategies. establishes frameworks for supplier governance and service monitoring. ensures commercial value from contracts and represents the organisation in significant supplier disputes.</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. assists in collecting contract performance data. x000d produces standard reports on contract performance under routine supervision.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. assists in collecting contract performance data. produces standard reports on contract performance under routine supervision.</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. acts as a routine contact point between the organisation and counterparties concerning contract management. x000d supports the collection of contract performance data. creates standard reports on contract performance.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. acts as a routine contact point between the organisation and counterparties concerning contract management. supports the collection of contract performance data. creates standard reports on contract performance.</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. sources and collects contract performance data such as pricing and supply chain costs, and monitors performance against key performance indicators. x000d monitors progress against business objectives specified in the business case. proactively manages risk and reward mechanisms in the contract. x000d identifies and reports underperformance and develops opportunities for improvement. monitors compliance with terms and conditions and takes appropriate steps to address noncompliance. x000d identifies where change is required and plans for variations. ensures, in consultation with stakeholders, that change management protocols are implemented.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. sources and collects contract performance data such as pricing and supply chain costs, and monitors performance against key performance indicators. monitors progress against business objectives specified in the business case. proactively manages risk and reward mechanisms in the contract. identifies and reports underperformance and develops opportunities for improvement. monitors compliance with terms and conditions and takes appropriate steps to address noncompliance. identifies where change is required and plans for variations. ensures, in consultation with stakeholders, that change management protocols are implemented.</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. oversees and measures the fulfilment of contractual obligations. x000d uses key performance indicators to monitor and challenge performance and identify opportunities for continual improvement. develops strategies to address underperformance and compliance failures, including the application of contract terms. x000d identifies where changes are required, evaluates the impact, and advises stakeholders about the implications and consequences. negotiates variations and seeks appropriate authorisation. x000d actively supports and engages with experts and stakeholders to ensure continual improvements are identified through review and benchmarking processes. develops and implements change management protocols.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. oversees and measures the fulfilment of contractual obligations. uses key performance indicators to monitor and challenge performance and identify opportunities for continual improvement. develops strategies to address underperformance and compliance failures, including the application of contract terms. identifies where changes are required, evaluates the impact, and advises stakeholders about the implications and consequences. negotiates variations and seeks appropriate authorisation. actively supports and engages with experts and stakeholders to ensure continual improvements are identified through review and benchmarking processes. develops and implements change management protocols.</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. negotiates and resolves contractual issues, including failure to meet contractual obligations. x000d promotes change control processes and leads variation negotiations when necessary. champions continual improvement programmes, jointly developing strategies and incentives to enhance performance. undertakes comprehensive financial evaluations. x000d ensures due diligence and legal vetting underpin all procurement processes, affirming risk assessment and compliance in contractual engagements. ensures lessons learned from reviews are documented and promoted to all stakeholders. x000d leads the advancement and application of effective contract management practices within a specific business domain or category.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. negotiates and resolves contractual issues, including failure to meet contractual obligations. promotes change control processes and leads variation negotiations when necessary. champions continual improvement programmes, jointly developing strategies and incentives to enhance performance. undertakes comprehensive financial evaluations. ensures due diligence and legal vetting underpin all procurement processes, affirming risk assessment and compliance in contractual engagements. ensures lessons learned from reviews are documented and promoted to all stakeholders. leads the advancement and application of effective contract management practices within a specific business domain or category.</t>
         </is>
       </c>
     </row>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. leads the strategic direction and governance of contract management processes across the organisation. advises executive leadership on contract management risks and strategies.x000d implements contract management strategies aligned with organisational goals and market dynamics, including oversight of significant contracts and associated legal risks. acts as the escalation point for major disputes. x000d promotes operational excellence in contract management, driving supply chain contracting improvements and innovation. x000d establishes strategic partnerships, aligning organisational and supplier goals. represents the organisation in key negotiations, ensuring strategic, compliant outcomes.</t>
+          <t>managing and operating formal contracts, addressing supplier and client needs in product and service provision. leads the strategic direction and governance of contract management processes across the organisation. advises executive leadership on contract management risks and strategies. implements contract management strategies aligned with organisational goals and market dynamics, including oversight of significant contracts and associated legal risks. acts as the escalation point for major disputes. promotes operational excellence in contract management, driving supply chain contracting improvements and innovation. establishes strategic partnerships, aligning organisational and supplier goals. represents the organisation in key negotiations, ensuring strategic, compliant outcomes.</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. deals with problems and issues, managing resolutions, corrective actions, lessons learned and the collection and dissemination of relevant information. x000d implements stakeholder engagementcommunications plans. collects and uses feedback from customers and stakeholders to help measure the effectiveness of stakeholder management. x000d helps develop and enhance customer and stakeholder relationships.</t>
+          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. deals with problems and issues, managing resolutions, corrective actions, lessons learned and the collection and dissemination of relevant information. implements stakeholder engagementcommunications plans. collects and uses feedback from customers and stakeholders to help measure the effectiveness of stakeholder management. helps develop and enhance customer and stakeholder relationships.</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. identifies the communications and relationship needs of stakeholder groups. translates communicationsstakeholder engagement strategies into specific activities and deliverables. x000d facilitates open communication and discussion between stakeholders. x000d acts as a single point of contact by developing, maintaining and working to stakeholder engagement strategies and plans. provides informed feedback to assess and promote understanding. x000d facilitates business decisionmaking processes. captures and disseminates technical and business information.</t>
+          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. identifies the communications and relationship needs of stakeholder groups. translates communicationsstakeholder engagement strategies into specific activities and deliverables. facilitates open communication and discussion between stakeholders. acts as a single point of contact by developing, maintaining and working to stakeholder engagement strategies and plans. provides informed feedback to assess and promote understanding. facilitates business decisionmaking processes. captures and disseminates technical and business information.</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. leads the development of comprehensive stakeholder management strategies and plans. x000d establishes and builds longterm, strategic relationships with key stakeholders to support service delivery and change initiatives. x000d acts as a principal point of contact, ensuring effective communication and alignment. negotiates and ensures agreements meet stakeholder needs.x000d oversees the monitoring of stakeholder relationships, capturing lessons learned and providing feedback. leads initiatives to enhance communication and relationships, promoting collaboration and understanding between all parties.</t>
+          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. leads the development of comprehensive stakeholder management strategies and plans. establishes and builds longterm, strategic relationships with key stakeholders to support service delivery and change initiatives. acts as a principal point of contact, ensuring effective communication and alignment. negotiates and ensures agreements meet stakeholder needs. oversees the monitoring of stakeholder relationships, capturing lessons learned and providing feedback. leads initiatives to enhance communication and relationships, promoting collaboration and understanding between all parties.</t>
         </is>
       </c>
     </row>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. determines the strategic approach to understanding stakeholder objectives and requirements. x000d works with all interested parties to identify stakeholders and establish effective relationships. establishes and promotes the overall vision for how stakeholder objectives are met and determines organisational roles and alignment. x000d actively manages relationships with the most senior stakeholders and is the ultimate escalation point for issue resolution.</t>
+          <t>systematically analysing, managing and influencing stakeholder relationships to achieve mutually beneficial outcomes through structured engagement. determines the strategic approach to understanding stakeholder objectives and requirements. works with all interested parties to identify stakeholders and establish effective relationships. establishes and promotes the overall vision for how stakeholder objectives are met and determines organisational roles and alignment. actively manages relationships with the most senior stakeholders and is the ultimate escalation point for issue resolution.</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. receives and handles routine customer inquiries and requests, following established procedures.x000d accurately records customer interactions and maintains relevant records.x000d escalates complex issues to appropriate team members or departments.</t>
+          <t>managing and operating customer service or service desk functions. receives and handles routine customer inquiries and requests, following established procedures. accurately records customer interactions and maintains relevant records. escalates complex issues to appropriate team members or departments.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. responds to common customer service requests, providing information to enable fulfilment or resolution.x000d allocates unresolved calls, requests, or issues to appropriate functions.x000d contributes to the maintenance of customer service knowledge bases and documentation.x000d assists in monitoring customer satisfaction metrics.</t>
+          <t>managing and operating customer service or service desk functions. responds to common customer service requests, providing information to enable fulfilment or resolution. allocates unresolved calls, requests, or issues to appropriate functions. contributes to the maintenance of customer service knowledge bases and documentation. assists in monitoring customer satisfaction metrics.</t>
         </is>
       </c>
     </row>
@@ -17762,7 +17762,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. acts as a routine contact point for customers, handling a wide range of inquiries and service requests.x000d performs initial investigation and diagnosis of customer issues, resolving them where possible or escalating as needed.x000d contributes to the development of service standards and procedures.x000d assists in analysing service performance data and identifying areas for improvement.</t>
+          <t>managing and operating customer service or service desk functions. acts as a routine contact point for customers, handling a wide range of inquiries and service requests. performs initial investigation and diagnosis of customer issues, resolving them where possible or escalating as needed. contributes to the development of service standards and procedures. assists in analysing service performance data and identifying areas for improvement.</t>
         </is>
       </c>
     </row>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. monitors service delivery across multiple channels and analyses performance data.x000d contributes to the development and implementation of service standards and procedures. provides technical and procedural guidance to team members.x000d identifies trends in customer inquiries and service issues, recommending process improvements.x000d collaborates with other departments to enhance the overall customer experience.</t>
+          <t>managing and operating customer service or service desk functions. monitors service delivery across multiple channels and analyses performance data. contributes to the development and implementation of service standards and procedures. provides technical and procedural guidance to team members. identifies trends in customer inquiries and service issues, recommending process improvements. collaborates with other departments to enhance the overall customer experience.</t>
         </is>
       </c>
     </row>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. manages daytoday operations of the customer service function, including resource planning and work allocation.x000d develops and implements service standards, policies and procedures. analyses service metrics and customer feedback to drive continuous improvement initiatives.x000d ensures the service catalogue is comprehensive, uptodate and aligned with organisational goals.x000d develops approaches to enhance customer satisfaction.</t>
+          <t>managing and operating customer service or service desk functions. manages daytoday operations of the customer service function, including resource planning and work allocation. develops and implements service standards, policies and procedures. analyses service metrics and customer feedback to drive continuous improvement initiatives. ensures the service catalogue is comprehensive, uptodate and aligned with organisational goals. develops approaches to enhance customer satisfaction.</t>
         </is>
       </c>
     </row>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>managing and operating customer service or service desk functions. shapes the strategic direction for customer service across the organisation.x000d defines service channels, service levels, standards and the monitoring process for customer service or service desk staff. champions the service culture required to deliver organisational outcomes.x000d leads the development and implementation of organisational frameworks for complaints, service standards and operational agreements.x000d takes responsibility for business continuity and legal, regulatory and contractual compliance.</t>
+          <t>managing and operating customer service or service desk functions. shapes the strategic direction for customer service across the organisation. defines service channels, service levels, standards and the monitoring process for customer service or service desk staff. champions the service culture required to deliver organisational outcomes. leads the development and implementation of organisational frameworks for complaints, service standards and operational agreements. takes responsibility for business continuity and legal, regulatory and contractual compliance.</t>
         </is>
       </c>
     </row>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. performs routine administrative tasks in a structured environment. x000d follows clear procedures. uses common office software and equipment. x000d organises and maintains information following agreed procedures.x000d assists with basic coordination activities.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. performs routine administrative tasks in a structured environment. follows clear procedures. uses common office software and equipment. organises and maintains information following agreed procedures. assists with basic coordination activities.</t>
         </is>
       </c>
     </row>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. assists with administrative tasks for a team. x000d maintains systems for organising information and documents. x000d coordinates team activities and acts as a point of contact for internal and external contacts.x000d uses relevant digital tools and platforms.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. assists with administrative tasks for a team. maintains systems for organising information and documents. coordinates team activities and acts as a point of contact for internal and external contacts. uses relevant digital tools and platforms.</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. provides administrative support function to teams and meetings.x000d takes an active part in team discussions. x000d sets up and maintains systems for organising information and documents. compiles and distributes reports. x000d provides guidance on administrative software, procedures, processes, tools and techniques.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. provides administrative support function to teams and meetings. takes an active part in team discussions. sets up and maintains systems for organising information and documents. compiles and distributes reports. provides guidance on administrative software, procedures, processes, tools and techniques.</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. assists the teams and managers in ensuring they have the information and resources needed to support ongoing processes. x000d assists in planning for meetings. liaises and organises across functions. x000d sets up and provides detailed guidance on software, procedures, processes, tools and techniques for administration and workplace productivity.x000d contributes to the development and maintenance of organisational policies, procedures and documentation.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. assists the teams and managers in ensuring they have the information and resources needed to support ongoing processes. assists in planning for meetings. liaises and organises across functions. sets up and provides detailed guidance on software, procedures, processes, tools and techniques for administration and workplace productivity. contributes to the development and maintenance of organisational policies, procedures and documentation.</t>
         </is>
       </c>
     </row>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. manages the delivery of business administration services. x000d manages and prioritises the schedules and communication of senior managers and leadership teams to ensure efficient use of time and resources.x000d handles sensitive, confidential information. x000d ensures managers have the information and resources needed to support ongoing processes and changes in processes.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. manages the delivery of business administration services. manages and prioritises the schedules and communication of senior managers and leadership teams to ensure efficient use of time and resources. handles sensitive, confidential information. ensures managers have the information and resources needed to support ongoing processes and changes in processes.</t>
         </is>
       </c>
     </row>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. leads and coordinates strategic initiatives working across departmental or functional boundaries. x000d designs, plans and coordinates highlevel meetings and events, ensuring alignment with strategic objectives and desired outcomes.x000d provides direction and receives progress updates from members of an executive team. meets collectively or individually with members of a leadership management team to follow up on action points, issues and risks. reports on progress and resolves issues. x000d manages highly sensitive and confidential issues and information.</t>
+          <t>managing and performing administrative services and tasks to enable individuals, teams and organisations to succeed in their objectives. leads and coordinates strategic initiatives working across departmental or functional boundaries. designs, plans and coordinates highlevel meetings and events, ensuring alignment with strategic objectives and desired outcomes. provides direction and receives progress updates from members of an executive team. meets collectively or individually with members of a leadership management team to follow up on action points, issues and risks. reports on progress and resolves issues. manages highly sensitive and confidential issues and information.</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. supports the development of proposals by engaging in document analysis and internal review. x000d understands and analyses bid documents and requirements, preparing initial response drafts that align with the organisations capabilities and stakeholder needs. x000d communicates with internal stakeholders to gather necessary information and clarify proposal requirements. x000d ensures proposal responses meet basic compliance standards and align with the specified requirements and organisational capabilities.</t>
+          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. supports the development of proposals by engaging in document analysis and internal review. understands and analyses bid documents and requirements, preparing initial response drafts that align with the organisations capabilities and stakeholder needs. communicates with internal stakeholders to gather necessary information and clarify proposal requirements. ensures proposal responses meet basic compliance standards and align with the specified requirements and organisational capabilities.</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18070,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. leads the creation of small to medium proposals, integrating technical analysis and broader context. x000d coordinates team efforts, shapes the proposal structure and addresses financial aspects including budgeting and pricing strategies. x000d identifies and manages proposal risks, ensuring timely compliance with stakeholder expectations. x000d engages with stakeholders and shapes proposal structure and content based on indepth discussions and feedback.</t>
+          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. leads the creation of small to medium proposals, integrating technical analysis and broader context. coordinates team efforts, shapes the proposal structure and addresses financial aspects including budgeting and pricing strategies. identifies and manages proposal risks, ensuring timely compliance with stakeholder expectations. engages with stakeholders and shapes proposal structure and content based on indepth discussions and feedback.</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. leads the formulation and execution of significant proposals, managing the process from initial evaluation to final submission. x000d oversees significant proposals, aligning them with organisational strategies and managing the process from inception to submission. x000d collaborates with highlevel stakeholders, negotiates with key stakeholders and secures advantageous partnerships. x000d refines and optimises the proposal development process for efficiency and effectiveness.</t>
+          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. leads the formulation and execution of significant proposals, managing the process from initial evaluation to final submission. oversees significant proposals, aligning them with organisational strategies and managing the process from inception to submission. collaborates with highlevel stakeholders, negotiates with key stakeholders and secures advantageous partnerships. refines and optimises the proposal development process for efficiency and effectiveness.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. directs major proposal initiatives, devising engagement strategies and promoting excellence in proposal practices throughout the organisation. x000d influences organisational policies and strategies in proposal management, setting standards and expectations.</t>
+          <t>managing preparation and submission of bids and proposals for contracts, grants, projects, or services. directs major proposal initiatives, devising engagement strategies and promoting excellence in proposal practices throughout the organisation. influences organisational policies and strategies in proposal management, setting standards and expectations.</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. identifies new leads and prospects and communicates them to the sales manager. x000d responds to assigned sales leads. assists in maintaining relationships with existing customers and identifies potential opportunities for additional sales or services.x000d applies agreed standards and tools to perform simple sales tasks or support complex sales processes. x000d monitors and reports on assigned sales quota, performance, customer satisfaction, market intelligence and competitors.</t>
+          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. identifies new leads and prospects and communicates them to the sales manager. responds to assigned sales leads. assists in maintaining relationships with existing customers and identifies potential opportunities for additional sales or services. applies agreed standards and tools to perform simple sales tasks or support complex sales processes. monitors and reports on assigned sales quota, performance, customer satisfaction, market intelligence and competitors.</t>
         </is>
       </c>
     </row>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. identifies and qualifies new sales leads and prospects with a view to developing a pipeline of potential opportunities. x000d manages existing sales leads. x000d collects and uses information to achieve sales objectives. x000d understands customers and their needs, and develops and enhances customer relationships before, during and after the conclusion of agreementscontracts. identifies opportunities for upselling and crossselling within the existing customer base.</t>
+          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. identifies and qualifies new sales leads and prospects with a view to developing a pipeline of potential opportunities. manages existing sales leads. collects and uses information to achieve sales objectives. understands customers and their needs, and develops and enhances customer relationships before, during and after the conclusion of agreementscontracts. identifies opportunities for upselling and crossselling within the existing customer base.</t>
         </is>
       </c>
     </row>
@@ -18208,7 +18208,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. designs and implements sales strategies and works with senior management to implement sales plans. x000d develops and maintains effective customer relationships at executive levels and qualifies new sales leads. collaborates with bid teams to align sales strategies.x000d agrees and signs contracts. maintains customer contact during and after sales to preempt issues and identify opportunities. develops strategies for account growth and retention. implements initiatives to ensure longterm value and loyalty.x000d plans, monitors and controls sales teams. contributes to the development of sales teams and productservice development.</t>
+          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. designs and implements sales strategies and works with senior management to implement sales plans. develops and maintains effective customer relationships at executive levels and qualifies new sales leads. collaborates with bid teams to align sales strategies. agrees and signs contracts. maintains customer contact during and after sales to preempt issues and identify opportunities. develops strategies for account growth and retention. implements initiatives to ensure longterm value and loyalty. plans, monitors and controls sales teams. contributes to the development of sales teams and productservice development.</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. oversees the organisations sales activities to align with business objectives.x000d approves sales proposals and targets. develops sales policy and strategy, and contributes to the marketing strategy. works with bid management to ensure sales strategies are effectively represented in major proposals.x000d negotiates with senior customer representatives on technical and contractual issues. agrees and signs contracts.x000d collaborates on evolving services, products, systems and contracts to meet future customer needs. implements strategies for lifetime customer value and partnerships. oversees key account management programmes.</t>
+          <t>finding prospective customers and working with them to identify needs, influence purchase decisions and enhance future business opportunities. oversees the organisations sales activities to align with business objectives. approves sales proposals and targets. develops sales policy and strategy, and contributes to the marketing strategy. works with bid management to ensure sales strategies are effectively represented in major proposals. negotiates with senior customer representatives on technical and contractual issues. agrees and signs contracts. collaborates on evolving services, products, systems and contracts to meet future customer needs. implements strategies for lifetime customer value and partnerships. oversees key account management programmes.</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. communicates effectively with customers to provide basic information about products and services.x000d seeks assistance from colleagues for the resolution of more complex customer service queries and complaints. x000d uses sales support systems to retrieve and enter data.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. communicates effectively with customers to provide basic information about products and services. seeks assistance from colleagues for the resolution of more complex customer service queries and complaints. uses sales support systems to retrieve and enter data.</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. communicates effectively with customers by telephone and in person. x000d assists in providing customer service, including technical advice and guidance on the successful use of products and services. x000d assists in devising solutions to customer requirements and solves straightforward problems.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. communicates effectively with customers by telephone and in person. assists in providing customer service, including technical advice and guidance on the successful use of products and services. assists in devising solutions to customer requirements and solves straightforward problems.</t>
         </is>
       </c>
     </row>
@@ -18317,7 +18317,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. helps customers to clarify their requirements and documents the conclusions reached. x000d contributes to preparing and supporting bids and sales proposals. x000d provides customer service, including technical advice and guidance on the successful use of complex products and services.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. helps customers to clarify their requirements and documents the conclusions reached. contributes to preparing and supporting bids and sales proposals. provides customer service, including technical advice and guidance on the successful use of complex products and services.</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. works closely with the sales team to help prospects to clarify their requirements. x000d devises solutions and assesses their feasibility and practicality. x000d demonstrates technical feasibility using physical or simulation models. resolves technical problems.x000d produces estimates of cost and risk and initial project plans to inform sales proposals.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. works closely with the sales team to help prospects to clarify their requirements. devises solutions and assesses their feasibility and practicality. demonstrates technical feasibility using physical or simulation models. resolves technical problems. produces estimates of cost and risk and initial project plans to inform sales proposals.</t>
         </is>
       </c>
     </row>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. works closely with the sales team to ensure customers are assisted and advised appropriately. x000d ensures reliable cost, effort and risk estimates and project plans are produced. x000d manages all sales support activities, taking full responsibility for the technical content of bids and sales proposals. x000d establishes metrics to provide data on performance and support continual improvement of sales support activities.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. works closely with the sales team to ensure customers are assisted and advised appropriately. ensures reliable cost, effort and risk estimates and project plans are produced. manages all sales support activities, taking full responsibility for the technical content of bids and sales proposals. establishes metrics to provide data on performance and support continual improvement of sales support activities.</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>providing advice and support to the sales force, customers and sales partners. leads the organisations salesrelated customer service activities to ensure they are aligned with corporate objectives and policy. x000d approves proposals and initiates the implementation of development activity in customer services and systems.</t>
+          <t>providing advice and support to the sales force, customers and sales partners. leads the organisations salesrelated customer service activities to ensure they are aligned with corporate objectives and policy. approves proposals and initiates the implementation of development activity in customer services and systems.</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. contributes to the development and execution of marketing plans. x000d applies recognised good practices to analyse marketing effectiveness and roi. x000d assists in defining target customers and brand positioning. implements solutions to marketing challenges within established guidelines. collaborates with team members to execute marketing activities.</t>
+          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. contributes to the development and execution of marketing plans. applies recognised good practices to analyse marketing effectiveness and roi. assists in defining target customers and brand positioning. implements solutions to marketing challenges within established guidelines. collaborates with team members to execute marketing activities.</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. develops and manages comprehensive marketing plans aligned with business objectives. x000d implements strategies to maximise marketing effectiveness given organisational goals. leads the definition of target customers and brand positioning.x000d analyses complex data to inform marketing decisions. creates innovative solutions to marketing challenges. x000d coordinates with other teams to execute integrated marketing approaches.</t>
+          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. develops and manages comprehensive marketing plans aligned with business objectives. implements strategies to maximise marketing effectiveness given organisational goals. leads the definition of target customers and brand positioning. analyses complex data to inform marketing decisions. creates innovative solutions to marketing challenges. coordinates with other teams to execute integrated marketing approaches.</t>
         </is>
       </c>
     </row>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. defines and oversees the execution of marketing strategies to achieve organisational goals. x000d ensures alignment of marketing plans with business objectives and market insights. evaluates and optimises marketing effectiveness and budget allocation to drive outcomes.x000d identifies and addresses current and future marketing capability needs. x000d collaborates with senior leadership to integrate marketing strategies with organisational vision.</t>
+          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. defines and oversees the execution of marketing strategies to achieve organisational goals. ensures alignment of marketing plans with business objectives and market insights. evaluates and optimises marketing effectiveness and budget allocation to drive outcomes. identifies and addresses current and future marketing capability needs. collaborates with senior leadership to integrate marketing strategies with organisational vision.</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. leads the creation of longterm marketing strategies aligned with organisational vision. x000d directs the marketing function, ensuring integration of marketing plans with business goals. oversees the evaluation and optimisation of marketing activities, ensuring maximum impact and efficiency. x000d provides strategic advice to senior leadership on marketing trends and opportunities. x000d promotes a culture of creativity and continuous improvement within the marketing team. ensures the marketing function adapts to changing market conditions and business needs.</t>
+          <t>developing, implementing and managing marketing strategies and plans to achieve organisational objectives and drive business growth. leads the creation of longterm marketing strategies aligned with organisational vision. directs the marketing function, ensuring integration of marketing plans with business goals. oversees the evaluation and optimisation of marketing activities, ensuring maximum impact and efficiency. provides strategic advice to senior leadership on marketing trends and opportunities. promotes a culture of creativity and continuous improvement within the marketing team. ensures the marketing function adapts to changing market conditions and business needs.</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. assists in the design and execution of market research studies. x000d collects and analyses data using standard methods and tools. x000d contributes to the preparation of research reports and presentations.</t>
+          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. assists in the design and execution of market research studies. collects and analyses data using standard methods and tools. contributes to the preparation of research reports and presentations.</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. designs and conducts market research studies independently. x000d analyses market data to identify trends, opportunities and challenges. x000d segments markets and identifies target customers based on research findings. x000d prepares research reports and presentations to communicate findings and recommendations.</t>
+          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. designs and conducts market research studies independently. analyses market data to identify trends, opportunities and challenges. segments markets and identifies target customers based on research findings. prepares research reports and presentations to communicate findings and recommendations.</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. leads the design and execution of complex market research studies. x000d analyses and synthesises market data from multiple sources to generate insights and recommendations. x000d presents research findings and strategic recommendations to stakeholders. advises stakeholders on the implications of research findings for business strategy and decisionmaking. x000d contributes to the development of organisational market research methods and standards.</t>
+          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. leads the design and execution of complex market research studies. analyses and synthesises market data from multiple sources to generate insights and recommendations. presents research findings and strategic recommendations to stakeholders. advises stakeholders on the implications of research findings for business strategy and decisionmaking. contributes to the development of organisational market research methods and standards.</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18621,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. sets the overall direction and strategy for market research in the organisation. x000d develops organisational policies, standards and guidelines for market research. ensures market research capabilities and resources are aligned with business needs and objectives. x000d communicates highlevel market insights and strategic implications to senior leadership and stakeholders. x000d collaborates with internal and external partners to influence organisational strategy and drive the effective use of market research in decisionmaking and strategy development.</t>
+          <t>gathering, analysing and interpreting data about markets, customers and competitors to inform business decisions and strategies. sets the overall direction and strategy for market research in the organisation. develops organisational policies, standards and guidelines for market research. ensures market research capabilities and resources are aligned with business needs and objectives. communicates highlevel market insights and strategic implications to senior leadership and stakeholders. collaborates with internal and external partners to influence organisational strategy and drive the effective use of market research in decisionmaking and strategy development.</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. contributes to the development and implementation of brand identity elements and guidelines. x000d supports brand research and analysis. x000d ensures consistent application of brand standards across assigned projects. x000d monitors brand performance metrics and reports on key findings.</t>
+          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. contributes to the development and implementation of brand identity elements and guidelines. supports brand research and analysis. ensures consistent application of brand standards across assigned projects. monitors brand performance metrics and reports on key findings.</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. leads the development and execution of brand strategies and plans. x000d defines brand positioning, values and value proposition. applies principles of brand architecture to manage brand portfolio. x000d conducts indepth brand performance analysis and provides strategic recommendations. x000d uses creative approaches to differentiate the brand. collaborates with internal and external stakeholders to align brand initiatives with business objectives.</t>
+          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. leads the development and execution of brand strategies and plans. defines brand positioning, values and value proposition. applies principles of brand architecture to manage brand portfolio. conducts indepth brand performance analysis and provides strategic recommendations. uses creative approaches to differentiate the brand. collaborates with internal and external stakeholders to align brand initiatives with business objectives.</t>
         </is>
       </c>
     </row>
@@ -18705,7 +18705,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. establishes the overall brand vision, strategy and governance for the organisation. x000d oversees brand research, analysis and strategic planning. x000d evaluates brand performance and equity, making decisions to enhance brand value and organisational outcomes. ensures alignment of brand strategy with organisational goals and market dynamics. x000d governs the application of visual identity and distinctive brand assets across the organisation.</t>
+          <t>managing brand strategy to establish and enhance brand identity and value aligned with organisational goals. establishes the overall brand vision, strategy and governance for the organisation. oversees brand research, analysis and strategic planning. evaluates brand performance and equity, making decisions to enhance brand value and organisational outcomes. ensures alignment of brand strategy with organisational goals and market dynamics. governs the application of visual identity and distinctive brand assets across the organisation.</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. assists in implementing customer engagement and loyalty initiatives. x000d uses marketing technologies for customer engagement tasks. sets up campaigns in lifecycle management tools.x000d collects and analyses customer data to support personalised communications. x000d monitors and reports on customer engagement metrics.</t>
+          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. assists in implementing customer engagement and loyalty initiatives. uses marketing technologies for customer engagement tasks. sets up campaigns in lifecycle management tools. collects and analyses customer data to support personalised communications. monitors and reports on customer engagement metrics.</t>
         </is>
       </c>
     </row>
@@ -18761,7 +18761,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. develops and executes customer engagement and loyalty initiatives. x000d creates and manages loyalty programmes. x000d analyses customer data to inform targeted communications and experiences. develops customer segmentation approaches.x000d applies appropriate marketing technologies to support initiatives. measures and reports on the effectiveness of engagement and loyalty efforts.</t>
+          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. develops and executes customer engagement and loyalty initiatives. creates and manages loyalty programmes. analyses customer data to inform targeted communications and experiences. develops customer segmentation approaches. applies appropriate marketing technologies to support initiatives. measures and reports on the effectiveness of engagement and loyalty efforts.</t>
         </is>
       </c>
     </row>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. leads the development and implementation of comprehensive customer engagement and loyalty plans. x000d oversees the creation and management of loyalty programmes and initiatives. develops comprehensive plans for customer communications across all lifecycle stages.x000d uses advanced analytics to optimise personalised customer experiences. provides recommendations based on customer engagement and loyalty insights.x000d collaborates with crossfunctional teams to improve customer retention and satisfaction. evaluates and recommends marketing technologies for customer engagement.</t>
+          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. leads the development and implementation of comprehensive customer engagement and loyalty plans. oversees the creation and management of loyalty programmes and initiatives. develops comprehensive plans for customer communications across all lifecycle stages. uses advanced analytics to optimise personalised customer experiences. provides recommendations based on customer engagement and loyalty insights. collaborates with crossfunctional teams to improve customer retention and satisfaction. evaluates and recommends marketing technologies for customer engagement.</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. defines organisational vision and strategy for customer engagement and loyalty. x000d drives innovation in loyalty programme development and implementation. aligns customer engagement strategies with overall business objectives. x000d leads the assessment and adoption of advanced marketing technologies. directs the development of customer journeys and database management strategies. x000d ensures integration of customer engagement initiatives across all business functions.</t>
+          <t>developing and executing strategies to attract, engage and retain customers through targeted communications and loyalty initiatives. defines organisational vision and strategy for customer engagement and loyalty. drives innovation in loyalty programme development and implementation. aligns customer engagement strategies with overall business objectives. leads the assessment and adoption of advanced marketing technologies. directs the development of customer journeys and database management strategies. ensures integration of customer engagement initiatives across all business functions.</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. assists in the execution of marketing campaigns. x000d uses selected tools and channels to engage target audiences. x000d monitors campaign performance and collects data for analysis. x000d participates in marketing events and initiatives.</t>
+          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. assists in the execution of marketing campaigns. uses selected tools and channels to engage target audiences. monitors campaign performance and collects data for analysis. participates in marketing events and initiatives.</t>
         </is>
       </c>
     </row>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. plans and executes marketing campaigns across multiple channels. x000d selects appropriate tools and platforms to reach desired audiences. x000d creates and distributes engaging marketing content and materials. writes campaign briefs and contributes to creative evaluation.x000d analyses campaign performance and makes recommendations for optimisation.</t>
+          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. plans and executes marketing campaigns across multiple channels. selects appropriate tools and platforms to reach desired audiences. creates and distributes engaging marketing content and materials. writes campaign briefs and contributes to creative evaluation. analyses campaign performance and makes recommendations for optimisation.</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. develops and oversees complex, multichannel marketing campaign strategies. x000d selects optimal channels, tools and creative partners. leads creative briefings and evaluates concepts.x000d manages stakeholders and ensures brand consistency.x000d monitors campaign performance and adjusts tactics as needed. analyses campaign results and reports on key metrics and outcomes.</t>
+          <t>executing, monitoring and optimising marketing campaigns across various channels to engage target audiences and achieve desired outcomes. develops and oversees complex, multichannel marketing campaign strategies. selects optimal channels, tools and creative partners. leads creative briefings and evaluates concepts. manages stakeholders and ensures brand consistency. monitors campaign performance and adjusts tactics as needed. analyses campaign results and reports on key metrics and outcomes.</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. performs basic digital marketing tasks under routine supervision. x000d assists in the implementation of digital marketing campaigns across various platforms. x000d collects and organises basic performance data from digital marketing activities. x000d contributes to the creation and distribution of digital marketing content following established guidelines.</t>
+          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. performs basic digital marketing tasks under routine supervision. assists in the implementation of digital marketing campaigns across various platforms. collects and organises basic performance data from digital marketing activities. contributes to the creation and distribution of digital marketing content following established guidelines.</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. implements digital marketing activities across multiple channels. x000d monitors campaign performance and makes basic optimisations. x000d assists in the development of digital marketing content. follows procedures to comply with regulatory requirements and platform policies.x000d contributes to the analysis of marketing metrics and prepares reports. supports the planning and execution of marketing performance improvement initiatives.</t>
+          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. implements digital marketing activities across multiple channels. monitors campaign performance and makes basic optimisations. assists in the development of digital marketing content. follows procedures to comply with regulatory requirements and platform policies. contributes to the analysis of marketing metrics and prepares reports. supports the planning and execution of marketing performance improvement initiatives.</t>
         </is>
       </c>
     </row>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. plans and executes digital marketing activities across various platforms. x000d analyses detailed marketing data to derive insights and improve campaign performance. recommends and implements improvements to digital marketing activities based on performance data.x000d manages relationships with digital marketing vendors and platform representatives. x000d leads the implementation of marketing automation processes. applies organisational guidelines and uses appropriate tools to ensure digital marketing activities adhere to relevant regulations and platform policies.</t>
+          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. plans and executes digital marketing activities across various platforms. analyses detailed marketing data to derive insights and improve campaign performance. recommends and implements improvements to digital marketing activities based on performance data. manages relationships with digital marketing vendors and platform representatives. leads the implementation of marketing automation processes. applies organisational guidelines and uses appropriate tools to ensure digital marketing activities adhere to relevant regulations and platform policies.</t>
         </is>
       </c>
     </row>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. leads the development and implementation of comprehensive digital marketing plans. x000d oversees the integration with broader marketing and business objectives. manages budgets and resources for digital marketing initiatives. x000d provides guidance on recognised good practices for digital marketing and emerging trends to stakeholders across the organisation. evaluates and recommends new digital marketing technologies and approaches. establishes and maintains strategic relationships with digital marketing vendors and platform representatives. x000d develops standards and procedures for compliant digital marketing practices.</t>
+          <t>planning and executing activities to promote products, services and brands through digital channels and technologies. leads the development and implementation of comprehensive digital marketing plans. oversees the integration with broader marketing and business objectives. manages budgets and resources for digital marketing initiatives. provides guidance on recognised good practices for digital marketing and emerging trends to stakeholders across the organisation. evaluates and recommends new digital marketing technologies and approaches. establishes and maintains strategic relationships with digital marketing vendors and platform representatives. develops standards and procedures for compliant digital marketing practices.</t>
         </is>
       </c>
     </row>
